--- a/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ise_rya" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.17</v>
+        <v>0.0594</v>
+      </c>
+      <c r="E2">
+        <v>-0.05769999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.1305151305151305</v>
+        <v>0.0397916827235392</v>
       </c>
       <c r="H2">
-        <v>-0.1305151305151305</v>
+        <v>0.0397916827235392</v>
       </c>
       <c r="I2">
-        <v>-0.2727452727452727</v>
+        <v>0.1324003831628552</v>
       </c>
       <c r="J2">
-        <v>-0.2727452727452727</v>
+        <v>0.129657486087253</v>
       </c>
       <c r="K2">
-        <v>-755.9</v>
+        <v>1049.4</v>
       </c>
       <c r="L2">
-        <v>-0.2494472494472494</v>
+        <v>0.1155434196183786</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4773.1</v>
+        <v>1690.7</v>
       </c>
       <c r="V2">
-        <v>0.2428885473808482</v>
+        <v>0.1137867214052563</v>
       </c>
       <c r="W2">
-        <v>-0.1292954518242307</v>
+        <v>0.1835481783359278</v>
       </c>
       <c r="X2">
-        <v>0.07412993405604008</v>
+        <v>0.1098122565193614</v>
       </c>
       <c r="Y2">
-        <v>-0.2034253858802708</v>
+        <v>0.07373592181656641</v>
       </c>
       <c r="Z2">
-        <v>0.3390241992325163</v>
+        <v>1.19481937537822</v>
       </c>
       <c r="AA2">
-        <v>-0.09246724768692034</v>
+        <v>0.1549172765398818</v>
       </c>
       <c r="AB2">
-        <v>0.06383565308287981</v>
+        <v>0.09694641897054093</v>
       </c>
       <c r="AC2">
-        <v>-0.1563029007698001</v>
+        <v>0.05797085756934089</v>
       </c>
       <c r="AD2">
-        <v>6657.2</v>
+        <v>5037.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6657.2</v>
+        <v>5037.8</v>
       </c>
       <c r="AG2">
-        <v>1884.099999999999</v>
+        <v>3347.1</v>
       </c>
       <c r="AH2">
-        <v>0.2530427312741841</v>
+        <v>0.2532028568125732</v>
       </c>
       <c r="AI2">
-        <v>0.5379772920117984</v>
+        <v>0.4352499028035768</v>
       </c>
       <c r="AJ2">
-        <v>0.08748810104246474</v>
+        <v>0.1838500241683878</v>
       </c>
       <c r="AK2">
-        <v>0.2478622359039124</v>
+        <v>0.3386450555454381</v>
       </c>
       <c r="AL2">
-        <v>115</v>
+        <v>81.3</v>
       </c>
       <c r="AM2">
-        <v>111.52</v>
+        <v>81.3</v>
       </c>
       <c r="AN2">
-        <v>-33.5882946518668</v>
+        <v>2.558427708089991</v>
       </c>
       <c r="AO2">
-        <v>-7.18695652173913</v>
+        <v>14.79089790897909</v>
       </c>
       <c r="AP2">
-        <v>-9.506054490413721</v>
+        <v>1.69981209689706</v>
       </c>
       <c r="AQ2">
-        <v>-7.41122668579627</v>
+        <v>14.79089790897909</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.17</v>
+        <v>0.0594</v>
+      </c>
+      <c r="E3">
+        <v>-0.05769999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.1305151305151305</v>
+        <v>0.0397916827235392</v>
       </c>
       <c r="H3">
-        <v>-0.1305151305151305</v>
+        <v>0.0397916827235392</v>
       </c>
       <c r="I3">
-        <v>-0.2727452727452727</v>
+        <v>0.1324003831628552</v>
       </c>
       <c r="J3">
-        <v>-0.2727452727452727</v>
+        <v>0.129657486087253</v>
       </c>
       <c r="K3">
-        <v>-755.9</v>
+        <v>1049.4</v>
       </c>
       <c r="L3">
-        <v>-0.2494472494472494</v>
+        <v>0.1155434196183786</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4773.1</v>
+        <v>1690.7</v>
       </c>
       <c r="V3">
-        <v>0.2428885473808482</v>
+        <v>0.1137867214052563</v>
       </c>
       <c r="W3">
-        <v>-0.1292954518242307</v>
+        <v>0.1835481783359278</v>
       </c>
       <c r="X3">
-        <v>0.07412993405604008</v>
+        <v>0.1098122565193614</v>
       </c>
       <c r="Y3">
-        <v>-0.2034253858802708</v>
+        <v>0.07373592181656641</v>
       </c>
       <c r="Z3">
-        <v>0.3390241992325163</v>
+        <v>1.19481937537822</v>
       </c>
       <c r="AA3">
-        <v>-0.09246724768692034</v>
+        <v>0.1549172765398818</v>
       </c>
       <c r="AB3">
-        <v>0.06383565308287981</v>
+        <v>0.09694641897054093</v>
       </c>
       <c r="AC3">
-        <v>-0.1563029007698001</v>
+        <v>0.05797085756934089</v>
       </c>
       <c r="AD3">
-        <v>6657.2</v>
+        <v>5037.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6657.2</v>
+        <v>5037.8</v>
       </c>
       <c r="AG3">
-        <v>1884.099999999999</v>
+        <v>3347.1</v>
       </c>
       <c r="AH3">
-        <v>0.2530427312741841</v>
+        <v>0.2532028568125732</v>
       </c>
       <c r="AI3">
-        <v>0.5379772920117984</v>
+        <v>0.4352499028035768</v>
       </c>
       <c r="AJ3">
-        <v>0.08748810104246474</v>
+        <v>0.1838500241683878</v>
       </c>
       <c r="AK3">
-        <v>0.2478622359039124</v>
+        <v>0.3386450555454381</v>
       </c>
       <c r="AL3">
-        <v>115</v>
+        <v>81.3</v>
       </c>
       <c r="AM3">
-        <v>111.52</v>
+        <v>81.3</v>
       </c>
       <c r="AN3">
-        <v>-33.5882946518668</v>
+        <v>2.558427708089991</v>
       </c>
       <c r="AO3">
-        <v>-7.18695652173913</v>
+        <v>14.79089790897909</v>
       </c>
       <c r="AP3">
-        <v>-9.506054490413721</v>
+        <v>1.69981209689706</v>
       </c>
       <c r="AQ3">
-        <v>-7.41122668579627</v>
+        <v>14.79089790897909</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ryanair Holdings plc (ISE:RYA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ISE:RYA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.253202856812573</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>14858.5</v>
+      </c>
+      <c r="H2">
+        <v>21020.3595680305</v>
+      </c>
+      <c r="I2">
+        <v>18205.6</v>
+      </c>
+      <c r="J2">
+        <v>19329.6595680305</v>
+      </c>
+      <c r="K2">
+        <v>5037.8</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.0969464189705409</v>
+      </c>
+      <c r="N2">
+        <v>0.0935650847902615</v>
+      </c>
+      <c r="O2">
+        <v>0.0589998853211009</v>
+      </c>
+      <c r="P2">
+        <v>0.0475373853211009</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.109812256519361</v>
+      </c>
+      <c r="T2">
+        <v>0.0935650847902615</v>
+      </c>
+      <c r="U2">
+        <v>0.995770293696714</v>
+      </c>
+      <c r="V2">
+        <v>0.767944116112626</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0.008628440366972481</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>14858.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="AD2">
+        <v>0.125</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1969.1</v>
+      </c>
+      <c r="AH2">
+        <v>820.1</v>
+      </c>
+      <c r="AI2">
+        <v>1735.4</v>
+      </c>
+      <c r="AJ2">
+        <v>5037.8</v>
+      </c>
+      <c r="AK2">
+        <v>5037.8</v>
+      </c>
+      <c r="AL2">
+        <v>81.3</v>
+      </c>
+      <c r="AM2">
+        <v>5037.8</v>
+      </c>
+      <c r="AN2">
+        <v>1690.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09356508479026146</v>
+      </c>
+      <c r="C2">
+        <v>21020.35956803052</v>
+      </c>
+      <c r="D2">
+        <v>19329.65956803051</v>
+      </c>
+      <c r="E2">
+        <v>-5037.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1690.7</v>
+      </c>
+      <c r="H2">
+        <v>14858.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1969.1</v>
+      </c>
+      <c r="K2">
+        <v>820.1</v>
+      </c>
+      <c r="L2">
+        <v>1149</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1149</v>
+      </c>
+      <c r="O2">
+        <v>143.625</v>
+      </c>
+      <c r="P2">
+        <v>1005.375</v>
+      </c>
+      <c r="Q2">
+        <v>1825.475</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09356508479026146</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V2">
+        <v>0.125</v>
+      </c>
+      <c r="W2">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09358400228748463</v>
+      </c>
+      <c r="C3">
+        <v>20814.72183150279</v>
+      </c>
+      <c r="D3">
+        <v>19322.98483150279</v>
+      </c>
+      <c r="E3">
+        <v>-4838.837</v>
+      </c>
+      <c r="F3">
+        <v>198.963</v>
+      </c>
+      <c r="G3">
+        <v>1690.7</v>
+      </c>
+      <c r="H3">
+        <v>14858.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1969.1</v>
+      </c>
+      <c r="K3">
+        <v>820.1</v>
+      </c>
+      <c r="L3">
+        <v>1149</v>
+      </c>
+      <c r="M3">
+        <v>10.80934948073395</v>
+      </c>
+      <c r="N3">
+        <v>1138.190650519266</v>
+      </c>
+      <c r="O3">
+        <v>142.2738313149083</v>
+      </c>
+      <c r="P3">
+        <v>995.9168192043578</v>
+      </c>
+      <c r="Q3">
+        <v>1816.016819204358</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09404911963057942</v>
+      </c>
+      <c r="T3">
+        <v>0.774731500977258</v>
+      </c>
+      <c r="U3">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V3">
+        <v>0.125</v>
+      </c>
+      <c r="W3">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>106.2968684700149</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09360291978470782</v>
+      </c>
+      <c r="C4">
+        <v>20609.08870309851</v>
+      </c>
+      <c r="D4">
+        <v>19316.31470309851</v>
+      </c>
+      <c r="E4">
+        <v>-4639.874</v>
+      </c>
+      <c r="F4">
+        <v>397.926</v>
+      </c>
+      <c r="G4">
+        <v>1690.7</v>
+      </c>
+      <c r="H4">
+        <v>14858.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1969.1</v>
+      </c>
+      <c r="K4">
+        <v>820.1</v>
+      </c>
+      <c r="L4">
+        <v>1149</v>
+      </c>
+      <c r="M4">
+        <v>21.61869896146789</v>
+      </c>
+      <c r="N4">
+        <v>1127.381301038532</v>
+      </c>
+      <c r="O4">
+        <v>140.9226626298165</v>
+      </c>
+      <c r="P4">
+        <v>986.4586384087155</v>
+      </c>
+      <c r="Q4">
+        <v>1806.558638408716</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09454303273294469</v>
+      </c>
+      <c r="T4">
+        <v>0.7816574039003515</v>
+      </c>
+      <c r="U4">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V4">
+        <v>0.125</v>
+      </c>
+      <c r="W4">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>53.14843423500744</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09362183728193098</v>
+      </c>
+      <c r="C5">
+        <v>20403.46017804728</v>
+      </c>
+      <c r="D5">
+        <v>19309.64917804728</v>
+      </c>
+      <c r="E5">
+        <v>-4440.911</v>
+      </c>
+      <c r="F5">
+        <v>596.889</v>
+      </c>
+      <c r="G5">
+        <v>1690.7</v>
+      </c>
+      <c r="H5">
+        <v>14858.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1969.1</v>
+      </c>
+      <c r="K5">
+        <v>820.1</v>
+      </c>
+      <c r="L5">
+        <v>1149</v>
+      </c>
+      <c r="M5">
+        <v>32.42804844220184</v>
+      </c>
+      <c r="N5">
+        <v>1116.571951557798</v>
+      </c>
+      <c r="O5">
+        <v>139.5714939447248</v>
+      </c>
+      <c r="P5">
+        <v>977.0004576130734</v>
+      </c>
+      <c r="Q5">
+        <v>1797.100457613074</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09504712961061645</v>
+      </c>
+      <c r="T5">
+        <v>0.7887261089455708</v>
+      </c>
+      <c r="U5">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V5">
+        <v>0.125</v>
+      </c>
+      <c r="W5">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>35.43228949000496</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09364075477915419</v>
+      </c>
+      <c r="C6">
+        <v>20197.83625158523</v>
+      </c>
+      <c r="D6">
+        <v>19302.98825158523</v>
+      </c>
+      <c r="E6">
+        <v>-4241.948</v>
+      </c>
+      <c r="F6">
+        <v>795.852</v>
+      </c>
+      <c r="G6">
+        <v>1690.7</v>
+      </c>
+      <c r="H6">
+        <v>14858.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1969.1</v>
+      </c>
+      <c r="K6">
+        <v>820.1</v>
+      </c>
+      <c r="L6">
+        <v>1149</v>
+      </c>
+      <c r="M6">
+        <v>43.23739792293578</v>
+      </c>
+      <c r="N6">
+        <v>1105.762602077064</v>
+      </c>
+      <c r="O6">
+        <v>138.220325259633</v>
+      </c>
+      <c r="P6">
+        <v>967.5422768174312</v>
+      </c>
+      <c r="Q6">
+        <v>1787.642276817431</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09556172850657307</v>
+      </c>
+      <c r="T6">
+        <v>0.7959420786792323</v>
+      </c>
+      <c r="U6">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V6">
+        <v>0.125</v>
+      </c>
+      <c r="W6">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>26.57421711750372</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09365967227637736</v>
+      </c>
+      <c r="C7">
+        <v>19992.21691895516</v>
+      </c>
+      <c r="D7">
+        <v>19296.33191895516</v>
+      </c>
+      <c r="E7">
+        <v>-4042.985</v>
+      </c>
+      <c r="F7">
+        <v>994.8150000000001</v>
+      </c>
+      <c r="G7">
+        <v>1690.7</v>
+      </c>
+      <c r="H7">
+        <v>14858.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1969.1</v>
+      </c>
+      <c r="K7">
+        <v>820.1</v>
+      </c>
+      <c r="L7">
+        <v>1149</v>
+      </c>
+      <c r="M7">
+        <v>54.04674740366973</v>
+      </c>
+      <c r="N7">
+        <v>1094.95325259633</v>
+      </c>
+      <c r="O7">
+        <v>136.8691565745413</v>
+      </c>
+      <c r="P7">
+        <v>958.0840960217889</v>
+      </c>
+      <c r="Q7">
+        <v>1778.184096021789</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09608716106349718</v>
+      </c>
+      <c r="T7">
+        <v>0.8033099635651813</v>
+      </c>
+      <c r="U7">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V7">
+        <v>0.125</v>
+      </c>
+      <c r="W7">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.25937369400297</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09367858977360055</v>
+      </c>
+      <c r="C8">
+        <v>19786.60217540635</v>
+      </c>
+      <c r="D8">
+        <v>19289.68017540635</v>
+      </c>
+      <c r="E8">
+        <v>-3844.022</v>
+      </c>
+      <c r="F8">
+        <v>1193.778</v>
+      </c>
+      <c r="G8">
+        <v>1690.7</v>
+      </c>
+      <c r="H8">
+        <v>14858.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1969.1</v>
+      </c>
+      <c r="K8">
+        <v>820.1</v>
+      </c>
+      <c r="L8">
+        <v>1149</v>
+      </c>
+      <c r="M8">
+        <v>64.85609688440368</v>
+      </c>
+      <c r="N8">
+        <v>1084.143903115596</v>
+      </c>
+      <c r="O8">
+        <v>135.5179878894495</v>
+      </c>
+      <c r="P8">
+        <v>948.6259152261467</v>
+      </c>
+      <c r="Q8">
+        <v>1768.725915226147</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09662377303652606</v>
+      </c>
+      <c r="T8">
+        <v>0.810834611959342</v>
+      </c>
+      <c r="U8">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V8">
+        <v>0.125</v>
+      </c>
+      <c r="W8">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>17.71614474500248</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09369750727082374</v>
+      </c>
+      <c r="C9">
+        <v>19580.99201619465</v>
+      </c>
+      <c r="D9">
+        <v>19283.03301619465</v>
+      </c>
+      <c r="E9">
+        <v>-3645.059</v>
+      </c>
+      <c r="F9">
+        <v>1392.741</v>
+      </c>
+      <c r="G9">
+        <v>1690.7</v>
+      </c>
+      <c r="H9">
+        <v>14858.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1969.1</v>
+      </c>
+      <c r="K9">
+        <v>820.1</v>
+      </c>
+      <c r="L9">
+        <v>1149</v>
+      </c>
+      <c r="M9">
+        <v>75.66544636513763</v>
+      </c>
+      <c r="N9">
+        <v>1073.334553634862</v>
+      </c>
+      <c r="O9">
+        <v>134.1668192043578</v>
+      </c>
+      <c r="P9">
+        <v>939.1677344305047</v>
+      </c>
+      <c r="Q9">
+        <v>1759.267734430505</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09717192505198567</v>
+      </c>
+      <c r="T9">
+        <v>0.818521080749076</v>
+      </c>
+      <c r="U9">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V9">
+        <v>0.125</v>
+      </c>
+      <c r="W9">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.18526692428784</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09371642476804694</v>
+      </c>
+      <c r="C10">
+        <v>19375.38643658246</v>
+      </c>
+      <c r="D10">
+        <v>19276.39043658246</v>
+      </c>
+      <c r="E10">
+        <v>-3446.096</v>
+      </c>
+      <c r="F10">
+        <v>1591.704</v>
+      </c>
+      <c r="G10">
+        <v>1690.7</v>
+      </c>
+      <c r="H10">
+        <v>14858.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1969.1</v>
+      </c>
+      <c r="K10">
+        <v>820.1</v>
+      </c>
+      <c r="L10">
+        <v>1149</v>
+      </c>
+      <c r="M10">
+        <v>86.47479584587157</v>
+      </c>
+      <c r="N10">
+        <v>1062.525204154128</v>
+      </c>
+      <c r="O10">
+        <v>132.8156505192661</v>
+      </c>
+      <c r="P10">
+        <v>929.7095536348625</v>
+      </c>
+      <c r="Q10">
+        <v>1749.809553634862</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09773199341560745</v>
+      </c>
+      <c r="T10">
+        <v>0.826374646686413</v>
+      </c>
+      <c r="U10">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V10">
+        <v>0.125</v>
+      </c>
+      <c r="W10">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.28710855875186</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0937353422652701</v>
+      </c>
+      <c r="C11">
+        <v>19169.7854318387</v>
+      </c>
+      <c r="D11">
+        <v>19269.7524318387</v>
+      </c>
+      <c r="E11">
+        <v>-3247.133</v>
+      </c>
+      <c r="F11">
+        <v>1790.667</v>
+      </c>
+      <c r="G11">
+        <v>1690.7</v>
+      </c>
+      <c r="H11">
+        <v>14858.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1969.1</v>
+      </c>
+      <c r="K11">
+        <v>820.1</v>
+      </c>
+      <c r="L11">
+        <v>1149</v>
+      </c>
+      <c r="M11">
+        <v>97.28414532660551</v>
+      </c>
+      <c r="N11">
+        <v>1051.715854673394</v>
+      </c>
+      <c r="O11">
+        <v>131.4644818341743</v>
+      </c>
+      <c r="P11">
+        <v>920.2513728392202</v>
+      </c>
+      <c r="Q11">
+        <v>1740.35137283922</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09830437097403408</v>
+      </c>
+      <c r="T11">
+        <v>0.8344008184685264</v>
+      </c>
+      <c r="U11">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V11">
+        <v>0.125</v>
+      </c>
+      <c r="W11">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.81076316333499</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0937542597624933</v>
+      </c>
+      <c r="C12">
+        <v>18964.18899723879</v>
+      </c>
+      <c r="D12">
+        <v>19263.11899723879</v>
+      </c>
+      <c r="E12">
+        <v>-3048.17</v>
+      </c>
+      <c r="F12">
+        <v>1989.63</v>
+      </c>
+      <c r="G12">
+        <v>1690.7</v>
+      </c>
+      <c r="H12">
+        <v>14858.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1969.1</v>
+      </c>
+      <c r="K12">
+        <v>820.1</v>
+      </c>
+      <c r="L12">
+        <v>1149</v>
+      </c>
+      <c r="M12">
+        <v>108.0934948073395</v>
+      </c>
+      <c r="N12">
+        <v>1040.90650519266</v>
+      </c>
+      <c r="O12">
+        <v>130.1133131490826</v>
+      </c>
+      <c r="P12">
+        <v>910.7931920435778</v>
+      </c>
+      <c r="Q12">
+        <v>1730.893192043578</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09888946803375911</v>
+      </c>
+      <c r="T12">
+        <v>0.842605349623576</v>
+      </c>
+      <c r="U12">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V12">
+        <v>0.125</v>
+      </c>
+      <c r="W12">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.62968684700149</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09377317725971647</v>
+      </c>
+      <c r="C13">
+        <v>18758.59712806468</v>
+      </c>
+      <c r="D13">
+        <v>19256.49012806468</v>
+      </c>
+      <c r="E13">
+        <v>-2849.207</v>
+      </c>
+      <c r="F13">
+        <v>2188.593</v>
+      </c>
+      <c r="G13">
+        <v>1690.7</v>
+      </c>
+      <c r="H13">
+        <v>14858.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1969.1</v>
+      </c>
+      <c r="K13">
+        <v>820.1</v>
+      </c>
+      <c r="L13">
+        <v>1149</v>
+      </c>
+      <c r="M13">
+        <v>118.9028442880734</v>
+      </c>
+      <c r="N13">
+        <v>1030.097155711927</v>
+      </c>
+      <c r="O13">
+        <v>128.7621444639908</v>
+      </c>
+      <c r="P13">
+        <v>901.3350112479359</v>
+      </c>
+      <c r="Q13">
+        <v>1721.435011247936</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09948771334201727</v>
+      </c>
+      <c r="T13">
+        <v>0.8509942522652557</v>
+      </c>
+      <c r="U13">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V13">
+        <v>0.125</v>
+      </c>
+      <c r="W13">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>9.663351679092264</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09379209475693964</v>
+      </c>
+      <c r="C14">
+        <v>18553.00981960479</v>
+      </c>
+      <c r="D14">
+        <v>19249.86581960479</v>
+      </c>
+      <c r="E14">
+        <v>-2650.244</v>
+      </c>
+      <c r="F14">
+        <v>2387.556</v>
+      </c>
+      <c r="G14">
+        <v>1690.7</v>
+      </c>
+      <c r="H14">
+        <v>14858.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1969.1</v>
+      </c>
+      <c r="K14">
+        <v>820.1</v>
+      </c>
+      <c r="L14">
+        <v>1149</v>
+      </c>
+      <c r="M14">
+        <v>129.7121937688074</v>
+      </c>
+      <c r="N14">
+        <v>1019.287806231193</v>
+      </c>
+      <c r="O14">
+        <v>127.4109757788991</v>
+      </c>
+      <c r="P14">
+        <v>891.8768304522936</v>
+      </c>
+      <c r="Q14">
+        <v>1711.976830452294</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.100099555134554</v>
+      </c>
+      <c r="T14">
+        <v>0.8595738117851555</v>
+      </c>
+      <c r="U14">
+        <v>0.05432844036697249</v>
+      </c>
+      <c r="V14">
+        <v>0.125</v>
+      </c>
+      <c r="W14">
+        <v>0.04753738532110093</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.85807237250124</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09399301225416284</v>
+      </c>
+      <c r="C15">
+        <v>18283.9720999184</v>
+      </c>
+      <c r="D15">
+        <v>19179.7910999184</v>
+      </c>
+      <c r="E15">
+        <v>-2451.281</v>
+      </c>
+      <c r="F15">
+        <v>2586.519</v>
+      </c>
+      <c r="G15">
+        <v>1690.7</v>
+      </c>
+      <c r="H15">
+        <v>14858.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1969.1</v>
+      </c>
+      <c r="K15">
+        <v>820.1</v>
+      </c>
+      <c r="L15">
+        <v>1149</v>
+      </c>
+      <c r="M15">
+        <v>144.6599736495413</v>
+      </c>
+      <c r="N15">
+        <v>1004.340026350459</v>
+      </c>
+      <c r="O15">
+        <v>125.5425032938073</v>
+      </c>
+      <c r="P15">
+        <v>878.7975230566514</v>
+      </c>
+      <c r="Q15">
+        <v>1698.897523056651</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1007254622556548</v>
+      </c>
+      <c r="T15">
+        <v>0.8683506025583863</v>
+      </c>
+      <c r="U15">
+        <v>0.05592844036697248</v>
+      </c>
+      <c r="V15">
+        <v>0.125</v>
+      </c>
+      <c r="W15">
+        <v>0.04893738532110092</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.942763786087856</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.094025929751386</v>
+      </c>
+      <c r="C16">
+        <v>18073.57695702621</v>
+      </c>
+      <c r="D16">
+        <v>19168.3589570262</v>
+      </c>
+      <c r="E16">
+        <v>-2252.318</v>
+      </c>
+      <c r="F16">
+        <v>2785.482</v>
+      </c>
+      <c r="G16">
+        <v>1690.7</v>
+      </c>
+      <c r="H16">
+        <v>14858.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1969.1</v>
+      </c>
+      <c r="K16">
+        <v>820.1</v>
+      </c>
+      <c r="L16">
+        <v>1149</v>
+      </c>
+      <c r="M16">
+        <v>155.7876639302752</v>
+      </c>
+      <c r="N16">
+        <v>993.2123360697248</v>
+      </c>
+      <c r="O16">
+        <v>124.1515420087156</v>
+      </c>
+      <c r="P16">
+        <v>869.0607940610091</v>
+      </c>
+      <c r="Q16">
+        <v>1689.160794061009</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1013659253563161</v>
+      </c>
+      <c r="T16">
+        <v>0.8773315047449479</v>
+      </c>
+      <c r="U16">
+        <v>0.05592844036697248</v>
+      </c>
+      <c r="V16">
+        <v>0.125</v>
+      </c>
+      <c r="W16">
+        <v>0.04893738532110092</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.375423515653009</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09455759724860918</v>
+      </c>
+      <c r="C17">
+        <v>17691.83718873905</v>
+      </c>
+      <c r="D17">
+        <v>18985.58218873905</v>
+      </c>
+      <c r="E17">
+        <v>-2053.355</v>
+      </c>
+      <c r="F17">
+        <v>2984.445</v>
+      </c>
+      <c r="G17">
+        <v>1690.7</v>
+      </c>
+      <c r="H17">
+        <v>14858.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1969.1</v>
+      </c>
+      <c r="K17">
+        <v>820.1</v>
+      </c>
+      <c r="L17">
+        <v>1149</v>
+      </c>
+      <c r="M17">
+        <v>178.2562452110092</v>
+      </c>
+      <c r="N17">
+        <v>970.7437547889908</v>
+      </c>
+      <c r="O17">
+        <v>121.3429693486239</v>
+      </c>
+      <c r="P17">
+        <v>849.4007854403669</v>
+      </c>
+      <c r="Q17">
+        <v>1669.500785440367</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.102021458176993</v>
+      </c>
+      <c r="T17">
+        <v>0.8865237222770757</v>
+      </c>
+      <c r="U17">
+        <v>0.05972844036697248</v>
+      </c>
+      <c r="V17">
+        <v>0.125</v>
+      </c>
+      <c r="W17">
+        <v>0.05226238532110092</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.44577696921576</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09462376474583238</v>
+      </c>
+      <c r="C18">
+        <v>17470.37071799547</v>
+      </c>
+      <c r="D18">
+        <v>18963.07871799547</v>
+      </c>
+      <c r="E18">
+        <v>-1854.392</v>
+      </c>
+      <c r="F18">
+        <v>3183.408</v>
+      </c>
+      <c r="G18">
+        <v>1690.7</v>
+      </c>
+      <c r="H18">
+        <v>14858.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1969.1</v>
+      </c>
+      <c r="K18">
+        <v>820.1</v>
+      </c>
+      <c r="L18">
+        <v>1149</v>
+      </c>
+      <c r="M18">
+        <v>190.1399948917431</v>
+      </c>
+      <c r="N18">
+        <v>958.8600051082569</v>
+      </c>
+      <c r="O18">
+        <v>119.8575006385321</v>
+      </c>
+      <c r="P18">
+        <v>839.0025044697248</v>
+      </c>
+      <c r="Q18">
+        <v>1659.102504469725</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1026925989219717</v>
+      </c>
+      <c r="T18">
+        <v>0.8959348021313972</v>
+      </c>
+      <c r="U18">
+        <v>0.05972844036697248</v>
+      </c>
+      <c r="V18">
+        <v>0.125</v>
+      </c>
+      <c r="W18">
+        <v>0.05226238532110092</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>6.042915908639775</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09468993224305555</v>
+      </c>
+      <c r="C19">
+        <v>17248.95753049195</v>
+      </c>
+      <c r="D19">
+        <v>18940.62853049195</v>
+      </c>
+      <c r="E19">
+        <v>-1655.429</v>
+      </c>
+      <c r="F19">
+        <v>3382.371</v>
+      </c>
+      <c r="G19">
+        <v>1690.7</v>
+      </c>
+      <c r="H19">
+        <v>14858.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1969.1</v>
+      </c>
+      <c r="K19">
+        <v>820.1</v>
+      </c>
+      <c r="L19">
+        <v>1149</v>
+      </c>
+      <c r="M19">
+        <v>202.0237445724771</v>
+      </c>
+      <c r="N19">
+        <v>946.9762554275229</v>
+      </c>
+      <c r="O19">
+        <v>118.3720319284404</v>
+      </c>
+      <c r="P19">
+        <v>828.6042234990825</v>
+      </c>
+      <c r="Q19">
+        <v>1648.704223499083</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1033799117330945</v>
+      </c>
+      <c r="T19">
+        <v>0.9055726549942564</v>
+      </c>
+      <c r="U19">
+        <v>0.05972844036697248</v>
+      </c>
+      <c r="V19">
+        <v>0.125</v>
+      </c>
+      <c r="W19">
+        <v>0.05226238532110092</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.687450266955081</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09505534974027875</v>
+      </c>
+      <c r="C20">
+        <v>16926.96201704388</v>
+      </c>
+      <c r="D20">
+        <v>18817.59601704388</v>
+      </c>
+      <c r="E20">
+        <v>-1456.466</v>
+      </c>
+      <c r="F20">
+        <v>3581.334</v>
+      </c>
+      <c r="G20">
+        <v>1690.7</v>
+      </c>
+      <c r="H20">
+        <v>14858.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1969.1</v>
+      </c>
+      <c r="K20">
+        <v>820.1</v>
+      </c>
+      <c r="L20">
+        <v>1149</v>
+      </c>
+      <c r="M20">
+        <v>220.712028853211</v>
+      </c>
+      <c r="N20">
+        <v>928.287971146789</v>
+      </c>
+      <c r="O20">
+        <v>116.0359963933486</v>
+      </c>
+      <c r="P20">
+        <v>812.2519747534404</v>
+      </c>
+      <c r="Q20">
+        <v>1632.351974753441</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1040839882713178</v>
+      </c>
+      <c r="T20">
+        <v>0.9154455774391367</v>
+      </c>
+      <c r="U20">
+        <v>0.06162844036697249</v>
+      </c>
+      <c r="V20">
+        <v>0.125</v>
+      </c>
+      <c r="W20">
+        <v>0.05392488532110093</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.205878474182146</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09513814223750193</v>
+      </c>
+      <c r="C21">
+        <v>16700.34535818839</v>
+      </c>
+      <c r="D21">
+        <v>18789.94235818839</v>
+      </c>
+      <c r="E21">
+        <v>-1257.503</v>
+      </c>
+      <c r="F21">
+        <v>3780.297</v>
+      </c>
+      <c r="G21">
+        <v>1690.7</v>
+      </c>
+      <c r="H21">
+        <v>14858.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1969.1</v>
+      </c>
+      <c r="K21">
+        <v>820.1</v>
+      </c>
+      <c r="L21">
+        <v>1149</v>
+      </c>
+      <c r="M21">
+        <v>232.973808233945</v>
+      </c>
+      <c r="N21">
+        <v>916.026191766055</v>
+      </c>
+      <c r="O21">
+        <v>114.5032739707569</v>
+      </c>
+      <c r="P21">
+        <v>801.5229177952981</v>
+      </c>
+      <c r="Q21">
+        <v>1621.622917795298</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1048054494154231</v>
+      </c>
+      <c r="T21">
+        <v>0.9255622757468533</v>
+      </c>
+      <c r="U21">
+        <v>0.06162844036697249</v>
+      </c>
+      <c r="V21">
+        <v>0.125</v>
+      </c>
+      <c r="W21">
+        <v>0.05392488532110093</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.931884870277822</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09522093473472511</v>
+      </c>
+      <c r="C22">
+        <v>16473.80985770026</v>
+      </c>
+      <c r="D22">
+        <v>18762.36985770026</v>
+      </c>
+      <c r="E22">
+        <v>-1058.54</v>
+      </c>
+      <c r="F22">
+        <v>3979.26</v>
+      </c>
+      <c r="G22">
+        <v>1690.7</v>
+      </c>
+      <c r="H22">
+        <v>14858.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1969.1</v>
+      </c>
+      <c r="K22">
+        <v>820.1</v>
+      </c>
+      <c r="L22">
+        <v>1149</v>
+      </c>
+      <c r="M22">
+        <v>245.235587614679</v>
+      </c>
+      <c r="N22">
+        <v>903.7644123853211</v>
+      </c>
+      <c r="O22">
+        <v>112.9705515481651</v>
+      </c>
+      <c r="P22">
+        <v>790.793860837156</v>
+      </c>
+      <c r="Q22">
+        <v>1610.893860837156</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1055449470881311</v>
+      </c>
+      <c r="T22">
+        <v>0.9359318915122631</v>
+      </c>
+      <c r="U22">
+        <v>0.06162844036697249</v>
+      </c>
+      <c r="V22">
+        <v>0.125</v>
+      </c>
+      <c r="W22">
+        <v>0.05392488532110093</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.685290626763931</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09530372723194828</v>
+      </c>
+      <c r="C23">
+        <v>16247.35515882583</v>
+      </c>
+      <c r="D23">
+        <v>18734.87815882582</v>
+      </c>
+      <c r="E23">
+        <v>-859.5770000000002</v>
+      </c>
+      <c r="F23">
+        <v>4178.223</v>
+      </c>
+      <c r="G23">
+        <v>1690.7</v>
+      </c>
+      <c r="H23">
+        <v>14858.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1969.1</v>
+      </c>
+      <c r="K23">
+        <v>820.1</v>
+      </c>
+      <c r="L23">
+        <v>1149</v>
+      </c>
+      <c r="M23">
+        <v>257.4973669954129</v>
+      </c>
+      <c r="N23">
+        <v>891.5026330045871</v>
+      </c>
+      <c r="O23">
+        <v>111.4378291255734</v>
+      </c>
+      <c r="P23">
+        <v>780.0648038790137</v>
+      </c>
+      <c r="Q23">
+        <v>1600.164803879014</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1063031662209077</v>
+      </c>
+      <c r="T23">
+        <v>0.9465640291957844</v>
+      </c>
+      <c r="U23">
+        <v>0.06162844036697249</v>
+      </c>
+      <c r="V23">
+        <v>0.125</v>
+      </c>
+      <c r="W23">
+        <v>0.05392488532110093</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.462181549298982</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09538651972917148</v>
+      </c>
+      <c r="C24">
+        <v>16020.9809068993</v>
+      </c>
+      <c r="D24">
+        <v>18707.4669068993</v>
+      </c>
+      <c r="E24">
+        <v>-660.6140000000005</v>
+      </c>
+      <c r="F24">
+        <v>4377.186</v>
+      </c>
+      <c r="G24">
+        <v>1690.7</v>
+      </c>
+      <c r="H24">
+        <v>14858.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1969.1</v>
+      </c>
+      <c r="K24">
+        <v>820.1</v>
+      </c>
+      <c r="L24">
+        <v>1149</v>
+      </c>
+      <c r="M24">
+        <v>269.7591463761468</v>
+      </c>
+      <c r="N24">
+        <v>879.2408536238531</v>
+      </c>
+      <c r="O24">
+        <v>109.9051067029816</v>
+      </c>
+      <c r="P24">
+        <v>769.3357469208715</v>
+      </c>
+      <c r="Q24">
+        <v>1589.435746920872</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1070808268699093</v>
+      </c>
+      <c r="T24">
+        <v>0.9574687857942679</v>
+      </c>
+      <c r="U24">
+        <v>0.06162844036697249</v>
+      </c>
+      <c r="V24">
+        <v>0.125</v>
+      </c>
+      <c r="W24">
+        <v>0.05392488532110093</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.259355115239938</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09587181222639464</v>
+      </c>
+      <c r="C25">
+        <v>15662.94475015503</v>
+      </c>
+      <c r="D25">
+        <v>18548.39375015503</v>
+      </c>
+      <c r="E25">
+        <v>-461.6509999999998</v>
+      </c>
+      <c r="F25">
+        <v>4576.149</v>
+      </c>
+      <c r="G25">
+        <v>1690.7</v>
+      </c>
+      <c r="H25">
+        <v>14858.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1969.1</v>
+      </c>
+      <c r="K25">
+        <v>820.1</v>
+      </c>
+      <c r="L25">
+        <v>1149</v>
+      </c>
+      <c r="M25">
+        <v>291.1732237568808</v>
+      </c>
+      <c r="N25">
+        <v>857.8267762431192</v>
+      </c>
+      <c r="O25">
+        <v>107.2283470303899</v>
+      </c>
+      <c r="P25">
+        <v>750.5984292127293</v>
+      </c>
+      <c r="Q25">
+        <v>1570.698429212729</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1078786864968071</v>
+      </c>
+      <c r="T25">
+        <v>0.9686567828238806</v>
+      </c>
+      <c r="U25">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V25">
+        <v>0.125</v>
+      </c>
+      <c r="W25">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.946104608023208</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09597210472361783</v>
+      </c>
+      <c r="C26">
+        <v>15431.44377140342</v>
+      </c>
+      <c r="D26">
+        <v>18515.85577140342</v>
+      </c>
+      <c r="E26">
+        <v>-262.6880000000001</v>
+      </c>
+      <c r="F26">
+        <v>4775.112</v>
+      </c>
+      <c r="G26">
+        <v>1690.7</v>
+      </c>
+      <c r="H26">
+        <v>14858.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1969.1</v>
+      </c>
+      <c r="K26">
+        <v>820.1</v>
+      </c>
+      <c r="L26">
+        <v>1149</v>
+      </c>
+      <c r="M26">
+        <v>303.8329291376147</v>
+      </c>
+      <c r="N26">
+        <v>845.1670708623853</v>
+      </c>
+      <c r="O26">
+        <v>105.6458838577982</v>
+      </c>
+      <c r="P26">
+        <v>739.5211870045872</v>
+      </c>
+      <c r="Q26">
+        <v>1559.621187004587</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1086975424296758</v>
+      </c>
+      <c r="T26">
+        <v>0.9801392008279569</v>
+      </c>
+      <c r="U26">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V26">
+        <v>0.125</v>
+      </c>
+      <c r="W26">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.781683582688908</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09607239722084102</v>
+      </c>
+      <c r="C27">
+        <v>15200.05675034528</v>
+      </c>
+      <c r="D27">
+        <v>18483.43175034528</v>
+      </c>
+      <c r="E27">
+        <v>-63.72500000000036</v>
+      </c>
+      <c r="F27">
+        <v>4974.075</v>
+      </c>
+      <c r="G27">
+        <v>1690.7</v>
+      </c>
+      <c r="H27">
+        <v>14858.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1969.1</v>
+      </c>
+      <c r="K27">
+        <v>820.1</v>
+      </c>
+      <c r="L27">
+        <v>1149</v>
+      </c>
+      <c r="M27">
+        <v>316.4926345183487</v>
+      </c>
+      <c r="N27">
+        <v>832.5073654816513</v>
+      </c>
+      <c r="O27">
+        <v>104.0634206852064</v>
+      </c>
+      <c r="P27">
+        <v>728.4439447964448</v>
+      </c>
+      <c r="Q27">
+        <v>1548.543944796445</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1095382345207544</v>
+      </c>
+      <c r="T27">
+        <v>0.9919278166454754</v>
+      </c>
+      <c r="U27">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V27">
+        <v>0.125</v>
+      </c>
+      <c r="W27">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.630416239381351</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09617268971806421</v>
+      </c>
+      <c r="C28">
+        <v>14968.78308935648</v>
+      </c>
+      <c r="D28">
+        <v>18451.12108935647</v>
+      </c>
+      <c r="E28">
+        <v>135.2379999999994</v>
+      </c>
+      <c r="F28">
+        <v>5173.038</v>
+      </c>
+      <c r="G28">
+        <v>1690.7</v>
+      </c>
+      <c r="H28">
+        <v>14858.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1969.1</v>
+      </c>
+      <c r="K28">
+        <v>820.1</v>
+      </c>
+      <c r="L28">
+        <v>1149</v>
+      </c>
+      <c r="M28">
+        <v>329.1523398990826</v>
+      </c>
+      <c r="N28">
+        <v>819.8476601009174</v>
+      </c>
+      <c r="O28">
+        <v>102.4809575126147</v>
+      </c>
+      <c r="P28">
+        <v>717.3667025883028</v>
+      </c>
+      <c r="Q28">
+        <v>1537.466702588303</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1104016480197</v>
+      </c>
+      <c r="T28">
+        <v>1.004035043701305</v>
+      </c>
+      <c r="U28">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V28">
+        <v>0.125</v>
+      </c>
+      <c r="W28">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>3.490784845558992</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09627298221528739</v>
+      </c>
+      <c r="C29">
+        <v>14737.62219498435</v>
+      </c>
+      <c r="D29">
+        <v>18418.92319498435</v>
+      </c>
+      <c r="E29">
+        <v>334.201</v>
+      </c>
+      <c r="F29">
+        <v>5372.001</v>
+      </c>
+      <c r="G29">
+        <v>1690.7</v>
+      </c>
+      <c r="H29">
+        <v>14858.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1969.1</v>
+      </c>
+      <c r="K29">
+        <v>820.1</v>
+      </c>
+      <c r="L29">
+        <v>1149</v>
+      </c>
+      <c r="M29">
+        <v>341.8120452798166</v>
+      </c>
+      <c r="N29">
+        <v>807.1879547201834</v>
+      </c>
+      <c r="O29">
+        <v>100.8984943400229</v>
+      </c>
+      <c r="P29">
+        <v>706.2894603801604</v>
+      </c>
+      <c r="Q29">
+        <v>1526.38946038016</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1112887166830002</v>
+      </c>
+      <c r="T29">
+        <v>1.016473975607979</v>
+      </c>
+      <c r="U29">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V29">
+        <v>0.125</v>
+      </c>
+      <c r="W29">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.361496517945696</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09637327471251057</v>
+      </c>
+      <c r="C30">
+        <v>14506.57347791143</v>
+      </c>
+      <c r="D30">
+        <v>18386.83747791143</v>
+      </c>
+      <c r="E30">
+        <v>533.1639999999998</v>
+      </c>
+      <c r="F30">
+        <v>5570.964</v>
+      </c>
+      <c r="G30">
+        <v>1690.7</v>
+      </c>
+      <c r="H30">
+        <v>14858.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1969.1</v>
+      </c>
+      <c r="K30">
+        <v>820.1</v>
+      </c>
+      <c r="L30">
+        <v>1149</v>
+      </c>
+      <c r="M30">
+        <v>354.4717506605505</v>
+      </c>
+      <c r="N30">
+        <v>794.5282493394495</v>
+      </c>
+      <c r="O30">
+        <v>99.31603116743119</v>
+      </c>
+      <c r="P30">
+        <v>695.2122181720183</v>
+      </c>
+      <c r="Q30">
+        <v>1515.312218172018</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1122004261425032</v>
+      </c>
+      <c r="T30">
+        <v>1.02925843340095</v>
+      </c>
+      <c r="U30">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V30">
+        <v>0.125</v>
+      </c>
+      <c r="W30">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.241443070876207</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09647356720973374</v>
+      </c>
+      <c r="C31">
+        <v>14275.63635291947</v>
+      </c>
+      <c r="D31">
+        <v>18354.86335291947</v>
+      </c>
+      <c r="E31">
+        <v>732.1269999999995</v>
+      </c>
+      <c r="F31">
+        <v>5769.927</v>
+      </c>
+      <c r="G31">
+        <v>1690.7</v>
+      </c>
+      <c r="H31">
+        <v>14858.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1969.1</v>
+      </c>
+      <c r="K31">
+        <v>820.1</v>
+      </c>
+      <c r="L31">
+        <v>1149</v>
+      </c>
+      <c r="M31">
+        <v>367.1314560412844</v>
+      </c>
+      <c r="N31">
+        <v>781.8685439587156</v>
+      </c>
+      <c r="O31">
+        <v>97.73356799483945</v>
+      </c>
+      <c r="P31">
+        <v>684.1349759638762</v>
+      </c>
+      <c r="Q31">
+        <v>1504.234975963876</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1131378175586119</v>
+      </c>
+      <c r="T31">
+        <v>1.042403016765554</v>
+      </c>
+      <c r="U31">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V31">
+        <v>0.125</v>
+      </c>
+      <c r="W31">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.129669171880476</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09657385970695692</v>
+      </c>
+      <c r="C32">
+        <v>14044.81023885384</v>
+      </c>
+      <c r="D32">
+        <v>18323.00023885384</v>
+      </c>
+      <c r="E32">
+        <v>931.0899999999992</v>
+      </c>
+      <c r="F32">
+        <v>5968.889999999999</v>
+      </c>
+      <c r="G32">
+        <v>1690.7</v>
+      </c>
+      <c r="H32">
+        <v>14858.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1969.1</v>
+      </c>
+      <c r="K32">
+        <v>820.1</v>
+      </c>
+      <c r="L32">
+        <v>1149</v>
+      </c>
+      <c r="M32">
+        <v>379.7911614220184</v>
+      </c>
+      <c r="N32">
+        <v>769.2088385779816</v>
+      </c>
+      <c r="O32">
+        <v>96.1511048222477</v>
+      </c>
+      <c r="P32">
+        <v>673.0577337557339</v>
+      </c>
+      <c r="Q32">
+        <v>1493.157733755734</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1141019915866095</v>
+      </c>
+      <c r="T32">
+        <v>1.055923159654861</v>
+      </c>
+      <c r="U32">
+        <v>0.06362844036697249</v>
+      </c>
+      <c r="V32">
+        <v>0.125</v>
+      </c>
+      <c r="W32">
+        <v>0.05567488532110093</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.025346866151127</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09770490220418011</v>
+      </c>
+      <c r="C33">
+        <v>13494.02436552253</v>
+      </c>
+      <c r="D33">
+        <v>17971.17736552253</v>
+      </c>
+      <c r="E33">
+        <v>1130.053</v>
+      </c>
+      <c r="F33">
+        <v>6167.853</v>
+      </c>
+      <c r="G33">
+        <v>1690.7</v>
+      </c>
+      <c r="H33">
+        <v>14858.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1969.1</v>
+      </c>
+      <c r="K33">
+        <v>820.1</v>
+      </c>
+      <c r="L33">
+        <v>1149</v>
+      </c>
+      <c r="M33">
+        <v>415.8887082027524</v>
+      </c>
+      <c r="N33">
+        <v>733.1112917972476</v>
+      </c>
+      <c r="O33">
+        <v>91.63891147465596</v>
+      </c>
+      <c r="P33">
+        <v>641.4723803225917</v>
+      </c>
+      <c r="Q33">
+        <v>1461.572380322592</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1150941126878824</v>
+      </c>
+      <c r="T33">
+        <v>1.069835190743858</v>
+      </c>
+      <c r="U33">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="V33">
+        <v>0.125</v>
+      </c>
+      <c r="W33">
+        <v>0.05899988532110093</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.762758346975471</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09783844470140328</v>
+      </c>
+      <c r="C34">
+        <v>13254.41131256856</v>
+      </c>
+      <c r="D34">
+        <v>17930.52731256856</v>
+      </c>
+      <c r="E34">
+        <v>1329.016</v>
+      </c>
+      <c r="F34">
+        <v>6366.816</v>
+      </c>
+      <c r="G34">
+        <v>1690.7</v>
+      </c>
+      <c r="H34">
+        <v>14858.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1969.1</v>
+      </c>
+      <c r="K34">
+        <v>820.1</v>
+      </c>
+      <c r="L34">
+        <v>1149</v>
+      </c>
+      <c r="M34">
+        <v>429.3044729834863</v>
+      </c>
+      <c r="N34">
+        <v>719.6955270165138</v>
+      </c>
+      <c r="O34">
+        <v>89.96194087706422</v>
+      </c>
+      <c r="P34">
+        <v>629.7335861394496</v>
+      </c>
+      <c r="Q34">
+        <v>1449.83358613945</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1161154138215456</v>
+      </c>
+      <c r="T34">
+        <v>1.084156399217825</v>
+      </c>
+      <c r="U34">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="V34">
+        <v>0.125</v>
+      </c>
+      <c r="W34">
+        <v>0.05899988532110093</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.676422148632487</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09797198719862647</v>
+      </c>
+      <c r="C35">
+        <v>13014.98174203052</v>
+      </c>
+      <c r="D35">
+        <v>17890.06074203052</v>
+      </c>
+      <c r="E35">
+        <v>1527.979</v>
+      </c>
+      <c r="F35">
+        <v>6565.779</v>
+      </c>
+      <c r="G35">
+        <v>1690.7</v>
+      </c>
+      <c r="H35">
+        <v>14858.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1969.1</v>
+      </c>
+      <c r="K35">
+        <v>820.1</v>
+      </c>
+      <c r="L35">
+        <v>1149</v>
+      </c>
+      <c r="M35">
+        <v>442.7202377642203</v>
+      </c>
+      <c r="N35">
+        <v>706.2797622357798</v>
+      </c>
+      <c r="O35">
+        <v>88.28497027947247</v>
+      </c>
+      <c r="P35">
+        <v>617.9947919563074</v>
+      </c>
+      <c r="Q35">
+        <v>1438.094791956307</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1171672015562137</v>
+      </c>
+      <c r="T35">
+        <v>1.09890510645221</v>
+      </c>
+      <c r="U35">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="V35">
+        <v>0.125</v>
+      </c>
+      <c r="W35">
+        <v>0.05899988532110093</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.595318447158776</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09810552969584967</v>
+      </c>
+      <c r="C36">
+        <v>12775.73441442704</v>
+      </c>
+      <c r="D36">
+        <v>17849.77641442704</v>
+      </c>
+      <c r="E36">
+        <v>1726.942</v>
+      </c>
+      <c r="F36">
+        <v>6764.742</v>
+      </c>
+      <c r="G36">
+        <v>1690.7</v>
+      </c>
+      <c r="H36">
+        <v>14858.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1969.1</v>
+      </c>
+      <c r="K36">
+        <v>820.1</v>
+      </c>
+      <c r="L36">
+        <v>1149</v>
+      </c>
+      <c r="M36">
+        <v>456.1360025449542</v>
+      </c>
+      <c r="N36">
+        <v>692.8639974550458</v>
+      </c>
+      <c r="O36">
+        <v>86.60799968188073</v>
+      </c>
+      <c r="P36">
+        <v>606.2559977731651</v>
+      </c>
+      <c r="Q36">
+        <v>1426.355997773165</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1182508616464778</v>
+      </c>
+      <c r="T36">
+        <v>1.114100744208848</v>
+      </c>
+      <c r="U36">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="V36">
+        <v>0.125</v>
+      </c>
+      <c r="W36">
+        <v>0.05899988532110093</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.518985551654106</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09952532219307283</v>
+      </c>
+      <c r="C37">
+        <v>12159.43351130751</v>
+      </c>
+      <c r="D37">
+        <v>17432.43851130752</v>
+      </c>
+      <c r="E37">
+        <v>1925.905000000001</v>
+      </c>
+      <c r="F37">
+        <v>6963.705000000001</v>
+      </c>
+      <c r="G37">
+        <v>1690.7</v>
+      </c>
+      <c r="H37">
+        <v>14858.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1969.1</v>
+      </c>
+      <c r="K37">
+        <v>820.1</v>
+      </c>
+      <c r="L37">
+        <v>1149</v>
+      </c>
+      <c r="M37">
+        <v>498.7993283256882</v>
+      </c>
+      <c r="N37">
+        <v>650.2006716743118</v>
+      </c>
+      <c r="O37">
+        <v>81.27508395928898</v>
+      </c>
+      <c r="P37">
+        <v>568.9255877150229</v>
+      </c>
+      <c r="Q37">
+        <v>1389.025587715023</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1193678651241347</v>
+      </c>
+      <c r="T37">
+        <v>1.129763940050306</v>
+      </c>
+      <c r="U37">
+        <v>0.07162844036697248</v>
+      </c>
+      <c r="V37">
+        <v>0.125</v>
+      </c>
+      <c r="W37">
+        <v>0.06267488532110092</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.303531570214479</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.101932114690296</v>
+      </c>
+      <c r="C38">
+        <v>11295.89175573846</v>
+      </c>
+      <c r="D38">
+        <v>16767.85975573846</v>
+      </c>
+      <c r="E38">
+        <v>2124.867999999999</v>
+      </c>
+      <c r="F38">
+        <v>7162.668</v>
+      </c>
+      <c r="G38">
+        <v>1690.7</v>
+      </c>
+      <c r="H38">
+        <v>14858.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1969.1</v>
+      </c>
+      <c r="K38">
+        <v>820.1</v>
+      </c>
+      <c r="L38">
+        <v>1149</v>
+      </c>
+      <c r="M38">
+        <v>563.9056805064221</v>
+      </c>
+      <c r="N38">
+        <v>585.0943194935779</v>
+      </c>
+      <c r="O38">
+        <v>73.13678993669724</v>
+      </c>
+      <c r="P38">
+        <v>511.9575295568807</v>
+      </c>
+      <c r="Q38">
+        <v>1332.057529556881</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1205197749604683</v>
+      </c>
+      <c r="T38">
+        <v>1.145916610761809</v>
+      </c>
+      <c r="U38">
+        <v>0.07872844036697249</v>
+      </c>
+      <c r="V38">
+        <v>0.125</v>
+      </c>
+      <c r="W38">
+        <v>0.06888738532110093</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.037574792593199</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1090604071875192</v>
+      </c>
+      <c r="C39">
+        <v>9395.740082403352</v>
+      </c>
+      <c r="D39">
+        <v>15066.67108240335</v>
+      </c>
+      <c r="E39">
+        <v>2323.830999999999</v>
+      </c>
+      <c r="F39">
+        <v>7361.630999999999</v>
+      </c>
+      <c r="G39">
+        <v>1690.7</v>
+      </c>
+      <c r="H39">
+        <v>14858.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1969.1</v>
+      </c>
+      <c r="K39">
+        <v>820.1</v>
+      </c>
+      <c r="L39">
+        <v>1149</v>
+      </c>
+      <c r="M39">
+        <v>736.3724674871559</v>
+      </c>
+      <c r="N39">
+        <v>412.6275325128441</v>
+      </c>
+      <c r="O39">
+        <v>51.57844156410552</v>
+      </c>
+      <c r="P39">
+        <v>361.0490909487386</v>
+      </c>
+      <c r="Q39">
+        <v>1181.149090948739</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1217082533630347</v>
+      </c>
+      <c r="T39">
+        <v>1.162582064670503</v>
+      </c>
+      <c r="U39">
+        <v>0.1000284403669725</v>
+      </c>
+      <c r="V39">
+        <v>0.125</v>
+      </c>
+      <c r="W39">
+        <v>0.08752488532110092</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.56035165725427</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1094791996847424</v>
+      </c>
+      <c r="C40">
+        <v>9107.503168216655</v>
+      </c>
+      <c r="D40">
+        <v>14977.39716821666</v>
+      </c>
+      <c r="E40">
+        <v>2522.794</v>
+      </c>
+      <c r="F40">
+        <v>7560.594</v>
+      </c>
+      <c r="G40">
+        <v>1690.7</v>
+      </c>
+      <c r="H40">
+        <v>14858.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1969.1</v>
+      </c>
+      <c r="K40">
+        <v>820.1</v>
+      </c>
+      <c r="L40">
+        <v>1149</v>
+      </c>
+      <c r="M40">
+        <v>756.2744260678899</v>
+      </c>
+      <c r="N40">
+        <v>392.7255739321101</v>
+      </c>
+      <c r="O40">
+        <v>49.09069674151377</v>
+      </c>
+      <c r="P40">
+        <v>343.6348771905964</v>
+      </c>
+      <c r="Q40">
+        <v>1163.734877190596</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1229350697785871</v>
+      </c>
+      <c r="T40">
+        <v>1.179785113866575</v>
+      </c>
+      <c r="U40">
+        <v>0.1000284403669725</v>
+      </c>
+      <c r="V40">
+        <v>0.125</v>
+      </c>
+      <c r="W40">
+        <v>0.08752488532110092</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.519289771537053</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1324110603087026</v>
+      </c>
+      <c r="C41">
+        <v>5239.533714934217</v>
+      </c>
+      <c r="D41">
+        <v>11308.39071493422</v>
+      </c>
+      <c r="E41">
+        <v>2721.757</v>
+      </c>
+      <c r="F41">
+        <v>7759.557</v>
+      </c>
+      <c r="G41">
+        <v>1690.7</v>
+      </c>
+      <c r="H41">
+        <v>14858.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1969.1</v>
+      </c>
+      <c r="K41">
+        <v>820.1</v>
+      </c>
+      <c r="L41">
+        <v>1149</v>
+      </c>
+      <c r="M41">
+        <v>1265.804431348624</v>
+      </c>
+      <c r="N41">
+        <v>-116.8044313486239</v>
+      </c>
+      <c r="O41">
+        <v>-14.60055391857799</v>
+      </c>
+      <c r="P41">
+        <v>-102.2038774300459</v>
+      </c>
+      <c r="Q41">
+        <v>717.8961225699541</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1246059793695406</v>
+      </c>
+      <c r="T41">
+        <v>1.203215465409772</v>
+      </c>
+      <c r="U41">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V41">
+        <v>0.113465395161382</v>
+      </c>
+      <c r="W41">
+        <v>0.144619007418674</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.9077231612910557</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1336543447123723</v>
+      </c>
+      <c r="C42">
+        <v>4892.348239209843</v>
+      </c>
+      <c r="D42">
+        <v>11160.16823920984</v>
+      </c>
+      <c r="E42">
+        <v>2920.72</v>
+      </c>
+      <c r="F42">
+        <v>7958.52</v>
+      </c>
+      <c r="G42">
+        <v>1690.7</v>
+      </c>
+      <c r="H42">
+        <v>14858.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1969.1</v>
+      </c>
+      <c r="K42">
+        <v>820.1</v>
+      </c>
+      <c r="L42">
+        <v>1149</v>
+      </c>
+      <c r="M42">
+        <v>1298.260955229358</v>
+      </c>
+      <c r="N42">
+        <v>-149.2609552293579</v>
+      </c>
+      <c r="O42">
+        <v>-18.65761940366974</v>
+      </c>
+      <c r="P42">
+        <v>-130.6033358256882</v>
+      </c>
+      <c r="Q42">
+        <v>689.4966641743118</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1260360790256996</v>
+      </c>
+      <c r="T42">
+        <v>1.223269056499935</v>
+      </c>
+      <c r="U42">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V42">
+        <v>0.1106287602823474</v>
+      </c>
+      <c r="W42">
+        <v>0.1450817432423815</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8850300822587793</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1348976291160421</v>
+      </c>
+      <c r="C43">
+        <v>4548.998085834965</v>
+      </c>
+      <c r="D43">
+        <v>11015.78108583496</v>
+      </c>
+      <c r="E43">
+        <v>3119.683</v>
+      </c>
+      <c r="F43">
+        <v>8157.483</v>
+      </c>
+      <c r="G43">
+        <v>1690.7</v>
+      </c>
+      <c r="H43">
+        <v>14858.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1969.1</v>
+      </c>
+      <c r="K43">
+        <v>820.1</v>
+      </c>
+      <c r="L43">
+        <v>1149</v>
+      </c>
+      <c r="M43">
+        <v>1330.717479110092</v>
+      </c>
+      <c r="N43">
+        <v>-181.717479110092</v>
+      </c>
+      <c r="O43">
+        <v>-22.7146848887615</v>
+      </c>
+      <c r="P43">
+        <v>-159.0027942213305</v>
+      </c>
+      <c r="Q43">
+        <v>661.0972057786696</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1275146566363047</v>
+      </c>
+      <c r="T43">
+        <v>1.244002430338917</v>
+      </c>
+      <c r="U43">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V43">
+        <v>0.1079304978364365</v>
+      </c>
+      <c r="W43">
+        <v>0.1455219065868837</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8634439826914919</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1361409135197118</v>
+      </c>
+      <c r="C44">
+        <v>4209.336295130839</v>
+      </c>
+      <c r="D44">
+        <v>10875.08229513084</v>
+      </c>
+      <c r="E44">
+        <v>3318.646</v>
+      </c>
+      <c r="F44">
+        <v>8356.446</v>
+      </c>
+      <c r="G44">
+        <v>1690.7</v>
+      </c>
+      <c r="H44">
+        <v>14858.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1969.1</v>
+      </c>
+      <c r="K44">
+        <v>820.1</v>
+      </c>
+      <c r="L44">
+        <v>1149</v>
+      </c>
+      <c r="M44">
+        <v>1363.174002990826</v>
+      </c>
+      <c r="N44">
+        <v>-214.1740029908258</v>
+      </c>
+      <c r="O44">
+        <v>-26.77175037385322</v>
+      </c>
+      <c r="P44">
+        <v>-187.4022526169726</v>
+      </c>
+      <c r="Q44">
+        <v>632.6977473830275</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1290442196817582</v>
+      </c>
+      <c r="T44">
+        <v>1.265450748103381</v>
+      </c>
+      <c r="U44">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V44">
+        <v>0.1053607240784261</v>
+      </c>
+      <c r="W44">
+        <v>0.1459411097721239</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8428857926274088</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1373841979233815</v>
+      </c>
+      <c r="C45">
+        <v>3873.223320885787</v>
+      </c>
+      <c r="D45">
+        <v>10737.93232088579</v>
+      </c>
+      <c r="E45">
+        <v>3517.608999999999</v>
+      </c>
+      <c r="F45">
+        <v>8555.409</v>
+      </c>
+      <c r="G45">
+        <v>1690.7</v>
+      </c>
+      <c r="H45">
+        <v>14858.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1969.1</v>
+      </c>
+      <c r="K45">
+        <v>820.1</v>
+      </c>
+      <c r="L45">
+        <v>1149</v>
+      </c>
+      <c r="M45">
+        <v>1395.63052687156</v>
+      </c>
+      <c r="N45">
+        <v>-246.6305268715598</v>
+      </c>
+      <c r="O45">
+        <v>-30.82881585894498</v>
+      </c>
+      <c r="P45">
+        <v>-215.8017110126148</v>
+      </c>
+      <c r="Q45">
+        <v>604.2982889873851</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1306274516059996</v>
+      </c>
+      <c r="T45">
+        <v>1.287651638420984</v>
+      </c>
+      <c r="U45">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V45">
+        <v>0.1029104746812534</v>
+      </c>
+      <c r="W45">
+        <v>0.1463408151347948</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8232837974500272</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1386274823270512</v>
+      </c>
+      <c r="C46">
+        <v>3540.526568706398</v>
+      </c>
+      <c r="D46">
+        <v>10604.1985687064</v>
+      </c>
+      <c r="E46">
+        <v>3716.571999999999</v>
+      </c>
+      <c r="F46">
+        <v>8754.371999999999</v>
+      </c>
+      <c r="G46">
+        <v>1690.7</v>
+      </c>
+      <c r="H46">
+        <v>14858.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1969.1</v>
+      </c>
+      <c r="K46">
+        <v>820.1</v>
+      </c>
+      <c r="L46">
+        <v>1149</v>
+      </c>
+      <c r="M46">
+        <v>1428.087050752294</v>
+      </c>
+      <c r="N46">
+        <v>-279.0870507522936</v>
+      </c>
+      <c r="O46">
+        <v>-34.8858813440367</v>
+      </c>
+      <c r="P46">
+        <v>-244.2011694082569</v>
+      </c>
+      <c r="Q46">
+        <v>575.898830591743</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1322672275275353</v>
+      </c>
+      <c r="T46">
+        <v>1.310645417678502</v>
+      </c>
+      <c r="U46">
+        <v>0.1631284403669725</v>
+      </c>
+      <c r="V46">
+        <v>0.1005716002566795</v>
+      </c>
+      <c r="W46">
+        <v>0.1467223520718898</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8045728020534357</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1672018614301714</v>
+      </c>
+      <c r="C47">
+        <v>981.7193529606247</v>
+      </c>
+      <c r="D47">
+        <v>8244.354352960623</v>
+      </c>
+      <c r="E47">
+        <v>3915.534999999999</v>
+      </c>
+      <c r="F47">
+        <v>8953.334999999999</v>
+      </c>
+      <c r="G47">
+        <v>1690.7</v>
+      </c>
+      <c r="H47">
+        <v>14858.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1969.1</v>
+      </c>
+      <c r="K47">
+        <v>820.1</v>
+      </c>
+      <c r="L47">
+        <v>1149</v>
+      </c>
+      <c r="M47">
+        <v>1991.476340133027</v>
+      </c>
+      <c r="N47">
+        <v>-842.4763401330272</v>
+      </c>
+      <c r="O47">
+        <v>-105.3095425166284</v>
+      </c>
+      <c r="P47">
+        <v>-737.1667976163988</v>
+      </c>
+      <c r="Q47">
+        <v>82.93320238360127</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1351413492997638</v>
+      </c>
+      <c r="T47">
+        <v>1.350947827734601</v>
+      </c>
+      <c r="U47">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V47">
+        <v>0.0721198625891815</v>
+      </c>
+      <c r="W47">
+        <v>0.2063869318117805</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.576958900713452</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1690381458338411</v>
+      </c>
+      <c r="C48">
+        <v>666.5156062904225</v>
+      </c>
+      <c r="D48">
+        <v>8128.113606290422</v>
+      </c>
+      <c r="E48">
+        <v>4114.498000000001</v>
+      </c>
+      <c r="F48">
+        <v>9152.298000000001</v>
+      </c>
+      <c r="G48">
+        <v>1690.7</v>
+      </c>
+      <c r="H48">
+        <v>14858.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1969.1</v>
+      </c>
+      <c r="K48">
+        <v>820.1</v>
+      </c>
+      <c r="L48">
+        <v>1149</v>
+      </c>
+      <c r="M48">
+        <v>2035.731369913761</v>
+      </c>
+      <c r="N48">
+        <v>-886.7313699137615</v>
+      </c>
+      <c r="O48">
+        <v>-110.8414212392202</v>
+      </c>
+      <c r="P48">
+        <v>-775.8899486745413</v>
+      </c>
+      <c r="Q48">
+        <v>44.21005132545872</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1369254483608706</v>
+      </c>
+      <c r="T48">
+        <v>1.375965380100056</v>
+      </c>
+      <c r="U48">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V48">
+        <v>0.07055203948941667</v>
+      </c>
+      <c r="W48">
+        <v>0.2067356602586325</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5644163159153334</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1708744302375108</v>
+      </c>
+      <c r="C49">
+        <v>354.544144170648</v>
+      </c>
+      <c r="D49">
+        <v>8015.105144170648</v>
+      </c>
+      <c r="E49">
+        <v>4313.461</v>
+      </c>
+      <c r="F49">
+        <v>9351.261</v>
+      </c>
+      <c r="G49">
+        <v>1690.7</v>
+      </c>
+      <c r="H49">
+        <v>14858.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1969.1</v>
+      </c>
+      <c r="K49">
+        <v>820.1</v>
+      </c>
+      <c r="L49">
+        <v>1149</v>
+      </c>
+      <c r="M49">
+        <v>2079.986399694496</v>
+      </c>
+      <c r="N49">
+        <v>-930.9863996944955</v>
+      </c>
+      <c r="O49">
+        <v>-116.3732999618119</v>
+      </c>
+      <c r="P49">
+        <v>-814.6130997326836</v>
+      </c>
+      <c r="Q49">
+        <v>5.4869002673164</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1387768719148493</v>
+      </c>
+      <c r="T49">
+        <v>1.40192699104534</v>
+      </c>
+      <c r="U49">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V49">
+        <v>0.0690509322662376</v>
+      </c>
+      <c r="W49">
+        <v>0.2070695491971078</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5524074581299008</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1727107146411805</v>
+      </c>
+      <c r="C50">
+        <v>45.6719960531791</v>
+      </c>
+      <c r="D50">
+        <v>7905.195996053179</v>
+      </c>
+      <c r="E50">
+        <v>4512.424</v>
+      </c>
+      <c r="F50">
+        <v>9550.224</v>
+      </c>
+      <c r="G50">
+        <v>1690.7</v>
+      </c>
+      <c r="H50">
+        <v>14858.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1969.1</v>
+      </c>
+      <c r="K50">
+        <v>820.1</v>
+      </c>
+      <c r="L50">
+        <v>1149</v>
+      </c>
+      <c r="M50">
+        <v>2124.241429475229</v>
+      </c>
+      <c r="N50">
+        <v>-975.2414294752293</v>
+      </c>
+      <c r="O50">
+        <v>-121.9051786844037</v>
+      </c>
+      <c r="P50">
+        <v>-853.3362507908257</v>
+      </c>
+      <c r="Q50">
+        <v>-33.23625079082569</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1406995040670579</v>
+      </c>
+      <c r="T50">
+        <v>1.42888712548852</v>
+      </c>
+      <c r="U50">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V50">
+        <v>0.06761237117735765</v>
+      </c>
+      <c r="W50">
+        <v>0.20738952609648</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5408989694188612</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1745469990448502</v>
+      </c>
+      <c r="C51">
+        <v>-260.2266137035331</v>
+      </c>
+      <c r="D51">
+        <v>7798.260386296466</v>
+      </c>
+      <c r="E51">
+        <v>4711.387</v>
+      </c>
+      <c r="F51">
+        <v>9749.187</v>
+      </c>
+      <c r="G51">
+        <v>1690.7</v>
+      </c>
+      <c r="H51">
+        <v>14858.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1969.1</v>
+      </c>
+      <c r="K51">
+        <v>820.1</v>
+      </c>
+      <c r="L51">
+        <v>1149</v>
+      </c>
+      <c r="M51">
+        <v>2168.496459255963</v>
+      </c>
+      <c r="N51">
+        <v>-1019.496459255963</v>
+      </c>
+      <c r="O51">
+        <v>-127.4370574069954</v>
+      </c>
+      <c r="P51">
+        <v>-892.0594018489678</v>
+      </c>
+      <c r="Q51">
+        <v>-71.95940184896779</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1426975335585689</v>
+      </c>
+      <c r="T51">
+        <v>1.456904520105942</v>
+      </c>
+      <c r="U51">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V51">
+        <v>0.06623252686761566</v>
+      </c>
+      <c r="W51">
+        <v>0.2076964427142451</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5298602149409253</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1763832834485199</v>
+      </c>
+      <c r="C52">
+        <v>-563.2707459761859</v>
+      </c>
+      <c r="D52">
+        <v>7694.179254023813</v>
+      </c>
+      <c r="E52">
+        <v>4910.349999999999</v>
+      </c>
+      <c r="F52">
+        <v>9948.15</v>
+      </c>
+      <c r="G52">
+        <v>1690.7</v>
+      </c>
+      <c r="H52">
+        <v>14858.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1969.1</v>
+      </c>
+      <c r="K52">
+        <v>820.1</v>
+      </c>
+      <c r="L52">
+        <v>1149</v>
+      </c>
+      <c r="M52">
+        <v>2212.751489036697</v>
+      </c>
+      <c r="N52">
+        <v>-1063.751489036697</v>
+      </c>
+      <c r="O52">
+        <v>-132.9689361295871</v>
+      </c>
+      <c r="P52">
+        <v>-930.7825529071099</v>
+      </c>
+      <c r="Q52">
+        <v>-110.6825529071099</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1447754842297402</v>
+      </c>
+      <c r="T52">
+        <v>1.486042610508061</v>
+      </c>
+      <c r="U52">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V52">
+        <v>0.06490787633026335</v>
+      </c>
+      <c r="W52">
+        <v>0.2079910826672997</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5192630106421068</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1782195678521897</v>
+      </c>
+      <c r="C53">
+        <v>-863.5731890748921</v>
+      </c>
+      <c r="D53">
+        <v>7592.839810925107</v>
+      </c>
+      <c r="E53">
+        <v>5109.312999999999</v>
+      </c>
+      <c r="F53">
+        <v>10147.113</v>
+      </c>
+      <c r="G53">
+        <v>1690.7</v>
+      </c>
+      <c r="H53">
+        <v>14858.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1969.1</v>
+      </c>
+      <c r="K53">
+        <v>820.1</v>
+      </c>
+      <c r="L53">
+        <v>1149</v>
+      </c>
+      <c r="M53">
+        <v>2257.006518817431</v>
+      </c>
+      <c r="N53">
+        <v>-1108.006518817431</v>
+      </c>
+      <c r="O53">
+        <v>-138.5008148521788</v>
+      </c>
+      <c r="P53">
+        <v>-969.505703965252</v>
+      </c>
+      <c r="Q53">
+        <v>-149.405703965252</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1469382492140207</v>
+      </c>
+      <c r="T53">
+        <v>1.516370010722511</v>
+      </c>
+      <c r="U53">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V53">
+        <v>0.06363517287280721</v>
+      </c>
+      <c r="W53">
+        <v>0.2082741681123913</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5090813829824576</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1800558522558594</v>
+      </c>
+      <c r="C54">
+        <v>-1161.240866450735</v>
+      </c>
+      <c r="D54">
+        <v>7494.135133549264</v>
+      </c>
+      <c r="E54">
+        <v>5308.275999999999</v>
+      </c>
+      <c r="F54">
+        <v>10346.076</v>
+      </c>
+      <c r="G54">
+        <v>1690.7</v>
+      </c>
+      <c r="H54">
+        <v>14858.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1969.1</v>
+      </c>
+      <c r="K54">
+        <v>820.1</v>
+      </c>
+      <c r="L54">
+        <v>1149</v>
+      </c>
+      <c r="M54">
+        <v>2301.261548598165</v>
+      </c>
+      <c r="N54">
+        <v>-1152.261548598165</v>
+      </c>
+      <c r="O54">
+        <v>-144.0326935747706</v>
+      </c>
+      <c r="P54">
+        <v>-1008.228855023394</v>
+      </c>
+      <c r="Q54">
+        <v>-188.1288550233941</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1491911294059794</v>
+      </c>
+      <c r="T54">
+        <v>1.547961052612563</v>
+      </c>
+      <c r="U54">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V54">
+        <v>0.06241141954833015</v>
+      </c>
+      <c r="W54">
+        <v>0.2085463656557486</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4992913563866412</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1818921366595291</v>
+      </c>
+      <c r="C55">
+        <v>-1456.375213010984</v>
+      </c>
+      <c r="D55">
+        <v>7397.963786989016</v>
+      </c>
+      <c r="E55">
+        <v>5507.239</v>
+      </c>
+      <c r="F55">
+        <v>10545.039</v>
+      </c>
+      <c r="G55">
+        <v>1690.7</v>
+      </c>
+      <c r="H55">
+        <v>14858.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1969.1</v>
+      </c>
+      <c r="K55">
+        <v>820.1</v>
+      </c>
+      <c r="L55">
+        <v>1149</v>
+      </c>
+      <c r="M55">
+        <v>2345.516578378899</v>
+      </c>
+      <c r="N55">
+        <v>-1196.516578378899</v>
+      </c>
+      <c r="O55">
+        <v>-149.5645722973624</v>
+      </c>
+      <c r="P55">
+        <v>-1046.952006081537</v>
+      </c>
+      <c r="Q55">
+        <v>-226.8520060815366</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1515398768401492</v>
+      </c>
+      <c r="T55">
+        <v>1.580896394157511</v>
+      </c>
+      <c r="U55">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V55">
+        <v>0.06123384559458806</v>
+      </c>
+      <c r="W55">
+        <v>0.2088082915936962</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.4898707647567044</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1837284210631989</v>
+      </c>
+      <c r="C56">
+        <v>-1749.072522826154</v>
+      </c>
+      <c r="D56">
+        <v>7304.229477173846</v>
+      </c>
+      <c r="E56">
+        <v>5706.202</v>
+      </c>
+      <c r="F56">
+        <v>10744.002</v>
+      </c>
+      <c r="G56">
+        <v>1690.7</v>
+      </c>
+      <c r="H56">
+        <v>14858.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1969.1</v>
+      </c>
+      <c r="K56">
+        <v>820.1</v>
+      </c>
+      <c r="L56">
+        <v>1149</v>
+      </c>
+      <c r="M56">
+        <v>2389.771608159633</v>
+      </c>
+      <c r="N56">
+        <v>-1240.771608159633</v>
+      </c>
+      <c r="O56">
+        <v>-155.0964510199541</v>
+      </c>
+      <c r="P56">
+        <v>-1085.675157139679</v>
+      </c>
+      <c r="Q56">
+        <v>-265.5751571396785</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1539907437279785</v>
+      </c>
+      <c r="T56">
+        <v>1.615263707073979</v>
+      </c>
+      <c r="U56">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V56">
+        <v>0.06009988549098458</v>
+      </c>
+      <c r="W56">
+        <v>0.2090605165709791</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4807990839278766</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1855647054668686</v>
+      </c>
+      <c r="C57">
+        <v>-2039.424270734535</v>
+      </c>
+      <c r="D57">
+        <v>7212.840729265466</v>
+      </c>
+      <c r="E57">
+        <v>5905.165</v>
+      </c>
+      <c r="F57">
+        <v>10942.965</v>
+      </c>
+      <c r="G57">
+        <v>1690.7</v>
+      </c>
+      <c r="H57">
+        <v>14858.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1969.1</v>
+      </c>
+      <c r="K57">
+        <v>820.1</v>
+      </c>
+      <c r="L57">
+        <v>1149</v>
+      </c>
+      <c r="M57">
+        <v>2434.026637940367</v>
+      </c>
+      <c r="N57">
+        <v>-1285.026637940367</v>
+      </c>
+      <c r="O57">
+        <v>-160.6283297425459</v>
+      </c>
+      <c r="P57">
+        <v>-1124.398308197821</v>
+      </c>
+      <c r="Q57">
+        <v>-304.298308197821</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1565505380330447</v>
+      </c>
+      <c r="T57">
+        <v>1.651158456120068</v>
+      </c>
+      <c r="U57">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V57">
+        <v>0.0590071603002394</v>
+      </c>
+      <c r="W57">
+        <v>0.2093035697309063</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.4720572824019152</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1874009898705383</v>
+      </c>
+      <c r="C58">
+        <v>-2327.517410101995</v>
+      </c>
+      <c r="D58">
+        <v>7123.710589898004</v>
+      </c>
+      <c r="E58">
+        <v>6104.128</v>
+      </c>
+      <c r="F58">
+        <v>11141.928</v>
+      </c>
+      <c r="G58">
+        <v>1690.7</v>
+      </c>
+      <c r="H58">
+        <v>14858.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1969.1</v>
+      </c>
+      <c r="K58">
+        <v>820.1</v>
+      </c>
+      <c r="L58">
+        <v>1149</v>
+      </c>
+      <c r="M58">
+        <v>2478.281667721101</v>
+      </c>
+      <c r="N58">
+        <v>-1329.281667721101</v>
+      </c>
+      <c r="O58">
+        <v>-166.1602084651376</v>
+      </c>
+      <c r="P58">
+        <v>-1163.121459255963</v>
+      </c>
+      <c r="Q58">
+        <v>-343.0214592559631</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1592266866247048</v>
+      </c>
+      <c r="T58">
+        <v>1.688684784668251</v>
+      </c>
+      <c r="U58">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V58">
+        <v>0.0579534610091637</v>
+      </c>
+      <c r="W58">
+        <v>0.209537942420836</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4636276880733096</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1892372742742081</v>
+      </c>
+      <c r="C59">
+        <v>-2613.434648774541</v>
+      </c>
+      <c r="D59">
+        <v>7036.75635122546</v>
+      </c>
+      <c r="E59">
+        <v>6303.091000000001</v>
+      </c>
+      <c r="F59">
+        <v>11340.891</v>
+      </c>
+      <c r="G59">
+        <v>1690.7</v>
+      </c>
+      <c r="H59">
+        <v>14858.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1969.1</v>
+      </c>
+      <c r="K59">
+        <v>820.1</v>
+      </c>
+      <c r="L59">
+        <v>1149</v>
+      </c>
+      <c r="M59">
+        <v>2522.536697501835</v>
+      </c>
+      <c r="N59">
+        <v>-1373.536697501835</v>
+      </c>
+      <c r="O59">
+        <v>-171.6920871877294</v>
+      </c>
+      <c r="P59">
+        <v>-1201.844610314106</v>
+      </c>
+      <c r="Q59">
+        <v>-381.7446103141057</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.162027307243884</v>
+      </c>
+      <c r="T59">
+        <v>1.727956523846582</v>
+      </c>
+      <c r="U59">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V59">
+        <v>0.05693673362303801</v>
+      </c>
+      <c r="W59">
+        <v>0.2097640915076104</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4554938689843041</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1910735586778777</v>
+      </c>
+      <c r="C60">
+        <v>-2897.254705064353</v>
+      </c>
+      <c r="D60">
+        <v>6951.899294935646</v>
+      </c>
+      <c r="E60">
+        <v>6502.053999999999</v>
+      </c>
+      <c r="F60">
+        <v>11539.854</v>
+      </c>
+      <c r="G60">
+        <v>1690.7</v>
+      </c>
+      <c r="H60">
+        <v>14858.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1969.1</v>
+      </c>
+      <c r="K60">
+        <v>820.1</v>
+      </c>
+      <c r="L60">
+        <v>1149</v>
+      </c>
+      <c r="M60">
+        <v>2566.791727282568</v>
+      </c>
+      <c r="N60">
+        <v>-1417.791727282568</v>
+      </c>
+      <c r="O60">
+        <v>-177.2239659103211</v>
+      </c>
+      <c r="P60">
+        <v>-1240.567761372247</v>
+      </c>
+      <c r="Q60">
+        <v>-420.4677613722473</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1649612907496907</v>
+      </c>
+      <c r="T60">
+        <v>1.769098345842929</v>
+      </c>
+      <c r="U60">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V60">
+        <v>0.05595506580195116</v>
+      </c>
+      <c r="W60">
+        <v>0.2099824423500131</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4476405264156093</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1929098430815475</v>
+      </c>
+      <c r="C61">
+        <v>-3179.05254543479</v>
+      </c>
+      <c r="D61">
+        <v>6869.064454565209</v>
+      </c>
+      <c r="E61">
+        <v>6701.016999999999</v>
+      </c>
+      <c r="F61">
+        <v>11738.817</v>
+      </c>
+      <c r="G61">
+        <v>1690.7</v>
+      </c>
+      <c r="H61">
+        <v>14858.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1969.1</v>
+      </c>
+      <c r="K61">
+        <v>820.1</v>
+      </c>
+      <c r="L61">
+        <v>1149</v>
+      </c>
+      <c r="M61">
+        <v>2611.046757063302</v>
+      </c>
+      <c r="N61">
+        <v>-1462.046757063302</v>
+      </c>
+      <c r="O61">
+        <v>-182.7558446329128</v>
+      </c>
+      <c r="P61">
+        <v>-1279.290912430389</v>
+      </c>
+      <c r="Q61">
+        <v>-459.1909124303894</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1680383954021222</v>
+      </c>
+      <c r="T61">
+        <v>1.812247085985439</v>
+      </c>
+      <c r="U61">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V61">
+        <v>0.05500667485615538</v>
+      </c>
+      <c r="W61">
+        <v>0.2101933914689446</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4400533988492431</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1947461274852172</v>
+      </c>
+      <c r="C62">
+        <v>-3458.899605392711</v>
+      </c>
+      <c r="D62">
+        <v>6788.180394607288</v>
+      </c>
+      <c r="E62">
+        <v>6899.979999999999</v>
+      </c>
+      <c r="F62">
+        <v>11937.78</v>
+      </c>
+      <c r="G62">
+        <v>1690.7</v>
+      </c>
+      <c r="H62">
+        <v>14858.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1969.1</v>
+      </c>
+      <c r="K62">
+        <v>820.1</v>
+      </c>
+      <c r="L62">
+        <v>1149</v>
+      </c>
+      <c r="M62">
+        <v>2655.301786844036</v>
+      </c>
+      <c r="N62">
+        <v>-1506.301786844036</v>
+      </c>
+      <c r="O62">
+        <v>-188.2877233555045</v>
+      </c>
+      <c r="P62">
+        <v>-1318.014063488532</v>
+      </c>
+      <c r="Q62">
+        <v>-497.9140634885315</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1712693552871753</v>
+      </c>
+      <c r="T62">
+        <v>1.857553263135076</v>
+      </c>
+      <c r="U62">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V62">
+        <v>0.05408989694188613</v>
+      </c>
+      <c r="W62">
+        <v>0.2103973089505785</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.432719175535089</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1965824118888869</v>
+      </c>
+      <c r="C63">
+        <v>-3736.863994956282</v>
+      </c>
+      <c r="D63">
+        <v>6709.179005043716</v>
+      </c>
+      <c r="E63">
+        <v>7098.942999999998</v>
+      </c>
+      <c r="F63">
+        <v>12136.743</v>
+      </c>
+      <c r="G63">
+        <v>1690.7</v>
+      </c>
+      <c r="H63">
+        <v>14858.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1969.1</v>
+      </c>
+      <c r="K63">
+        <v>820.1</v>
+      </c>
+      <c r="L63">
+        <v>1149</v>
+      </c>
+      <c r="M63">
+        <v>2699.55681662477</v>
+      </c>
+      <c r="N63">
+        <v>-1550.55681662477</v>
+      </c>
+      <c r="O63">
+        <v>-193.8196020780962</v>
+      </c>
+      <c r="P63">
+        <v>-1356.737214546674</v>
+      </c>
+      <c r="Q63">
+        <v>-536.6372145466736</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1746660054227439</v>
+      </c>
+      <c r="T63">
+        <v>1.905182833984693</v>
+      </c>
+      <c r="U63">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V63">
+        <v>0.053203177319888</v>
+      </c>
+      <c r="W63">
+        <v>0.2105945406131423</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.425625418559104</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1984186962925567</v>
+      </c>
+      <c r="C64">
+        <v>-4013.010689940296</v>
+      </c>
+      <c r="D64">
+        <v>6631.995310059703</v>
+      </c>
+      <c r="E64">
+        <v>7297.906</v>
+      </c>
+      <c r="F64">
+        <v>12335.706</v>
+      </c>
+      <c r="G64">
+        <v>1690.7</v>
+      </c>
+      <c r="H64">
+        <v>14858.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1969.1</v>
+      </c>
+      <c r="K64">
+        <v>820.1</v>
+      </c>
+      <c r="L64">
+        <v>1149</v>
+      </c>
+      <c r="M64">
+        <v>2743.811846405504</v>
+      </c>
+      <c r="N64">
+        <v>-1594.811846405504</v>
+      </c>
+      <c r="O64">
+        <v>-199.351480800688</v>
+      </c>
+      <c r="P64">
+        <v>-1395.460365604816</v>
+      </c>
+      <c r="Q64">
+        <v>-575.3603656048161</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1782414266180792</v>
+      </c>
+      <c r="T64">
+        <v>1.955319224352711</v>
+      </c>
+      <c r="U64">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V64">
+        <v>0.05234506155666399</v>
+      </c>
+      <c r="W64">
+        <v>0.2107854099640105</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4187604924533119</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2002549806962264</v>
+      </c>
+      <c r="C65">
+        <v>-4287.40171018816</v>
+      </c>
+      <c r="D65">
+        <v>6556.56728981184</v>
+      </c>
+      <c r="E65">
+        <v>7496.869</v>
+      </c>
+      <c r="F65">
+        <v>12534.669</v>
+      </c>
+      <c r="G65">
+        <v>1690.7</v>
+      </c>
+      <c r="H65">
+        <v>14858.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1969.1</v>
+      </c>
+      <c r="K65">
+        <v>820.1</v>
+      </c>
+      <c r="L65">
+        <v>1149</v>
+      </c>
+      <c r="M65">
+        <v>2788.066876186238</v>
+      </c>
+      <c r="N65">
+        <v>-1639.066876186238</v>
+      </c>
+      <c r="O65">
+        <v>-204.8833595232798</v>
+      </c>
+      <c r="P65">
+        <v>-1434.183516662959</v>
+      </c>
+      <c r="Q65">
+        <v>-614.0835166629587</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1820101138239733</v>
+      </c>
+      <c r="T65">
+        <v>2.008165689875757</v>
+      </c>
+      <c r="U65">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V65">
+        <v>0.05151418756370106</v>
+      </c>
+      <c r="W65">
+        <v>0.2109702199704067</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4121135005096085</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2020912650998961</v>
+      </c>
+      <c r="C66">
+        <v>-4560.096285778117</v>
+      </c>
+      <c r="D66">
+        <v>6482.835714221883</v>
+      </c>
+      <c r="E66">
+        <v>7695.831999999999</v>
+      </c>
+      <c r="F66">
+        <v>12733.632</v>
+      </c>
+      <c r="G66">
+        <v>1690.7</v>
+      </c>
+      <c r="H66">
+        <v>14858.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1969.1</v>
+      </c>
+      <c r="K66">
+        <v>820.1</v>
+      </c>
+      <c r="L66">
+        <v>1149</v>
+      </c>
+      <c r="M66">
+        <v>2832.321905966972</v>
+      </c>
+      <c r="N66">
+        <v>-1683.321905966972</v>
+      </c>
+      <c r="O66">
+        <v>-210.4152382458715</v>
+      </c>
+      <c r="P66">
+        <v>-1472.906667721101</v>
+      </c>
+      <c r="Q66">
+        <v>-652.8066677211008</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1859881725413059</v>
+      </c>
+      <c r="T66">
+        <v>2.063948070150084</v>
+      </c>
+      <c r="U66">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V66">
+        <v>0.05070927838301824</v>
+      </c>
+      <c r="W66">
+        <v>0.2111492546641031</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4056742270641459</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2039275495035658</v>
+      </c>
+      <c r="C67">
+        <v>-4831.151012139752</v>
+      </c>
+      <c r="D67">
+        <v>6410.743987860247</v>
+      </c>
+      <c r="E67">
+        <v>7894.794999999999</v>
+      </c>
+      <c r="F67">
+        <v>12932.595</v>
+      </c>
+      <c r="G67">
+        <v>1690.7</v>
+      </c>
+      <c r="H67">
+        <v>14858.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1969.1</v>
+      </c>
+      <c r="K67">
+        <v>820.1</v>
+      </c>
+      <c r="L67">
+        <v>1149</v>
+      </c>
+      <c r="M67">
+        <v>2876.576935747706</v>
+      </c>
+      <c r="N67">
+        <v>-1727.576935747706</v>
+      </c>
+      <c r="O67">
+        <v>-215.9471169684633</v>
+      </c>
+      <c r="P67">
+        <v>-1511.629818779243</v>
+      </c>
+      <c r="Q67">
+        <v>-691.5298187792429</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1901935488996289</v>
+      </c>
+      <c r="T67">
+        <v>2.122918015011515</v>
+      </c>
+      <c r="U67">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V67">
+        <v>0.04992913563866411</v>
+      </c>
+      <c r="W67">
+        <v>0.2113227805979934</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3994330851093129</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2057638339072355</v>
+      </c>
+      <c r="C68">
+        <v>-5100.619994934611</v>
+      </c>
+      <c r="D68">
+        <v>6340.23800506539</v>
+      </c>
+      <c r="E68">
+        <v>8093.758000000001</v>
+      </c>
+      <c r="F68">
+        <v>13131.558</v>
+      </c>
+      <c r="G68">
+        <v>1690.7</v>
+      </c>
+      <c r="H68">
+        <v>14858.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1969.1</v>
+      </c>
+      <c r="K68">
+        <v>820.1</v>
+      </c>
+      <c r="L68">
+        <v>1149</v>
+      </c>
+      <c r="M68">
+        <v>2920.83196552844</v>
+      </c>
+      <c r="N68">
+        <v>-1771.83196552844</v>
+      </c>
+      <c r="O68">
+        <v>-221.478995691055</v>
+      </c>
+      <c r="P68">
+        <v>-1550.352969837385</v>
+      </c>
+      <c r="Q68">
+        <v>-730.2529698373854</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1946463003378533</v>
+      </c>
+      <c r="T68">
+        <v>2.185356780158913</v>
+      </c>
+      <c r="U68">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V68">
+        <v>0.04917263358353283</v>
+      </c>
+      <c r="W68">
+        <v>0.2114910481702506</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3933810686682626</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2076001183109052</v>
+      </c>
+      <c r="C69">
+        <v>-5368.554985480328</v>
+      </c>
+      <c r="D69">
+        <v>6271.266014519672</v>
+      </c>
+      <c r="E69">
+        <v>8292.721000000001</v>
+      </c>
+      <c r="F69">
+        <v>13330.521</v>
+      </c>
+      <c r="G69">
+        <v>1690.7</v>
+      </c>
+      <c r="H69">
+        <v>14858.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1969.1</v>
+      </c>
+      <c r="K69">
+        <v>820.1</v>
+      </c>
+      <c r="L69">
+        <v>1149</v>
+      </c>
+      <c r="M69">
+        <v>2965.086995309174</v>
+      </c>
+      <c r="N69">
+        <v>-1816.086995309174</v>
+      </c>
+      <c r="O69">
+        <v>-227.0108744136468</v>
+      </c>
+      <c r="P69">
+        <v>-1589.076120895527</v>
+      </c>
+      <c r="Q69">
+        <v>-768.9761208955273</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1993689154996064</v>
+      </c>
+      <c r="T69">
+        <v>2.251579712891001</v>
+      </c>
+      <c r="U69">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V69">
+        <v>0.048438713679301</v>
+      </c>
+      <c r="W69">
+        <v>0.2116542928299032</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.387509709434408</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.209436402714575</v>
+      </c>
+      <c r="C70">
+        <v>-5635.005507430667</v>
+      </c>
+      <c r="D70">
+        <v>6203.778492569334</v>
+      </c>
+      <c r="E70">
+        <v>8491.684000000001</v>
+      </c>
+      <c r="F70">
+        <v>13529.484</v>
+      </c>
+      <c r="G70">
+        <v>1690.7</v>
+      </c>
+      <c r="H70">
+        <v>14858.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1969.1</v>
+      </c>
+      <c r="K70">
+        <v>820.1</v>
+      </c>
+      <c r="L70">
+        <v>1149</v>
+      </c>
+      <c r="M70">
+        <v>3009.342025089908</v>
+      </c>
+      <c r="N70">
+        <v>-1860.342025089908</v>
+      </c>
+      <c r="O70">
+        <v>-232.5427531362385</v>
+      </c>
+      <c r="P70">
+        <v>-1627.79927195367</v>
+      </c>
+      <c r="Q70">
+        <v>-807.6992719536696</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2043866941089691</v>
+      </c>
+      <c r="T70">
+        <v>2.321941578918845</v>
+      </c>
+      <c r="U70">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V70">
+        <v>0.0477263796546054</v>
+      </c>
+      <c r="W70">
+        <v>0.2118127361760366</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3818110372368432</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2112726871182447</v>
+      </c>
+      <c r="C71">
+        <v>-5900.018975363113</v>
+      </c>
+      <c r="D71">
+        <v>6137.728024636887</v>
+      </c>
+      <c r="E71">
+        <v>8690.647000000001</v>
+      </c>
+      <c r="F71">
+        <v>13728.447</v>
+      </c>
+      <c r="G71">
+        <v>1690.7</v>
+      </c>
+      <c r="H71">
+        <v>14858.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1969.1</v>
+      </c>
+      <c r="K71">
+        <v>820.1</v>
+      </c>
+      <c r="L71">
+        <v>1149</v>
+      </c>
+      <c r="M71">
+        <v>3053.597054870642</v>
+      </c>
+      <c r="N71">
+        <v>-1904.597054870642</v>
+      </c>
+      <c r="O71">
+        <v>-238.0746318588302</v>
+      </c>
+      <c r="P71">
+        <v>-1666.522423011811</v>
+      </c>
+      <c r="Q71">
+        <v>-846.4224230118115</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2097282003705488</v>
+      </c>
+      <c r="T71">
+        <v>2.396842920174292</v>
+      </c>
+      <c r="U71">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V71">
+        <v>0.04703469299294445</v>
+      </c>
+      <c r="W71">
+        <v>0.2119665869614124</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3762775439435556</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2131089715219144</v>
+      </c>
+      <c r="C72">
+        <v>-6163.640805870817</v>
+      </c>
+      <c r="D72">
+        <v>6073.069194129185</v>
+      </c>
+      <c r="E72">
+        <v>8889.610000000001</v>
+      </c>
+      <c r="F72">
+        <v>13927.41</v>
+      </c>
+      <c r="G72">
+        <v>1690.7</v>
+      </c>
+      <c r="H72">
+        <v>14858.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1969.1</v>
+      </c>
+      <c r="K72">
+        <v>820.1</v>
+      </c>
+      <c r="L72">
+        <v>1149</v>
+      </c>
+      <c r="M72">
+        <v>3097.852084651376</v>
+      </c>
+      <c r="N72">
+        <v>-1948.852084651376</v>
+      </c>
+      <c r="O72">
+        <v>-243.606510581422</v>
+      </c>
+      <c r="P72">
+        <v>-1705.245574069954</v>
+      </c>
+      <c r="Q72">
+        <v>-885.145574069954</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2154258070495671</v>
+      </c>
+      <c r="T72">
+        <v>2.476737684180101</v>
+      </c>
+      <c r="U72">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V72">
+        <v>0.04636276880733096</v>
+      </c>
+      <c r="W72">
+        <v>0.2121160420100633</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3709021504586476</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2149452559255842</v>
+      </c>
+      <c r="C73">
+        <v>-6425.914521705808</v>
+      </c>
+      <c r="D73">
+        <v>6009.758478294192</v>
+      </c>
+      <c r="E73">
+        <v>9088.573</v>
+      </c>
+      <c r="F73">
+        <v>14126.373</v>
+      </c>
+      <c r="G73">
+        <v>1690.7</v>
+      </c>
+      <c r="H73">
+        <v>14858.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1969.1</v>
+      </c>
+      <c r="K73">
+        <v>820.1</v>
+      </c>
+      <c r="L73">
+        <v>1149</v>
+      </c>
+      <c r="M73">
+        <v>3142.10711443211</v>
+      </c>
+      <c r="N73">
+        <v>-1993.10711443211</v>
+      </c>
+      <c r="O73">
+        <v>-249.1383893040137</v>
+      </c>
+      <c r="P73">
+        <v>-1743.968725128096</v>
+      </c>
+      <c r="Q73">
+        <v>-923.8687251280961</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2215163521202418</v>
+      </c>
+      <c r="T73">
+        <v>2.562142431910449</v>
+      </c>
+      <c r="U73">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V73">
+        <v>0.04570977206356573</v>
+      </c>
+      <c r="W73">
+        <v>0.2122612870573437</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3656781765085259</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2167815403292539</v>
+      </c>
+      <c r="C74">
+        <v>-6686.881849475408</v>
+      </c>
+      <c r="D74">
+        <v>5947.754150524592</v>
+      </c>
+      <c r="E74">
+        <v>9287.536</v>
+      </c>
+      <c r="F74">
+        <v>14325.336</v>
+      </c>
+      <c r="G74">
+        <v>1690.7</v>
+      </c>
+      <c r="H74">
+        <v>14858.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1969.1</v>
+      </c>
+      <c r="K74">
+        <v>820.1</v>
+      </c>
+      <c r="L74">
+        <v>1149</v>
+      </c>
+      <c r="M74">
+        <v>3186.362144212844</v>
+      </c>
+      <c r="N74">
+        <v>-2037.362144212844</v>
+      </c>
+      <c r="O74">
+        <v>-254.6702680266055</v>
+      </c>
+      <c r="P74">
+        <v>-1782.691876186238</v>
+      </c>
+      <c r="Q74">
+        <v>-962.5918761862382</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2280419361245361</v>
+      </c>
+      <c r="T74">
+        <v>2.653647518764394</v>
+      </c>
+      <c r="U74">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V74">
+        <v>0.04507491411823843</v>
+      </c>
+      <c r="W74">
+        <v>0.2124024975199775</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3605993129459075</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2186178247329236</v>
+      </c>
+      <c r="C75">
+        <v>-6946.58281135261</v>
+      </c>
+      <c r="D75">
+        <v>5887.016188647389</v>
+      </c>
+      <c r="E75">
+        <v>9486.499</v>
+      </c>
+      <c r="F75">
+        <v>14524.299</v>
+      </c>
+      <c r="G75">
+        <v>1690.7</v>
+      </c>
+      <c r="H75">
+        <v>14858.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1969.1</v>
+      </c>
+      <c r="K75">
+        <v>820.1</v>
+      </c>
+      <c r="L75">
+        <v>1149</v>
+      </c>
+      <c r="M75">
+        <v>3230.617173993578</v>
+      </c>
+      <c r="N75">
+        <v>-2081.617173993578</v>
+      </c>
+      <c r="O75">
+        <v>-260.2021467491972</v>
+      </c>
+      <c r="P75">
+        <v>-1821.41502724438</v>
+      </c>
+      <c r="Q75">
+        <v>-1001.31502724438</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2350508967217411</v>
+      </c>
+      <c r="T75">
+        <v>2.751930760200112</v>
+      </c>
+      <c r="U75">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V75">
+        <v>0.04445744954127626</v>
+      </c>
+      <c r="W75">
+        <v>0.212539839202813</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3556595963302102</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2204541091365934</v>
+      </c>
+      <c r="C76">
+        <v>-7205.055811224048</v>
+      </c>
+      <c r="D76">
+        <v>5827.506188775951</v>
+      </c>
+      <c r="E76">
+        <v>9685.462</v>
+      </c>
+      <c r="F76">
+        <v>14723.262</v>
+      </c>
+      <c r="G76">
+        <v>1690.7</v>
+      </c>
+      <c r="H76">
+        <v>14858.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1969.1</v>
+      </c>
+      <c r="K76">
+        <v>820.1</v>
+      </c>
+      <c r="L76">
+        <v>1149</v>
+      </c>
+      <c r="M76">
+        <v>3274.872203774311</v>
+      </c>
+      <c r="N76">
+        <v>-2125.872203774311</v>
+      </c>
+      <c r="O76">
+        <v>-265.7340254717889</v>
+      </c>
+      <c r="P76">
+        <v>-1860.138178302522</v>
+      </c>
+      <c r="Q76">
+        <v>-1040.038178302522</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2425990081341158</v>
+      </c>
+      <c r="T76">
+        <v>2.857774250977039</v>
+      </c>
+      <c r="U76">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V76">
+        <v>0.04385667319612389</v>
+      </c>
+      <c r="W76">
+        <v>0.2126734689482746</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.350853385568991</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.222290393540263</v>
+      </c>
+      <c r="C77">
+        <v>-7462.337715665167</v>
+      </c>
+      <c r="D77">
+        <v>5769.187284334832</v>
+      </c>
+      <c r="E77">
+        <v>9884.424999999999</v>
+      </c>
+      <c r="F77">
+        <v>14922.225</v>
+      </c>
+      <c r="G77">
+        <v>1690.7</v>
+      </c>
+      <c r="H77">
+        <v>14858.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1969.1</v>
+      </c>
+      <c r="K77">
+        <v>820.1</v>
+      </c>
+      <c r="L77">
+        <v>1149</v>
+      </c>
+      <c r="M77">
+        <v>3319.127233555045</v>
+      </c>
+      <c r="N77">
+        <v>-2170.127233555045</v>
+      </c>
+      <c r="O77">
+        <v>-271.2659041943807</v>
+      </c>
+      <c r="P77">
+        <v>-1898.861329360665</v>
+      </c>
+      <c r="Q77">
+        <v>-1078.761329360665</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2507509684594805</v>
+      </c>
+      <c r="T77">
+        <v>2.972085221016121</v>
+      </c>
+      <c r="U77">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V77">
+        <v>0.0432719175535089</v>
+      </c>
+      <c r="W77">
+        <v>0.2128035352338573</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3461753404280712</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2241266779439328</v>
+      </c>
+      <c r="C78">
+        <v>-7718.463930101455</v>
+      </c>
+      <c r="D78">
+        <v>5712.024069898545</v>
+      </c>
+      <c r="E78">
+        <v>10083.388</v>
+      </c>
+      <c r="F78">
+        <v>15121.188</v>
+      </c>
+      <c r="G78">
+        <v>1690.7</v>
+      </c>
+      <c r="H78">
+        <v>14858.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1969.1</v>
+      </c>
+      <c r="K78">
+        <v>820.1</v>
+      </c>
+      <c r="L78">
+        <v>1149</v>
+      </c>
+      <c r="M78">
+        <v>3363.382263335779</v>
+      </c>
+      <c r="N78">
+        <v>-2214.382263335779</v>
+      </c>
+      <c r="O78">
+        <v>-276.7977829169724</v>
+      </c>
+      <c r="P78">
+        <v>-1937.584480418807</v>
+      </c>
+      <c r="Q78">
+        <v>-1117.484480418807</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2595822588119588</v>
+      </c>
+      <c r="T78">
+        <v>3.095922105225126</v>
+      </c>
+      <c r="U78">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V78">
+        <v>0.04270255021727851</v>
+      </c>
+      <c r="W78">
+        <v>0.2129301787224509</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3416204017382282</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2259629623476025</v>
+      </c>
+      <c r="C79">
+        <v>-7973.468470486247</v>
+      </c>
+      <c r="D79">
+        <v>5655.982529513753</v>
+      </c>
+      <c r="E79">
+        <v>10282.351</v>
+      </c>
+      <c r="F79">
+        <v>15320.151</v>
+      </c>
+      <c r="G79">
+        <v>1690.7</v>
+      </c>
+      <c r="H79">
+        <v>14858.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1969.1</v>
+      </c>
+      <c r="K79">
+        <v>820.1</v>
+      </c>
+      <c r="L79">
+        <v>1149</v>
+      </c>
+      <c r="M79">
+        <v>3407.637293116513</v>
+      </c>
+      <c r="N79">
+        <v>-2258.637293116513</v>
+      </c>
+      <c r="O79">
+        <v>-282.3296616395642</v>
+      </c>
+      <c r="P79">
+        <v>-1976.307631476949</v>
+      </c>
+      <c r="Q79">
+        <v>-1156.207631476949</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.269181487455957</v>
+      </c>
+      <c r="T79">
+        <v>3.230527414147958</v>
+      </c>
+      <c r="U79">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V79">
+        <v>0.04214797164302815</v>
+      </c>
+      <c r="W79">
+        <v>0.2130535327697823</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3371837731442252</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2277992467512722</v>
+      </c>
+      <c r="C80">
+        <v>-8227.384030800114</v>
+      </c>
+      <c r="D80">
+        <v>5601.029969199885</v>
+      </c>
+      <c r="E80">
+        <v>10481.314</v>
+      </c>
+      <c r="F80">
+        <v>15519.114</v>
+      </c>
+      <c r="G80">
+        <v>1690.7</v>
+      </c>
+      <c r="H80">
+        <v>14858.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1969.1</v>
+      </c>
+      <c r="K80">
+        <v>820.1</v>
+      </c>
+      <c r="L80">
+        <v>1149</v>
+      </c>
+      <c r="M80">
+        <v>3451.892322897247</v>
+      </c>
+      <c r="N80">
+        <v>-2302.892322897247</v>
+      </c>
+      <c r="O80">
+        <v>-287.8615403621559</v>
+      </c>
+      <c r="P80">
+        <v>-2015.030782535091</v>
+      </c>
+      <c r="Q80">
+        <v>-1194.930782535091</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2796533732494096</v>
+      </c>
+      <c r="T80">
+        <v>3.377369569336502</v>
+      </c>
+      <c r="U80">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V80">
+        <v>0.0416076130322201</v>
+      </c>
+      <c r="W80">
+        <v>0.2131737238928232</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3328609042577607</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.229635531154942</v>
+      </c>
+      <c r="C81">
+        <v>-8480.242046653204</v>
+      </c>
+      <c r="D81">
+        <v>5547.134953346796</v>
+      </c>
+      <c r="E81">
+        <v>10680.277</v>
+      </c>
+      <c r="F81">
+        <v>15718.077</v>
+      </c>
+      <c r="G81">
+        <v>1690.7</v>
+      </c>
+      <c r="H81">
+        <v>14858.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1969.1</v>
+      </c>
+      <c r="K81">
+        <v>820.1</v>
+      </c>
+      <c r="L81">
+        <v>1149</v>
+      </c>
+      <c r="M81">
+        <v>3496.147352677981</v>
+      </c>
+      <c r="N81">
+        <v>-2347.147352677981</v>
+      </c>
+      <c r="O81">
+        <v>-293.3934190847477</v>
+      </c>
+      <c r="P81">
+        <v>-2053.753933593234</v>
+      </c>
+      <c r="Q81">
+        <v>-1233.653933593234</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2911225814993815</v>
+      </c>
+      <c r="T81">
+        <v>3.538196691685859</v>
+      </c>
+      <c r="U81">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V81">
+        <v>0.04108093438624262</v>
+      </c>
+      <c r="W81">
+        <v>0.2132908722026226</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.328647475089941</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2314718155586117</v>
+      </c>
+      <c r="C82">
+        <v>-8732.072755250592</v>
+      </c>
+      <c r="D82">
+        <v>5494.267244749409</v>
+      </c>
+      <c r="E82">
+        <v>10879.24</v>
+      </c>
+      <c r="F82">
+        <v>15917.04</v>
+      </c>
+      <c r="G82">
+        <v>1690.7</v>
+      </c>
+      <c r="H82">
+        <v>14858.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1969.1</v>
+      </c>
+      <c r="K82">
+        <v>820.1</v>
+      </c>
+      <c r="L82">
+        <v>1149</v>
+      </c>
+      <c r="M82">
+        <v>3540.402382458716</v>
+      </c>
+      <c r="N82">
+        <v>-2391.402382458716</v>
+      </c>
+      <c r="O82">
+        <v>-298.9252978073395</v>
+      </c>
+      <c r="P82">
+        <v>-2092.477084651376</v>
+      </c>
+      <c r="Q82">
+        <v>-1272.377084651376</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3037387105743506</v>
+      </c>
+      <c r="T82">
+        <v>3.715106526270152</v>
+      </c>
+      <c r="U82">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V82">
+        <v>0.04056742270641459</v>
+      </c>
+      <c r="W82">
+        <v>0.213405091804677</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3245393816513167</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2333080999622814</v>
+      </c>
+      <c r="C83">
+        <v>-8982.905251960923</v>
+      </c>
+      <c r="D83">
+        <v>5442.397748039078</v>
+      </c>
+      <c r="E83">
+        <v>11078.203</v>
+      </c>
+      <c r="F83">
+        <v>16116.003</v>
+      </c>
+      <c r="G83">
+        <v>1690.7</v>
+      </c>
+      <c r="H83">
+        <v>14858.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1969.1</v>
+      </c>
+      <c r="K83">
+        <v>820.1</v>
+      </c>
+      <c r="L83">
+        <v>1149</v>
+      </c>
+      <c r="M83">
+        <v>3584.65741223945</v>
+      </c>
+      <c r="N83">
+        <v>-2435.65741223945</v>
+      </c>
+      <c r="O83">
+        <v>-304.4571765299312</v>
+      </c>
+      <c r="P83">
+        <v>-2131.200235709518</v>
+      </c>
+      <c r="Q83">
+        <v>-1311.100235709519</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3176828532361586</v>
+      </c>
+      <c r="T83">
+        <v>3.910638448705423</v>
+      </c>
+      <c r="U83">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V83">
+        <v>0.04006659032732305</v>
+      </c>
+      <c r="W83">
+        <v>0.2135164911696436</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3205327226185843</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2351443843659511</v>
+      </c>
+      <c r="C84">
+        <v>-9232.767543710796</v>
+      </c>
+      <c r="D84">
+        <v>5391.498456289205</v>
+      </c>
+      <c r="E84">
+        <v>11277.166</v>
+      </c>
+      <c r="F84">
+        <v>16314.966</v>
+      </c>
+      <c r="G84">
+        <v>1690.7</v>
+      </c>
+      <c r="H84">
+        <v>14858.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1969.1</v>
+      </c>
+      <c r="K84">
+        <v>820.1</v>
+      </c>
+      <c r="L84">
+        <v>1149</v>
+      </c>
+      <c r="M84">
+        <v>3628.912442020183</v>
+      </c>
+      <c r="N84">
+        <v>-2479.912442020183</v>
+      </c>
+      <c r="O84">
+        <v>-309.9890552525229</v>
+      </c>
+      <c r="P84">
+        <v>-2169.92338676766</v>
+      </c>
+      <c r="Q84">
+        <v>-1349.82338676766</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3331763450826118</v>
+      </c>
+      <c r="T84">
+        <v>4.127896140300169</v>
+      </c>
+      <c r="U84">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V84">
+        <v>0.0395779733721118</v>
+      </c>
+      <c r="W84">
+        <v>0.2136251734769281</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3166237869768943</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2369806687696209</v>
+      </c>
+      <c r="C85">
+        <v>-9481.686599410668</v>
+      </c>
+      <c r="D85">
+        <v>5341.542400589332</v>
+      </c>
+      <c r="E85">
+        <v>11476.129</v>
+      </c>
+      <c r="F85">
+        <v>16513.929</v>
+      </c>
+      <c r="G85">
+        <v>1690.7</v>
+      </c>
+      <c r="H85">
+        <v>14858.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1969.1</v>
+      </c>
+      <c r="K85">
+        <v>820.1</v>
+      </c>
+      <c r="L85">
+        <v>1149</v>
+      </c>
+      <c r="M85">
+        <v>3673.167471800917</v>
+      </c>
+      <c r="N85">
+        <v>-2524.167471800917</v>
+      </c>
+      <c r="O85">
+        <v>-315.5209339751146</v>
+      </c>
+      <c r="P85">
+        <v>-2208.646537825803</v>
+      </c>
+      <c r="Q85">
+        <v>-1388.546537825803</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3504926006757066</v>
+      </c>
+      <c r="T85">
+        <v>4.370713560317826</v>
+      </c>
+      <c r="U85">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V85">
+        <v>0.03910113031943575</v>
+      </c>
+      <c r="W85">
+        <v>0.2137312369334346</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.312809042555486</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2388169531732906</v>
+      </c>
+      <c r="C86">
+        <v>-9729.688397603164</v>
+      </c>
+      <c r="D86">
+        <v>5292.503602396837</v>
+      </c>
+      <c r="E86">
+        <v>11675.092</v>
+      </c>
+      <c r="F86">
+        <v>16712.892</v>
+      </c>
+      <c r="G86">
+        <v>1690.7</v>
+      </c>
+      <c r="H86">
+        <v>14858.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1969.1</v>
+      </c>
+      <c r="K86">
+        <v>820.1</v>
+      </c>
+      <c r="L86">
+        <v>1149</v>
+      </c>
+      <c r="M86">
+        <v>3717.422501581651</v>
+      </c>
+      <c r="N86">
+        <v>-2568.422501581651</v>
+      </c>
+      <c r="O86">
+        <v>-321.0528126977064</v>
+      </c>
+      <c r="P86">
+        <v>-2247.369688883944</v>
+      </c>
+      <c r="Q86">
+        <v>-1427.269688883945</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3699733882179382</v>
+      </c>
+      <c r="T86">
+        <v>4.643883157837688</v>
+      </c>
+      <c r="U86">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V86">
+        <v>0.0386356406727758</v>
+      </c>
+      <c r="W86">
+        <v>0.2138347750695482</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3090851253822064</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2406532375769603</v>
+      </c>
+      <c r="C87">
+        <v>-9976.797971510565</v>
+      </c>
+      <c r="D87">
+        <v>5244.357028489436</v>
+      </c>
+      <c r="E87">
+        <v>11874.055</v>
+      </c>
+      <c r="F87">
+        <v>16911.855</v>
+      </c>
+      <c r="G87">
+        <v>1690.7</v>
+      </c>
+      <c r="H87">
+        <v>14858.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1969.1</v>
+      </c>
+      <c r="K87">
+        <v>820.1</v>
+      </c>
+      <c r="L87">
+        <v>1149</v>
+      </c>
+      <c r="M87">
+        <v>3761.677531362385</v>
+      </c>
+      <c r="N87">
+        <v>-2612.677531362385</v>
+      </c>
+      <c r="O87">
+        <v>-326.5846914202981</v>
+      </c>
+      <c r="P87">
+        <v>-2286.092839942087</v>
+      </c>
+      <c r="Q87">
+        <v>-1465.992839942087</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3920516140991341</v>
+      </c>
+      <c r="T87">
+        <v>4.953475368360201</v>
+      </c>
+      <c r="U87">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V87">
+        <v>0.03818110372368432</v>
+      </c>
+      <c r="W87">
+        <v>0.2139358770142238</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3054488297894746</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.24248952198063</v>
+      </c>
+      <c r="C88">
+        <v>-10223.03945164567</v>
+      </c>
+      <c r="D88">
+        <v>5197.07854835433</v>
+      </c>
+      <c r="E88">
+        <v>12073.018</v>
+      </c>
+      <c r="F88">
+        <v>17110.818</v>
+      </c>
+      <c r="G88">
+        <v>1690.7</v>
+      </c>
+      <c r="H88">
+        <v>14858.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1969.1</v>
+      </c>
+      <c r="K88">
+        <v>820.1</v>
+      </c>
+      <c r="L88">
+        <v>1149</v>
+      </c>
+      <c r="M88">
+        <v>3805.932561143119</v>
+      </c>
+      <c r="N88">
+        <v>-2656.932561143119</v>
+      </c>
+      <c r="O88">
+        <v>-332.1165701428898</v>
+      </c>
+      <c r="P88">
+        <v>-2324.815991000229</v>
+      </c>
+      <c r="Q88">
+        <v>-1504.715991000229</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4172838722490722</v>
+      </c>
+      <c r="T88">
+        <v>5.307295037528787</v>
+      </c>
+      <c r="U88">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V88">
+        <v>0.0377371374013159</v>
+      </c>
+      <c r="W88">
+        <v>0.2140346277508836</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3018970992105272</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2443258063842998</v>
+      </c>
+      <c r="C89">
+        <v>-10468.43610613841</v>
+      </c>
+      <c r="D89">
+        <v>5150.644893861593</v>
+      </c>
+      <c r="E89">
+        <v>12271.981</v>
+      </c>
+      <c r="F89">
+        <v>17309.781</v>
+      </c>
+      <c r="G89">
+        <v>1690.7</v>
+      </c>
+      <c r="H89">
+        <v>14858.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1969.1</v>
+      </c>
+      <c r="K89">
+        <v>820.1</v>
+      </c>
+      <c r="L89">
+        <v>1149</v>
+      </c>
+      <c r="M89">
+        <v>3850.187590923852</v>
+      </c>
+      <c r="N89">
+        <v>-2701.187590923852</v>
+      </c>
+      <c r="O89">
+        <v>-337.6484488654816</v>
+      </c>
+      <c r="P89">
+        <v>-2363.539142058371</v>
+      </c>
+      <c r="Q89">
+        <v>-1543.439142058371</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4463980162682316</v>
+      </c>
+      <c r="T89">
+        <v>5.715548501954078</v>
+      </c>
+      <c r="U89">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V89">
+        <v>0.03730337720130078</v>
+      </c>
+      <c r="W89">
+        <v>0.2141311083556663</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2984270176104062</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2461620907879694</v>
+      </c>
+      <c r="C90">
+        <v>-10713.01037891975</v>
+      </c>
+      <c r="D90">
+        <v>5105.033621080254</v>
+      </c>
+      <c r="E90">
+        <v>12470.944</v>
+      </c>
+      <c r="F90">
+        <v>17508.744</v>
+      </c>
+      <c r="G90">
+        <v>1690.7</v>
+      </c>
+      <c r="H90">
+        <v>14858.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1969.1</v>
+      </c>
+      <c r="K90">
+        <v>820.1</v>
+      </c>
+      <c r="L90">
+        <v>1149</v>
+      </c>
+      <c r="M90">
+        <v>3894.442620704587</v>
+      </c>
+      <c r="N90">
+        <v>-2745.442620704587</v>
+      </c>
+      <c r="O90">
+        <v>-343.1803275880733</v>
+      </c>
+      <c r="P90">
+        <v>-2402.262293116513</v>
+      </c>
+      <c r="Q90">
+        <v>-1582.162293116513</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4803645176239176</v>
+      </c>
+      <c r="T90">
+        <v>6.191844210450252</v>
+      </c>
+      <c r="U90">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V90">
+        <v>0.03687947518764963</v>
+      </c>
+      <c r="W90">
+        <v>0.2142253962194311</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.295035801501197</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2479983751916392</v>
+      </c>
+      <c r="C91">
+        <v>-10956.78392589465</v>
+      </c>
+      <c r="D91">
+        <v>5060.223074105345</v>
+      </c>
+      <c r="E91">
+        <v>12669.907</v>
+      </c>
+      <c r="F91">
+        <v>17707.707</v>
+      </c>
+      <c r="G91">
+        <v>1690.7</v>
+      </c>
+      <c r="H91">
+        <v>14858.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1969.1</v>
+      </c>
+      <c r="K91">
+        <v>820.1</v>
+      </c>
+      <c r="L91">
+        <v>1149</v>
+      </c>
+      <c r="M91">
+        <v>3938.697650485321</v>
+      </c>
+      <c r="N91">
+        <v>-2789.697650485321</v>
+      </c>
+      <c r="O91">
+        <v>-348.7122063106651</v>
+      </c>
+      <c r="P91">
+        <v>-2440.985444174656</v>
+      </c>
+      <c r="Q91">
+        <v>-1620.885444174656</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5205067464988191</v>
+      </c>
+      <c r="T91">
+        <v>6.754739138673002</v>
+      </c>
+      <c r="U91">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V91">
+        <v>0.0364650990619457</v>
+      </c>
+      <c r="W91">
+        <v>0.2143175652547967</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2917207924955656</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2498346595953089</v>
+      </c>
+      <c r="C92">
+        <v>-11199.77764922649</v>
+      </c>
+      <c r="D92">
+        <v>5016.192350773509</v>
+      </c>
+      <c r="E92">
+        <v>12868.87</v>
+      </c>
+      <c r="F92">
+        <v>17906.67</v>
+      </c>
+      <c r="G92">
+        <v>1690.7</v>
+      </c>
+      <c r="H92">
+        <v>14858.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1969.1</v>
+      </c>
+      <c r="K92">
+        <v>820.1</v>
+      </c>
+      <c r="L92">
+        <v>1149</v>
+      </c>
+      <c r="M92">
+        <v>3982.952680266054</v>
+      </c>
+      <c r="N92">
+        <v>-2833.952680266054</v>
+      </c>
+      <c r="O92">
+        <v>-354.2440850332568</v>
+      </c>
+      <c r="P92">
+        <v>-2479.708595232798</v>
+      </c>
+      <c r="Q92">
+        <v>-1659.608595232798</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5686774211487013</v>
+      </c>
+      <c r="T92">
+        <v>7.430213052540305</v>
+      </c>
+      <c r="U92">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V92">
+        <v>0.03605993129459075</v>
+      </c>
+      <c r="W92">
+        <v>0.2144076860893765</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.288479450356726</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2516709439989787</v>
+      </c>
+      <c r="C93">
+        <v>-11442.01172984695</v>
+      </c>
+      <c r="D93">
+        <v>4972.92127015305</v>
+      </c>
+      <c r="E93">
+        <v>13067.833</v>
+      </c>
+      <c r="F93">
+        <v>18105.633</v>
+      </c>
+      <c r="G93">
+        <v>1690.7</v>
+      </c>
+      <c r="H93">
+        <v>14858.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1969.1</v>
+      </c>
+      <c r="K93">
+        <v>820.1</v>
+      </c>
+      <c r="L93">
+        <v>1149</v>
+      </c>
+      <c r="M93">
+        <v>4027.207710046789</v>
+      </c>
+      <c r="N93">
+        <v>-2878.207710046789</v>
+      </c>
+      <c r="O93">
+        <v>-359.7759637558486</v>
+      </c>
+      <c r="P93">
+        <v>-2518.43174629094</v>
+      </c>
+      <c r="Q93">
+        <v>-1698.33174629094</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6275526901652237</v>
+      </c>
+      <c r="T93">
+        <v>8.255792280600339</v>
+      </c>
+      <c r="U93">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V93">
+        <v>0.0356636683133315</v>
+      </c>
+      <c r="W93">
+        <v>0.2144958262462731</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2853093465066521</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2535072284026484</v>
+      </c>
+      <c r="C94">
+        <v>-11683.50565829774</v>
+      </c>
+      <c r="D94">
+        <v>4930.390341702266</v>
+      </c>
+      <c r="E94">
+        <v>13266.796</v>
+      </c>
+      <c r="F94">
+        <v>18304.596</v>
+      </c>
+      <c r="G94">
+        <v>1690.7</v>
+      </c>
+      <c r="H94">
+        <v>14858.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1969.1</v>
+      </c>
+      <c r="K94">
+        <v>820.1</v>
+      </c>
+      <c r="L94">
+        <v>1149</v>
+      </c>
+      <c r="M94">
+        <v>4071.462739827523</v>
+      </c>
+      <c r="N94">
+        <v>-2922.462739827523</v>
+      </c>
+      <c r="O94">
+        <v>-365.3078424784404</v>
+      </c>
+      <c r="P94">
+        <v>-2557.154897349083</v>
+      </c>
+      <c r="Q94">
+        <v>-1737.054897349083</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7011467764358768</v>
+      </c>
+      <c r="T94">
+        <v>9.287766315675384</v>
+      </c>
+      <c r="U94">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V94">
+        <v>0.03527601974470834</v>
+      </c>
+      <c r="W94">
+        <v>0.2145820503128025</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2822081579576667</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2553435128063181</v>
+      </c>
+      <c r="C95">
+        <v>-11924.27826400303</v>
+      </c>
+      <c r="D95">
+        <v>4888.580735996969</v>
+      </c>
+      <c r="E95">
+        <v>13465.759</v>
+      </c>
+      <c r="F95">
+        <v>18503.559</v>
+      </c>
+      <c r="G95">
+        <v>1690.7</v>
+      </c>
+      <c r="H95">
+        <v>14858.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1969.1</v>
+      </c>
+      <c r="K95">
+        <v>820.1</v>
+      </c>
+      <c r="L95">
+        <v>1149</v>
+      </c>
+      <c r="M95">
+        <v>4115.717769608257</v>
+      </c>
+      <c r="N95">
+        <v>-2966.717769608257</v>
+      </c>
+      <c r="O95">
+        <v>-370.8397212010321</v>
+      </c>
+      <c r="P95">
+        <v>-2595.878048407225</v>
+      </c>
+      <c r="Q95">
+        <v>-1775.778048407225</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.795767744498145</v>
+      </c>
+      <c r="T95">
+        <v>10.61459007505758</v>
+      </c>
+      <c r="U95">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V95">
+        <v>0.03489670770444266</v>
+      </c>
+      <c r="W95">
+        <v>0.2146664200983312</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2791736616355412</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2571797972099878</v>
+      </c>
+      <c r="C96">
+        <v>-12164.3477430651</v>
+      </c>
+      <c r="D96">
+        <v>4847.474256934898</v>
+      </c>
+      <c r="E96">
+        <v>13664.722</v>
+      </c>
+      <c r="F96">
+        <v>18702.522</v>
+      </c>
+      <c r="G96">
+        <v>1690.7</v>
+      </c>
+      <c r="H96">
+        <v>14858.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1969.1</v>
+      </c>
+      <c r="K96">
+        <v>820.1</v>
+      </c>
+      <c r="L96">
+        <v>1149</v>
+      </c>
+      <c r="M96">
+        <v>4159.972799388991</v>
+      </c>
+      <c r="N96">
+        <v>-3010.972799388991</v>
+      </c>
+      <c r="O96">
+        <v>-376.3715999236239</v>
+      </c>
+      <c r="P96">
+        <v>-2634.601199465367</v>
+      </c>
+      <c r="Q96">
+        <v>-1814.501199465367</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.921929035247836</v>
+      </c>
+      <c r="T96">
+        <v>12.38368842090052</v>
+      </c>
+      <c r="U96">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V96">
+        <v>0.0345254661331188</v>
+      </c>
+      <c r="W96">
+        <v>0.2147489947820401</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2762037290649504</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2590160816136576</v>
+      </c>
+      <c r="C97">
+        <v>-12403.73168466925</v>
+      </c>
+      <c r="D97">
+        <v>4807.053315330751</v>
+      </c>
+      <c r="E97">
+        <v>13863.685</v>
+      </c>
+      <c r="F97">
+        <v>18901.485</v>
+      </c>
+      <c r="G97">
+        <v>1690.7</v>
+      </c>
+      <c r="H97">
+        <v>14858.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1969.1</v>
+      </c>
+      <c r="K97">
+        <v>820.1</v>
+      </c>
+      <c r="L97">
+        <v>1149</v>
+      </c>
+      <c r="M97">
+        <v>4204.227829169725</v>
+      </c>
+      <c r="N97">
+        <v>-3055.227829169725</v>
+      </c>
+      <c r="O97">
+        <v>-381.9034786462156</v>
+      </c>
+      <c r="P97">
+        <v>-2673.324350523509</v>
+      </c>
+      <c r="Q97">
+        <v>-1853.224350523509</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.098554842297404</v>
+      </c>
+      <c r="T97">
+        <v>14.86042610508063</v>
+      </c>
+      <c r="U97">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V97">
+        <v>0.03416204017382281</v>
+      </c>
+      <c r="W97">
+        <v>0.2148298310513552</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2732963213905825</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2608523660173273</v>
+      </c>
+      <c r="C98">
+        <v>-12642.44709617862</v>
+      </c>
+      <c r="D98">
+        <v>4767.30090382138</v>
+      </c>
+      <c r="E98">
+        <v>14062.648</v>
+      </c>
+      <c r="F98">
+        <v>19100.448</v>
+      </c>
+      <c r="G98">
+        <v>1690.7</v>
+      </c>
+      <c r="H98">
+        <v>14858.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1969.1</v>
+      </c>
+      <c r="K98">
+        <v>820.1</v>
+      </c>
+      <c r="L98">
+        <v>1149</v>
+      </c>
+      <c r="M98">
+        <v>4248.482858950459</v>
+      </c>
+      <c r="N98">
+        <v>-3099.482858950459</v>
+      </c>
+      <c r="O98">
+        <v>-387.4353573688073</v>
+      </c>
+      <c r="P98">
+        <v>-2712.047501581651</v>
+      </c>
+      <c r="Q98">
+        <v>-1891.947501581652</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.363493552871752</v>
+      </c>
+      <c r="T98">
+        <v>18.57553263135074</v>
+      </c>
+      <c r="U98">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V98">
+        <v>0.03380618558867882</v>
+      </c>
+      <c r="W98">
+        <v>0.2149089832317262</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2704494847094305</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.262688650420997</v>
+      </c>
+      <c r="C99">
+        <v>-12880.51042699408</v>
+      </c>
+      <c r="D99">
+        <v>4728.20057300592</v>
+      </c>
+      <c r="E99">
+        <v>14261.611</v>
+      </c>
+      <c r="F99">
+        <v>19299.411</v>
+      </c>
+      <c r="G99">
+        <v>1690.7</v>
+      </c>
+      <c r="H99">
+        <v>14858.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1969.1</v>
+      </c>
+      <c r="K99">
+        <v>820.1</v>
+      </c>
+      <c r="L99">
+        <v>1149</v>
+      </c>
+      <c r="M99">
+        <v>4292.737888731192</v>
+      </c>
+      <c r="N99">
+        <v>-3143.737888731192</v>
+      </c>
+      <c r="O99">
+        <v>-392.9672360913991</v>
+      </c>
+      <c r="P99">
+        <v>-2750.770652639793</v>
+      </c>
+      <c r="Q99">
+        <v>-1930.670652639793</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.805058070495669</v>
+      </c>
+      <c r="T99">
+        <v>24.76737684180099</v>
+      </c>
+      <c r="U99">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V99">
+        <v>0.03345766821147595</v>
+      </c>
+      <c r="W99">
+        <v>0.2149865034083782</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2676613456918076</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2645249348246668</v>
+      </c>
+      <c r="C100">
+        <v>-13117.93759124947</v>
+      </c>
+      <c r="D100">
+        <v>4689.736408750528</v>
+      </c>
+      <c r="E100">
+        <v>14460.574</v>
+      </c>
+      <c r="F100">
+        <v>19498.374</v>
+      </c>
+      <c r="G100">
+        <v>1690.7</v>
+      </c>
+      <c r="H100">
+        <v>14858.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1969.1</v>
+      </c>
+      <c r="K100">
+        <v>820.1</v>
+      </c>
+      <c r="L100">
+        <v>1149</v>
+      </c>
+      <c r="M100">
+        <v>4336.992918511926</v>
+      </c>
+      <c r="N100">
+        <v>-3187.992918511926</v>
+      </c>
+      <c r="O100">
+        <v>-398.4991148139908</v>
+      </c>
+      <c r="P100">
+        <v>-2789.493803697936</v>
+      </c>
+      <c r="Q100">
+        <v>-1969.393803697936</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.688187105743504</v>
+      </c>
+      <c r="T100">
+        <v>37.15106526270149</v>
+      </c>
+      <c r="U100">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V100">
+        <v>0.03311626343380783</v>
+      </c>
+      <c r="W100">
+        <v>0.2150624415406088</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2649301074704626</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2663612192283364</v>
+      </c>
+      <c r="C101">
+        <v>-13354.74398940805</v>
+      </c>
+      <c r="D101">
+        <v>4651.893010591946</v>
+      </c>
+      <c r="E101">
+        <v>14659.537</v>
+      </c>
+      <c r="F101">
+        <v>19697.337</v>
+      </c>
+      <c r="G101">
+        <v>1690.7</v>
+      </c>
+      <c r="H101">
+        <v>14858.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1969.1</v>
+      </c>
+      <c r="K101">
+        <v>820.1</v>
+      </c>
+      <c r="L101">
+        <v>1149</v>
+      </c>
+      <c r="M101">
+        <v>4381.24794829266</v>
+      </c>
+      <c r="N101">
+        <v>-3232.24794829266</v>
+      </c>
+      <c r="O101">
+        <v>-404.0309935365825</v>
+      </c>
+      <c r="P101">
+        <v>-2828.216954756077</v>
+      </c>
+      <c r="Q101">
+        <v>-2008.116954756078</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.337574211487008</v>
+      </c>
+      <c r="T101">
+        <v>74.30213052540297</v>
+      </c>
+      <c r="U101">
+        <v>0.2224284403669725</v>
+      </c>
+      <c r="V101">
+        <v>0.03278175572235523</v>
+      </c>
+      <c r="W101">
+        <v>0.2151368455691579</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2622540457788418</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
@@ -650,10 +650,10 @@
         <v>0.1913104886168746</v>
       </c>
       <c r="X2">
-        <v>0.09223451751258592</v>
+        <v>0.09221283213511225</v>
       </c>
       <c r="Y2">
-        <v>0.09907597110428869</v>
+        <v>0.09909765648176236</v>
       </c>
       <c r="Z2">
         <v>1.793128386308938</v>
@@ -662,10 +662,10 @@
         <v>0.1933666904279902</v>
       </c>
       <c r="AB2">
-        <v>0.08752629043690402</v>
+        <v>0.08750731399392614</v>
       </c>
       <c r="AC2">
-        <v>0.1058403999910862</v>
+        <v>0.1058593764340641</v>
       </c>
       <c r="AD2">
         <v>3059.4</v>
@@ -787,10 +787,10 @@
         <v>0.1913104886168746</v>
       </c>
       <c r="X3">
-        <v>0.09223451751258592</v>
+        <v>0.09221283213511225</v>
       </c>
       <c r="Y3">
-        <v>0.09907597110428869</v>
+        <v>0.09909765648176236</v>
       </c>
       <c r="Z3">
         <v>1.793128386308938</v>
@@ -799,10 +799,10 @@
         <v>0.1933666904279902</v>
       </c>
       <c r="AB3">
-        <v>0.08752629043690402</v>
+        <v>0.08750731399392614</v>
       </c>
       <c r="AC3">
-        <v>0.1058403999910862</v>
+        <v>0.1058593764340641</v>
       </c>
       <c r="AD3">
         <v>3059.4</v>
@@ -1139,7 +1139,7 @@
         <v>19.2008639308855</v>
       </c>
       <c r="F2">
-        <v>8.997057512210199</v>
+        <v>9.221037567637079</v>
       </c>
       <c r="G2">
         <v>1.00764113036032</v>
@@ -1157,13 +1157,13 @@
         <v>21431.5</v>
       </c>
       <c r="L2">
-        <v>21309.7381867993</v>
+        <v>21392.3762701796</v>
       </c>
       <c r="M2">
         <v>21227.2</v>
       </c>
       <c r="N2">
-        <v>21474.7641867993</v>
+        <v>21557.4022701796</v>
       </c>
       <c r="O2">
         <v>3059.4</v>
@@ -1172,16 +1172,16 @@
         <v>3428.726</v>
       </c>
       <c r="Q2">
-        <v>0.08752629043690401</v>
+        <v>0.0875073139939261</v>
       </c>
       <c r="R2">
-        <v>0.0870045986190197</v>
+        <v>0.08681415851437189</v>
       </c>
       <c r="S2">
         <v>0.0545445395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09223451751258591</v>
+        <v>0.09221283213511219</v>
       </c>
       <c r="X2">
-        <v>0.09295827102076661</v>
+        <v>0.0929362476432691</v>
       </c>
       <c r="Y2">
         <v>0.904672486472362</v>
@@ -1236,7 +1236,7 @@
         <v>21431.5</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183672</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08707848659324097</v>
+        <v>0.08705920913303966</v>
       </c>
       <c r="C2">
-        <v>24703.05088068647</v>
+        <v>24703.19865789174</v>
       </c>
       <c r="D2">
-        <v>21439.35088068647</v>
+        <v>21439.49865789174</v>
       </c>
       <c r="E2">
         <v>-3059.4</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08707848659324097</v>
+        <v>0.08705920913303966</v>
       </c>
       <c r="T2">
         <v>0.8042187817285175</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0870732088807966</v>
+        <v>0.08704170551742052</v>
       </c>
       <c r="C3">
-        <v>24460.66752870004</v>
+        <v>24466.66855719447</v>
       </c>
       <c r="D3">
-        <v>21441.87652870004</v>
+        <v>21447.87755719446</v>
       </c>
       <c r="E3">
         <v>-2814.491</v>
@@ -1539,37 +1539,37 @@
         <v>1778</v>
       </c>
       <c r="M3">
-        <v>14.11572615020456</v>
+        <v>13.77285355020457</v>
       </c>
       <c r="N3">
-        <v>1763.884273849795</v>
+        <v>1764.227146449795</v>
       </c>
       <c r="O3">
-        <v>220.4855342312244</v>
+        <v>220.5283933062244</v>
       </c>
       <c r="P3">
-        <v>1543.398739618571</v>
+        <v>1543.698753143571</v>
       </c>
       <c r="Q3">
-        <v>2801.598739618571</v>
+        <v>2801.898753143571</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08744332170201963</v>
+        <v>0.08742387386022561</v>
       </c>
       <c r="T3">
         <v>0.8113267760114715</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>125.9588051709428</v>
+        <v>129.094525946919</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08706793116835221</v>
+        <v>0.08702420190180139</v>
       </c>
       <c r="C4">
-        <v>24218.28477184818</v>
+        <v>24230.1450082737</v>
       </c>
       <c r="D4">
-        <v>21444.40277184818</v>
+        <v>21456.26300827369</v>
       </c>
       <c r="E4">
         <v>-2569.582</v>
@@ -1621,37 +1621,37 @@
         <v>1778</v>
       </c>
       <c r="M4">
-        <v>28.23145230040913</v>
+        <v>27.54570710040913</v>
       </c>
       <c r="N4">
-        <v>1749.768547699591</v>
+        <v>1750.454292899591</v>
       </c>
       <c r="O4">
-        <v>218.7210684624488</v>
+        <v>218.8067866124488</v>
       </c>
       <c r="P4">
-        <v>1531.047479237142</v>
+        <v>1531.647506287142</v>
       </c>
       <c r="Q4">
-        <v>2789.247479237142</v>
+        <v>2789.847506287142</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08781560242526312</v>
+        <v>0.08779598072470107</v>
       </c>
       <c r="T4">
         <v>0.8185798314022409</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.97940258547143</v>
+        <v>64.54726297345954</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08706265345590784</v>
+        <v>0.08700669828618227</v>
       </c>
       <c r="C5">
-        <v>23975.90261034127</v>
+        <v>23993.62801881706</v>
       </c>
       <c r="D5">
-        <v>21446.92961034126</v>
+        <v>21464.65501881706</v>
       </c>
       <c r="E5">
         <v>-2324.673</v>
@@ -1703,37 +1703,37 @@
         <v>1778</v>
       </c>
       <c r="M5">
-        <v>42.34717845061369</v>
+        <v>41.31856065061369</v>
       </c>
       <c r="N5">
-        <v>1735.652821549386</v>
+        <v>1736.681439349386</v>
       </c>
       <c r="O5">
-        <v>216.9566026936733</v>
+        <v>217.0851799186732</v>
       </c>
       <c r="P5">
-        <v>1518.696218855713</v>
+        <v>1519.596259430713</v>
       </c>
       <c r="Q5">
-        <v>2776.896218855713</v>
+        <v>2777.796259430713</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08819555903970755</v>
+        <v>0.08817575989566057</v>
       </c>
       <c r="T5">
         <v>0.8259824343268407</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.98626839031429</v>
+        <v>43.03150864897303</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08705737574346345</v>
+        <v>0.08698919467056315</v>
       </c>
       <c r="C6">
-        <v>23733.52104438979</v>
+        <v>23757.11759652422</v>
       </c>
       <c r="D6">
-        <v>21449.45704438979</v>
+        <v>21473.05359652422</v>
       </c>
       <c r="E6">
         <v>-2079.764</v>
@@ -1785,37 +1785,37 @@
         <v>1778</v>
       </c>
       <c r="M6">
-        <v>56.46290460081826</v>
+        <v>55.09141420081826</v>
       </c>
       <c r="N6">
-        <v>1721.537095399181</v>
+        <v>1722.908585799182</v>
       </c>
       <c r="O6">
-        <v>215.1921369248977</v>
+        <v>215.3635732248977</v>
       </c>
       <c r="P6">
-        <v>1506.344958474284</v>
+        <v>1507.545012574284</v>
       </c>
       <c r="Q6">
-        <v>2764.544958474284</v>
+        <v>2765.745012574284</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08858343141695288</v>
+        <v>0.08856345113268173</v>
       </c>
       <c r="T6">
         <v>0.833539258145703</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.48970129273571</v>
+        <v>32.27363148672977</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08705209803101908</v>
+        <v>0.08697169105494401</v>
       </c>
       <c r="C7">
-        <v>23491.1400742043</v>
+        <v>23520.61374910689</v>
       </c>
       <c r="D7">
-        <v>21451.98507420429</v>
+        <v>21481.4587491069</v>
       </c>
       <c r="E7">
         <v>-1834.855</v>
@@ -1867,37 +1867,37 @@
         <v>1778</v>
       </c>
       <c r="M7">
-        <v>70.57863075102283</v>
+        <v>68.86426775102282</v>
       </c>
       <c r="N7">
-        <v>1707.421369248977</v>
+        <v>1709.135732248977</v>
       </c>
       <c r="O7">
-        <v>213.4276711561221</v>
+        <v>213.6419665311221</v>
       </c>
       <c r="P7">
-        <v>1493.993698092855</v>
+        <v>1495.493765717855</v>
       </c>
       <c r="Q7">
-        <v>2752.193698092855</v>
+        <v>2753.693765717855</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08897946952845602</v>
+        <v>0.08895930429048227</v>
       </c>
       <c r="T7">
         <v>0.8412551729923308</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.19176103418857</v>
+        <v>25.81890518938382</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08704682031857471</v>
+        <v>0.0869541874393249</v>
       </c>
       <c r="C8">
-        <v>23248.75969999548</v>
+        <v>23284.11648428886</v>
       </c>
       <c r="D8">
-        <v>21454.51369999548</v>
+        <v>21489.87048428886</v>
       </c>
       <c r="E8">
         <v>-1589.946</v>
@@ -1949,37 +1949,37 @@
         <v>1778</v>
       </c>
       <c r="M8">
-        <v>84.69435690122738</v>
+        <v>82.63712130122738</v>
       </c>
       <c r="N8">
-        <v>1693.305643098772</v>
+        <v>1695.362878698772</v>
       </c>
       <c r="O8">
-        <v>211.6632053873466</v>
+        <v>211.9203598373466</v>
       </c>
       <c r="P8">
-        <v>1481.642437711426</v>
+        <v>1483.442518861426</v>
       </c>
       <c r="Q8">
-        <v>2739.842437711426</v>
+        <v>2741.642518861426</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0893839339827571</v>
+        <v>0.0893635798558956</v>
       </c>
       <c r="T8">
         <v>0.8491352562399507</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.99313419515714</v>
+        <v>21.51575432448652</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08704154260613033</v>
+        <v>0.08693668382370577</v>
       </c>
       <c r="C9">
-        <v>23006.37992197413</v>
+        <v>23047.62580980603</v>
       </c>
       <c r="D9">
-        <v>21457.04292197413</v>
+        <v>21498.28880980603</v>
       </c>
       <c r="E9">
         <v>-1345.037</v>
@@ -2031,37 +2031,37 @@
         <v>1778</v>
       </c>
       <c r="M9">
-        <v>98.81008305143196</v>
+        <v>96.40997485143197</v>
       </c>
       <c r="N9">
-        <v>1679.189916948568</v>
+        <v>1681.590025148568</v>
       </c>
       <c r="O9">
-        <v>209.898739618571</v>
+        <v>210.198753143571</v>
       </c>
       <c r="P9">
-        <v>1469.291177329997</v>
+        <v>1471.391272004997</v>
       </c>
       <c r="Q9">
-        <v>2727.491177329997</v>
+        <v>2729.591272004997</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08979709659736572</v>
+        <v>0.08977654951948985</v>
       </c>
       <c r="T9">
         <v>0.8571848036434333</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.9941150244204</v>
+        <v>18.44207513527415</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08703626489368596</v>
+        <v>0.08691918020808666</v>
       </c>
       <c r="C10">
-        <v>22764.0007403511</v>
+        <v>22811.14173340642</v>
       </c>
       <c r="D10">
-        <v>21459.5727403511</v>
+        <v>21506.71373340642</v>
       </c>
       <c r="E10">
         <v>-1100.128</v>
@@ -2113,37 +2113,37 @@
         <v>1778</v>
       </c>
       <c r="M10">
-        <v>112.9258092016365</v>
+        <v>110.1828284016365</v>
       </c>
       <c r="N10">
-        <v>1665.074190798363</v>
+        <v>1667.817171598363</v>
       </c>
       <c r="O10">
-        <v>208.1342738497954</v>
+        <v>208.4771464497954</v>
       </c>
       <c r="P10">
-        <v>1456.939916948568</v>
+        <v>1459.340025148568</v>
       </c>
       <c r="Q10">
-        <v>2715.139916948568</v>
+        <v>2717.540025148568</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0902192410079441</v>
+        <v>0.09019849678446659</v>
       </c>
       <c r="T10">
         <v>0.8654093412078613</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.74485064636786</v>
+        <v>16.13681574336488</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08703098718124158</v>
+        <v>0.08690167659246752</v>
       </c>
       <c r="C11">
-        <v>22521.62215533737</v>
+        <v>22574.66426285021</v>
       </c>
       <c r="D11">
-        <v>21462.10315533737</v>
+        <v>21515.14526285021</v>
       </c>
       <c r="E11">
         <v>-855.2190000000001</v>
@@ -2195,37 +2195,37 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>127.0415353518411</v>
+        <v>123.9556819518411</v>
       </c>
       <c r="N11">
-        <v>1650.958464648159</v>
+        <v>1654.044318048159</v>
       </c>
       <c r="O11">
-        <v>206.3698080810198</v>
+        <v>206.7555397560198</v>
       </c>
       <c r="P11">
-        <v>1444.588656567139</v>
+        <v>1447.288778292139</v>
       </c>
       <c r="Q11">
-        <v>2702.788656567139</v>
+        <v>2705.488778292139</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09065066331765606</v>
+        <v>0.09062971761570654</v>
       </c>
       <c r="T11">
         <v>0.8738146378396391</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.99542279677143</v>
+        <v>14.34383621632434</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0870257094687972</v>
+        <v>0.0868841729768484</v>
       </c>
       <c r="C12">
-        <v>22279.24416714401</v>
+        <v>22338.19340590973</v>
       </c>
       <c r="D12">
-        <v>21464.63416714401</v>
+        <v>21523.58340590973</v>
       </c>
       <c r="E12">
         <v>-610.3099999999999</v>
@@ -2277,37 +2277,37 @@
         <v>1778</v>
       </c>
       <c r="M12">
-        <v>141.1572615020457</v>
+        <v>137.7285355020456</v>
       </c>
       <c r="N12">
-        <v>1636.842738497954</v>
+        <v>1640.271464497954</v>
       </c>
       <c r="O12">
-        <v>204.6053423122443</v>
+        <v>205.0339330622443</v>
       </c>
       <c r="P12">
-        <v>1432.23739618571</v>
+        <v>1435.23753143571</v>
       </c>
       <c r="Q12">
-        <v>2690.43739618571</v>
+        <v>2693.43753143571</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09109167278980607</v>
+        <v>0.09107052113208519</v>
       </c>
       <c r="T12">
         <v>0.8824067188410123</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.59588051709428</v>
+        <v>12.90945259469191</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08702043175635281</v>
+        <v>0.08686666936122928</v>
       </c>
       <c r="C13">
-        <v>22036.86677598221</v>
+        <v>22101.72917036953</v>
       </c>
       <c r="D13">
-        <v>21467.1657759822</v>
+        <v>21532.02817036953</v>
       </c>
       <c r="E13">
         <v>-365.4009999999998</v>
@@ -2359,37 +2359,37 @@
         <v>1778</v>
       </c>
       <c r="M13">
-        <v>155.2729876522502</v>
+        <v>151.5013890522502</v>
       </c>
       <c r="N13">
-        <v>1622.72701234775</v>
+        <v>1626.49861094775</v>
       </c>
       <c r="O13">
-        <v>202.8408765434687</v>
+        <v>203.3123263684687</v>
       </c>
       <c r="P13">
-        <v>1419.886135804281</v>
+        <v>1423.186284579281</v>
       </c>
       <c r="Q13">
-        <v>2678.086135804281</v>
+        <v>2681.386284579281</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09154259258717293</v>
+        <v>0.09152123034546109</v>
       </c>
       <c r="T13">
         <v>0.8911918803143263</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.45080047008571</v>
+        <v>11.73586599517446</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08701515404390844</v>
+        <v>0.08684916574561015</v>
       </c>
       <c r="C14">
-        <v>21794.48998206321</v>
+        <v>21865.27156402639</v>
       </c>
       <c r="D14">
-        <v>21469.69798206321</v>
+        <v>21540.47956402638</v>
       </c>
       <c r="E14">
         <v>-120.4920000000002</v>
@@ -2441,37 +2441,37 @@
         <v>1778</v>
       </c>
       <c r="M14">
-        <v>169.3887138024548</v>
+        <v>165.2742426024548</v>
       </c>
       <c r="N14">
-        <v>1608.611286197545</v>
+        <v>1612.725757397545</v>
       </c>
       <c r="O14">
-        <v>201.0764107746931</v>
+        <v>201.5907196746931</v>
       </c>
       <c r="P14">
-        <v>1407.534875422852</v>
+        <v>1411.135037722852</v>
       </c>
       <c r="Q14">
-        <v>2665.734875422852</v>
+        <v>2669.335037722852</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09200376056175269</v>
+        <v>0.09198218295005008</v>
       </c>
       <c r="T14">
         <v>0.9001767045483975</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.49656709757857</v>
+        <v>10.75787716224326</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08700987633146406</v>
+        <v>0.08683166212999102</v>
       </c>
       <c r="C15">
-        <v>21552.11378559841</v>
+        <v>21628.8205946893</v>
       </c>
       <c r="D15">
-        <v>21472.2307855984</v>
+        <v>21548.93759468929</v>
       </c>
       <c r="E15">
         <v>124.4170000000004</v>
@@ -2523,37 +2523,37 @@
         <v>1778</v>
       </c>
       <c r="M15">
-        <v>183.5044399526593</v>
+        <v>179.0470961526593</v>
       </c>
       <c r="N15">
-        <v>1594.49556004734</v>
+        <v>1598.95290384734</v>
       </c>
       <c r="O15">
-        <v>199.3119450059176</v>
+        <v>199.8691129809175</v>
       </c>
       <c r="P15">
-        <v>1395.183615041423</v>
+        <v>1399.083790866423</v>
       </c>
       <c r="Q15">
-        <v>2653.383615041423</v>
+        <v>2657.283790866423</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09247553009896645</v>
+        <v>0.09245373216623881</v>
       </c>
       <c r="T15">
         <v>0.9093680764660105</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.689138859303295</v>
+        <v>9.930348149763006</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0870045986190197</v>
+        <v>0.08681415851437188</v>
       </c>
       <c r="C16">
-        <v>21309.73818679926</v>
+        <v>21392.37627017956</v>
       </c>
       <c r="D16">
-        <v>21474.76418679926</v>
+        <v>21557.40227017955</v>
       </c>
       <c r="E16">
         <v>369.3260000000005</v>
@@ -2605,37 +2605,37 @@
         <v>1778</v>
       </c>
       <c r="M16">
-        <v>197.6201661028639</v>
+        <v>192.8199497028639</v>
       </c>
       <c r="N16">
-        <v>1580.379833897136</v>
+        <v>1585.180050297136</v>
       </c>
       <c r="O16">
-        <v>197.547479237142</v>
+        <v>198.147506287142</v>
       </c>
       <c r="P16">
-        <v>1382.832354659994</v>
+        <v>1387.032544009994</v>
       </c>
       <c r="Q16">
-        <v>2641.032354659994</v>
+        <v>2645.232544009994</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09295827102076659</v>
+        <v>0.09293624764326915</v>
       </c>
       <c r="T16">
         <v>0.9187732012189168</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.997057512210201</v>
+        <v>9.221037567637076</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08714369590657531</v>
+        <v>0.08699352989875277</v>
       </c>
       <c r="C17">
-        <v>20998.25900016468</v>
+        <v>21061.03785684442</v>
       </c>
       <c r="D17">
-        <v>21408.19400016468</v>
+        <v>21470.97285684442</v>
       </c>
       <c r="E17">
         <v>614.2350000000001</v>
@@ -2687,37 +2687,37 @@
         <v>1778</v>
       </c>
       <c r="M17">
-        <v>215.7768907530684</v>
+        <v>212.1032557530685</v>
       </c>
       <c r="N17">
-        <v>1562.223109246931</v>
+        <v>1565.896744246931</v>
       </c>
       <c r="O17">
-        <v>195.2778886558664</v>
+        <v>195.7370930308664</v>
       </c>
       <c r="P17">
-        <v>1366.945220591065</v>
+        <v>1370.159651216065</v>
       </c>
       <c r="Q17">
-        <v>2625.145220591065</v>
+        <v>2628.359651216065</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09345237055249142</v>
+        <v>0.09343011642564136</v>
       </c>
       <c r="T17">
         <v>0.9283996230248326</v>
       </c>
       <c r="U17">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.239992678524198</v>
+        <v>8.382709608521782</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08714804319413094</v>
+        <v>0.08698915128313364</v>
       </c>
       <c r="C18">
-        <v>20751.27609432077</v>
+        <v>20818.23042282876</v>
       </c>
       <c r="D18">
-        <v>21406.12009432077</v>
+        <v>21473.07442282876</v>
       </c>
       <c r="E18">
         <v>859.1440000000002</v>
@@ -2769,37 +2769,37 @@
         <v>1778</v>
       </c>
       <c r="M18">
-        <v>230.162016803273</v>
+        <v>226.243472803273</v>
       </c>
       <c r="N18">
-        <v>1547.837983196727</v>
+        <v>1551.756527196727</v>
       </c>
       <c r="O18">
-        <v>193.4797478995908</v>
+        <v>193.9695658995908</v>
       </c>
       <c r="P18">
-        <v>1354.358235297136</v>
+        <v>1357.786961297136</v>
       </c>
       <c r="Q18">
-        <v>2612.558235297136</v>
+        <v>2615.986961297136</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09395823435878115</v>
+        <v>0.09393574398854627</v>
       </c>
       <c r="T18">
         <v>0.9382552453499371</v>
       </c>
       <c r="U18">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.724993136116436</v>
+        <v>7.85879025798917</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08715239048168655</v>
+        <v>0.08698477266751452</v>
       </c>
       <c r="C19">
-        <v>20504.2935902547</v>
+        <v>20575.42340025341</v>
       </c>
       <c r="D19">
-        <v>21404.0465902547</v>
+        <v>21475.17640025341</v>
       </c>
       <c r="E19">
         <v>1104.053</v>
@@ -2851,37 +2851,37 @@
         <v>1778</v>
       </c>
       <c r="M19">
-        <v>244.5471428534776</v>
+        <v>240.3836898534776</v>
       </c>
       <c r="N19">
-        <v>1533.452857146522</v>
+        <v>1537.616310146522</v>
       </c>
       <c r="O19">
-        <v>191.6816071433153</v>
+        <v>192.2020387683153</v>
       </c>
       <c r="P19">
-        <v>1341.771250003207</v>
+        <v>1345.414271378207</v>
       </c>
       <c r="Q19">
-        <v>2599.971250003207</v>
+        <v>2603.614271378207</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09447628765437904</v>
+        <v>0.09445355534814767</v>
       </c>
       <c r="T19">
         <v>0.9483483525503451</v>
       </c>
       <c r="U19">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.270581775168409</v>
+        <v>7.396508478107454</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08715673776924218</v>
+        <v>0.08698039405189539</v>
       </c>
       <c r="C20">
-        <v>20257.3114878497</v>
+        <v>20332.61678923921</v>
       </c>
       <c r="D20">
-        <v>21401.9734878497</v>
+        <v>21477.27878923921</v>
       </c>
       <c r="E20">
         <v>1348.962</v>
@@ -2933,37 +2933,37 @@
         <v>1778</v>
       </c>
       <c r="M20">
-        <v>258.9322689036821</v>
+        <v>254.5239069036821</v>
       </c>
       <c r="N20">
-        <v>1519.067731096318</v>
+        <v>1523.476093096318</v>
       </c>
       <c r="O20">
-        <v>189.8834663870397</v>
+        <v>190.4345116370397</v>
       </c>
       <c r="P20">
-        <v>1329.184264709278</v>
+        <v>1333.041581459278</v>
       </c>
       <c r="Q20">
-        <v>2587.384264709278</v>
+        <v>2591.241581459278</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09500697639621104</v>
+        <v>0.0949839962531052</v>
       </c>
       <c r="T20">
         <v>0.9586876330971047</v>
       </c>
       <c r="U20">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.866660565436832</v>
+        <v>6.985591340434818</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08752683505679781</v>
+        <v>0.08725864043627626</v>
       </c>
       <c r="C21">
-        <v>19837.37353795982</v>
+        <v>19954.92100190802</v>
       </c>
       <c r="D21">
-        <v>21226.94453795982</v>
+        <v>21344.49200190802</v>
       </c>
       <c r="E21">
         <v>1593.871000000001</v>
@@ -3015,37 +3015,37 @@
         <v>1778</v>
       </c>
       <c r="M21">
-        <v>283.5545911538867</v>
+        <v>276.5746846538867</v>
       </c>
       <c r="N21">
-        <v>1494.445408846113</v>
+        <v>1501.425315346113</v>
       </c>
       <c r="O21">
-        <v>186.8056761057641</v>
+        <v>187.6781644182641</v>
       </c>
       <c r="P21">
-        <v>1307.639732740349</v>
+        <v>1313.747150927849</v>
       </c>
       <c r="Q21">
-        <v>2565.839732740349</v>
+        <v>2571.947150927849</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09555076856376729</v>
+        <v>0.09552753446435798</v>
       </c>
       <c r="T21">
         <v>0.9692822045215619</v>
       </c>
       <c r="U21">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.270397501816744</v>
+        <v>6.428643323683216</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08755043234435342</v>
+        <v>0.08726913682065715</v>
       </c>
       <c r="C22">
-        <v>19581.40178192845</v>
+        <v>19705.03497086322</v>
       </c>
       <c r="D22">
-        <v>21215.88178192845</v>
+        <v>21339.51497086322</v>
       </c>
       <c r="E22">
         <v>1838.78</v>
@@ -3097,37 +3097,37 @@
         <v>1778</v>
       </c>
       <c r="M22">
-        <v>298.4785170040913</v>
+        <v>291.1312470040913</v>
       </c>
       <c r="N22">
-        <v>1479.521482995909</v>
+        <v>1486.868752995908</v>
       </c>
       <c r="O22">
-        <v>184.9401853744886</v>
+        <v>185.8585941244885</v>
       </c>
       <c r="P22">
-        <v>1294.58129762142</v>
+        <v>1301.01015887142</v>
       </c>
       <c r="Q22">
-        <v>2552.78129762142</v>
+        <v>2559.21015887142</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09610815553551244</v>
+        <v>0.09608466113089209</v>
       </c>
       <c r="T22">
         <v>0.9801416402316306</v>
       </c>
       <c r="U22">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.956877626725909</v>
+        <v>6.107211157499055</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08757402963190902</v>
+        <v>0.08727963320503801</v>
       </c>
       <c r="C23">
-        <v>19325.44155094925</v>
+        <v>19455.15126032936</v>
       </c>
       <c r="D23">
-        <v>21204.83055094925</v>
+        <v>21334.54026032936</v>
       </c>
       <c r="E23">
         <v>2083.689</v>
@@ -3179,37 +3179,37 @@
         <v>1778</v>
       </c>
       <c r="M23">
-        <v>313.4024428542958</v>
+        <v>305.6878093542958</v>
       </c>
       <c r="N23">
-        <v>1464.597557145704</v>
+        <v>1472.312190645704</v>
       </c>
       <c r="O23">
-        <v>183.074694643213</v>
+        <v>184.039023830713</v>
       </c>
       <c r="P23">
-        <v>1281.522862502491</v>
+        <v>1288.273166814991</v>
       </c>
       <c r="Q23">
-        <v>2539.722862502491</v>
+        <v>2546.473166814991</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09667965356983341</v>
+        <v>0.09665589226999666</v>
       </c>
       <c r="T23">
         <v>0.991275998364739</v>
       </c>
       <c r="U23">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.673216787358007</v>
+        <v>5.81639157857053</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08788637691946466</v>
+        <v>0.08744412958941888</v>
       </c>
       <c r="C24">
-        <v>18935.32944461432</v>
+        <v>19132.58189659754</v>
       </c>
       <c r="D24">
-        <v>21059.62744461432</v>
+        <v>21256.87989659754</v>
       </c>
       <c r="E24">
         <v>2328.598</v>
@@ -3261,37 +3261,37 @@
         <v>1778</v>
       </c>
       <c r="M24">
-        <v>336.4083657045004</v>
+        <v>324.5547701045004</v>
       </c>
       <c r="N24">
-        <v>1441.591634295499</v>
+        <v>1453.445229895499</v>
       </c>
       <c r="O24">
-        <v>180.1989542869374</v>
+        <v>181.6806537369374</v>
       </c>
       <c r="P24">
-        <v>1261.392680008562</v>
+        <v>1271.764576158562</v>
       </c>
       <c r="Q24">
-        <v>2519.592680008562</v>
+        <v>2529.964576158562</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09726580539990622</v>
+        <v>0.09724177036138598</v>
       </c>
       <c r="T24">
         <v>1.002695852860235</v>
       </c>
       <c r="U24">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.285243118959137</v>
+        <v>5.478274127437776</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08792309920702028</v>
+        <v>0.08746162597379975</v>
       </c>
       <c r="C25">
-        <v>18673.47963050955</v>
+        <v>18879.44593463692</v>
       </c>
       <c r="D25">
-        <v>21042.68663050955</v>
+        <v>21248.65293463692</v>
       </c>
       <c r="E25">
         <v>2573.507</v>
@@ -3343,37 +3343,37 @@
         <v>1778</v>
       </c>
       <c r="M25">
-        <v>351.699655054705</v>
+        <v>339.307259654705</v>
       </c>
       <c r="N25">
-        <v>1426.300344945295</v>
+        <v>1438.692740345295</v>
       </c>
       <c r="O25">
-        <v>178.2875431181619</v>
+        <v>179.8365925431619</v>
       </c>
       <c r="P25">
-        <v>1248.012801827133</v>
+        <v>1258.856147802133</v>
       </c>
       <c r="Q25">
-        <v>2506.212801827133</v>
+        <v>2517.056147802133</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09786718195283804</v>
+        <v>0.09784286606553866</v>
       </c>
       <c r="T25">
         <v>1.014412326953016</v>
       </c>
       <c r="U25">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.055449939873958</v>
+        <v>5.240088295810046</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0879598214945759</v>
+        <v>0.08747912235818062</v>
       </c>
       <c r="C26">
-        <v>18411.65704960319</v>
+        <v>18626.31633830649</v>
       </c>
       <c r="D26">
-        <v>21025.77304960318</v>
+        <v>21240.43233830649</v>
       </c>
       <c r="E26">
         <v>2818.416</v>
@@ -3425,37 +3425,37 @@
         <v>1778</v>
       </c>
       <c r="M26">
-        <v>366.9909444049095</v>
+        <v>354.0597492049095</v>
       </c>
       <c r="N26">
-        <v>1411.00905559509</v>
+        <v>1423.94025079509</v>
       </c>
       <c r="O26">
-        <v>176.3761319493863</v>
+        <v>177.9925313493863</v>
       </c>
       <c r="P26">
-        <v>1234.632923645704</v>
+        <v>1245.947719445704</v>
       </c>
       <c r="Q26">
-        <v>2492.832923645704</v>
+        <v>2504.147719445704</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09848438420453123</v>
+        <v>0.09845978007769535</v>
       </c>
       <c r="T26">
         <v>1.026437129311397</v>
       </c>
       <c r="U26">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.84480619237921</v>
+        <v>5.021751283484628</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08799654378213152</v>
+        <v>0.08749661874256151</v>
       </c>
       <c r="C27">
-        <v>18149.86163627989</v>
+        <v>18373.19310022096</v>
       </c>
       <c r="D27">
-        <v>21008.88663627988</v>
+        <v>21232.21810022096</v>
       </c>
       <c r="E27">
         <v>3063.325</v>
@@ -3507,37 +3507,37 @@
         <v>1778</v>
       </c>
       <c r="M27">
-        <v>382.2822337551141</v>
+        <v>368.8122387551141</v>
       </c>
       <c r="N27">
-        <v>1395.717766244886</v>
+        <v>1409.187761244886</v>
       </c>
       <c r="O27">
-        <v>174.4647207806107</v>
+        <v>176.1484701556107</v>
       </c>
       <c r="P27">
-        <v>1221.253045464275</v>
+        <v>1233.039291089275</v>
       </c>
       <c r="Q27">
-        <v>2479.453045464275</v>
+        <v>2491.239291089275</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09911804518293625</v>
+        <v>0.09909314513017622</v>
       </c>
       <c r="T27">
         <v>1.038782593066002</v>
       </c>
       <c r="U27">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.651013944684041</v>
+        <v>4.820881232145243</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08803326606968717</v>
+        <v>0.08751411512694239</v>
       </c>
       <c r="C28">
-        <v>17888.09332513493</v>
+        <v>18120.07621300649</v>
       </c>
       <c r="D28">
-        <v>20992.02732513493</v>
+        <v>21224.0102130065</v>
       </c>
       <c r="E28">
         <v>3308.234000000001</v>
@@ -3589,37 +3589,37 @@
         <v>1778</v>
       </c>
       <c r="M28">
-        <v>397.5735231053187</v>
+        <v>383.5647283053187</v>
       </c>
       <c r="N28">
-        <v>1380.426476894681</v>
+        <v>1394.435271694681</v>
       </c>
       <c r="O28">
-        <v>172.5533096118351</v>
+        <v>174.3044089618351</v>
       </c>
       <c r="P28">
-        <v>1207.873167282846</v>
+        <v>1220.130862732846</v>
       </c>
       <c r="Q28">
-        <v>2466.073167282846</v>
+        <v>2478.330862732846</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09976883213373061</v>
+        <v>0.09974362815704849</v>
       </c>
       <c r="T28">
         <v>1.051461718003163</v>
       </c>
       <c r="U28">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.472128792965423</v>
+        <v>4.635462723216579</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08806998835724278</v>
+        <v>0.08753161151132326</v>
       </c>
       <c r="C29">
-        <v>17626.35205097342</v>
+        <v>17866.96566930065</v>
       </c>
       <c r="D29">
-        <v>20975.19505097342</v>
+        <v>21215.80866930065</v>
       </c>
       <c r="E29">
         <v>3553.143</v>
@@ -3671,37 +3671,37 @@
         <v>1778</v>
       </c>
       <c r="M29">
-        <v>412.8648124555232</v>
+        <v>398.3172178555232</v>
       </c>
       <c r="N29">
-        <v>1365.135187544477</v>
+        <v>1379.682782144477</v>
       </c>
       <c r="O29">
-        <v>170.6418984430596</v>
+        <v>172.4603477680596</v>
       </c>
       <c r="P29">
-        <v>1194.493289101417</v>
+        <v>1207.222434376417</v>
       </c>
       <c r="Q29">
-        <v>2452.693289101417</v>
+        <v>2465.422434376417</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1004374488639988</v>
+        <v>0.1004119326367117</v>
       </c>
       <c r="T29">
         <v>1.064488216226274</v>
       </c>
       <c r="U29">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.306494393225964</v>
+        <v>4.463778918653002</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0884497106447984</v>
+        <v>0.08754910789570412</v>
       </c>
       <c r="C30">
-        <v>17208.9606673687</v>
+        <v>17613.86146175233</v>
       </c>
       <c r="D30">
-        <v>20802.7126673687</v>
+        <v>21207.61346175233</v>
       </c>
       <c r="E30">
         <v>3798.052000000001</v>
@@ -3753,45 +3753,45 @@
         <v>1778</v>
       </c>
       <c r="M30">
-        <v>437.7565346057278</v>
+        <v>413.0697074057279</v>
       </c>
       <c r="N30">
-        <v>1340.243465394272</v>
+        <v>1364.930292594272</v>
       </c>
       <c r="O30">
-        <v>167.530433174284</v>
+        <v>170.616286574284</v>
       </c>
       <c r="P30">
-        <v>1172.713032219988</v>
+        <v>1194.314006019988</v>
       </c>
       <c r="Q30">
-        <v>2430.913032219988</v>
+        <v>2452.514006019988</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1011246382812188</v>
+        <v>0.101098801129699</v>
       </c>
       <c r="T30">
         <v>1.077876561622249</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.061618409880237</v>
+        <v>4.304358242986823</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08849868293235401</v>
+        <v>0.08782035428008499</v>
       </c>
       <c r="C31">
-        <v>16942.01313490166</v>
+        <v>17242.70728097039</v>
       </c>
       <c r="D31">
-        <v>20780.67413490166</v>
+        <v>21081.36828097039</v>
       </c>
       <c r="E31">
         <v>4042.961</v>
@@ -3835,37 +3835,37 @@
         <v>1778</v>
       </c>
       <c r="M31">
-        <v>453.3906965559323</v>
+        <v>434.9245579559324</v>
       </c>
       <c r="N31">
-        <v>1324.609303444067</v>
+        <v>1343.075442044067</v>
       </c>
       <c r="O31">
-        <v>165.5761629305084</v>
+        <v>167.8844302555084</v>
       </c>
       <c r="P31">
-        <v>1159.033140513559</v>
+        <v>1175.191011788559</v>
       </c>
       <c r="Q31">
-        <v>2417.233140513559</v>
+        <v>2433.391011788559</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1018311851468112</v>
+        <v>0.1018050180309394</v>
       </c>
       <c r="T31">
         <v>1.091642043508252</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.921562602642989</v>
+        <v>4.0880653149509</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08854765521990964</v>
+        <v>0.08784660066446587</v>
       </c>
       <c r="C32">
-        <v>16675.11224855379</v>
+        <v>16985.66223406088</v>
       </c>
       <c r="D32">
-        <v>20758.68224855379</v>
+        <v>21069.23223406088</v>
       </c>
       <c r="E32">
         <v>4287.870000000001</v>
@@ -3917,37 +3917,37 @@
         <v>1778</v>
       </c>
       <c r="M32">
-        <v>469.0248585061369</v>
+        <v>449.921956506137</v>
       </c>
       <c r="N32">
-        <v>1308.975141493863</v>
+        <v>1328.078043493863</v>
       </c>
       <c r="O32">
-        <v>163.6218926867328</v>
+        <v>166.0097554367329</v>
       </c>
       <c r="P32">
-        <v>1145.35324880713</v>
+        <v>1162.06828805713</v>
       </c>
       <c r="Q32">
-        <v>2403.55324880713</v>
+        <v>2420.26828805713</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1025579190657063</v>
+        <v>0.1025314125579295</v>
       </c>
       <c r="T32">
         <v>1.105800824876711</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.790843849221556</v>
+        <v>3.951796471119204</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08859662750746525</v>
+        <v>0.08787284704884675</v>
       </c>
       <c r="C33">
-        <v>16408.25786038696</v>
+        <v>16728.63115198455</v>
       </c>
       <c r="D33">
-        <v>20736.73686038695</v>
+        <v>21057.11015198455</v>
       </c>
       <c r="E33">
         <v>4532.779</v>
@@ -3999,37 +3999,37 @@
         <v>1778</v>
       </c>
       <c r="M33">
-        <v>484.6590204563415</v>
+        <v>464.9193550563415</v>
       </c>
       <c r="N33">
-        <v>1293.340979543658</v>
+        <v>1313.080644943658</v>
       </c>
       <c r="O33">
-        <v>161.6676224429573</v>
+        <v>164.1350806179573</v>
       </c>
       <c r="P33">
-        <v>1131.673357100701</v>
+        <v>1148.945564325701</v>
       </c>
       <c r="Q33">
-        <v>2389.873357100701</v>
+        <v>2407.145564325701</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1033057177358737</v>
+        <v>0.1032788619987455</v>
       </c>
       <c r="T33">
         <v>1.120370005705127</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.668558563762796</v>
+        <v>3.824319165599229</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08864559979502087</v>
+        <v>0.08789909343322762</v>
       </c>
       <c r="C34">
-        <v>16141.44982308787</v>
+        <v>16471.61401065146</v>
       </c>
       <c r="D34">
-        <v>20714.83782308787</v>
+        <v>21045.00201065146</v>
       </c>
       <c r="E34">
         <v>4777.688</v>
@@ -4081,37 +4081,37 @@
         <v>1778</v>
       </c>
       <c r="M34">
-        <v>500.2931824065461</v>
+        <v>479.9167536065461</v>
       </c>
       <c r="N34">
-        <v>1277.706817593454</v>
+        <v>1298.083246393454</v>
       </c>
       <c r="O34">
-        <v>159.7133521991817</v>
+        <v>162.2604057991817</v>
       </c>
       <c r="P34">
-        <v>1117.993465394272</v>
+        <v>1135.822840594272</v>
       </c>
       <c r="Q34">
-        <v>2376.193465394272</v>
+        <v>2394.022840594272</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1040755104845755</v>
+        <v>0.1040482952466442</v>
       </c>
       <c r="T34">
         <v>1.135367691852025</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.553916108645208</v>
+        <v>3.704809191674253</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0886945720825765</v>
+        <v>0.08792533981760849</v>
       </c>
       <c r="C35">
-        <v>15874.68798996492</v>
+        <v>16214.61078602706</v>
       </c>
       <c r="D35">
-        <v>20692.98498996492</v>
+        <v>21032.90778602706</v>
       </c>
       <c r="E35">
         <v>5022.597000000002</v>
@@ -4163,37 +4163,37 @@
         <v>1778</v>
       </c>
       <c r="M35">
-        <v>515.9273443567506</v>
+        <v>494.9141521567507</v>
       </c>
       <c r="N35">
-        <v>1262.072655643249</v>
+        <v>1283.085847843249</v>
       </c>
       <c r="O35">
-        <v>157.7590819554061</v>
+        <v>160.3857309804062</v>
       </c>
       <c r="P35">
-        <v>1104.313573687843</v>
+        <v>1122.700116862843</v>
       </c>
       <c r="Q35">
-        <v>2362.513573687843</v>
+        <v>2380.900116862843</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1048682821212982</v>
+        <v>0.1048406966511967</v>
       </c>
       <c r="T35">
         <v>1.150813070122711</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.446221681110505</v>
+        <v>3.592542246472003</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08874354437013213</v>
+        <v>0.08795158620198937</v>
       </c>
       <c r="C36">
-        <v>15607.97221494481</v>
+        <v>15957.62145413199</v>
       </c>
       <c r="D36">
-        <v>20671.17821494481</v>
+        <v>21020.82745413199</v>
       </c>
       <c r="E36">
         <v>5267.506000000001</v>
@@ -4245,37 +4245,37 @@
         <v>1778</v>
       </c>
       <c r="M36">
-        <v>531.5615063069552</v>
+        <v>509.9115507069552</v>
       </c>
       <c r="N36">
-        <v>1246.438493693045</v>
+        <v>1268.088449293045</v>
       </c>
       <c r="O36">
-        <v>155.8048117116306</v>
+        <v>158.5110561616306</v>
       </c>
       <c r="P36">
-        <v>1090.633681981414</v>
+        <v>1109.577393131414</v>
       </c>
       <c r="Q36">
-        <v>2348.833681981414</v>
+        <v>2367.777393131414</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1056850771409519</v>
+        <v>0.1056571102195235</v>
       </c>
       <c r="T36">
         <v>1.166726490159175</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.344862219901373</v>
+        <v>3.486879239222826</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08879251665768774</v>
+        <v>0.08797783258637024</v>
       </c>
       <c r="C37">
-        <v>15341.30235256938</v>
+        <v>15700.64599104196</v>
       </c>
       <c r="D37">
-        <v>20649.41735256938</v>
+        <v>21008.76099104196</v>
       </c>
       <c r="E37">
         <v>5512.415000000001</v>
@@ -4327,37 +4327,37 @@
         <v>1778</v>
       </c>
       <c r="M37">
-        <v>547.1956682571597</v>
+        <v>524.9089492571597</v>
       </c>
       <c r="N37">
-        <v>1230.80433174284</v>
+        <v>1253.09105074284</v>
       </c>
       <c r="O37">
-        <v>153.850541467855</v>
+        <v>156.636381342855</v>
       </c>
       <c r="P37">
-        <v>1076.953790274985</v>
+        <v>1096.454669399985</v>
       </c>
       <c r="Q37">
-        <v>2335.153790274985</v>
+        <v>2354.654669399985</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1065270043150564</v>
+        <v>0.1064986442053372</v>
       </c>
       <c r="T37">
         <v>1.183129553889069</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.249294727904191</v>
+        <v>3.387254118102175</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08884148894524338</v>
+        <v>0.08800407897075112</v>
       </c>
       <c r="C38">
-        <v>15074.67825799226</v>
+        <v>15443.68437288759</v>
       </c>
       <c r="D38">
-        <v>20627.70225799226</v>
+        <v>20996.70837288759</v>
       </c>
       <c r="E38">
         <v>5757.324000000001</v>
@@ -4409,37 +4409,37 @@
         <v>1778</v>
       </c>
       <c r="M38">
-        <v>562.8298302073642</v>
+        <v>539.9063478073643</v>
       </c>
       <c r="N38">
-        <v>1215.170169792636</v>
+        <v>1238.093652192636</v>
       </c>
       <c r="O38">
-        <v>151.8962712240794</v>
+        <v>154.7617065240794</v>
       </c>
       <c r="P38">
-        <v>1063.273898568556</v>
+        <v>1083.331945668556</v>
       </c>
       <c r="Q38">
-        <v>2321.473898568556</v>
+        <v>2341.531945668556</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1073952417133518</v>
+        <v>0.1073664761282076</v>
       </c>
       <c r="T38">
         <v>1.200045213360522</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.159036541017964</v>
+        <v>3.29316372593267</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08889046123279898</v>
+        <v>0.088030325355132</v>
       </c>
       <c r="C39">
-        <v>14808.09978697582</v>
+        <v>15186.73657585423</v>
       </c>
       <c r="D39">
-        <v>20606.03278697582</v>
+        <v>20984.66957585423</v>
       </c>
       <c r="E39">
         <v>6002.233</v>
@@ -4491,37 +4491,37 @@
         <v>1778</v>
       </c>
       <c r="M39">
-        <v>578.4639921575688</v>
+        <v>554.9037463575688</v>
       </c>
       <c r="N39">
-        <v>1199.536007842431</v>
+        <v>1223.096253642431</v>
       </c>
       <c r="O39">
-        <v>149.9420009803039</v>
+        <v>152.8870317053039</v>
       </c>
       <c r="P39">
-        <v>1049.594006862127</v>
+        <v>1070.209221937127</v>
       </c>
       <c r="Q39">
-        <v>2307.794006862127</v>
+        <v>2328.409221937127</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1082910422036565</v>
+        <v>0.1082618582708517</v>
       </c>
       <c r="T39">
         <v>1.217497877894561</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.073657175044505</v>
+        <v>3.204159300907463</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08980393352035462</v>
+        <v>0.08805657173951285</v>
       </c>
       <c r="C40">
-        <v>14167.17802218156</v>
+        <v>14929.80257618185</v>
       </c>
       <c r="D40">
-        <v>20210.02002218156</v>
+        <v>20972.64457618185</v>
       </c>
       <c r="E40">
         <v>6247.142000000002</v>
@@ -4573,45 +4573,45 @@
         <v>1778</v>
       </c>
       <c r="M40">
-        <v>618.2951633077734</v>
+        <v>569.9011449077735</v>
       </c>
       <c r="N40">
-        <v>1159.704836692226</v>
+        <v>1208.098855092226</v>
       </c>
       <c r="O40">
-        <v>144.9631045865283</v>
+        <v>151.0123568865283</v>
       </c>
       <c r="P40">
-        <v>1014.741732105698</v>
+        <v>1057.086498205698</v>
       </c>
       <c r="Q40">
-        <v>2272.941732105698</v>
+        <v>2315.286498205698</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.109215739483971</v>
+        <v>0.1091861237084198</v>
       </c>
       <c r="T40">
         <v>1.235513531607118</v>
       </c>
       <c r="U40">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.875649213375702</v>
+        <v>3.119839319304634</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08987565580791024</v>
+        <v>0.08808281812389374</v>
       </c>
       <c r="C41">
-        <v>13891.81915058119</v>
+        <v>14672.88235016479</v>
       </c>
       <c r="D41">
-        <v>20179.57015058119</v>
+        <v>20960.63335016479</v>
       </c>
       <c r="E41">
         <v>6492.051000000001</v>
@@ -4655,45 +4655,45 @@
         <v>1778</v>
       </c>
       <c r="M41">
-        <v>634.566088657978</v>
+        <v>584.898543457978</v>
       </c>
       <c r="N41">
-        <v>1143.433911342022</v>
+        <v>1193.101456542022</v>
       </c>
       <c r="O41">
-        <v>142.9292389177527</v>
+        <v>149.1376820677527</v>
       </c>
       <c r="P41">
-        <v>1000.504672424269</v>
+        <v>1043.963774474269</v>
       </c>
       <c r="Q41">
-        <v>2258.704672424269</v>
+        <v>2302.163774474269</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1101707547079024</v>
+        <v>0.1101406929308262</v>
       </c>
       <c r="T41">
         <v>1.254119862490577</v>
       </c>
       <c r="U41">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.801914618160941</v>
+        <v>3.039843439322464</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08994737809546587</v>
+        <v>0.0889840645082746</v>
       </c>
       <c r="C42">
-        <v>13616.5518968815</v>
+        <v>14023.71890222078</v>
       </c>
       <c r="D42">
-        <v>20149.2118968815</v>
+        <v>20556.37890222078</v>
       </c>
       <c r="E42">
         <v>6736.960000000001</v>
@@ -4737,37 +4737,37 @@
         <v>1778</v>
       </c>
       <c r="M42">
-        <v>650.8370140081825</v>
+        <v>624.3868420081825</v>
       </c>
       <c r="N42">
-        <v>1127.162985991817</v>
+        <v>1153.613157991817</v>
       </c>
       <c r="O42">
-        <v>140.8953732489772</v>
+        <v>144.2016447489772</v>
       </c>
       <c r="P42">
-        <v>986.2676127428401</v>
+        <v>1009.41151324284</v>
       </c>
       <c r="Q42">
-        <v>2244.46761274284</v>
+        <v>2267.61151324284</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1111576037726316</v>
+        <v>0.1111270811273128</v>
       </c>
       <c r="T42">
         <v>1.273346404403486</v>
       </c>
       <c r="U42">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.731866752706917</v>
+        <v>2.847593639676186</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09001910038302149</v>
+        <v>0.08903218589265546</v>
       </c>
       <c r="C43">
-        <v>13341.37584821227</v>
+        <v>13757.66310507704</v>
       </c>
       <c r="D43">
-        <v>20118.94484821227</v>
+        <v>20535.23210507704</v>
       </c>
       <c r="E43">
         <v>6981.869000000002</v>
@@ -4819,37 +4819,37 @@
         <v>1778</v>
       </c>
       <c r="M43">
-        <v>667.1079393583872</v>
+        <v>639.9965130583872</v>
       </c>
       <c r="N43">
-        <v>1110.892060641613</v>
+        <v>1138.003486941613</v>
       </c>
       <c r="O43">
-        <v>138.8615075802016</v>
+        <v>142.2504358677016</v>
       </c>
       <c r="P43">
-        <v>972.0305530614112</v>
+        <v>995.7530510739111</v>
       </c>
       <c r="Q43">
-        <v>2230.230553061411</v>
+        <v>2253.953051073911</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1121779053480295</v>
+        <v>0.1121469062118159</v>
       </c>
       <c r="T43">
         <v>1.293224693499883</v>
       </c>
       <c r="U43">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.665235856299431</v>
+        <v>2.778140136269449</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09009082267057711</v>
+        <v>0.08908030727703638</v>
       </c>
       <c r="C44">
-        <v>13066.29059418027</v>
+        <v>13491.65077156792</v>
       </c>
       <c r="D44">
-        <v>20088.76859418027</v>
+        <v>20514.12877156792</v>
       </c>
       <c r="E44">
         <v>7226.778</v>
@@ -4901,37 +4901,37 @@
         <v>1778</v>
       </c>
       <c r="M44">
-        <v>683.3788647085915</v>
+        <v>655.6061841085916</v>
       </c>
       <c r="N44">
-        <v>1094.621135291408</v>
+        <v>1122.393815891408</v>
       </c>
       <c r="O44">
-        <v>136.827641911426</v>
+        <v>140.299226986426</v>
       </c>
       <c r="P44">
-        <v>957.7934933799822</v>
+        <v>982.0945889049822</v>
       </c>
       <c r="Q44">
-        <v>2215.993493379982</v>
+        <v>2240.294588904982</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1132333897363721</v>
+        <v>0.1132018976785432</v>
       </c>
       <c r="T44">
         <v>1.313788440840983</v>
       </c>
       <c r="U44">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.601777859720874</v>
+        <v>2.711993942548748</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09016254495813272</v>
+        <v>0.08912842866141724</v>
       </c>
       <c r="C45">
-        <v>12791.29572685077</v>
+        <v>13225.6817678329</v>
       </c>
       <c r="D45">
-        <v>20058.68272685077</v>
+        <v>20493.0687678329</v>
       </c>
       <c r="E45">
         <v>7471.687000000002</v>
@@ -4983,37 +4983,37 @@
         <v>1778</v>
       </c>
       <c r="M45">
-        <v>699.6497900587962</v>
+        <v>671.2158551587962</v>
       </c>
       <c r="N45">
-        <v>1078.350209941204</v>
+        <v>1106.784144841204</v>
       </c>
       <c r="O45">
-        <v>134.7937762426504</v>
+        <v>138.3480181051505</v>
       </c>
       <c r="P45">
-        <v>943.5564336985531</v>
+        <v>968.4361267360532</v>
       </c>
       <c r="Q45">
-        <v>2201.756433698553</v>
+        <v>2226.636126736053</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1143259086646566</v>
+        <v>0.1142939063897171</v>
       </c>
       <c r="T45">
         <v>1.335073723176508</v>
       </c>
       <c r="U45">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.541271397866899</v>
+        <v>2.648924315977847</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09127376724568836</v>
+        <v>0.08917655004579811</v>
       </c>
       <c r="C46">
-        <v>12091.50722661764</v>
+        <v>12959.75596056051</v>
       </c>
       <c r="D46">
-        <v>19603.80322661765</v>
+        <v>20472.05196056051</v>
       </c>
       <c r="E46">
         <v>7716.596000000001</v>
@@ -5065,45 +5065,45 @@
         <v>1778</v>
       </c>
       <c r="M46">
-        <v>745.0159046090008</v>
+        <v>686.8255262090008</v>
       </c>
       <c r="N46">
-        <v>1032.984095390999</v>
+        <v>1091.174473790999</v>
       </c>
       <c r="O46">
-        <v>129.1230119238749</v>
+        <v>136.3968092238749</v>
       </c>
       <c r="P46">
-        <v>903.861083467124</v>
+        <v>954.777664567124</v>
       </c>
       <c r="Q46">
-        <v>2162.061083467124</v>
+        <v>2212.977664567124</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1154574461260942</v>
+        <v>0.1154249154120044</v>
       </c>
       <c r="T46">
         <v>1.357119194166873</v>
       </c>
       <c r="U46">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.386526232528055</v>
+        <v>2.588721490614714</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09136911453324398</v>
+        <v>0.08922467143017898</v>
       </c>
       <c r="C47">
-        <v>11808.52694869422</v>
+        <v>12693.87321698563</v>
       </c>
       <c r="D47">
-        <v>19565.73194869422</v>
+        <v>20451.07821698563</v>
       </c>
       <c r="E47">
         <v>7961.505000000001</v>
@@ -5147,45 +5147,45 @@
         <v>1778</v>
       </c>
       <c r="M47">
-        <v>761.9480842592054</v>
+        <v>702.4351972592053</v>
       </c>
       <c r="N47">
-        <v>1016.051915740794</v>
+        <v>1075.564802740794</v>
       </c>
       <c r="O47">
-        <v>127.0064894675993</v>
+        <v>134.4456003425993</v>
       </c>
       <c r="P47">
-        <v>889.0454262731951</v>
+        <v>941.1192023981952</v>
       </c>
       <c r="Q47">
-        <v>2147.245426273195</v>
+        <v>2199.319202398195</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1166301304043112</v>
+        <v>0.1165970520351021</v>
       </c>
       <c r="T47">
         <v>1.379966318647797</v>
       </c>
       <c r="U47">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.333492316249654</v>
+        <v>2.531194346378832</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09146446182079959</v>
+        <v>0.09068154281455987</v>
       </c>
       <c r="C48">
-        <v>11525.69425568713</v>
+        <v>11833.71917013086</v>
       </c>
       <c r="D48">
-        <v>19527.80825568713</v>
+        <v>19835.83317013086</v>
       </c>
       <c r="E48">
         <v>8206.414000000001</v>
@@ -5229,37 +5229,37 @@
         <v>1778</v>
       </c>
       <c r="M48">
-        <v>778.8802639094099</v>
+        <v>757.4752173094099</v>
       </c>
       <c r="N48">
-        <v>999.1197360905899</v>
+        <v>1020.52478269059</v>
       </c>
       <c r="O48">
-        <v>124.8899670113237</v>
+        <v>127.5655978363237</v>
       </c>
       <c r="P48">
-        <v>874.2297690792661</v>
+        <v>892.9591848542661</v>
       </c>
       <c r="Q48">
-        <v>2132.429769079266</v>
+        <v>2151.159184854266</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1178462474335734</v>
+        <v>0.117812601125722</v>
       </c>
       <c r="T48">
         <v>1.403659632924311</v>
       </c>
       <c r="U48">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.28276422241814</v>
+        <v>2.347271513800208</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09349268410835522</v>
+        <v>0.09076028919894073</v>
       </c>
       <c r="C49">
-        <v>10507.5204788148</v>
+        <v>11556.60792515325</v>
       </c>
       <c r="D49">
-        <v>18754.5434788148</v>
+        <v>19803.63092515325</v>
       </c>
       <c r="E49">
         <v>8451.323000000002</v>
@@ -5311,45 +5311,45 @@
         <v>1778</v>
       </c>
       <c r="M49">
-        <v>849.9128416596147</v>
+        <v>773.9420698596145</v>
       </c>
       <c r="N49">
-        <v>928.087158340385</v>
+        <v>1004.057930140385</v>
       </c>
       <c r="O49">
-        <v>116.0108947925481</v>
+        <v>125.5072412675482</v>
       </c>
       <c r="P49">
-        <v>812.0762635478369</v>
+        <v>878.5506888728371</v>
       </c>
       <c r="Q49">
-        <v>2070.276263547837</v>
+        <v>2136.750688872837</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1191082556714869</v>
+        <v>0.1190740199933464</v>
       </c>
       <c r="T49">
         <v>1.428247034532013</v>
       </c>
       <c r="U49">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.091979215807729</v>
+        <v>2.297329566698076</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09362915639591084</v>
+        <v>0.09201503558332161</v>
       </c>
       <c r="C50">
-        <v>10212.77417525028</v>
+        <v>10812.33815649051</v>
       </c>
       <c r="D50">
-        <v>18704.70617525028</v>
+        <v>19304.27015649051</v>
       </c>
       <c r="E50">
         <v>8696.232</v>
@@ -5393,37 +5393,37 @@
         <v>1778</v>
       </c>
       <c r="M50">
-        <v>867.9960936098191</v>
+        <v>823.3246920098189</v>
       </c>
       <c r="N50">
-        <v>910.0039063901806</v>
+        <v>954.6753079901808</v>
       </c>
       <c r="O50">
-        <v>113.7504882987726</v>
+        <v>119.3344134987726</v>
       </c>
       <c r="P50">
-        <v>796.2534180914081</v>
+        <v>835.3408944914082</v>
       </c>
       <c r="Q50">
-        <v>2054.453418091408</v>
+        <v>2093.540894491408</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1204188026877817</v>
+        <v>0.120383954971264</v>
       </c>
       <c r="T50">
         <v>1.45378010543232</v>
       </c>
       <c r="U50">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.048396315478402</v>
+        <v>2.159536835534134</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09376562868346647</v>
+        <v>0.09211828196770247</v>
       </c>
       <c r="C51">
-        <v>9918.292039578908</v>
+        <v>10527.45846003309</v>
       </c>
       <c r="D51">
-        <v>18655.13303957891</v>
+        <v>19264.29946003309</v>
       </c>
       <c r="E51">
         <v>8941.141000000001</v>
@@ -5475,37 +5475,37 @@
         <v>1778</v>
       </c>
       <c r="M51">
-        <v>886.0793455600237</v>
+        <v>840.4772897600236</v>
       </c>
       <c r="N51">
-        <v>891.920654439976</v>
+        <v>937.5227102399762</v>
       </c>
       <c r="O51">
-        <v>111.490081804997</v>
+        <v>117.190338779997</v>
       </c>
       <c r="P51">
-        <v>780.4305726349791</v>
+        <v>820.3323714599792</v>
       </c>
       <c r="Q51">
-        <v>2038.630572634979</v>
+        <v>2078.532371459979</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1217807437047156</v>
+        <v>0.1217452599483156</v>
       </c>
       <c r="T51">
         <v>1.480314473230678</v>
       </c>
       <c r="U51">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V51">
         <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.006592309040067</v>
+        <v>2.11546465521711</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1000271009710221</v>
+        <v>0.09222152835208335</v>
       </c>
       <c r="C52">
-        <v>7650.883176091887</v>
+        <v>10242.74394520129</v>
       </c>
       <c r="D52">
-        <v>16632.63317609189</v>
+        <v>19224.49394520129</v>
       </c>
       <c r="E52">
         <v>9186.050000000001</v>
@@ -5557,45 +5557,45 @@
         <v>1778</v>
       </c>
       <c r="M52">
-        <v>1075.598897510228</v>
+        <v>857.6298875102282</v>
       </c>
       <c r="N52">
-        <v>702.4011024897716</v>
+        <v>920.3701124897716</v>
       </c>
       <c r="O52">
-        <v>87.80013781122145</v>
+        <v>115.0462640612214</v>
       </c>
       <c r="P52">
-        <v>614.6009646785501</v>
+        <v>805.3238484285501</v>
       </c>
       <c r="Q52">
-        <v>1872.80096467855</v>
+        <v>2063.52384842855</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1231971623623268</v>
+        <v>0.1231610171244494</v>
       </c>
       <c r="T52">
         <v>1.50791021574097</v>
       </c>
       <c r="U52">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V52">
         <v>0.125</v>
       </c>
       <c r="W52">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.653032560851144</v>
+        <v>2.073155362112768</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1002860732585777</v>
+        <v>0.09232477473646422</v>
       </c>
       <c r="C53">
-        <v>7331.726141752326</v>
+        <v>9958.193590170013</v>
       </c>
       <c r="D53">
-        <v>16558.38514175233</v>
+        <v>19184.85259017001</v>
       </c>
       <c r="E53">
         <v>9430.959000000001</v>
@@ -5639,45 +5639,45 @@
         <v>1778</v>
       </c>
       <c r="M53">
-        <v>1097.110875460433</v>
+        <v>874.7824852604327</v>
       </c>
       <c r="N53">
-        <v>680.8891245395671</v>
+        <v>903.217514739567</v>
       </c>
       <c r="O53">
-        <v>85.11114056744589</v>
+        <v>112.9021893424459</v>
       </c>
       <c r="P53">
-        <v>595.7779839721212</v>
+        <v>790.3153253971211</v>
       </c>
       <c r="Q53">
-        <v>1853.977983972121</v>
+        <v>2048.515325397121</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1246713940263711</v>
+        <v>0.1246345603077722</v>
       </c>
       <c r="T53">
         <v>1.536632315088417</v>
       </c>
       <c r="U53">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.6206201576972</v>
+        <v>2.032505256973302</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1005450455461333</v>
+        <v>0.09597702112084511</v>
       </c>
       <c r="C54">
-        <v>7013.229047533701</v>
+        <v>8409.034321387482</v>
       </c>
       <c r="D54">
-        <v>16484.7970475337</v>
+        <v>17880.60232138748</v>
       </c>
       <c r="E54">
         <v>9675.868000000002</v>
@@ -5721,45 +5721,45 @@
         <v>1778</v>
       </c>
       <c r="M54">
-        <v>1118.622853410637</v>
+        <v>991.2701734106375</v>
       </c>
       <c r="N54">
-        <v>659.3771465893624</v>
+        <v>786.7298265893622</v>
       </c>
       <c r="O54">
-        <v>82.4221433236703</v>
+        <v>98.34122832367028</v>
       </c>
       <c r="P54">
-        <v>576.9550032656921</v>
+        <v>688.3885982656919</v>
       </c>
       <c r="Q54">
-        <v>1835.155003265692</v>
+        <v>1946.588598265692</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1262070520097507</v>
+        <v>0.1261695011237335</v>
       </c>
       <c r="T54">
         <v>1.566551168575341</v>
       </c>
       <c r="U54">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V54">
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.589454385433792</v>
+        <v>1.793658326147836</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1008040178336889</v>
+        <v>0.09614851750522596</v>
       </c>
       <c r="C55">
-        <v>6695.383133729329</v>
+        <v>8107.227538578119</v>
       </c>
       <c r="D55">
-        <v>16411.86013372933</v>
+        <v>17823.70453857812</v>
       </c>
       <c r="E55">
         <v>9920.777000000002</v>
@@ -5803,45 +5803,45 @@
         <v>1778</v>
       </c>
       <c r="M55">
-        <v>1140.134831360842</v>
+        <v>1010.333061360842</v>
       </c>
       <c r="N55">
-        <v>637.8651686391579</v>
+        <v>767.6669386391577</v>
       </c>
       <c r="O55">
-        <v>79.73314607989474</v>
+        <v>95.95836732989471</v>
       </c>
       <c r="P55">
-        <v>558.1320225592632</v>
+        <v>671.708571309263</v>
       </c>
       <c r="Q55">
-        <v>1816.332022559263</v>
+        <v>1929.908571309263</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1278080571413591</v>
+        <v>0.1277697585701612</v>
       </c>
       <c r="T55">
         <v>1.597743164763837</v>
       </c>
       <c r="U55">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V55">
         <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.559464680048249</v>
+        <v>1.759815716220519</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1010629901212446</v>
+        <v>0.09816276388960685</v>
       </c>
       <c r="C56">
-        <v>6378.179794978727</v>
+        <v>7220.173111829952</v>
       </c>
       <c r="D56">
-        <v>16339.56579497873</v>
+        <v>17181.55911182995</v>
       </c>
       <c r="E56">
         <v>10165.686</v>
@@ -5885,37 +5885,37 @@
         <v>1778</v>
       </c>
       <c r="M56">
-        <v>1161.646809311046</v>
+        <v>1080.973784711046</v>
       </c>
       <c r="N56">
-        <v>616.3531906889534</v>
+        <v>697.0262152889534</v>
       </c>
       <c r="O56">
-        <v>77.04414883611918</v>
+        <v>87.12827691111917</v>
       </c>
       <c r="P56">
-        <v>539.3090418528343</v>
+        <v>609.8979383778342</v>
       </c>
       <c r="Q56">
-        <v>1797.509041852834</v>
+        <v>1868.097938377834</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1294786711917331</v>
+        <v>0.1294395924273032</v>
       </c>
       <c r="T56">
         <v>1.630291334699658</v>
       </c>
       <c r="U56">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V56">
         <v>0.125</v>
       </c>
       <c r="W56">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.5305857044918</v>
+        <v>1.64481324630391</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1013219624088002</v>
+        <v>0.09836838527398772</v>
       </c>
       <c r="C57">
-        <v>6061.610576883089</v>
+        <v>6912.304890653289</v>
       </c>
       <c r="D57">
-        <v>16267.90557688309</v>
+        <v>17118.59989065329</v>
       </c>
       <c r="E57">
         <v>10410.595</v>
@@ -5967,37 +5967,37 @@
         <v>1778</v>
       </c>
       <c r="M57">
-        <v>1183.158787261251</v>
+        <v>1100.991817761251</v>
       </c>
       <c r="N57">
-        <v>594.8412127387487</v>
+        <v>677.0081822387485</v>
       </c>
       <c r="O57">
-        <v>74.35515159234359</v>
+        <v>84.62602277984357</v>
       </c>
       <c r="P57">
-        <v>520.4860611464051</v>
+        <v>592.382159458905</v>
       </c>
       <c r="Q57">
-        <v>1778.686061146405</v>
+        <v>1850.582159458905</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.131223534755457</v>
+        <v>0.1311836411225404</v>
       </c>
       <c r="T57">
         <v>1.66428608996596</v>
       </c>
       <c r="U57">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V57">
         <v>0.125</v>
       </c>
       <c r="W57">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.50275687350104</v>
+        <v>1.614907550916565</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1262466653852088</v>
+        <v>0.09857400665836857</v>
       </c>
       <c r="C58">
-        <v>988.1583048394241</v>
+        <v>6604.896393947292</v>
       </c>
       <c r="D58">
-        <v>11439.36230483943</v>
+        <v>17056.10039394729</v>
       </c>
       <c r="E58">
         <v>10655.504</v>
@@ -6049,45 +6049,45 @@
         <v>1778</v>
       </c>
       <c r="M58">
-        <v>1876.701061211456</v>
+        <v>1121.009850811456</v>
       </c>
       <c r="N58">
-        <v>-98.70106121145614</v>
+        <v>656.9901491885441</v>
       </c>
       <c r="O58">
-        <v>-12.33763265143202</v>
+        <v>82.12376864856802</v>
       </c>
       <c r="P58">
-        <v>-86.36342856002412</v>
+        <v>574.8663805399761</v>
       </c>
       <c r="Q58">
-        <v>1171.836571439976</v>
+        <v>1833.066380539976</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1333930892393756</v>
+        <v>0.1330069647584702</v>
       </c>
       <c r="T58">
-        <v>1.706554995828326</v>
+        <v>1.69982606138073</v>
       </c>
       <c r="U58">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1184258934966085</v>
+        <v>0.125</v>
       </c>
       <c r="W58">
-        <v>0.1206316180712206</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.9474071479728677</v>
+        <v>1.58606991607877</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1271570315518342</v>
+        <v>0.09877962804274945</v>
       </c>
       <c r="C59">
-        <v>620.564845015524</v>
+        <v>6297.942604707954</v>
       </c>
       <c r="D59">
-        <v>11316.67784501553</v>
+        <v>16994.05560470796</v>
       </c>
       <c r="E59">
         <v>10900.413</v>
@@ -6131,45 +6131,45 @@
         <v>1778</v>
       </c>
       <c r="M59">
-        <v>1910.213580161661</v>
+        <v>1141.02788386166</v>
       </c>
       <c r="N59">
-        <v>-132.2135801616607</v>
+        <v>636.9721161383395</v>
       </c>
       <c r="O59">
-        <v>-16.52669752020759</v>
+        <v>79.62151451729244</v>
       </c>
       <c r="P59">
-        <v>-115.6868826414531</v>
+        <v>557.3506016210471</v>
       </c>
       <c r="Q59">
-        <v>1142.513117358547</v>
+        <v>1815.550601621047</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1354301378263378</v>
+        <v>0.1349150941449083</v>
       </c>
       <c r="T59">
-        <v>1.746242321312706</v>
+        <v>1.737019054721769</v>
       </c>
       <c r="U59">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V59">
-        <v>0.116348246242282</v>
+        <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.1209159162921208</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.930785969938256</v>
+        <v>1.558244128077388</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1280673977184595</v>
+        <v>0.09898524942713033</v>
       </c>
       <c r="C60">
-        <v>255.5749859188491</v>
+        <v>5991.438578667907</v>
       </c>
       <c r="D60">
-        <v>11196.59698591885</v>
+        <v>16932.46057866791</v>
       </c>
       <c r="E60">
         <v>11145.322</v>
@@ -6213,45 +6213,45 @@
         <v>1778</v>
       </c>
       <c r="M60">
-        <v>1943.726099111865</v>
+        <v>1161.045916911865</v>
       </c>
       <c r="N60">
-        <v>-165.7260991118649</v>
+        <v>616.9540830881351</v>
       </c>
       <c r="O60">
-        <v>-20.71576238898311</v>
+        <v>77.11926038601689</v>
       </c>
       <c r="P60">
-        <v>-145.0103367228818</v>
+        <v>539.8348227021182</v>
       </c>
       <c r="Q60">
-        <v>1113.189663277118</v>
+        <v>1798.034822702118</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1375641887269649</v>
+        <v>0.1369140868354626</v>
       </c>
       <c r="T60">
-        <v>1.787819519439198</v>
+        <v>1.775983142983809</v>
       </c>
       <c r="U60">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1143422419967254</v>
+        <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.1211904111260935</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.9147379359738036</v>
+        <v>1.531377850007088</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1289777638850848</v>
+        <v>0.09919087081151121</v>
       </c>
       <c r="C61">
-        <v>-106.8932823854684</v>
+        <v>5685.37944298297</v>
       </c>
       <c r="D61">
-        <v>11079.03771761453</v>
+        <v>16871.31044298297</v>
       </c>
       <c r="E61">
         <v>11390.231</v>
@@ -6295,45 +6295,45 @@
         <v>1778</v>
       </c>
       <c r="M61">
-        <v>1977.238618062069</v>
+        <v>1181.063949962069</v>
       </c>
       <c r="N61">
-        <v>-199.2386180620695</v>
+        <v>596.9360500379307</v>
       </c>
       <c r="O61">
-        <v>-24.90482725775868</v>
+        <v>74.61700625474134</v>
       </c>
       <c r="P61">
-        <v>-174.3337908043108</v>
+        <v>522.3190437831894</v>
       </c>
       <c r="Q61">
-        <v>1083.866209195689</v>
+        <v>1780.519043783189</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.139802339671525</v>
+        <v>0.1390105913645804</v>
       </c>
       <c r="T61">
-        <v>1.831424873571862</v>
+        <v>1.816847918478144</v>
       </c>
       <c r="U61">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V61">
-        <v>0.112404237895086</v>
+        <v>0.125</v>
       </c>
       <c r="W61">
-        <v>0.1214556010504399</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8992339031606882</v>
+        <v>1.505422293227307</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1298881300517102</v>
+        <v>0.1068514921958921</v>
       </c>
       <c r="C62">
-        <v>-466.9185613490481</v>
+        <v>3439.689653425161</v>
       </c>
       <c r="D62">
-        <v>10963.92143865095</v>
+        <v>14870.52965342516</v>
       </c>
       <c r="E62">
         <v>11635.14</v>
@@ -6377,45 +6377,45 @@
         <v>1778</v>
       </c>
       <c r="M62">
-        <v>2010.751137012274</v>
+        <v>1409.744451012274</v>
       </c>
       <c r="N62">
-        <v>-232.7511370122743</v>
+        <v>368.2555489877259</v>
       </c>
       <c r="O62">
-        <v>-29.09389212653429</v>
+        <v>46.03194362346574</v>
       </c>
       <c r="P62">
-        <v>-203.65724488574</v>
+        <v>322.2236053642602</v>
       </c>
       <c r="Q62">
-        <v>1054.54275511426</v>
+        <v>1580.42360536426</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1421523981633132</v>
+        <v>0.1412119211201542</v>
       </c>
       <c r="T62">
-        <v>1.877210495411158</v>
+        <v>1.859755932747197</v>
       </c>
       <c r="U62">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V62">
-        <v>0.1105308339301679</v>
+        <v>0.125</v>
       </c>
       <c r="W62">
-        <v>0.1217119513106415</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8842466714413433</v>
+        <v>1.261221492110359</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1307984962183355</v>
+        <v>0.1230072484909918</v>
       </c>
       <c r="C63">
-        <v>-824.5762191978101</v>
+        <v>219.7214671904185</v>
       </c>
       <c r="D63">
-        <v>10851.17278080219</v>
+        <v>11895.47046719042</v>
       </c>
       <c r="E63">
         <v>11880.049</v>
@@ -6459,37 +6459,37 @@
         <v>1778</v>
       </c>
       <c r="M63">
-        <v>2044.263655962479</v>
+        <v>1860.508433262479</v>
       </c>
       <c r="N63">
-        <v>-266.2636559624789</v>
+        <v>-82.50843326247877</v>
       </c>
       <c r="O63">
-        <v>-33.28295699530986</v>
+        <v>-10.31355415780985</v>
       </c>
       <c r="P63">
-        <v>-232.980698967169</v>
+        <v>-72.19487910466893</v>
       </c>
       <c r="Q63">
-        <v>1025.219301032831</v>
+        <v>1186.005120895331</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.144622972475193</v>
+        <v>0.1438838757384142</v>
       </c>
       <c r="T63">
-        <v>1.925344097857599</v>
+        <v>1.911837301563599</v>
       </c>
       <c r="U63">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.1087188530460668</v>
+        <v>0.1194565937066329</v>
       </c>
       <c r="W63">
-        <v>0.1219598966442791</v>
+        <v>0.1096598966442791</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8697508243685343</v>
+        <v>0.9556527496530629</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1317088623849609</v>
+        <v>0.1237946146576171</v>
       </c>
       <c r="C64">
-        <v>-1179.938555485856</v>
+        <v>-140.0521459984193</v>
       </c>
       <c r="D64">
-        <v>10740.71944451414</v>
+        <v>11780.60585400158</v>
       </c>
       <c r="E64">
         <v>12124.958</v>
@@ -6541,37 +6541,37 @@
         <v>1778</v>
       </c>
       <c r="M64">
-        <v>2077.776174912683</v>
+        <v>1891.008571512683</v>
       </c>
       <c r="N64">
-        <v>-299.7761749126832</v>
+        <v>-113.0085715126831</v>
       </c>
       <c r="O64">
-        <v>-37.47202186408541</v>
+        <v>-14.12607143908539</v>
       </c>
       <c r="P64">
-        <v>-262.3041530485979</v>
+        <v>-98.88250007359775</v>
       </c>
       <c r="Q64">
-        <v>995.8958469514022</v>
+        <v>1159.317499926402</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1472235770140139</v>
+        <v>0.1464650303631093</v>
       </c>
       <c r="T64">
-        <v>1.97601104780122</v>
+        <v>1.962148809499483</v>
       </c>
       <c r="U64">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.106965323158227</v>
+        <v>0.1175298744533001</v>
       </c>
       <c r="W64">
-        <v>0.1221998437413477</v>
+        <v>0.1098998437413477</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8557225852658161</v>
+        <v>0.9402389956264008</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1326192285515862</v>
+        <v>0.1245819808242424</v>
       </c>
       <c r="C65">
-        <v>-1533.07495570076</v>
+        <v>-497.6286715498663</v>
       </c>
       <c r="D65">
-        <v>10632.49204429924</v>
+        <v>11667.93832845013</v>
       </c>
       <c r="E65">
         <v>12369.867</v>
@@ -6623,37 +6623,37 @@
         <v>1778</v>
       </c>
       <c r="M65">
-        <v>2111.288693862888</v>
+        <v>1921.508709762888</v>
       </c>
       <c r="N65">
-        <v>-333.2886938628878</v>
+        <v>-143.508709762888</v>
       </c>
       <c r="O65">
-        <v>-41.66108673286098</v>
+        <v>-17.938588720361</v>
       </c>
       <c r="P65">
-        <v>-291.6276071300268</v>
+        <v>-125.570121042527</v>
       </c>
       <c r="Q65">
-        <v>966.5723928699732</v>
+        <v>1132.629878957473</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1499647547711493</v>
+        <v>0.1491857068594095</v>
       </c>
       <c r="T65">
-        <v>2.029416751795847</v>
+        <v>2.015179858404874</v>
       </c>
       <c r="U65">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.1052674608858742</v>
+        <v>0.1156643208905493</v>
       </c>
       <c r="W65">
-        <v>0.1224321734702554</v>
+        <v>0.1101321734702554</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8421396870869937</v>
+        <v>0.9253145671243943</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1335295947182115</v>
+        <v>0.1253693469908678</v>
       </c>
       <c r="C66">
-        <v>-1884.052036614927</v>
+        <v>-853.0705499089436</v>
       </c>
       <c r="D66">
-        <v>10526.42396338507</v>
+        <v>11557.40545009106</v>
       </c>
       <c r="E66">
         <v>12614.776</v>
@@ -6705,37 +6705,37 @@
         <v>1778</v>
       </c>
       <c r="M66">
-        <v>2144.801212813092</v>
+        <v>1952.008848013092</v>
       </c>
       <c r="N66">
-        <v>-366.8012128130924</v>
+        <v>-174.0088480130926</v>
       </c>
       <c r="O66">
-        <v>-45.85015160163655</v>
+        <v>-21.75110600163657</v>
       </c>
       <c r="P66">
-        <v>-320.9510612114559</v>
+        <v>-152.257742011456</v>
       </c>
       <c r="Q66">
-        <v>937.2489387885441</v>
+        <v>1105.942257988544</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1528582201814591</v>
+        <v>0.1520575320499487</v>
       </c>
       <c r="T66">
-        <v>2.085789439345732</v>
+        <v>2.071157076693899</v>
       </c>
       <c r="U66">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.1036226568095324</v>
+        <v>0.1138570658766345</v>
       </c>
       <c r="W66">
-        <v>0.1226572428951348</v>
+        <v>0.1103572428951348</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8289812544762594</v>
+        <v>0.9108565270130755</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1344399608848369</v>
+        <v>0.1261567131574931</v>
       </c>
       <c r="C67">
-        <v>-2232.933783022856</v>
+        <v>-1206.437877677568</v>
       </c>
       <c r="D67">
-        <v>10422.45121697715</v>
+        <v>11448.94712232243</v>
       </c>
       <c r="E67">
         <v>12859.685</v>
@@ -6787,37 +6787,37 @@
         <v>1778</v>
       </c>
       <c r="M67">
-        <v>2178.313731763297</v>
+        <v>1982.508986263297</v>
       </c>
       <c r="N67">
-        <v>-400.313731763297</v>
+        <v>-204.5089862632969</v>
       </c>
       <c r="O67">
-        <v>-50.03921647041213</v>
+        <v>-25.56362328291212</v>
       </c>
       <c r="P67">
-        <v>-350.2745152928849</v>
+        <v>-178.9453629803848</v>
       </c>
       <c r="Q67">
-        <v>907.9254847071152</v>
+        <v>1079.254637019615</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1559170264723579</v>
+        <v>0.1550934615370901</v>
       </c>
       <c r="T67">
-        <v>2.145383423327039</v>
+        <v>2.130332993170867</v>
       </c>
       <c r="U67">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V67">
-        <v>0.1020284620893858</v>
+        <v>0.1121054187093016</v>
       </c>
       <c r="W67">
-        <v>0.1228753871069409</v>
+        <v>0.1105753871069409</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8162276967150861</v>
+        <v>0.8968433496744129</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1353503270514622</v>
+        <v>0.1269440793241185</v>
       </c>
       <c r="C68">
-        <v>-2579.781676454131</v>
+        <v>-1557.788516568908</v>
       </c>
       <c r="D68">
-        <v>10320.51232354587</v>
+        <v>11342.5054834311</v>
       </c>
       <c r="E68">
         <v>13104.594</v>
@@ -6869,37 +6869,37 @@
         <v>1778</v>
       </c>
       <c r="M68">
-        <v>2211.826250713502</v>
+        <v>2013.009124513502</v>
       </c>
       <c r="N68">
-        <v>-433.8262507135021</v>
+        <v>-235.0091245135018</v>
       </c>
       <c r="O68">
-        <v>-54.22828133918776</v>
+        <v>-29.37614056418772</v>
       </c>
       <c r="P68">
-        <v>-379.5979693743143</v>
+        <v>-205.6329839493141</v>
       </c>
       <c r="Q68">
-        <v>878.6020306256858</v>
+        <v>1052.567016050686</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1591557625450743</v>
+        <v>0.1583079751117104</v>
       </c>
       <c r="T68">
-        <v>2.208482935777834</v>
+        <v>2.192989845911187</v>
       </c>
       <c r="U68">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V68">
-        <v>0.1004825763001526</v>
+        <v>0.1104068517591607</v>
       </c>
       <c r="W68">
-        <v>0.1230869208880863</v>
+        <v>0.1107869208880863</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.803860610401221</v>
+        <v>0.8832548140732854</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1941918560052638</v>
+        <v>0.1277314454907438</v>
       </c>
       <c r="C69">
-        <v>-6822.040895619695</v>
+        <v>-1907.178196339963</v>
       </c>
       <c r="D69">
-        <v>6323.162104380307</v>
+        <v>11238.02480366004</v>
       </c>
       <c r="E69">
         <v>13349.503</v>
@@ -6951,45 +6951,45 @@
         <v>1778</v>
       </c>
       <c r="M69">
-        <v>3638.454634363706</v>
+        <v>2043.509262763706</v>
       </c>
       <c r="N69">
-        <v>-1860.454634363706</v>
+        <v>-265.5092627637064</v>
       </c>
       <c r="O69">
-        <v>-232.5568292954633</v>
+        <v>-33.1886578454633</v>
       </c>
       <c r="P69">
-        <v>-1627.897805068243</v>
+        <v>-232.3206049182431</v>
       </c>
       <c r="Q69">
-        <v>-369.697805068243</v>
+        <v>1025.879395081757</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.165767036522732</v>
+        <v>0.1617173076908532</v>
       </c>
       <c r="T69">
-        <v>2.337288789451159</v>
+        <v>2.259444083666072</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V69">
-        <v>0.06108362542188659</v>
+        <v>0.1087589883000687</v>
       </c>
       <c r="W69">
-        <v>0.2081921402280034</v>
+        <v>0.1109921402280034</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4886690033750928</v>
+        <v>0.8700719064005498</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1959512221718892</v>
+        <v>0.1285188116573692</v>
       </c>
       <c r="C70">
-        <v>-7139.339618575923</v>
+        <v>-2254.66061208714</v>
       </c>
       <c r="D70">
-        <v>6250.772381424079</v>
+        <v>11135.45138791286</v>
       </c>
       <c r="E70">
         <v>13594.412</v>
@@ -7033,45 +7033,45 @@
         <v>1778</v>
       </c>
       <c r="M70">
-        <v>3692.759927413911</v>
+        <v>2074.009401013911</v>
       </c>
       <c r="N70">
-        <v>-1914.759927413911</v>
+        <v>-296.0094010139107</v>
       </c>
       <c r="O70">
-        <v>-239.3449909267389</v>
+        <v>-37.00117512673884</v>
       </c>
       <c r="P70">
-        <v>-1675.414936487172</v>
+        <v>-259.0082258871719</v>
       </c>
       <c r="Q70">
-        <v>-417.2149364871721</v>
+        <v>999.1917741128282</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1695160064140674</v>
+        <v>0.1653397235561923</v>
       </c>
       <c r="T70">
-        <v>2.410329064121508</v>
+        <v>2.330051711280636</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V70">
-        <v>0.06018533681274121</v>
+        <v>0.107159591413303</v>
       </c>
       <c r="W70">
-        <v>0.2083913237049818</v>
+        <v>0.1111913237049818</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.4814826945019296</v>
+        <v>0.8572767313064241</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1977105883385145</v>
+        <v>0.1293061778239945</v>
       </c>
       <c r="C71">
-        <v>-7454.999617578016</v>
+        <v>-2600.287516261742</v>
       </c>
       <c r="D71">
-        <v>6180.021382421985</v>
+        <v>11034.73348373826</v>
       </c>
       <c r="E71">
         <v>13839.321</v>
@@ -7115,45 +7115,45 @@
         <v>1778</v>
       </c>
       <c r="M71">
-        <v>3747.065220464116</v>
+        <v>2104.509539264115</v>
       </c>
       <c r="N71">
-        <v>-1969.065220464116</v>
+        <v>-326.5095392641153</v>
       </c>
       <c r="O71">
-        <v>-246.1331525580145</v>
+        <v>-40.81369240801442</v>
       </c>
       <c r="P71">
-        <v>-1722.932067906101</v>
+        <v>-285.695846856101</v>
       </c>
       <c r="Q71">
-        <v>-464.7320679061013</v>
+        <v>972.5041531438991</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1735068453306502</v>
+        <v>0.1691958436709082</v>
       </c>
       <c r="T71">
-        <v>2.488081614577041</v>
+        <v>2.405214669709044</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05931308555458553</v>
+        <v>0.1056065538565885</v>
       </c>
       <c r="W71">
-        <v>0.2085847337478449</v>
+        <v>0.1113847337478449</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4745046844366843</v>
+        <v>0.8448524308527078</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1994699545051399</v>
+        <v>0.1300935439906198</v>
       </c>
       <c r="C72">
-        <v>-7769.075914817558</v>
+        <v>-2944.108805736592</v>
       </c>
       <c r="D72">
-        <v>6110.854085182443</v>
+        <v>10935.82119426341</v>
       </c>
       <c r="E72">
         <v>14084.23</v>
@@ -7197,45 +7197,45 @@
         <v>1778</v>
       </c>
       <c r="M72">
-        <v>3801.37051351432</v>
+        <v>2135.00967751432</v>
       </c>
       <c r="N72">
-        <v>-2023.37051351432</v>
+        <v>-357.0096775143199</v>
       </c>
       <c r="O72">
-        <v>-252.92131418929</v>
+        <v>-44.62620968928999</v>
       </c>
       <c r="P72">
-        <v>-1770.44919932503</v>
+        <v>-312.3834678250299</v>
       </c>
       <c r="Q72">
-        <v>-512.2491993250301</v>
+        <v>945.8165321749701</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1777637401750052</v>
+        <v>0.1733090384599384</v>
       </c>
       <c r="T72">
-        <v>2.571017668396275</v>
+        <v>2.485388492032679</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V72">
-        <v>0.0584657557609486</v>
+        <v>0.1040978888014944</v>
       </c>
       <c r="W72">
-        <v>0.2087726177894833</v>
+        <v>0.1115726177894833</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.4677260460875887</v>
+        <v>0.8327831104119549</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2012293206717652</v>
+        <v>0.1308809101572452</v>
       </c>
       <c r="C73">
-        <v>-8081.621096498695</v>
+        <v>-3286.17260423168</v>
       </c>
       <c r="D73">
-        <v>6043.217903501306</v>
+        <v>10838.66639576832</v>
       </c>
       <c r="E73">
         <v>14329.139</v>
@@ -7279,45 +7279,45 @@
         <v>1778</v>
       </c>
       <c r="M73">
-        <v>3855.675806564524</v>
+        <v>2165.509815764524</v>
       </c>
       <c r="N73">
-        <v>-2077.675806564524</v>
+        <v>-387.5098157645245</v>
       </c>
       <c r="O73">
-        <v>-259.7094758205656</v>
+        <v>-48.43872697056557</v>
       </c>
       <c r="P73">
-        <v>-1817.966330743959</v>
+        <v>-339.071088793959</v>
       </c>
       <c r="Q73">
-        <v>-559.7663307439589</v>
+        <v>919.128911206041</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1823142139741433</v>
+        <v>0.1777059018551087</v>
       </c>
       <c r="T73">
-        <v>2.659673450065112</v>
+        <v>2.571091543482081</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05764229441220284</v>
+        <v>0.102631721353586</v>
       </c>
       <c r="W73">
-        <v>0.2089552093229066</v>
+        <v>0.1117552093229065</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4611383552976228</v>
+        <v>0.8210537708286878</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2029886868383906</v>
+        <v>0.1316682763238705</v>
       </c>
       <c r="C74">
-        <v>-8392.685446172392</v>
+        <v>-3626.525340384786</v>
       </c>
       <c r="D74">
-        <v>5977.062553827608</v>
+        <v>10743.22265961522</v>
       </c>
       <c r="E74">
         <v>14574.048</v>
@@ -7361,45 +7361,45 @@
         <v>1778</v>
       </c>
       <c r="M74">
-        <v>3909.981099614729</v>
+        <v>2196.009954014728</v>
       </c>
       <c r="N74">
-        <v>-2131.981099614729</v>
+        <v>-418.0099540147287</v>
       </c>
       <c r="O74">
-        <v>-266.4976374518411</v>
+        <v>-52.25124425184109</v>
       </c>
       <c r="P74">
-        <v>-1865.483462162888</v>
+        <v>-365.7587097628876</v>
       </c>
       <c r="Q74">
-        <v>-607.2834621628879</v>
+        <v>892.4412902371124</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.187189721616077</v>
+        <v>0.1824168269213626</v>
       </c>
       <c r="T74">
-        <v>2.754661787567437</v>
+        <v>2.662916241463584</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05684170698981113</v>
+        <v>0.1012062807792306</v>
       </c>
       <c r="W74">
-        <v>0.2091327288692903</v>
+        <v>0.1119327288692903</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4547336559184891</v>
+        <v>0.8096502462338451</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2047480530050159</v>
+        <v>0.1535967368354751</v>
       </c>
       <c r="C75">
-        <v>-8702.317069407854</v>
+        <v>-5987.271265884727</v>
       </c>
       <c r="D75">
-        <v>5912.339930592147</v>
+        <v>8627.385734115274</v>
       </c>
       <c r="E75">
         <v>14818.957</v>
@@ -7443,45 +7443,45 @@
         <v>1778</v>
       </c>
       <c r="M75">
-        <v>3964.286392664933</v>
+        <v>2730.679759664933</v>
       </c>
       <c r="N75">
-        <v>-2186.286392664933</v>
+        <v>-952.6797596649333</v>
       </c>
       <c r="O75">
-        <v>-273.2857990831167</v>
+        <v>-119.0849699581167</v>
       </c>
       <c r="P75">
-        <v>-1913.000593581817</v>
+        <v>-833.5947897068166</v>
       </c>
       <c r="Q75">
-        <v>-654.8005935818167</v>
+        <v>424.6052102931834</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.192426377972228</v>
+        <v>0.1895326143813363</v>
       </c>
       <c r="T75">
-        <v>2.856686298218083</v>
+        <v>2.801616183666705</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05606305346940277</v>
+        <v>0.08138999061071558</v>
       </c>
       <c r="W75">
-        <v>0.209305384866458</v>
+        <v>0.140305384866458</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4485044277552221</v>
+        <v>0.6511199248857247</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2065074191716412</v>
+        <v>0.1952664142234084</v>
       </c>
       <c r="C76">
-        <v>-9010.562010450643</v>
+        <v>-8581.67069071639</v>
       </c>
       <c r="D76">
-        <v>5849.003989549356</v>
+        <v>6277.895309283609</v>
       </c>
       <c r="E76">
         <v>15063.866</v>
@@ -7525,37 +7525,37 @@
         <v>1778</v>
       </c>
       <c r="M76">
-        <v>4018.591685715138</v>
+        <v>3746.742695715137</v>
       </c>
       <c r="N76">
-        <v>-2240.591685715138</v>
+        <v>-1968.742695715138</v>
       </c>
       <c r="O76">
-        <v>-280.0739607143922</v>
+        <v>-246.0928369643922</v>
       </c>
       <c r="P76">
-        <v>-1960.517725000745</v>
+        <v>-1722.649858750745</v>
       </c>
       <c r="Q76">
-        <v>-702.3177250007454</v>
+        <v>-464.4498587507453</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1980658540480829</v>
+        <v>0.1975235273241105</v>
       </c>
       <c r="T76">
-        <v>2.966558848149548</v>
+        <v>2.957373950399814</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05530544463873516</v>
+        <v>0.05931819130632329</v>
       </c>
       <c r="W76">
-        <v>0.2094733744853239</v>
+        <v>0.1944733744853239</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4424435571098814</v>
+        <v>0.4745455304505863</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2082667853382666</v>
+        <v>0.1968757803900337</v>
       </c>
       <c r="C77">
-        <v>-9317.464361462136</v>
+        <v>-8891.922717682011</v>
       </c>
       <c r="D77">
-        <v>5787.010638537867</v>
+        <v>6212.552282317992</v>
       </c>
       <c r="E77">
         <v>15308.775</v>
@@ -7607,37 +7607,37 @@
         <v>1778</v>
       </c>
       <c r="M77">
-        <v>4072.896978765343</v>
+        <v>3797.374353765343</v>
       </c>
       <c r="N77">
-        <v>-2294.896978765343</v>
+        <v>-2019.374353765343</v>
       </c>
       <c r="O77">
-        <v>-286.8621223456679</v>
+        <v>-252.4217942206679</v>
       </c>
       <c r="P77">
-        <v>-2008.034856419675</v>
+        <v>-1766.952559544675</v>
       </c>
       <c r="Q77">
-        <v>-749.8348564196751</v>
+        <v>-508.752559544675</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2041564882100063</v>
+        <v>0.203592468417075</v>
       </c>
       <c r="T77">
-        <v>3.08522120207553</v>
+        <v>3.075668908415807</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05456803871021868</v>
+        <v>0.05852728208890564</v>
       </c>
       <c r="W77">
-        <v>0.20963688438102</v>
+        <v>0.19463688438102</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4365443096817495</v>
+        <v>0.4682182567112452</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2100261515048919</v>
+        <v>0.1984851465566591</v>
       </c>
       <c r="C78">
-        <v>-9623.066364884815</v>
+        <v>-9200.828520228275</v>
       </c>
       <c r="D78">
-        <v>5726.317635115188</v>
+        <v>6148.555479771728</v>
       </c>
       <c r="E78">
         <v>15553.684</v>
@@ -7689,37 +7689,37 @@
         <v>1778</v>
       </c>
       <c r="M78">
-        <v>4127.202271815548</v>
+        <v>3848.006011815547</v>
       </c>
       <c r="N78">
-        <v>-2349.202271815548</v>
+        <v>-2070.006011815548</v>
       </c>
       <c r="O78">
-        <v>-293.6502839769435</v>
+        <v>-258.7507514769435</v>
       </c>
       <c r="P78">
-        <v>-2055.551987838604</v>
+        <v>-1811.255260338604</v>
       </c>
       <c r="Q78">
-        <v>-797.3519878386039</v>
+        <v>-553.0552603386043</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2107546752187565</v>
+        <v>0.2101671546011197</v>
       </c>
       <c r="T78">
-        <v>3.213772085495344</v>
+        <v>3.203821779599799</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.0538500382008737</v>
+        <v>0.05775718627194635</v>
       </c>
       <c r="W78">
-        <v>0.2097960913847242</v>
+        <v>0.1947960913847241</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4308003056069897</v>
+        <v>0.4620574901755707</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2117855176715173</v>
+        <v>0.2000945127232844</v>
       </c>
       <c r="C79">
-        <v>-9927.408509432964</v>
+        <v>-9508.429277380714</v>
       </c>
       <c r="D79">
-        <v>5666.884490567038</v>
+        <v>6085.863722619288</v>
       </c>
       <c r="E79">
         <v>15798.593</v>
@@ -7771,37 +7771,37 @@
         <v>1778</v>
       </c>
       <c r="M79">
-        <v>4181.507564865752</v>
+        <v>3898.637669865752</v>
       </c>
       <c r="N79">
-        <v>-2403.507564865752</v>
+        <v>-2120.637669865752</v>
       </c>
       <c r="O79">
-        <v>-300.438445608219</v>
+        <v>-265.079708733219</v>
       </c>
       <c r="P79">
-        <v>-2103.069119257533</v>
+        <v>-1855.557961132533</v>
       </c>
       <c r="Q79">
-        <v>-844.8691192575332</v>
+        <v>-597.3579611325333</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.217926617619572</v>
+        <v>0.2173135526272554</v>
       </c>
       <c r="T79">
-        <v>3.353501306603837</v>
+        <v>3.343118378712834</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05315068705540781</v>
+        <v>0.05700709294373926</v>
       </c>
       <c r="W79">
-        <v>0.2099511631415788</v>
+        <v>0.1949511631415788</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4252054964432626</v>
+        <v>0.456056743549914</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2135448838381426</v>
+        <v>0.2017038788899098</v>
       </c>
       <c r="C80">
-        <v>-10230.52962016704</v>
+        <v>-9814.764505641795</v>
       </c>
       <c r="D80">
-        <v>5608.672379832958</v>
+        <v>6024.437494358207</v>
       </c>
       <c r="E80">
         <v>16043.502</v>
@@ -7853,37 +7853,37 @@
         <v>1778</v>
       </c>
       <c r="M80">
-        <v>4235.812857915957</v>
+        <v>3949.269327915956</v>
       </c>
       <c r="N80">
-        <v>-2457.812857915957</v>
+        <v>-2171.269327915957</v>
       </c>
       <c r="O80">
-        <v>-307.2266072394946</v>
+        <v>-271.4086659894946</v>
       </c>
       <c r="P80">
-        <v>-2150.586250676462</v>
+        <v>-1899.860661926462</v>
       </c>
       <c r="Q80">
-        <v>-892.3862506764619</v>
+        <v>-641.6606619264619</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.225750554784098</v>
+        <v>0.2251096232012215</v>
       </c>
       <c r="T80">
-        <v>3.505933184176739</v>
+        <v>3.495078305017963</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05246926799059489</v>
+        <v>0.05627623277779389</v>
       </c>
       <c r="W80">
-        <v>0.2101022586995398</v>
+        <v>0.1951022586995398</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4197541439247592</v>
+        <v>0.450209862222351</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2153042500047679</v>
+        <v>0.2033132450565351</v>
       </c>
       <c r="C81">
-        <v>-10532.46694307286</v>
+        <v>-10119.87214205394</v>
       </c>
       <c r="D81">
-        <v>5551.644056927141</v>
+        <v>5964.238857946066</v>
       </c>
       <c r="E81">
         <v>16288.411</v>
@@ -7935,37 +7935,37 @@
         <v>1778</v>
       </c>
       <c r="M81">
-        <v>4290.118150966161</v>
+        <v>3999.900985966161</v>
       </c>
       <c r="N81">
-        <v>-2512.118150966161</v>
+        <v>-2221.900985966161</v>
       </c>
       <c r="O81">
-        <v>-314.0147688707701</v>
+        <v>-277.7376232457701</v>
       </c>
       <c r="P81">
-        <v>-2198.103382095391</v>
+        <v>-1944.163362720391</v>
       </c>
       <c r="Q81">
-        <v>-939.9033820953907</v>
+        <v>-685.9633627203909</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.234319628821436</v>
+        <v>0.2336481766869941</v>
       </c>
       <c r="T81">
-        <v>3.67288238342325</v>
+        <v>3.661510605256914</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05180510004134686</v>
+        <v>0.05556387540085978</v>
       </c>
       <c r="W81">
-        <v>0.2102495290535017</v>
+        <v>0.1952495290535017</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4144408003307749</v>
+        <v>0.4445110032068783</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2170636161713933</v>
+        <v>0.2049226112231605</v>
       </c>
       <c r="C82">
-        <v>-10833.25622453276</v>
+        <v>-10423.78862233184</v>
       </c>
       <c r="D82">
-        <v>5495.763775467236</v>
+        <v>5905.23137766816</v>
       </c>
       <c r="E82">
         <v>16533.32</v>
@@ -8017,37 +8017,37 @@
         <v>1778</v>
       </c>
       <c r="M82">
-        <v>4344.423444016365</v>
+        <v>4050.532644016365</v>
       </c>
       <c r="N82">
-        <v>-2566.423444016365</v>
+        <v>-2272.532644016365</v>
       </c>
       <c r="O82">
-        <v>-320.8029305020457</v>
+        <v>-284.0665805020457</v>
       </c>
       <c r="P82">
-        <v>-2245.62051351432</v>
+        <v>-1988.46606351432</v>
       </c>
       <c r="Q82">
-        <v>-987.42051351432</v>
+        <v>-730.2660635143195</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2437456102625079</v>
+        <v>0.2430405855213437</v>
       </c>
       <c r="T82">
-        <v>3.856526502594413</v>
+        <v>3.844586135519759</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.05115753629083002</v>
+        <v>0.05486932695834904</v>
       </c>
       <c r="W82">
-        <v>0.2103931176486147</v>
+        <v>0.1953931176486146</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4092602903266402</v>
+        <v>0.4389546156667924</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2188229823380186</v>
+        <v>0.2065319773897858</v>
       </c>
       <c r="C83">
-        <v>-11132.93178604511</v>
+        <v>-10726.5489544022</v>
       </c>
       <c r="D83">
-        <v>5440.997213954895</v>
+        <v>5847.380045597797</v>
       </c>
       <c r="E83">
         <v>16778.229</v>
@@ -8099,37 +8099,37 @@
         <v>1778</v>
       </c>
       <c r="M83">
-        <v>4398.72873706657</v>
+        <v>4101.16430206657</v>
       </c>
       <c r="N83">
-        <v>-2620.72873706657</v>
+        <v>-2323.16430206657</v>
       </c>
       <c r="O83">
-        <v>-327.5910921333212</v>
+        <v>-290.3955377583212</v>
       </c>
       <c r="P83">
-        <v>-2293.137644933249</v>
+        <v>-2032.768764308249</v>
       </c>
       <c r="Q83">
-        <v>-1034.937644933249</v>
+        <v>-774.5687643082485</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.254163800276324</v>
+        <v>0.2534216689698355</v>
       </c>
       <c r="T83">
-        <v>4.05950158167833</v>
+        <v>4.046932774231326</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.05052596176872101</v>
+        <v>0.05419192786009782</v>
       </c>
       <c r="W83">
-        <v>0.2105331608463173</v>
+        <v>0.1955331608463173</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4042076941497681</v>
+        <v>0.4335354228807826</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.220582348504644</v>
+        <v>0.2081413435564111</v>
       </c>
       <c r="C84">
-        <v>-11431.52659452025</v>
+        <v>-11028.18678766274</v>
       </c>
       <c r="D84">
-        <v>5387.311405479751</v>
+        <v>5790.651212337264</v>
       </c>
       <c r="E84">
         <v>17023.138</v>
@@ -8181,37 +8181,37 @@
         <v>1778</v>
       </c>
       <c r="M84">
-        <v>4453.034030116775</v>
+        <v>4151.795960116775</v>
       </c>
       <c r="N84">
-        <v>-2675.034030116775</v>
+        <v>-2373.795960116775</v>
       </c>
       <c r="O84">
-        <v>-334.3792537645969</v>
+        <v>-296.7244950145969</v>
       </c>
       <c r="P84">
-        <v>-2340.654776352178</v>
+        <v>-2077.071465102178</v>
       </c>
       <c r="Q84">
-        <v>-1082.454776352178</v>
+        <v>-818.871465102178</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2657395669583421</v>
+        <v>0.2649562061348263</v>
       </c>
       <c r="T84">
-        <v>4.285029447327126</v>
+        <v>4.271762372799733</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.0499097915032488</v>
+        <v>0.05353105069107223</v>
       </c>
       <c r="W84">
-        <v>0.2106697883562712</v>
+        <v>0.1956697883562712</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3992783320259904</v>
+        <v>0.4282484055285779</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2223417146712693</v>
+        <v>0.2097507097230365</v>
       </c>
       <c r="C85">
-        <v>-11729.07232845557</v>
+        <v>-11328.73447824836</v>
       </c>
       <c r="D85">
-        <v>5334.674671544434</v>
+        <v>5735.012521751649</v>
       </c>
       <c r="E85">
         <v>17268.047</v>
@@ -8263,37 +8263,37 @@
         <v>1778</v>
       </c>
       <c r="M85">
-        <v>4507.33932316698</v>
+        <v>4202.427618166979</v>
       </c>
       <c r="N85">
-        <v>-2729.33932316698</v>
+        <v>-2424.427618166979</v>
       </c>
       <c r="O85">
-        <v>-341.1674153958725</v>
+        <v>-303.0534522708724</v>
       </c>
       <c r="P85">
-        <v>-2388.171907771107</v>
+        <v>-2121.374165896107</v>
       </c>
       <c r="Q85">
-        <v>-1129.971907771107</v>
+        <v>-863.1741658961071</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2786771885441269</v>
+        <v>0.2778477476721691</v>
       </c>
       <c r="T85">
-        <v>4.537090003052252</v>
+        <v>4.523042512376188</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04930846871405303</v>
+        <v>0.05288609827310751</v>
       </c>
       <c r="W85">
-        <v>0.2108031236370696</v>
+        <v>0.1958031236370696</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3944677497124243</v>
+        <v>0.4230887861848601</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2241010808378947</v>
+        <v>0.2113600758896618</v>
       </c>
       <c r="C86">
-        <v>-12025.59944026862</v>
+        <v>-11628.22315057059</v>
       </c>
       <c r="D86">
-        <v>5283.056559731379</v>
+        <v>5680.432849429407</v>
       </c>
       <c r="E86">
         <v>17512.956</v>
@@ -8345,37 +8345,37 @@
         <v>1778</v>
       </c>
       <c r="M86">
-        <v>4561.644616217183</v>
+        <v>4253.059276217184</v>
       </c>
       <c r="N86">
-        <v>-2783.644616217183</v>
+        <v>-2475.059276217184</v>
       </c>
       <c r="O86">
-        <v>-347.9555770271479</v>
+        <v>-309.382409527148</v>
       </c>
       <c r="P86">
-        <v>-2435.689039190035</v>
+        <v>-2165.676866690036</v>
       </c>
       <c r="Q86">
-        <v>-1177.489039190035</v>
+        <v>-907.4768666900356</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2932320128281347</v>
+        <v>0.2923507319016796</v>
       </c>
       <c r="T86">
-        <v>4.820658128243015</v>
+        <v>4.805732669399698</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04872146313412384</v>
+        <v>0.05225650186509433</v>
       </c>
       <c r="W86">
-        <v>0.2109332842683251</v>
+        <v>0.1959332842683251</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3897717050729907</v>
+        <v>0.4180520149207546</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.22586044700452</v>
+        <v>0.2129694420562872</v>
       </c>
       <c r="C87">
-        <v>-12321.13721504624</v>
+        <v>-11926.68275537618</v>
       </c>
       <c r="D87">
-        <v>5232.427784953763</v>
+        <v>5626.882244623822</v>
       </c>
       <c r="E87">
         <v>17757.865</v>
@@ -8427,37 +8427,37 @@
         <v>1778</v>
       </c>
       <c r="M87">
-        <v>4615.949909267388</v>
+        <v>4303.690934267388</v>
       </c>
       <c r="N87">
-        <v>-2837.949909267388</v>
+        <v>-2525.690934267388</v>
       </c>
       <c r="O87">
-        <v>-354.7437386584235</v>
+        <v>-315.7113667834235</v>
       </c>
       <c r="P87">
-        <v>-2483.206170608964</v>
+        <v>-2209.979567483964</v>
       </c>
       <c r="Q87">
-        <v>-1225.006170608964</v>
+        <v>-951.7795674839642</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3097274803500104</v>
+        <v>0.3087874473617915</v>
       </c>
       <c r="T87">
-        <v>5.142035336792549</v>
+        <v>5.126114847359678</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04814826945019297</v>
+        <v>0.05164171949021086</v>
       </c>
       <c r="W87">
-        <v>0.2110603822964923</v>
+        <v>0.1960603822964923</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3851861556015438</v>
+        <v>0.413133755921687</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2276198131711453</v>
+        <v>0.2145788082229125</v>
       </c>
       <c r="C88">
-        <v>-12615.71382594758</v>
+        <v>-12224.14212455223</v>
       </c>
       <c r="D88">
-        <v>5182.760174052426</v>
+        <v>5574.331875447769</v>
       </c>
       <c r="E88">
         <v>18002.774</v>
@@ -8509,37 +8509,37 @@
         <v>1778</v>
       </c>
       <c r="M88">
-        <v>4670.255202317593</v>
+        <v>4354.322592317593</v>
       </c>
       <c r="N88">
-        <v>-2892.255202317593</v>
+        <v>-2576.322592317593</v>
       </c>
       <c r="O88">
-        <v>-361.5319002896991</v>
+        <v>-322.0403240396992</v>
       </c>
       <c r="P88">
-        <v>-2530.723302027894</v>
+        <v>-2254.282268277894</v>
       </c>
       <c r="Q88">
-        <v>-1272.523302027894</v>
+        <v>-996.0822682778942</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.328579443232154</v>
+        <v>0.327572265030491</v>
       </c>
       <c r="T88">
-        <v>5.509323575134874</v>
+        <v>5.492265907885369</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.0475884058519349</v>
+        <v>0.05104123437985957</v>
       </c>
       <c r="W88">
-        <v>0.2111845245565625</v>
+        <v>0.1961845245565625</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3807072468154793</v>
+        <v>0.4083298750388766</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2293791793377707</v>
+        <v>0.2161881743895379</v>
       </c>
       <c r="C89">
-        <v>-12909.35638648149</v>
+        <v>-12520.62902288892</v>
       </c>
       <c r="D89">
-        <v>5134.026613518516</v>
+        <v>5522.753977111085</v>
       </c>
       <c r="E89">
         <v>18247.683</v>
@@ -8591,37 +8591,37 @@
         <v>1778</v>
       </c>
       <c r="M89">
-        <v>4724.560495367798</v>
+        <v>4404.954250367798</v>
       </c>
       <c r="N89">
-        <v>-2946.560495367798</v>
+        <v>-2626.954250367798</v>
       </c>
       <c r="O89">
-        <v>-368.3200619209747</v>
+        <v>-328.3692812959747</v>
       </c>
       <c r="P89">
-        <v>-2578.240433446823</v>
+        <v>-2298.584969071823</v>
       </c>
       <c r="Q89">
-        <v>-1320.040433446823</v>
+        <v>-1040.384969071823</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3503317080961659</v>
+        <v>0.349247054648221</v>
       </c>
       <c r="T89">
-        <v>5.933117696299096</v>
+        <v>5.914747900799628</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04704141268122301</v>
+        <v>0.05045455352491866</v>
       </c>
       <c r="W89">
-        <v>0.2113058129715737</v>
+        <v>0.1963058129715737</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3763313014497841</v>
+        <v>0.4036364281993493</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.231138545504396</v>
+        <v>0.2177975405561632</v>
       </c>
       <c r="C90">
-        <v>-13202.09099986194</v>
+        <v>-12816.17019699475</v>
       </c>
       <c r="D90">
-        <v>5086.201000138059</v>
+        <v>5472.121803005256</v>
       </c>
       <c r="E90">
         <v>18492.592</v>
@@ -8673,37 +8673,37 @@
         <v>1778</v>
       </c>
       <c r="M90">
-        <v>4778.865788418002</v>
+        <v>4455.585908418002</v>
       </c>
       <c r="N90">
-        <v>-3000.865788418002</v>
+        <v>-2677.585908418002</v>
       </c>
       <c r="O90">
-        <v>-375.1082235522503</v>
+        <v>-334.6982385522502</v>
       </c>
       <c r="P90">
-        <v>-2625.757564865752</v>
+        <v>-2342.887669865752</v>
       </c>
       <c r="Q90">
-        <v>-1367.557564865752</v>
+        <v>-1084.687669865752</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.375709350437513</v>
+        <v>0.3745343092022395</v>
       </c>
       <c r="T90">
-        <v>6.427544170990688</v>
+        <v>6.407643559199598</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04650685117348184</v>
+        <v>0.04988120632577185</v>
       </c>
       <c r="W90">
-        <v>0.2114243448316982</v>
+        <v>0.1964243448316982</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3720548093878547</v>
+        <v>0.3990496506061749</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2328979116710213</v>
+        <v>0.2194069067227885</v>
       </c>
       <c r="C91">
-        <v>-13493.94280563034</v>
+        <v>-13110.79142154563</v>
       </c>
       <c r="D91">
-        <v>5039.258194369657</v>
+        <v>5422.409578454375</v>
       </c>
       <c r="E91">
         <v>18737.501</v>
@@ -8755,37 +8755,37 @@
         <v>1778</v>
       </c>
       <c r="M91">
-        <v>4833.171081468206</v>
+        <v>4506.217566468206</v>
       </c>
       <c r="N91">
-        <v>-3055.171081468206</v>
+        <v>-2728.217566468206</v>
       </c>
       <c r="O91">
-        <v>-381.8963851835258</v>
+        <v>-341.0271958085258</v>
       </c>
       <c r="P91">
-        <v>-2673.27469628468</v>
+        <v>-2387.19037065968</v>
       </c>
       <c r="Q91">
-        <v>-1415.07469628468</v>
+        <v>-1128.99037065968</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.405701109568196</v>
+        <v>0.4044192464024431</v>
       </c>
       <c r="T91">
-        <v>7.011866368353478</v>
+        <v>6.990156610035926</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04598430228389216</v>
+        <v>0.04932074333334745</v>
       </c>
       <c r="W91">
-        <v>0.2115402130545166</v>
+        <v>0.1965402130545166</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3678744182711373</v>
+        <v>0.3945659466667797</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2346572778376467</v>
+        <v>0.2210162728894139</v>
       </c>
       <c r="C92">
-        <v>-13784.93602371965</v>
+        <v>-13404.51754303565</v>
       </c>
       <c r="D92">
-        <v>4993.173976280355</v>
+        <v>5373.592456964347</v>
       </c>
       <c r="E92">
         <v>18982.41</v>
@@ -8837,37 +8837,37 @@
         <v>1778</v>
       </c>
       <c r="M92">
-        <v>4887.476374518411</v>
+        <v>4556.849224518411</v>
       </c>
       <c r="N92">
-        <v>-3109.476374518411</v>
+        <v>-2778.849224518411</v>
       </c>
       <c r="O92">
-        <v>-388.6845468148014</v>
+        <v>-347.3561530648013</v>
       </c>
       <c r="P92">
-        <v>-2720.79182770361</v>
+        <v>-2431.493071453609</v>
       </c>
       <c r="Q92">
-        <v>-1462.59182770361</v>
+        <v>-1173.293071453609</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4416912205250157</v>
+        <v>0.4402811710426874</v>
       </c>
       <c r="T92">
-        <v>7.713053005188826</v>
+        <v>7.689172271039518</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04547336559184891</v>
+        <v>0.04877273507408804</v>
       </c>
       <c r="W92">
-        <v>0.211653506427939</v>
+        <v>0.196653506427939</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3637869247347914</v>
+        <v>0.3901818805927043</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.236416644004272</v>
+        <v>0.2226256390560392</v>
       </c>
       <c r="C93">
-        <v>-14075.09399612256</v>
+        <v>-13697.37252118571</v>
       </c>
       <c r="D93">
-        <v>4947.925003877441</v>
+        <v>5325.646478814293</v>
       </c>
       <c r="E93">
         <v>19227.319</v>
@@ -8919,37 +8919,37 @@
         <v>1778</v>
       </c>
       <c r="M93">
-        <v>4941.781667568615</v>
+        <v>4607.480882568615</v>
       </c>
       <c r="N93">
-        <v>-3163.781667568615</v>
+        <v>-2829.480882568615</v>
       </c>
       <c r="O93">
-        <v>-395.4727084460769</v>
+        <v>-353.6851103210769</v>
       </c>
       <c r="P93">
-        <v>-2768.308959122538</v>
+        <v>-2475.795772247538</v>
       </c>
       <c r="Q93">
-        <v>-1510.108959122538</v>
+        <v>-1217.595772247538</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4856791339166842</v>
+        <v>0.4841124122696527</v>
       </c>
       <c r="T93">
-        <v>8.570058894654252</v>
+        <v>8.543524745599466</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04497365827765277</v>
+        <v>0.04823677095239477</v>
       </c>
       <c r="W93">
-        <v>0.2117643098371104</v>
+        <v>0.1967643098371104</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3597892662212222</v>
+        <v>0.3858941676191582</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2381760101708974</v>
+        <v>0.2242350052226646</v>
       </c>
       <c r="C94">
-        <v>-14364.43922631452</v>
+        <v>-13989.37946815484</v>
       </c>
       <c r="D94">
-        <v>4903.488773685483</v>
+        <v>5278.548531845157</v>
       </c>
       <c r="E94">
         <v>19472.228</v>
@@ -9001,37 +9001,37 @@
         <v>1778</v>
       </c>
       <c r="M94">
-        <v>4996.08696061882</v>
+        <v>4658.11254061882</v>
       </c>
       <c r="N94">
-        <v>-3218.08696061882</v>
+        <v>-2880.11254061882</v>
       </c>
       <c r="O94">
-        <v>-402.2608700773525</v>
+        <v>-360.0140675773525</v>
       </c>
       <c r="P94">
-        <v>-2815.826090541467</v>
+        <v>-2520.098473041468</v>
       </c>
       <c r="Q94">
-        <v>-1557.626090541467</v>
+        <v>-1261.898473041467</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5406640256562697</v>
+        <v>0.5389014638033596</v>
       </c>
       <c r="T94">
-        <v>9.641316256486036</v>
+        <v>9.611465338799404</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04448481416593916</v>
+        <v>0.04771245822465134</v>
       </c>
       <c r="W94">
-        <v>0.2118727044765172</v>
+        <v>0.1968727044765172</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3558785133275133</v>
+        <v>0.3816996657972107</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2399353763375227</v>
+        <v>0.2258443713892899</v>
       </c>
       <c r="C95">
-        <v>-14652.99341657123</v>
+        <v>-14280.5606856893</v>
       </c>
       <c r="D95">
-        <v>4859.843583428774</v>
+        <v>5232.276314310709</v>
       </c>
       <c r="E95">
         <v>19717.137</v>
@@ -9083,37 +9083,37 @@
         <v>1778</v>
       </c>
       <c r="M95">
-        <v>5050.392253669025</v>
+        <v>4708.744198669026</v>
       </c>
       <c r="N95">
-        <v>-3272.392253669025</v>
+        <v>-2930.744198669026</v>
       </c>
       <c r="O95">
-        <v>-409.0490317086281</v>
+        <v>-366.3430248336282</v>
       </c>
       <c r="P95">
-        <v>-2863.343221960397</v>
+        <v>-2564.401173835397</v>
       </c>
       <c r="Q95">
-        <v>-1605.143221960397</v>
+        <v>-1306.201173835397</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6113588864643084</v>
+        <v>0.6093445300609823</v>
       </c>
       <c r="T95">
-        <v>11.01864715026976</v>
+        <v>10.98453181577075</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04400648283082152</v>
+        <v>0.04719942103944003</v>
       </c>
       <c r="W95">
-        <v>0.2119787680484098</v>
+        <v>0.1969787680484099</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3520518626465722</v>
+        <v>0.3775953683155202</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2416947425041481</v>
+        <v>0.2274537375559152</v>
       </c>
       <c r="C96">
-        <v>-14940.77750331086</v>
+        <v>-14570.93770033454</v>
       </c>
       <c r="D96">
-        <v>4816.968496689141</v>
+        <v>5186.808299665459</v>
       </c>
       <c r="E96">
         <v>19962.046</v>
@@ -9165,37 +9165,37 @@
         <v>1778</v>
       </c>
       <c r="M96">
-        <v>5104.69754671923</v>
+        <v>4759.37585671923</v>
       </c>
       <c r="N96">
-        <v>-3326.69754671923</v>
+        <v>-2981.37585671923</v>
       </c>
       <c r="O96">
-        <v>-415.8371933399037</v>
+        <v>-372.6719820899037</v>
       </c>
       <c r="P96">
-        <v>-2910.860353379326</v>
+        <v>-2608.703874629326</v>
       </c>
       <c r="Q96">
-        <v>-1652.660353379326</v>
+        <v>-1350.503874629326</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7056187008750265</v>
+        <v>0.7032686184044795</v>
       </c>
       <c r="T96">
-        <v>12.85508834198139</v>
+        <v>12.81528711839921</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.04353832875815321</v>
+        <v>0.04669729953902045</v>
       </c>
       <c r="W96">
-        <v>0.2120825749485601</v>
+        <v>0.1970825749485601</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3483066300652257</v>
+        <v>0.3735783963121637</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2434541086707734</v>
+        <v>0.2290631037225405</v>
       </c>
       <c r="C97">
-        <v>-15227.81169058181</v>
+        <v>-14860.53129682729</v>
       </c>
       <c r="D97">
-        <v>4774.843309418196</v>
+        <v>5142.123703172711</v>
       </c>
       <c r="E97">
         <v>20206.955</v>
@@ -9247,37 +9247,37 @@
         <v>1778</v>
       </c>
       <c r="M97">
-        <v>5159.002839769434</v>
+        <v>4810.007514769434</v>
       </c>
       <c r="N97">
-        <v>-3381.002839769434</v>
+        <v>-3032.007514769434</v>
       </c>
       <c r="O97">
-        <v>-422.6253549711793</v>
+        <v>-379.0009393461793</v>
       </c>
       <c r="P97">
-        <v>-2958.377484798255</v>
+        <v>-2653.006575423255</v>
       </c>
       <c r="Q97">
-        <v>-1700.177484798255</v>
+        <v>-1394.806575423255</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8375824410500323</v>
+        <v>0.8347623420853757</v>
       </c>
       <c r="T97">
-        <v>15.42610601037767</v>
+        <v>15.37834454207906</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04308003056069896</v>
+        <v>0.04620574901755709</v>
       </c>
       <c r="W97">
-        <v>0.2121841964402861</v>
+        <v>0.1971841964402861</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3446402444855917</v>
+        <v>0.3696459921404567</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2452134748373987</v>
+        <v>0.2306724698891659</v>
       </c>
       <c r="C98">
-        <v>-15514.11548180854</v>
+        <v>-15149.3615497761</v>
       </c>
       <c r="D98">
-        <v>4733.44851819146</v>
+        <v>5098.202450223898</v>
       </c>
       <c r="E98">
         <v>20451.864</v>
@@ -9329,37 +9329,37 @@
         <v>1778</v>
       </c>
       <c r="M98">
-        <v>5213.308132819639</v>
+        <v>4860.639172819638</v>
       </c>
       <c r="N98">
-        <v>-3435.308132819639</v>
+        <v>-3082.639172819638</v>
       </c>
       <c r="O98">
-        <v>-429.4135166024548</v>
+        <v>-385.3298966024547</v>
       </c>
       <c r="P98">
-        <v>-3005.894616217184</v>
+        <v>-2697.309276217183</v>
       </c>
       <c r="Q98">
-        <v>-1747.694616217184</v>
+        <v>-1439.109276217183</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.035528051312538</v>
+        <v>1.032002927606718</v>
       </c>
       <c r="T98">
-        <v>19.28263251297205</v>
+        <v>19.22293067759878</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04263128024235835</v>
+        <v>0.04572443913195754</v>
       </c>
       <c r="W98">
-        <v>0.2122837008176013</v>
+        <v>0.1972837008176012</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3410502419388669</v>
+        <v>0.3657955130556604</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2469728410040241</v>
+        <v>0.2322818360557912</v>
       </c>
       <c r="C99">
-        <v>-15799.70770990036</v>
+        <v>-15437.44785373222</v>
       </c>
       <c r="D99">
-        <v>4692.765290099645</v>
+        <v>5055.025146267782</v>
       </c>
       <c r="E99">
         <v>20696.773</v>
@@ -9411,37 +9411,37 @@
         <v>1778</v>
       </c>
       <c r="M99">
-        <v>5267.613425869843</v>
+        <v>4911.270830869843</v>
       </c>
       <c r="N99">
-        <v>-3489.613425869843</v>
+        <v>-3133.270830869843</v>
       </c>
       <c r="O99">
-        <v>-436.2016782337304</v>
+        <v>-391.6588538587304</v>
       </c>
       <c r="P99">
-        <v>-3053.411747636113</v>
+        <v>-2741.611977011113</v>
       </c>
       <c r="Q99">
-        <v>-1795.211747636112</v>
+        <v>-1483.411977011113</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.365437401750051</v>
+        <v>1.360737236808957</v>
       </c>
       <c r="T99">
-        <v>25.71017668396273</v>
+        <v>25.63057423679837</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04219178250790105</v>
+        <v>0.04525305316152498</v>
       </c>
       <c r="W99">
-        <v>0.2123811535582706</v>
+        <v>0.1973811535582706</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3375342600632084</v>
+        <v>0.3620244252921999</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2487322071706494</v>
+        <v>0.2338912022224166</v>
       </c>
       <c r="C100">
-        <v>-16084.60656582067</v>
+        <v>-15724.80895174516</v>
       </c>
       <c r="D100">
-        <v>4652.775434179329</v>
+        <v>5012.57304825484</v>
       </c>
       <c r="E100">
         <v>20941.682</v>
@@ -9493,37 +9493,37 @@
         <v>1778</v>
       </c>
       <c r="M100">
-        <v>5321.918718920048</v>
+        <v>4961.902488920047</v>
       </c>
       <c r="N100">
-        <v>-3543.918718920048</v>
+        <v>-3183.902488920047</v>
       </c>
       <c r="O100">
-        <v>-442.989839865006</v>
+        <v>-397.9878111150059</v>
       </c>
       <c r="P100">
-        <v>-3100.928879055042</v>
+        <v>-2785.914677805041</v>
       </c>
       <c r="Q100">
-        <v>-1842.728879055042</v>
+        <v>-1527.714677805041</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.025256102625077</v>
+        <v>2.018205855213435</v>
       </c>
       <c r="T100">
-        <v>38.56526502594409</v>
+        <v>38.44586135519756</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.04176125411496328</v>
+        <v>0.04479128731293799</v>
       </c>
       <c r="W100">
-        <v>0.2124766174674978</v>
+        <v>0.1974766174674978</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3340900329197063</v>
+        <v>0.358330298503504</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2504915733372748</v>
+        <v>0.2355005683890419</v>
       </c>
       <c r="C101">
-        <v>-16368.82962570795</v>
+        <v>-16011.46296249147</v>
       </c>
       <c r="D101">
-        <v>4613.461374292056</v>
+        <v>4970.828037508532</v>
       </c>
       <c r="E101">
         <v>21186.591</v>
@@ -9575,37 +9575,37 @@
         <v>1778</v>
       </c>
       <c r="M101">
-        <v>5376.224011970253</v>
+        <v>5012.534146970252</v>
       </c>
       <c r="N101">
-        <v>-3598.224011970253</v>
+        <v>-3234.534146970252</v>
       </c>
       <c r="O101">
-        <v>-449.7780014962816</v>
+        <v>-404.3167683712815</v>
       </c>
       <c r="P101">
-        <v>-3148.446010473971</v>
+        <v>-2830.21737859897</v>
       </c>
       <c r="Q101">
-        <v>-1890.246010473971</v>
+        <v>-1572.01737859897</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.004712205250153</v>
+        <v>3.990611710426871</v>
       </c>
       <c r="T101">
-        <v>77.13053005188819</v>
+        <v>76.89172271039511</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.04133942326531719</v>
+        <v>0.04433885006735276</v>
       </c>
       <c r="W101">
-        <v>0.2125701528129022</v>
+        <v>0.1975701528129022</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3307153861225375</v>
+        <v>0.3547108005388222</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_air_transport.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08705920913303966</v>
+        <v>0.08704170551742052</v>
       </c>
       <c r="C2">
-        <v>24703.19865789174</v>
+        <v>24466.66855719447</v>
       </c>
       <c r="D2">
-        <v>21439.49865789174</v>
+        <v>21447.87755719446</v>
       </c>
       <c r="E2">
-        <v>-3059.4</v>
+        <v>-2814.491</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>244.909</v>
       </c>
       <c r="G2">
         <v>3263.7</v>
@@ -1457,28 +1457,28 @@
         <v>1778</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>13.77285355020457</v>
       </c>
       <c r="N2">
-        <v>1778</v>
+        <v>1764.227146449795</v>
       </c>
       <c r="O2">
-        <v>222.25</v>
+        <v>220.5283933062244</v>
       </c>
       <c r="P2">
-        <v>1555.75</v>
+        <v>1543.698753143571</v>
       </c>
       <c r="Q2">
-        <v>2813.95</v>
+        <v>2801.898753143571</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08705920913303966</v>
+        <v>0.08742387386022561</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8113267760114715</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>129.094525946919</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08704170551742052</v>
+        <v>0.08702420190180139</v>
       </c>
       <c r="C3">
-        <v>24466.66855719447</v>
+        <v>24230.1450082737</v>
       </c>
       <c r="D3">
-        <v>21447.87755719446</v>
+        <v>21456.26300827369</v>
       </c>
       <c r="E3">
-        <v>-2814.491</v>
+        <v>-2569.582</v>
       </c>
       <c r="F3">
-        <v>244.909</v>
+        <v>489.818</v>
       </c>
       <c r="G3">
         <v>3263.7</v>
@@ -1539,28 +1539,28 @@
         <v>1778</v>
       </c>
       <c r="M3">
-        <v>13.77285355020457</v>
+        <v>27.54570710040913</v>
       </c>
       <c r="N3">
-        <v>1764.227146449795</v>
+        <v>1750.454292899591</v>
       </c>
       <c r="O3">
-        <v>220.5283933062244</v>
+        <v>218.8067866124488</v>
       </c>
       <c r="P3">
-        <v>1543.698753143571</v>
+        <v>1531.647506287142</v>
       </c>
       <c r="Q3">
-        <v>2801.898753143571</v>
+        <v>2789.847506287142</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08742387386022561</v>
+        <v>0.08779598072470107</v>
       </c>
       <c r="T3">
-        <v>0.8113267760114715</v>
+        <v>0.8185798314022409</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.094525946919</v>
+        <v>64.54726297345954</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08702420190180139</v>
+        <v>0.08700669828618227</v>
       </c>
       <c r="C4">
-        <v>24230.1450082737</v>
+        <v>23993.62801881706</v>
       </c>
       <c r="D4">
-        <v>21456.26300827369</v>
+        <v>21464.65501881706</v>
       </c>
       <c r="E4">
-        <v>-2569.582</v>
+        <v>-2324.673</v>
       </c>
       <c r="F4">
-        <v>489.818</v>
+        <v>734.727</v>
       </c>
       <c r="G4">
         <v>3263.7</v>
@@ -1621,28 +1621,28 @@
         <v>1778</v>
       </c>
       <c r="M4">
-        <v>27.54570710040913</v>
+        <v>41.31856065061369</v>
       </c>
       <c r="N4">
-        <v>1750.454292899591</v>
+        <v>1736.681439349386</v>
       </c>
       <c r="O4">
-        <v>218.8067866124488</v>
+        <v>217.0851799186732</v>
       </c>
       <c r="P4">
-        <v>1531.647506287142</v>
+        <v>1519.596259430713</v>
       </c>
       <c r="Q4">
-        <v>2789.847506287142</v>
+        <v>2777.796259430713</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08779598072470107</v>
+        <v>0.08817575989566057</v>
       </c>
       <c r="T4">
-        <v>0.8185798314022409</v>
+        <v>0.8259824343268407</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.54726297345954</v>
+        <v>43.03150864897303</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08700669828618227</v>
+        <v>0.08698919467056315</v>
       </c>
       <c r="C5">
-        <v>23993.62801881706</v>
+        <v>23757.11759652422</v>
       </c>
       <c r="D5">
-        <v>21464.65501881706</v>
+        <v>21473.05359652422</v>
       </c>
       <c r="E5">
-        <v>-2324.673</v>
+        <v>-2079.764</v>
       </c>
       <c r="F5">
-        <v>734.727</v>
+        <v>979.6360000000001</v>
       </c>
       <c r="G5">
         <v>3263.7</v>
@@ -1703,28 +1703,28 @@
         <v>1778</v>
       </c>
       <c r="M5">
-        <v>41.31856065061369</v>
+        <v>55.09141420081826</v>
       </c>
       <c r="N5">
-        <v>1736.681439349386</v>
+        <v>1722.908585799182</v>
       </c>
       <c r="O5">
-        <v>217.0851799186732</v>
+        <v>215.3635732248977</v>
       </c>
       <c r="P5">
-        <v>1519.596259430713</v>
+        <v>1507.545012574284</v>
       </c>
       <c r="Q5">
-        <v>2777.796259430713</v>
+        <v>2765.745012574284</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08817575989566057</v>
+        <v>0.08856345113268173</v>
       </c>
       <c r="T5">
-        <v>0.8259824343268407</v>
+        <v>0.833539258145703</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.03150864897303</v>
+        <v>32.27363148672977</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08698919467056315</v>
+        <v>0.08697169105494401</v>
       </c>
       <c r="C6">
-        <v>23757.11759652422</v>
+        <v>23520.61374910689</v>
       </c>
       <c r="D6">
-        <v>21473.05359652422</v>
+        <v>21481.4587491069</v>
       </c>
       <c r="E6">
-        <v>-2079.764</v>
+        <v>-1834.855</v>
       </c>
       <c r="F6">
-        <v>979.6360000000001</v>
+        <v>1224.545</v>
       </c>
       <c r="G6">
         <v>3263.7</v>
@@ -1785,28 +1785,28 @@
         <v>1778</v>
       </c>
       <c r="M6">
-        <v>55.09141420081826</v>
+        <v>68.86426775102282</v>
       </c>
       <c r="N6">
-        <v>1722.908585799182</v>
+        <v>1709.135732248977</v>
       </c>
       <c r="O6">
-        <v>215.3635732248977</v>
+        <v>213.6419665311221</v>
       </c>
       <c r="P6">
-        <v>1507.545012574284</v>
+        <v>1495.493765717855</v>
       </c>
       <c r="Q6">
-        <v>2765.745012574284</v>
+        <v>2753.693765717855</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08856345113268173</v>
+        <v>0.08895930429048227</v>
       </c>
       <c r="T6">
-        <v>0.833539258145703</v>
+        <v>0.8412551729923308</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.27363148672977</v>
+        <v>25.81890518938382</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08697169105494401</v>
+        <v>0.0869541874393249</v>
       </c>
       <c r="C7">
-        <v>23520.61374910689</v>
+        <v>23284.11648428886</v>
       </c>
       <c r="D7">
-        <v>21481.4587491069</v>
+        <v>21489.87048428886</v>
       </c>
       <c r="E7">
-        <v>-1834.855</v>
+        <v>-1589.946</v>
       </c>
       <c r="F7">
-        <v>1224.545</v>
+        <v>1469.454</v>
       </c>
       <c r="G7">
         <v>3263.7</v>
@@ -1867,28 +1867,28 @@
         <v>1778</v>
       </c>
       <c r="M7">
-        <v>68.86426775102282</v>
+        <v>82.6371213012274</v>
       </c>
       <c r="N7">
-        <v>1709.135732248977</v>
+        <v>1695.362878698772</v>
       </c>
       <c r="O7">
-        <v>213.6419665311221</v>
+        <v>211.9203598373466</v>
       </c>
       <c r="P7">
-        <v>1495.493765717855</v>
+        <v>1483.442518861426</v>
       </c>
       <c r="Q7">
-        <v>2753.693765717855</v>
+        <v>2741.642518861426</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08895930429048227</v>
+        <v>0.0893635798558956</v>
       </c>
       <c r="T7">
-        <v>0.8412551729923308</v>
+        <v>0.8491352562399507</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.81890518938382</v>
+        <v>21.51575432448651</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0869541874393249</v>
+        <v>0.08693668382370578</v>
       </c>
       <c r="C8">
-        <v>23284.11648428886</v>
+        <v>23047.62580980603</v>
       </c>
       <c r="D8">
-        <v>21489.87048428886</v>
+        <v>21498.28880980603</v>
       </c>
       <c r="E8">
-        <v>-1589.946</v>
+        <v>-1345.037</v>
       </c>
       <c r="F8">
-        <v>1469.454</v>
+        <v>1714.363</v>
       </c>
       <c r="G8">
         <v>3263.7</v>
@@ -1949,28 +1949,28 @@
         <v>1778</v>
       </c>
       <c r="M8">
-        <v>82.63712130122738</v>
+        <v>96.40997485143194</v>
       </c>
       <c r="N8">
-        <v>1695.362878698772</v>
+        <v>1681.590025148568</v>
       </c>
       <c r="O8">
-        <v>211.9203598373466</v>
+        <v>210.198753143571</v>
       </c>
       <c r="P8">
-        <v>1483.442518861426</v>
+        <v>1471.391272004997</v>
       </c>
       <c r="Q8">
-        <v>2741.642518861426</v>
+        <v>2729.591272004997</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0893635798558956</v>
+        <v>0.08977654951948985</v>
       </c>
       <c r="T8">
-        <v>0.8491352562399507</v>
+        <v>0.8571848036434333</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.51575432448652</v>
+        <v>18.44207513527416</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08693668382370577</v>
+        <v>0.08691918020808666</v>
       </c>
       <c r="C9">
-        <v>23047.62580980603</v>
+        <v>22811.14173340642</v>
       </c>
       <c r="D9">
-        <v>21498.28880980603</v>
+        <v>21506.71373340642</v>
       </c>
       <c r="E9">
-        <v>-1345.037</v>
+        <v>-1100.128</v>
       </c>
       <c r="F9">
-        <v>1714.363</v>
+        <v>1959.272</v>
       </c>
       <c r="G9">
         <v>3263.7</v>
@@ -2031,28 +2031,28 @@
         <v>1778</v>
       </c>
       <c r="M9">
-        <v>96.40997485143197</v>
+        <v>110.1828284016365</v>
       </c>
       <c r="N9">
-        <v>1681.590025148568</v>
+        <v>1667.817171598363</v>
       </c>
       <c r="O9">
-        <v>210.198753143571</v>
+        <v>208.4771464497954</v>
       </c>
       <c r="P9">
-        <v>1471.391272004997</v>
+        <v>1459.340025148568</v>
       </c>
       <c r="Q9">
-        <v>2729.591272004997</v>
+        <v>2717.540025148568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08977654951948985</v>
+        <v>0.09019849678446659</v>
       </c>
       <c r="T9">
-        <v>0.8571848036434333</v>
+        <v>0.8654093412078613</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.44207513527415</v>
+        <v>16.13681574336488</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08691918020808666</v>
+        <v>0.08690167659246752</v>
       </c>
       <c r="C10">
-        <v>22811.14173340642</v>
+        <v>22574.66426285021</v>
       </c>
       <c r="D10">
-        <v>21506.71373340642</v>
+        <v>21515.14526285021</v>
       </c>
       <c r="E10">
-        <v>-1100.128</v>
+        <v>-855.2190000000001</v>
       </c>
       <c r="F10">
-        <v>1959.272</v>
+        <v>2204.181</v>
       </c>
       <c r="G10">
         <v>3263.7</v>
@@ -2113,28 +2113,28 @@
         <v>1778</v>
       </c>
       <c r="M10">
-        <v>110.1828284016365</v>
+        <v>123.9556819518411</v>
       </c>
       <c r="N10">
-        <v>1667.817171598363</v>
+        <v>1654.044318048159</v>
       </c>
       <c r="O10">
-        <v>208.4771464497954</v>
+        <v>206.7555397560198</v>
       </c>
       <c r="P10">
-        <v>1459.340025148568</v>
+        <v>1447.288778292139</v>
       </c>
       <c r="Q10">
-        <v>2717.540025148568</v>
+        <v>2705.488778292139</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09019849678446659</v>
+        <v>0.09062971761570654</v>
       </c>
       <c r="T10">
-        <v>0.8654093412078613</v>
+        <v>0.8738146378396391</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.13681574336488</v>
+        <v>14.34383621632434</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08690167659246752</v>
+        <v>0.0868841729768484</v>
       </c>
       <c r="C11">
-        <v>22574.66426285021</v>
+        <v>22338.19340590973</v>
       </c>
       <c r="D11">
-        <v>21515.14526285021</v>
+        <v>21523.58340590973</v>
       </c>
       <c r="E11">
-        <v>-855.2190000000001</v>
+        <v>-610.3099999999999</v>
       </c>
       <c r="F11">
-        <v>2204.181</v>
+        <v>2449.09</v>
       </c>
       <c r="G11">
         <v>3263.7</v>
@@ -2195,28 +2195,28 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>123.9556819518411</v>
+        <v>137.7285355020456</v>
       </c>
       <c r="N11">
-        <v>1654.044318048159</v>
+        <v>1640.271464497954</v>
       </c>
       <c r="O11">
-        <v>206.7555397560198</v>
+        <v>205.0339330622443</v>
       </c>
       <c r="P11">
-        <v>1447.288778292139</v>
+        <v>1435.23753143571</v>
       </c>
       <c r="Q11">
-        <v>2705.488778292139</v>
+        <v>2693.43753143571</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09062971761570654</v>
+        <v>0.09107052113208519</v>
       </c>
       <c r="T11">
-        <v>0.8738146378396391</v>
+        <v>0.8824067188410123</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.34383621632434</v>
+        <v>12.90945259469191</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0868841729768484</v>
+        <v>0.08686666936122928</v>
       </c>
       <c r="C12">
-        <v>22338.19340590973</v>
+        <v>22101.72917036953</v>
       </c>
       <c r="D12">
-        <v>21523.58340590973</v>
+        <v>21532.02817036953</v>
       </c>
       <c r="E12">
-        <v>-610.3099999999999</v>
+        <v>-365.4009999999998</v>
       </c>
       <c r="F12">
-        <v>2449.09</v>
+        <v>2693.999</v>
       </c>
       <c r="G12">
         <v>3263.7</v>
@@ -2277,28 +2277,28 @@
         <v>1778</v>
       </c>
       <c r="M12">
-        <v>137.7285355020456</v>
+        <v>151.5013890522502</v>
       </c>
       <c r="N12">
-        <v>1640.271464497954</v>
+        <v>1626.49861094775</v>
       </c>
       <c r="O12">
-        <v>205.0339330622443</v>
+        <v>203.3123263684687</v>
       </c>
       <c r="P12">
-        <v>1435.23753143571</v>
+        <v>1423.186284579281</v>
       </c>
       <c r="Q12">
-        <v>2693.43753143571</v>
+        <v>2681.386284579281</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09107052113208519</v>
+        <v>0.09152123034546109</v>
       </c>
       <c r="T12">
-        <v>0.8824067188410123</v>
+        <v>0.8911918803143263</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.90945259469191</v>
+        <v>11.73586599517446</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08686666936122928</v>
+        <v>0.08684916574561015</v>
       </c>
       <c r="C13">
-        <v>22101.72917036953</v>
+        <v>21865.27156402639</v>
       </c>
       <c r="D13">
-        <v>21532.02817036953</v>
+        <v>21540.47956402638</v>
       </c>
       <c r="E13">
-        <v>-365.4009999999998</v>
+        <v>-120.4920000000002</v>
       </c>
       <c r="F13">
-        <v>2693.999</v>
+        <v>2938.908</v>
       </c>
       <c r="G13">
         <v>3263.7</v>
@@ -2359,28 +2359,28 @@
         <v>1778</v>
       </c>
       <c r="M13">
-        <v>151.5013890522502</v>
+        <v>165.2742426024548</v>
       </c>
       <c r="N13">
-        <v>1626.49861094775</v>
+        <v>1612.725757397545</v>
       </c>
       <c r="O13">
-        <v>203.3123263684687</v>
+        <v>201.5907196746931</v>
       </c>
       <c r="P13">
-        <v>1423.186284579281</v>
+        <v>1411.135037722852</v>
       </c>
       <c r="Q13">
-        <v>2681.386284579281</v>
+        <v>2669.335037722852</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09152123034546109</v>
+        <v>0.09198218295005008</v>
       </c>
       <c r="T13">
-        <v>0.8911918803143263</v>
+        <v>0.9001767045483975</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.73586599517446</v>
+        <v>10.75787716224326</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08684916574561015</v>
+        <v>0.08683166212999102</v>
       </c>
       <c r="C14">
-        <v>21865.27156402639</v>
+        <v>21628.8205946893</v>
       </c>
       <c r="D14">
-        <v>21540.47956402638</v>
+        <v>21548.93759468929</v>
       </c>
       <c r="E14">
-        <v>-120.4920000000002</v>
+        <v>124.4170000000004</v>
       </c>
       <c r="F14">
-        <v>2938.908</v>
+        <v>3183.817</v>
       </c>
       <c r="G14">
         <v>3263.7</v>
@@ -2441,28 +2441,28 @@
         <v>1778</v>
       </c>
       <c r="M14">
-        <v>165.2742426024548</v>
+        <v>179.0470961526593</v>
       </c>
       <c r="N14">
-        <v>1612.725757397545</v>
+        <v>1598.95290384734</v>
       </c>
       <c r="O14">
-        <v>201.5907196746931</v>
+        <v>199.8691129809175</v>
       </c>
       <c r="P14">
-        <v>1411.135037722852</v>
+        <v>1399.083790866423</v>
       </c>
       <c r="Q14">
-        <v>2669.335037722852</v>
+        <v>2657.283790866423</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09198218295005008</v>
+        <v>0.09245373216623881</v>
       </c>
       <c r="T14">
-        <v>0.9001767045483975</v>
+        <v>0.9093680764660105</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.75787716224326</v>
+        <v>9.930348149763006</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08683166212999102</v>
+        <v>0.08681415851437188</v>
       </c>
       <c r="C15">
-        <v>21628.8205946893</v>
+        <v>21392.37627017956</v>
       </c>
       <c r="D15">
-        <v>21548.93759468929</v>
+        <v>21557.40227017955</v>
       </c>
       <c r="E15">
-        <v>124.4170000000004</v>
+        <v>369.3260000000005</v>
       </c>
       <c r="F15">
-        <v>3183.817</v>
+        <v>3428.726000000001</v>
       </c>
       <c r="G15">
         <v>3263.7</v>
@@ -2523,28 +2523,28 @@
         <v>1778</v>
       </c>
       <c r="M15">
-        <v>179.0470961526593</v>
+        <v>192.8199497028639</v>
       </c>
       <c r="N15">
-        <v>1598.95290384734</v>
+        <v>1585.180050297136</v>
       </c>
       <c r="O15">
-        <v>199.8691129809175</v>
+        <v>198.147506287142</v>
       </c>
       <c r="P15">
-        <v>1399.083790866423</v>
+        <v>1387.032544009994</v>
       </c>
       <c r="Q15">
-        <v>2657.283790866423</v>
+        <v>2645.232544009994</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09245373216623881</v>
+        <v>0.09293624764326915</v>
       </c>
       <c r="T15">
-        <v>0.9093680764660105</v>
+        <v>0.9187732012189168</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.930348149763006</v>
+        <v>9.221037567637076</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08681415851437188</v>
+        <v>0.08699352989875277</v>
       </c>
       <c r="C16">
-        <v>21392.37627017956</v>
+        <v>21061.03785684442</v>
       </c>
       <c r="D16">
-        <v>21557.40227017955</v>
+        <v>21470.97285684442</v>
       </c>
       <c r="E16">
-        <v>369.3260000000005</v>
+        <v>614.2350000000006</v>
       </c>
       <c r="F16">
-        <v>3428.726000000001</v>
+        <v>3673.635000000001</v>
       </c>
       <c r="G16">
         <v>3263.7</v>
@@ -2605,45 +2605,45 @@
         <v>1778</v>
       </c>
       <c r="M16">
-        <v>192.8199497028639</v>
+        <v>212.1032557530685</v>
       </c>
       <c r="N16">
-        <v>1585.180050297136</v>
+        <v>1565.896744246931</v>
       </c>
       <c r="O16">
-        <v>198.147506287142</v>
+        <v>195.7370930308664</v>
       </c>
       <c r="P16">
-        <v>1387.032544009994</v>
+        <v>1370.159651216065</v>
       </c>
       <c r="Q16">
-        <v>2645.232544009994</v>
+        <v>2628.359651216065</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09293624764326915</v>
+        <v>0.09343011642564136</v>
       </c>
       <c r="T16">
-        <v>0.9187732012189168</v>
+        <v>0.9283996230248327</v>
       </c>
       <c r="U16">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.221037567637076</v>
+        <v>8.382709608521781</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08699352989875277</v>
+        <v>0.08698915128313364</v>
       </c>
       <c r="C17">
-        <v>21061.03785684442</v>
+        <v>20818.23042282876</v>
       </c>
       <c r="D17">
-        <v>21470.97285684442</v>
+        <v>21473.07442282876</v>
       </c>
       <c r="E17">
-        <v>614.2350000000001</v>
+        <v>859.1440000000002</v>
       </c>
       <c r="F17">
-        <v>3673.635</v>
+        <v>3918.544</v>
       </c>
       <c r="G17">
         <v>3263.7</v>
@@ -2687,28 +2687,28 @@
         <v>1778</v>
       </c>
       <c r="M17">
-        <v>212.1032557530685</v>
+        <v>226.243472803273</v>
       </c>
       <c r="N17">
-        <v>1565.896744246931</v>
+        <v>1551.756527196727</v>
       </c>
       <c r="O17">
-        <v>195.7370930308664</v>
+        <v>193.9695658995908</v>
       </c>
       <c r="P17">
-        <v>1370.159651216065</v>
+        <v>1357.786961297136</v>
       </c>
       <c r="Q17">
-        <v>2628.359651216065</v>
+        <v>2615.986961297136</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09343011642564136</v>
+        <v>0.09393574398854627</v>
       </c>
       <c r="T17">
-        <v>0.9283996230248326</v>
+        <v>0.9382552453499371</v>
       </c>
       <c r="U17">
         <v>0.05773661666253409</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.382709608521782</v>
+        <v>7.85879025798917</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08698915128313364</v>
+        <v>0.08698477266751452</v>
       </c>
       <c r="C18">
-        <v>20818.23042282876</v>
+        <v>20575.42340025341</v>
       </c>
       <c r="D18">
-        <v>21473.07442282876</v>
+        <v>21475.17640025341</v>
       </c>
       <c r="E18">
-        <v>859.1440000000002</v>
+        <v>1104.053</v>
       </c>
       <c r="F18">
-        <v>3918.544</v>
+        <v>4163.453</v>
       </c>
       <c r="G18">
         <v>3263.7</v>
@@ -2769,28 +2769,28 @@
         <v>1778</v>
       </c>
       <c r="M18">
-        <v>226.243472803273</v>
+        <v>240.3836898534776</v>
       </c>
       <c r="N18">
-        <v>1551.756527196727</v>
+        <v>1537.616310146522</v>
       </c>
       <c r="O18">
-        <v>193.9695658995908</v>
+        <v>192.2020387683153</v>
       </c>
       <c r="P18">
-        <v>1357.786961297136</v>
+        <v>1345.414271378207</v>
       </c>
       <c r="Q18">
-        <v>2615.986961297136</v>
+        <v>2603.614271378207</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09393574398854627</v>
+        <v>0.09445355534814767</v>
       </c>
       <c r="T18">
-        <v>0.9382552453499371</v>
+        <v>0.9483483525503451</v>
       </c>
       <c r="U18">
         <v>0.05773661666253409</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.85879025798917</v>
+        <v>7.396508478107454</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08698477266751452</v>
+        <v>0.08698039405189539</v>
       </c>
       <c r="C19">
-        <v>20575.42340025341</v>
+        <v>20332.61678923921</v>
       </c>
       <c r="D19">
-        <v>21475.17640025341</v>
+        <v>21477.27878923921</v>
       </c>
       <c r="E19">
-        <v>1104.053</v>
+        <v>1348.962000000001</v>
       </c>
       <c r="F19">
-        <v>4163.453</v>
+        <v>4408.362000000001</v>
       </c>
       <c r="G19">
         <v>3263.7</v>
@@ -2851,28 +2851,28 @@
         <v>1778</v>
       </c>
       <c r="M19">
-        <v>240.3836898534776</v>
+        <v>254.5239069036822</v>
       </c>
       <c r="N19">
-        <v>1537.616310146522</v>
+        <v>1523.476093096318</v>
       </c>
       <c r="O19">
-        <v>192.2020387683153</v>
+        <v>190.4345116370397</v>
       </c>
       <c r="P19">
-        <v>1345.414271378207</v>
+        <v>1333.041581459278</v>
       </c>
       <c r="Q19">
-        <v>2603.614271378207</v>
+        <v>2591.241581459278</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09445355534814767</v>
+        <v>0.0949839962531052</v>
       </c>
       <c r="T19">
-        <v>0.9483483525503451</v>
+        <v>0.9586876330971047</v>
       </c>
       <c r="U19">
         <v>0.05773661666253409</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.396508478107454</v>
+        <v>6.985591340434817</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08698039405189539</v>
+        <v>0.08725864043627626</v>
       </c>
       <c r="C20">
-        <v>20332.61678923921</v>
+        <v>19954.92100190802</v>
       </c>
       <c r="D20">
-        <v>21477.27878923921</v>
+        <v>21344.49200190802</v>
       </c>
       <c r="E20">
-        <v>1348.962</v>
+        <v>1593.871000000001</v>
       </c>
       <c r="F20">
-        <v>4408.362</v>
+        <v>4653.271000000001</v>
       </c>
       <c r="G20">
         <v>3263.7</v>
@@ -2933,45 +2933,45 @@
         <v>1778</v>
       </c>
       <c r="M20">
-        <v>254.5239069036821</v>
+        <v>276.5746846538867</v>
       </c>
       <c r="N20">
-        <v>1523.476093096318</v>
+        <v>1501.425315346113</v>
       </c>
       <c r="O20">
-        <v>190.4345116370397</v>
+        <v>187.6781644182641</v>
       </c>
       <c r="P20">
-        <v>1333.041581459278</v>
+        <v>1313.747150927849</v>
       </c>
       <c r="Q20">
-        <v>2591.241581459278</v>
+        <v>2571.947150927849</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0949839962531052</v>
+        <v>0.09552753446435798</v>
       </c>
       <c r="T20">
-        <v>0.9586876330971047</v>
+        <v>0.9692822045215619</v>
       </c>
       <c r="U20">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.985591340434818</v>
+        <v>6.428643323683216</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08725864043627626</v>
+        <v>0.08726913682065715</v>
       </c>
       <c r="C21">
-        <v>19954.92100190802</v>
+        <v>19705.03497086322</v>
       </c>
       <c r="D21">
-        <v>21344.49200190802</v>
+        <v>21339.51497086322</v>
       </c>
       <c r="E21">
-        <v>1593.871000000001</v>
+        <v>1838.78</v>
       </c>
       <c r="F21">
-        <v>4653.271000000001</v>
+        <v>4898.18</v>
       </c>
       <c r="G21">
         <v>3263.7</v>
@@ -3015,28 +3015,28 @@
         <v>1778</v>
       </c>
       <c r="M21">
-        <v>276.5746846538867</v>
+        <v>291.1312470040913</v>
       </c>
       <c r="N21">
-        <v>1501.425315346113</v>
+        <v>1486.868752995908</v>
       </c>
       <c r="O21">
-        <v>187.6781644182641</v>
+        <v>185.8585941244885</v>
       </c>
       <c r="P21">
-        <v>1313.747150927849</v>
+        <v>1301.01015887142</v>
       </c>
       <c r="Q21">
-        <v>2571.947150927849</v>
+        <v>2559.21015887142</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09552753446435798</v>
+        <v>0.09608466113089209</v>
       </c>
       <c r="T21">
-        <v>0.9692822045215619</v>
+        <v>0.9801416402316306</v>
       </c>
       <c r="U21">
         <v>0.05943661666253409</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.428643323683216</v>
+        <v>6.107211157499055</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08726913682065715</v>
+        <v>0.08727963320503802</v>
       </c>
       <c r="C22">
-        <v>19705.03497086322</v>
+        <v>19455.15126032936</v>
       </c>
       <c r="D22">
-        <v>21339.51497086322</v>
+        <v>21334.54026032936</v>
       </c>
       <c r="E22">
-        <v>1838.78</v>
+        <v>2083.689000000001</v>
       </c>
       <c r="F22">
-        <v>4898.18</v>
+        <v>5143.089000000001</v>
       </c>
       <c r="G22">
         <v>3263.7</v>
@@ -3097,28 +3097,28 @@
         <v>1778</v>
       </c>
       <c r="M22">
-        <v>291.1312470040913</v>
+        <v>305.6878093542958</v>
       </c>
       <c r="N22">
-        <v>1486.868752995908</v>
+        <v>1472.312190645704</v>
       </c>
       <c r="O22">
-        <v>185.8585941244885</v>
+        <v>184.039023830713</v>
       </c>
       <c r="P22">
-        <v>1301.01015887142</v>
+        <v>1288.273166814991</v>
       </c>
       <c r="Q22">
-        <v>2559.21015887142</v>
+        <v>2546.473166814991</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09608466113089209</v>
+        <v>0.09665589226999668</v>
       </c>
       <c r="T22">
-        <v>0.9801416402316306</v>
+        <v>0.9912759983647392</v>
       </c>
       <c r="U22">
         <v>0.05943661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.107211157499055</v>
+        <v>5.81639157857053</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08727963320503801</v>
+        <v>0.08744412958941888</v>
       </c>
       <c r="C23">
-        <v>19455.15126032936</v>
+        <v>19132.58189659754</v>
       </c>
       <c r="D23">
-        <v>21334.54026032936</v>
+        <v>21256.87989659754</v>
       </c>
       <c r="E23">
-        <v>2083.689</v>
+        <v>2328.598</v>
       </c>
       <c r="F23">
-        <v>5143.089</v>
+        <v>5387.998000000001</v>
       </c>
       <c r="G23">
         <v>3263.7</v>
@@ -3179,45 +3179,45 @@
         <v>1778</v>
       </c>
       <c r="M23">
-        <v>305.6878093542958</v>
+        <v>324.5547701045004</v>
       </c>
       <c r="N23">
-        <v>1472.312190645704</v>
+        <v>1453.445229895499</v>
       </c>
       <c r="O23">
-        <v>184.039023830713</v>
+        <v>181.6806537369374</v>
       </c>
       <c r="P23">
-        <v>1288.273166814991</v>
+        <v>1271.764576158562</v>
       </c>
       <c r="Q23">
-        <v>2546.473166814991</v>
+        <v>2529.964576158562</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09665589226999666</v>
+        <v>0.09724177036138598</v>
       </c>
       <c r="T23">
-        <v>0.991275998364739</v>
+        <v>1.002695852860235</v>
       </c>
       <c r="U23">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.81639157857053</v>
+        <v>5.478274127437776</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08744412958941888</v>
+        <v>0.08746162597379975</v>
       </c>
       <c r="C24">
-        <v>19132.58189659754</v>
+        <v>18879.44593463692</v>
       </c>
       <c r="D24">
-        <v>21256.87989659754</v>
+        <v>21248.65293463692</v>
       </c>
       <c r="E24">
-        <v>2328.598</v>
+        <v>2573.507</v>
       </c>
       <c r="F24">
-        <v>5387.998000000001</v>
+        <v>5632.907</v>
       </c>
       <c r="G24">
         <v>3263.7</v>
@@ -3261,28 +3261,28 @@
         <v>1778</v>
       </c>
       <c r="M24">
-        <v>324.5547701045004</v>
+        <v>339.307259654705</v>
       </c>
       <c r="N24">
-        <v>1453.445229895499</v>
+        <v>1438.692740345295</v>
       </c>
       <c r="O24">
-        <v>181.6806537369374</v>
+        <v>179.8365925431619</v>
       </c>
       <c r="P24">
-        <v>1271.764576158562</v>
+        <v>1258.856147802133</v>
       </c>
       <c r="Q24">
-        <v>2529.964576158562</v>
+        <v>2517.056147802133</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09724177036138598</v>
+        <v>0.09784286606553866</v>
       </c>
       <c r="T24">
-        <v>1.002695852860235</v>
+        <v>1.014412326953016</v>
       </c>
       <c r="U24">
         <v>0.0602366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.478274127437776</v>
+        <v>5.240088295810046</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08746162597379975</v>
+        <v>0.08747912235818063</v>
       </c>
       <c r="C25">
-        <v>18879.44593463692</v>
+        <v>18626.31633830648</v>
       </c>
       <c r="D25">
-        <v>21248.65293463692</v>
+        <v>21240.43233830648</v>
       </c>
       <c r="E25">
-        <v>2573.507</v>
+        <v>2818.416000000001</v>
       </c>
       <c r="F25">
-        <v>5632.907</v>
+        <v>5877.816000000001</v>
       </c>
       <c r="G25">
         <v>3263.7</v>
@@ -3343,28 +3343,28 @@
         <v>1778</v>
       </c>
       <c r="M25">
-        <v>339.307259654705</v>
+        <v>354.0597492049096</v>
       </c>
       <c r="N25">
-        <v>1438.692740345295</v>
+        <v>1423.94025079509</v>
       </c>
       <c r="O25">
-        <v>179.8365925431619</v>
+        <v>177.9925313493863</v>
       </c>
       <c r="P25">
-        <v>1258.856147802133</v>
+        <v>1245.947719445704</v>
       </c>
       <c r="Q25">
-        <v>2517.056147802133</v>
+        <v>2504.147719445704</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09784286606553866</v>
+        <v>0.09845978007769536</v>
       </c>
       <c r="T25">
-        <v>1.014412326953016</v>
+        <v>1.026437129311397</v>
       </c>
       <c r="U25">
         <v>0.0602366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.240088295810046</v>
+        <v>5.021751283484627</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08747912235818062</v>
+        <v>0.08749661874256151</v>
       </c>
       <c r="C26">
-        <v>18626.31633830649</v>
+        <v>18373.19310022096</v>
       </c>
       <c r="D26">
-        <v>21240.43233830649</v>
+        <v>21232.21810022096</v>
       </c>
       <c r="E26">
-        <v>2818.416</v>
+        <v>3063.325</v>
       </c>
       <c r="F26">
-        <v>5877.816</v>
+        <v>6122.725</v>
       </c>
       <c r="G26">
         <v>3263.7</v>
@@ -3425,28 +3425,28 @@
         <v>1778</v>
       </c>
       <c r="M26">
-        <v>354.0597492049095</v>
+        <v>368.8122387551141</v>
       </c>
       <c r="N26">
-        <v>1423.94025079509</v>
+        <v>1409.187761244886</v>
       </c>
       <c r="O26">
-        <v>177.9925313493863</v>
+        <v>176.1484701556107</v>
       </c>
       <c r="P26">
-        <v>1245.947719445704</v>
+        <v>1233.039291089275</v>
       </c>
       <c r="Q26">
-        <v>2504.147719445704</v>
+        <v>2491.239291089275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09845978007769535</v>
+        <v>0.09909314513017622</v>
       </c>
       <c r="T26">
-        <v>1.026437129311397</v>
+        <v>1.038782593066002</v>
       </c>
       <c r="U26">
         <v>0.0602366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.021751283484628</v>
+        <v>4.820881232145243</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08749661874256151</v>
+        <v>0.08751411512694239</v>
       </c>
       <c r="C27">
-        <v>18373.19310022096</v>
+        <v>18120.07621300649</v>
       </c>
       <c r="D27">
-        <v>21232.21810022096</v>
+        <v>21224.0102130065</v>
       </c>
       <c r="E27">
-        <v>3063.325</v>
+        <v>3308.234000000001</v>
       </c>
       <c r="F27">
-        <v>6122.725</v>
+        <v>6367.634000000001</v>
       </c>
       <c r="G27">
         <v>3263.7</v>
@@ -3507,28 +3507,28 @@
         <v>1778</v>
       </c>
       <c r="M27">
-        <v>368.8122387551141</v>
+        <v>383.5647283053187</v>
       </c>
       <c r="N27">
-        <v>1409.187761244886</v>
+        <v>1394.435271694681</v>
       </c>
       <c r="O27">
-        <v>176.1484701556107</v>
+        <v>174.3044089618351</v>
       </c>
       <c r="P27">
-        <v>1233.039291089275</v>
+        <v>1220.130862732846</v>
       </c>
       <c r="Q27">
-        <v>2491.239291089275</v>
+        <v>2478.330862732846</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09909314513017622</v>
+        <v>0.09974362815704849</v>
       </c>
       <c r="T27">
-        <v>1.038782593066002</v>
+        <v>1.051461718003163</v>
       </c>
       <c r="U27">
         <v>0.0602366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.820881232145243</v>
+        <v>4.635462723216579</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08751411512694239</v>
+        <v>0.08753161151132326</v>
       </c>
       <c r="C28">
-        <v>18120.07621300649</v>
+        <v>17866.96566930065</v>
       </c>
       <c r="D28">
-        <v>21224.0102130065</v>
+        <v>21215.80866930065</v>
       </c>
       <c r="E28">
-        <v>3308.234000000001</v>
+        <v>3553.143</v>
       </c>
       <c r="F28">
-        <v>6367.634000000001</v>
+        <v>6612.543000000001</v>
       </c>
       <c r="G28">
         <v>3263.7</v>
@@ -3589,28 +3589,28 @@
         <v>1778</v>
       </c>
       <c r="M28">
-        <v>383.5647283053187</v>
+        <v>398.3172178555232</v>
       </c>
       <c r="N28">
-        <v>1394.435271694681</v>
+        <v>1379.682782144477</v>
       </c>
       <c r="O28">
-        <v>174.3044089618351</v>
+        <v>172.4603477680596</v>
       </c>
       <c r="P28">
-        <v>1220.130862732846</v>
+        <v>1207.222434376417</v>
       </c>
       <c r="Q28">
-        <v>2478.330862732846</v>
+        <v>2465.422434376417</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09974362815704849</v>
+        <v>0.1004119326367117</v>
       </c>
       <c r="T28">
-        <v>1.051461718003163</v>
+        <v>1.064488216226274</v>
       </c>
       <c r="U28">
         <v>0.0602366166625341</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.635462723216579</v>
+        <v>4.463778918653002</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08753161151132326</v>
+        <v>0.08754910789570412</v>
       </c>
       <c r="C29">
-        <v>17866.96566930065</v>
+        <v>17613.86146175233</v>
       </c>
       <c r="D29">
-        <v>21215.80866930065</v>
+        <v>21207.61346175233</v>
       </c>
       <c r="E29">
-        <v>3553.143</v>
+        <v>3798.052000000001</v>
       </c>
       <c r="F29">
-        <v>6612.543000000001</v>
+        <v>6857.452000000001</v>
       </c>
       <c r="G29">
         <v>3263.7</v>
@@ -3671,28 +3671,28 @@
         <v>1778</v>
       </c>
       <c r="M29">
-        <v>398.3172178555232</v>
+        <v>413.0697074057279</v>
       </c>
       <c r="N29">
-        <v>1379.682782144477</v>
+        <v>1364.930292594272</v>
       </c>
       <c r="O29">
-        <v>172.4603477680596</v>
+        <v>170.616286574284</v>
       </c>
       <c r="P29">
-        <v>1207.222434376417</v>
+        <v>1194.314006019988</v>
       </c>
       <c r="Q29">
-        <v>2465.422434376417</v>
+        <v>2452.514006019988</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1004119326367117</v>
+        <v>0.101098801129699</v>
       </c>
       <c r="T29">
-        <v>1.064488216226274</v>
+        <v>1.077876561622249</v>
       </c>
       <c r="U29">
         <v>0.0602366166625341</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.463778918653002</v>
+        <v>4.304358242986823</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08754910789570412</v>
+        <v>0.08782035428008501</v>
       </c>
       <c r="C30">
-        <v>17613.86146175233</v>
+        <v>17242.70728097038</v>
       </c>
       <c r="D30">
-        <v>21207.61346175233</v>
+        <v>21081.36828097038</v>
       </c>
       <c r="E30">
-        <v>3798.052000000001</v>
+        <v>4042.961000000002</v>
       </c>
       <c r="F30">
-        <v>6857.452000000001</v>
+        <v>7102.361000000002</v>
       </c>
       <c r="G30">
         <v>3263.7</v>
@@ -3753,45 +3753,45 @@
         <v>1778</v>
       </c>
       <c r="M30">
-        <v>413.0697074057279</v>
+        <v>434.9245579559324</v>
       </c>
       <c r="N30">
-        <v>1364.930292594272</v>
+        <v>1343.075442044067</v>
       </c>
       <c r="O30">
-        <v>170.616286574284</v>
+        <v>167.8844302555084</v>
       </c>
       <c r="P30">
-        <v>1194.314006019988</v>
+        <v>1175.191011788559</v>
       </c>
       <c r="Q30">
-        <v>2452.514006019988</v>
+        <v>2433.391011788559</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.101098801129699</v>
+        <v>0.1018050180309394</v>
       </c>
       <c r="T30">
-        <v>1.077876561622249</v>
+        <v>1.091642043508252</v>
       </c>
       <c r="U30">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.304358242986823</v>
+        <v>4.088065314950899</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08782035428008499</v>
+        <v>0.08784660066446587</v>
       </c>
       <c r="C31">
-        <v>17242.70728097039</v>
+        <v>16985.66223406088</v>
       </c>
       <c r="D31">
-        <v>21081.36828097039</v>
+        <v>21069.23223406088</v>
       </c>
       <c r="E31">
-        <v>4042.961</v>
+        <v>4287.870000000001</v>
       </c>
       <c r="F31">
-        <v>7102.361</v>
+        <v>7347.27</v>
       </c>
       <c r="G31">
         <v>3263.7</v>
@@ -3835,28 +3835,28 @@
         <v>1778</v>
       </c>
       <c r="M31">
-        <v>434.9245579559324</v>
+        <v>449.921956506137</v>
       </c>
       <c r="N31">
-        <v>1343.075442044067</v>
+        <v>1328.078043493863</v>
       </c>
       <c r="O31">
-        <v>167.8844302555084</v>
+        <v>166.0097554367329</v>
       </c>
       <c r="P31">
-        <v>1175.191011788559</v>
+        <v>1162.06828805713</v>
       </c>
       <c r="Q31">
-        <v>2433.391011788559</v>
+        <v>2420.26828805713</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1018050180309394</v>
+        <v>0.1025314125579295</v>
       </c>
       <c r="T31">
-        <v>1.091642043508252</v>
+        <v>1.105800824876711</v>
       </c>
       <c r="U31">
         <v>0.0612366166625341</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.0880653149509</v>
+        <v>3.951796471119204</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08784660066446587</v>
+        <v>0.08787284704884675</v>
       </c>
       <c r="C32">
-        <v>16985.66223406088</v>
+        <v>16728.63115198455</v>
       </c>
       <c r="D32">
-        <v>21069.23223406088</v>
+        <v>21057.11015198455</v>
       </c>
       <c r="E32">
-        <v>4287.870000000001</v>
+        <v>4532.779</v>
       </c>
       <c r="F32">
-        <v>7347.27</v>
+        <v>7592.179</v>
       </c>
       <c r="G32">
         <v>3263.7</v>
@@ -3917,28 +3917,28 @@
         <v>1778</v>
       </c>
       <c r="M32">
-        <v>449.921956506137</v>
+        <v>464.9193550563415</v>
       </c>
       <c r="N32">
-        <v>1328.078043493863</v>
+        <v>1313.080644943658</v>
       </c>
       <c r="O32">
-        <v>166.0097554367329</v>
+        <v>164.1350806179573</v>
       </c>
       <c r="P32">
-        <v>1162.06828805713</v>
+        <v>1148.945564325701</v>
       </c>
       <c r="Q32">
-        <v>2420.26828805713</v>
+        <v>2407.145564325701</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1025314125579295</v>
+        <v>0.1032788619987455</v>
       </c>
       <c r="T32">
-        <v>1.105800824876711</v>
+        <v>1.120370005705127</v>
       </c>
       <c r="U32">
         <v>0.0612366166625341</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.951796471119204</v>
+        <v>3.824319165599229</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08787284704884675</v>
+        <v>0.08789909343322762</v>
       </c>
       <c r="C33">
-        <v>16728.63115198455</v>
+        <v>16471.61401065146</v>
       </c>
       <c r="D33">
-        <v>21057.11015198455</v>
+        <v>21045.00201065146</v>
       </c>
       <c r="E33">
-        <v>4532.779</v>
+        <v>4777.688</v>
       </c>
       <c r="F33">
-        <v>7592.179</v>
+        <v>7837.088000000001</v>
       </c>
       <c r="G33">
         <v>3263.7</v>
@@ -3999,28 +3999,28 @@
         <v>1778</v>
       </c>
       <c r="M33">
-        <v>464.9193550563415</v>
+        <v>479.9167536065461</v>
       </c>
       <c r="N33">
-        <v>1313.080644943658</v>
+        <v>1298.083246393454</v>
       </c>
       <c r="O33">
-        <v>164.1350806179573</v>
+        <v>162.2604057991817</v>
       </c>
       <c r="P33">
-        <v>1148.945564325701</v>
+        <v>1135.822840594272</v>
       </c>
       <c r="Q33">
-        <v>2407.145564325701</v>
+        <v>2394.022840594272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1032788619987455</v>
+        <v>0.1040482952466442</v>
       </c>
       <c r="T33">
-        <v>1.120370005705127</v>
+        <v>1.135367691852025</v>
       </c>
       <c r="U33">
         <v>0.0612366166625341</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.824319165599229</v>
+        <v>3.704809191674253</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08789909343322762</v>
+        <v>0.08792533981760849</v>
       </c>
       <c r="C34">
-        <v>16471.61401065146</v>
+        <v>16214.61078602706</v>
       </c>
       <c r="D34">
-        <v>21045.00201065146</v>
+        <v>21032.90778602706</v>
       </c>
       <c r="E34">
-        <v>4777.688</v>
+        <v>5022.597000000002</v>
       </c>
       <c r="F34">
-        <v>7837.088000000001</v>
+        <v>8081.997000000001</v>
       </c>
       <c r="G34">
         <v>3263.7</v>
@@ -4081,28 +4081,28 @@
         <v>1778</v>
       </c>
       <c r="M34">
-        <v>479.9167536065461</v>
+        <v>494.9141521567507</v>
       </c>
       <c r="N34">
-        <v>1298.083246393454</v>
+        <v>1283.085847843249</v>
       </c>
       <c r="O34">
-        <v>162.2604057991817</v>
+        <v>160.3857309804062</v>
       </c>
       <c r="P34">
-        <v>1135.822840594272</v>
+        <v>1122.700116862843</v>
       </c>
       <c r="Q34">
-        <v>2394.022840594272</v>
+        <v>2380.900116862843</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1040482952466442</v>
+        <v>0.1048406966511967</v>
       </c>
       <c r="T34">
-        <v>1.135367691852025</v>
+        <v>1.150813070122711</v>
       </c>
       <c r="U34">
         <v>0.0612366166625341</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.704809191674253</v>
+        <v>3.592542246472003</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08792533981760849</v>
+        <v>0.08795158620198937</v>
       </c>
       <c r="C35">
-        <v>16214.61078602706</v>
+        <v>15957.62145413199</v>
       </c>
       <c r="D35">
-        <v>21032.90778602706</v>
+        <v>21020.82745413199</v>
       </c>
       <c r="E35">
-        <v>5022.597000000002</v>
+        <v>5267.506000000001</v>
       </c>
       <c r="F35">
-        <v>8081.997000000001</v>
+        <v>8326.906000000001</v>
       </c>
       <c r="G35">
         <v>3263.7</v>
@@ -4163,28 +4163,28 @@
         <v>1778</v>
       </c>
       <c r="M35">
-        <v>494.9141521567507</v>
+        <v>509.9115507069552</v>
       </c>
       <c r="N35">
-        <v>1283.085847843249</v>
+        <v>1268.088449293045</v>
       </c>
       <c r="O35">
-        <v>160.3857309804062</v>
+        <v>158.5110561616306</v>
       </c>
       <c r="P35">
-        <v>1122.700116862843</v>
+        <v>1109.577393131414</v>
       </c>
       <c r="Q35">
-        <v>2380.900116862843</v>
+        <v>2367.777393131414</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1048406966511967</v>
+        <v>0.1056571102195235</v>
       </c>
       <c r="T35">
-        <v>1.150813070122711</v>
+        <v>1.166726490159175</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.592542246472003</v>
+        <v>3.486879239222826</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08795158620198937</v>
+        <v>0.08797783258637024</v>
       </c>
       <c r="C36">
-        <v>15957.62145413199</v>
+        <v>15700.64599104196</v>
       </c>
       <c r="D36">
-        <v>21020.82745413199</v>
+        <v>21008.76099104196</v>
       </c>
       <c r="E36">
-        <v>5267.506000000001</v>
+        <v>5512.415000000001</v>
       </c>
       <c r="F36">
-        <v>8326.906000000001</v>
+        <v>8571.815000000001</v>
       </c>
       <c r="G36">
         <v>3263.7</v>
@@ -4245,28 +4245,28 @@
         <v>1778</v>
       </c>
       <c r="M36">
-        <v>509.9115507069552</v>
+        <v>524.9089492571597</v>
       </c>
       <c r="N36">
-        <v>1268.088449293045</v>
+        <v>1253.09105074284</v>
       </c>
       <c r="O36">
-        <v>158.5110561616306</v>
+        <v>156.636381342855</v>
       </c>
       <c r="P36">
-        <v>1109.577393131414</v>
+        <v>1096.454669399985</v>
       </c>
       <c r="Q36">
-        <v>2367.777393131414</v>
+        <v>2354.654669399985</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1056571102195235</v>
+        <v>0.1064986442053372</v>
       </c>
       <c r="T36">
-        <v>1.166726490159175</v>
+        <v>1.183129553889069</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.486879239222826</v>
+        <v>3.387254118102175</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08797783258637024</v>
+        <v>0.0880040789707511</v>
       </c>
       <c r="C37">
-        <v>15700.64599104196</v>
+        <v>15443.68437288759</v>
       </c>
       <c r="D37">
-        <v>21008.76099104196</v>
+        <v>20996.7083728876</v>
       </c>
       <c r="E37">
-        <v>5512.415000000001</v>
+        <v>5757.324000000002</v>
       </c>
       <c r="F37">
-        <v>8571.815000000001</v>
+        <v>8816.724000000002</v>
       </c>
       <c r="G37">
         <v>3263.7</v>
@@ -4327,28 +4327,28 @@
         <v>1778</v>
       </c>
       <c r="M37">
-        <v>524.9089492571597</v>
+        <v>539.9063478073645</v>
       </c>
       <c r="N37">
-        <v>1253.09105074284</v>
+        <v>1238.093652192635</v>
       </c>
       <c r="O37">
-        <v>156.636381342855</v>
+        <v>154.7617065240794</v>
       </c>
       <c r="P37">
-        <v>1096.454669399985</v>
+        <v>1083.331945668556</v>
       </c>
       <c r="Q37">
-        <v>2354.654669399985</v>
+        <v>2341.531945668556</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1064986442053372</v>
+        <v>0.1073664761282076</v>
       </c>
       <c r="T37">
-        <v>1.183129553889069</v>
+        <v>1.200045213360522</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.387254118102175</v>
+        <v>3.293163725932669</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08800407897075112</v>
+        <v>0.088030325355132</v>
       </c>
       <c r="C38">
-        <v>15443.68437288759</v>
+        <v>15186.73657585423</v>
       </c>
       <c r="D38">
-        <v>20996.70837288759</v>
+        <v>20984.66957585423</v>
       </c>
       <c r="E38">
-        <v>5757.324000000001</v>
+        <v>6002.233</v>
       </c>
       <c r="F38">
-        <v>8816.724</v>
+        <v>9061.633</v>
       </c>
       <c r="G38">
         <v>3263.7</v>
@@ -4409,28 +4409,28 @@
         <v>1778</v>
       </c>
       <c r="M38">
-        <v>539.9063478073643</v>
+        <v>554.9037463575688</v>
       </c>
       <c r="N38">
-        <v>1238.093652192636</v>
+        <v>1223.096253642431</v>
       </c>
       <c r="O38">
-        <v>154.7617065240794</v>
+        <v>152.8870317053039</v>
       </c>
       <c r="P38">
-        <v>1083.331945668556</v>
+        <v>1070.209221937127</v>
       </c>
       <c r="Q38">
-        <v>2341.531945668556</v>
+        <v>2328.409221937127</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1073664761282076</v>
+        <v>0.1082618582708517</v>
       </c>
       <c r="T38">
-        <v>1.200045213360522</v>
+        <v>1.217497877894561</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.29316372593267</v>
+        <v>3.204159300907463</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.088030325355132</v>
+        <v>0.08805657173951285</v>
       </c>
       <c r="C39">
-        <v>15186.73657585423</v>
+        <v>14929.80257618185</v>
       </c>
       <c r="D39">
-        <v>20984.66957585423</v>
+        <v>20972.64457618185</v>
       </c>
       <c r="E39">
-        <v>6002.233</v>
+        <v>6247.142000000002</v>
       </c>
       <c r="F39">
-        <v>9061.633</v>
+        <v>9306.542000000001</v>
       </c>
       <c r="G39">
         <v>3263.7</v>
@@ -4491,28 +4491,28 @@
         <v>1778</v>
       </c>
       <c r="M39">
-        <v>554.9037463575688</v>
+        <v>569.9011449077735</v>
       </c>
       <c r="N39">
-        <v>1223.096253642431</v>
+        <v>1208.098855092226</v>
       </c>
       <c r="O39">
-        <v>152.8870317053039</v>
+        <v>151.0123568865283</v>
       </c>
       <c r="P39">
-        <v>1070.209221937127</v>
+        <v>1057.086498205698</v>
       </c>
       <c r="Q39">
-        <v>2328.409221937127</v>
+        <v>2315.286498205698</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1082618582708517</v>
+        <v>0.1091861237084198</v>
       </c>
       <c r="T39">
-        <v>1.217497877894561</v>
+        <v>1.235513531607118</v>
       </c>
       <c r="U39">
         <v>0.0612366166625341</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.204159300907463</v>
+        <v>3.119839319304634</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08805657173951285</v>
+        <v>0.08808281812389374</v>
       </c>
       <c r="C40">
-        <v>14929.80257618185</v>
+        <v>14672.88235016479</v>
       </c>
       <c r="D40">
-        <v>20972.64457618185</v>
+        <v>20960.63335016479</v>
       </c>
       <c r="E40">
-        <v>6247.142000000002</v>
+        <v>6492.051000000001</v>
       </c>
       <c r="F40">
-        <v>9306.542000000001</v>
+        <v>9551.451000000001</v>
       </c>
       <c r="G40">
         <v>3263.7</v>
@@ -4573,28 +4573,28 @@
         <v>1778</v>
       </c>
       <c r="M40">
-        <v>569.9011449077735</v>
+        <v>584.898543457978</v>
       </c>
       <c r="N40">
-        <v>1208.098855092226</v>
+        <v>1193.101456542022</v>
       </c>
       <c r="O40">
-        <v>151.0123568865283</v>
+        <v>149.1376820677527</v>
       </c>
       <c r="P40">
-        <v>1057.086498205698</v>
+        <v>1043.963774474269</v>
       </c>
       <c r="Q40">
-        <v>2315.286498205698</v>
+        <v>2302.163774474269</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1091861237084198</v>
+        <v>0.1101406929308262</v>
       </c>
       <c r="T40">
-        <v>1.235513531607118</v>
+        <v>1.254119862490577</v>
       </c>
       <c r="U40">
         <v>0.0612366166625341</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.119839319304634</v>
+        <v>3.039843439322464</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08808281812389374</v>
+        <v>0.0889840645082746</v>
       </c>
       <c r="C41">
-        <v>14672.88235016479</v>
+        <v>14023.71890222078</v>
       </c>
       <c r="D41">
-        <v>20960.63335016479</v>
+        <v>20556.37890222078</v>
       </c>
       <c r="E41">
-        <v>6492.051000000001</v>
+        <v>6736.960000000001</v>
       </c>
       <c r="F41">
-        <v>9551.451000000001</v>
+        <v>9796.360000000001</v>
       </c>
       <c r="G41">
         <v>3263.7</v>
@@ -4655,45 +4655,45 @@
         <v>1778</v>
       </c>
       <c r="M41">
-        <v>584.898543457978</v>
+        <v>624.3868420081825</v>
       </c>
       <c r="N41">
-        <v>1193.101456542022</v>
+        <v>1153.613157991817</v>
       </c>
       <c r="O41">
-        <v>149.1376820677527</v>
+        <v>144.2016447489772</v>
       </c>
       <c r="P41">
-        <v>1043.963774474269</v>
+        <v>1009.41151324284</v>
       </c>
       <c r="Q41">
-        <v>2302.163774474269</v>
+        <v>2267.61151324284</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1101406929308262</v>
+        <v>0.1111270811273128</v>
       </c>
       <c r="T41">
-        <v>1.254119862490577</v>
+        <v>1.273346404403486</v>
       </c>
       <c r="U41">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.039843439322464</v>
+        <v>2.847593639676186</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0889840645082746</v>
+        <v>0.08903218589265546</v>
       </c>
       <c r="C42">
-        <v>14023.71890222078</v>
+        <v>13757.66310507704</v>
       </c>
       <c r="D42">
-        <v>20556.37890222078</v>
+        <v>20535.23210507704</v>
       </c>
       <c r="E42">
-        <v>6736.960000000001</v>
+        <v>6981.869000000002</v>
       </c>
       <c r="F42">
-        <v>9796.360000000001</v>
+        <v>10041.269</v>
       </c>
       <c r="G42">
         <v>3263.7</v>
@@ -4737,28 +4737,28 @@
         <v>1778</v>
       </c>
       <c r="M42">
-        <v>624.3868420081825</v>
+        <v>639.9965130583872</v>
       </c>
       <c r="N42">
-        <v>1153.613157991817</v>
+        <v>1138.003486941613</v>
       </c>
       <c r="O42">
-        <v>144.2016447489772</v>
+        <v>142.2504358677016</v>
       </c>
       <c r="P42">
-        <v>1009.41151324284</v>
+        <v>995.7530510739111</v>
       </c>
       <c r="Q42">
-        <v>2267.61151324284</v>
+        <v>2253.953051073911</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1111270811273128</v>
+        <v>0.1121469062118159</v>
       </c>
       <c r="T42">
-        <v>1.273346404403486</v>
+        <v>1.293224693499883</v>
       </c>
       <c r="U42">
         <v>0.06373661666253409</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.847593639676186</v>
+        <v>2.778140136269449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08903218589265546</v>
+        <v>0.08908030727703636</v>
       </c>
       <c r="C43">
-        <v>13757.66310507704</v>
+        <v>13491.65077156792</v>
       </c>
       <c r="D43">
-        <v>20535.23210507704</v>
+        <v>20514.12877156792</v>
       </c>
       <c r="E43">
-        <v>6981.869000000002</v>
+        <v>7226.778000000002</v>
       </c>
       <c r="F43">
-        <v>10041.269</v>
+        <v>10286.178</v>
       </c>
       <c r="G43">
         <v>3263.7</v>
@@ -4819,28 +4819,28 @@
         <v>1778</v>
       </c>
       <c r="M43">
-        <v>639.9965130583872</v>
+        <v>655.6061841085917</v>
       </c>
       <c r="N43">
-        <v>1138.003486941613</v>
+        <v>1122.393815891408</v>
       </c>
       <c r="O43">
-        <v>142.2504358677016</v>
+        <v>140.299226986426</v>
       </c>
       <c r="P43">
-        <v>995.7530510739111</v>
+        <v>982.0945889049819</v>
       </c>
       <c r="Q43">
-        <v>2253.953051073911</v>
+        <v>2240.294588904982</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1121469062118159</v>
+        <v>0.1132018976785432</v>
       </c>
       <c r="T43">
-        <v>1.293224693499883</v>
+        <v>1.313788440840983</v>
       </c>
       <c r="U43">
         <v>0.06373661666253409</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.778140136269449</v>
+        <v>2.711993942548748</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08908030727703638</v>
+        <v>0.08912842866141724</v>
       </c>
       <c r="C44">
-        <v>13491.65077156792</v>
+        <v>13225.6817678329</v>
       </c>
       <c r="D44">
-        <v>20514.12877156792</v>
+        <v>20493.0687678329</v>
       </c>
       <c r="E44">
-        <v>7226.778</v>
+        <v>7471.687000000002</v>
       </c>
       <c r="F44">
-        <v>10286.178</v>
+        <v>10531.087</v>
       </c>
       <c r="G44">
         <v>3263.7</v>
@@ -4901,28 +4901,28 @@
         <v>1778</v>
       </c>
       <c r="M44">
-        <v>655.6061841085916</v>
+        <v>671.2158551587962</v>
       </c>
       <c r="N44">
-        <v>1122.393815891408</v>
+        <v>1106.784144841204</v>
       </c>
       <c r="O44">
-        <v>140.299226986426</v>
+        <v>138.3480181051505</v>
       </c>
       <c r="P44">
-        <v>982.0945889049822</v>
+        <v>968.4361267360532</v>
       </c>
       <c r="Q44">
-        <v>2240.294588904982</v>
+        <v>2226.636126736053</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1132018976785432</v>
+        <v>0.1142939063897171</v>
       </c>
       <c r="T44">
-        <v>1.313788440840983</v>
+        <v>1.335073723176508</v>
       </c>
       <c r="U44">
         <v>0.06373661666253409</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.711993942548748</v>
+        <v>2.648924315977847</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08912842866141724</v>
+        <v>0.08917655004579811</v>
       </c>
       <c r="C45">
-        <v>13225.6817678329</v>
+        <v>12959.75596056051</v>
       </c>
       <c r="D45">
-        <v>20493.0687678329</v>
+        <v>20472.05196056051</v>
       </c>
       <c r="E45">
-        <v>7471.687000000002</v>
+        <v>7716.596000000001</v>
       </c>
       <c r="F45">
-        <v>10531.087</v>
+        <v>10775.996</v>
       </c>
       <c r="G45">
         <v>3263.7</v>
@@ -4983,28 +4983,28 @@
         <v>1778</v>
       </c>
       <c r="M45">
-        <v>671.2158551587962</v>
+        <v>686.8255262090008</v>
       </c>
       <c r="N45">
-        <v>1106.784144841204</v>
+        <v>1091.174473790999</v>
       </c>
       <c r="O45">
-        <v>138.3480181051505</v>
+        <v>136.3968092238749</v>
       </c>
       <c r="P45">
-        <v>968.4361267360532</v>
+        <v>954.777664567124</v>
       </c>
       <c r="Q45">
-        <v>2226.636126736053</v>
+        <v>2212.977664567124</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1142939063897171</v>
+        <v>0.1154249154120044</v>
       </c>
       <c r="T45">
-        <v>1.335073723176508</v>
+        <v>1.357119194166873</v>
       </c>
       <c r="U45">
         <v>0.06373661666253409</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.648924315977847</v>
+        <v>2.588721490614714</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08917655004579811</v>
+        <v>0.08922467143017898</v>
       </c>
       <c r="C46">
-        <v>12959.75596056051</v>
+        <v>12693.87321698563</v>
       </c>
       <c r="D46">
-        <v>20472.05196056051</v>
+        <v>20451.07821698563</v>
       </c>
       <c r="E46">
-        <v>7716.596000000001</v>
+        <v>7961.505000000001</v>
       </c>
       <c r="F46">
-        <v>10775.996</v>
+        <v>11020.905</v>
       </c>
       <c r="G46">
         <v>3263.7</v>
@@ -5065,28 +5065,28 @@
         <v>1778</v>
       </c>
       <c r="M46">
-        <v>686.8255262090008</v>
+        <v>702.4351972592053</v>
       </c>
       <c r="N46">
-        <v>1091.174473790999</v>
+        <v>1075.564802740794</v>
       </c>
       <c r="O46">
-        <v>136.3968092238749</v>
+        <v>134.4456003425993</v>
       </c>
       <c r="P46">
-        <v>954.777664567124</v>
+        <v>941.1192023981952</v>
       </c>
       <c r="Q46">
-        <v>2212.977664567124</v>
+        <v>2199.319202398195</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1154249154120044</v>
+        <v>0.1165970520351021</v>
       </c>
       <c r="T46">
-        <v>1.357119194166873</v>
+        <v>1.379966318647797</v>
       </c>
       <c r="U46">
         <v>0.06373661666253409</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.588721490614714</v>
+        <v>2.531194346378832</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08922467143017898</v>
+        <v>0.09068154281455987</v>
       </c>
       <c r="C47">
-        <v>12693.87321698563</v>
+        <v>11833.71917013086</v>
       </c>
       <c r="D47">
-        <v>20451.07821698563</v>
+        <v>19835.83317013086</v>
       </c>
       <c r="E47">
-        <v>7961.505000000001</v>
+        <v>8206.414000000001</v>
       </c>
       <c r="F47">
-        <v>11020.905</v>
+        <v>11265.814</v>
       </c>
       <c r="G47">
         <v>3263.7</v>
@@ -5147,45 +5147,45 @@
         <v>1778</v>
       </c>
       <c r="M47">
-        <v>702.4351972592053</v>
+        <v>757.4752173094099</v>
       </c>
       <c r="N47">
-        <v>1075.564802740794</v>
+        <v>1020.52478269059</v>
       </c>
       <c r="O47">
-        <v>134.4456003425993</v>
+        <v>127.5655978363237</v>
       </c>
       <c r="P47">
-        <v>941.1192023981952</v>
+        <v>892.9591848542661</v>
       </c>
       <c r="Q47">
-        <v>2199.319202398195</v>
+        <v>2151.159184854266</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1165970520351021</v>
+        <v>0.117812601125722</v>
       </c>
       <c r="T47">
-        <v>1.379966318647797</v>
+        <v>1.403659632924311</v>
       </c>
       <c r="U47">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.531194346378832</v>
+        <v>2.347271513800208</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09068154281455987</v>
+        <v>0.09076028919894073</v>
       </c>
       <c r="C48">
-        <v>11833.71917013086</v>
+        <v>11556.60792515325</v>
       </c>
       <c r="D48">
-        <v>19835.83317013086</v>
+        <v>19803.63092515325</v>
       </c>
       <c r="E48">
-        <v>8206.414000000001</v>
+        <v>8451.323000000002</v>
       </c>
       <c r="F48">
-        <v>11265.814</v>
+        <v>11510.723</v>
       </c>
       <c r="G48">
         <v>3263.7</v>
@@ -5229,28 +5229,28 @@
         <v>1778</v>
       </c>
       <c r="M48">
-        <v>757.4752173094099</v>
+        <v>773.9420698596145</v>
       </c>
       <c r="N48">
-        <v>1020.52478269059</v>
+        <v>1004.057930140385</v>
       </c>
       <c r="O48">
-        <v>127.5655978363237</v>
+        <v>125.5072412675482</v>
       </c>
       <c r="P48">
-        <v>892.9591848542661</v>
+        <v>878.5506888728371</v>
       </c>
       <c r="Q48">
-        <v>2151.159184854266</v>
+        <v>2136.750688872837</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.117812601125722</v>
+        <v>0.1190740199933464</v>
       </c>
       <c r="T48">
-        <v>1.403659632924311</v>
+        <v>1.428247034532013</v>
       </c>
       <c r="U48">
         <v>0.0672366166625341</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.347271513800208</v>
+        <v>2.297329566698076</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09076028919894073</v>
+        <v>0.09201503558332161</v>
       </c>
       <c r="C49">
-        <v>11556.60792515325</v>
+        <v>10812.33815649051</v>
       </c>
       <c r="D49">
-        <v>19803.63092515325</v>
+        <v>19304.27015649051</v>
       </c>
       <c r="E49">
-        <v>8451.323000000002</v>
+        <v>8696.232000000002</v>
       </c>
       <c r="F49">
-        <v>11510.723</v>
+        <v>11755.632</v>
       </c>
       <c r="G49">
         <v>3263.7</v>
@@ -5311,45 +5311,45 @@
         <v>1778</v>
       </c>
       <c r="M49">
-        <v>773.9420698596145</v>
+        <v>823.324692009819</v>
       </c>
       <c r="N49">
-        <v>1004.057930140385</v>
+        <v>954.6753079901807</v>
       </c>
       <c r="O49">
-        <v>125.5072412675482</v>
+        <v>119.3344134987726</v>
       </c>
       <c r="P49">
-        <v>878.5506888728371</v>
+        <v>835.3408944914081</v>
       </c>
       <c r="Q49">
-        <v>2136.750688872837</v>
+        <v>2093.540894491408</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1190740199933464</v>
+        <v>0.120383954971264</v>
       </c>
       <c r="T49">
-        <v>1.428247034532013</v>
+        <v>1.45378010543232</v>
       </c>
       <c r="U49">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.297329566698076</v>
+        <v>2.159536835534134</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09201503558332161</v>
+        <v>0.09211828196770247</v>
       </c>
       <c r="C50">
-        <v>10812.33815649051</v>
+        <v>10527.45846003309</v>
       </c>
       <c r="D50">
-        <v>19304.27015649051</v>
+        <v>19264.29946003309</v>
       </c>
       <c r="E50">
-        <v>8696.232</v>
+        <v>8941.141000000001</v>
       </c>
       <c r="F50">
-        <v>11755.632</v>
+        <v>12000.541</v>
       </c>
       <c r="G50">
         <v>3263.7</v>
@@ -5393,28 +5393,28 @@
         <v>1778</v>
       </c>
       <c r="M50">
-        <v>823.3246920098189</v>
+        <v>840.4772897600236</v>
       </c>
       <c r="N50">
-        <v>954.6753079901808</v>
+        <v>937.5227102399762</v>
       </c>
       <c r="O50">
-        <v>119.3344134987726</v>
+        <v>117.190338779997</v>
       </c>
       <c r="P50">
-        <v>835.3408944914082</v>
+        <v>820.3323714599792</v>
       </c>
       <c r="Q50">
-        <v>2093.540894491408</v>
+        <v>2078.532371459979</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.120383954971264</v>
+        <v>0.1217452599483156</v>
       </c>
       <c r="T50">
-        <v>1.45378010543232</v>
+        <v>1.480314473230678</v>
       </c>
       <c r="U50">
         <v>0.07003661666253409</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.159536835534134</v>
+        <v>2.11546465521711</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09211828196770247</v>
+        <v>0.09222152835208335</v>
       </c>
       <c r="C51">
-        <v>10527.45846003309</v>
+        <v>10242.74394520129</v>
       </c>
       <c r="D51">
-        <v>19264.29946003309</v>
+        <v>19224.49394520129</v>
       </c>
       <c r="E51">
-        <v>8941.141000000001</v>
+        <v>9186.050000000001</v>
       </c>
       <c r="F51">
-        <v>12000.541</v>
+        <v>12245.45</v>
       </c>
       <c r="G51">
         <v>3263.7</v>
@@ -5475,28 +5475,28 @@
         <v>1778</v>
       </c>
       <c r="M51">
-        <v>840.4772897600236</v>
+        <v>857.6298875102282</v>
       </c>
       <c r="N51">
-        <v>937.5227102399762</v>
+        <v>920.3701124897716</v>
       </c>
       <c r="O51">
-        <v>117.190338779997</v>
+        <v>115.0462640612214</v>
       </c>
       <c r="P51">
-        <v>820.3323714599792</v>
+        <v>805.3238484285501</v>
       </c>
       <c r="Q51">
-        <v>2078.532371459979</v>
+        <v>2063.52384842855</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1217452599483156</v>
+        <v>0.1231610171244494</v>
       </c>
       <c r="T51">
-        <v>1.480314473230678</v>
+        <v>1.50791021574097</v>
       </c>
       <c r="U51">
         <v>0.07003661666253409</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.11546465521711</v>
+        <v>2.073155362112768</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09222152835208335</v>
+        <v>0.09232477473646422</v>
       </c>
       <c r="C52">
-        <v>10242.74394520129</v>
+        <v>9958.193590170013</v>
       </c>
       <c r="D52">
-        <v>19224.49394520129</v>
+        <v>19184.85259017001</v>
       </c>
       <c r="E52">
-        <v>9186.050000000001</v>
+        <v>9430.959000000001</v>
       </c>
       <c r="F52">
-        <v>12245.45</v>
+        <v>12490.359</v>
       </c>
       <c r="G52">
         <v>3263.7</v>
@@ -5557,28 +5557,28 @@
         <v>1778</v>
       </c>
       <c r="M52">
-        <v>857.6298875102282</v>
+        <v>874.7824852604327</v>
       </c>
       <c r="N52">
-        <v>920.3701124897716</v>
+        <v>903.217514739567</v>
       </c>
       <c r="O52">
-        <v>115.0462640612214</v>
+        <v>112.9021893424459</v>
       </c>
       <c r="P52">
-        <v>805.3238484285501</v>
+        <v>790.3153253971211</v>
       </c>
       <c r="Q52">
-        <v>2063.52384842855</v>
+        <v>2048.515325397121</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1231610171244494</v>
+        <v>0.1246345603077722</v>
       </c>
       <c r="T52">
-        <v>1.50791021574097</v>
+        <v>1.536632315088417</v>
       </c>
       <c r="U52">
         <v>0.07003661666253409</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.073155362112768</v>
+        <v>2.032505256973302</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09232477473646422</v>
+        <v>0.09597702112084511</v>
       </c>
       <c r="C53">
-        <v>9958.193590170013</v>
+        <v>8409.034321387482</v>
       </c>
       <c r="D53">
-        <v>19184.85259017001</v>
+        <v>17880.60232138748</v>
       </c>
       <c r="E53">
-        <v>9430.959000000001</v>
+        <v>9675.868000000002</v>
       </c>
       <c r="F53">
-        <v>12490.359</v>
+        <v>12735.268</v>
       </c>
       <c r="G53">
         <v>3263.7</v>
@@ -5639,45 +5639,45 @@
         <v>1778</v>
       </c>
       <c r="M53">
-        <v>874.7824852604327</v>
+        <v>991.2701734106375</v>
       </c>
       <c r="N53">
-        <v>903.217514739567</v>
+        <v>786.7298265893622</v>
       </c>
       <c r="O53">
-        <v>112.9021893424459</v>
+        <v>98.34122832367028</v>
       </c>
       <c r="P53">
-        <v>790.3153253971211</v>
+        <v>688.3885982656919</v>
       </c>
       <c r="Q53">
-        <v>2048.515325397121</v>
+        <v>1946.588598265692</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1246345603077722</v>
+        <v>0.1261695011237335</v>
       </c>
       <c r="T53">
-        <v>1.536632315088417</v>
+        <v>1.566551168575341</v>
       </c>
       <c r="U53">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.032505256973302</v>
+        <v>1.793658326147836</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09597702112084511</v>
+        <v>0.09614851750522596</v>
       </c>
       <c r="C54">
-        <v>8409.034321387482</v>
+        <v>8107.227538578119</v>
       </c>
       <c r="D54">
-        <v>17880.60232138748</v>
+        <v>17823.70453857812</v>
       </c>
       <c r="E54">
-        <v>9675.868000000002</v>
+        <v>9920.777000000002</v>
       </c>
       <c r="F54">
-        <v>12735.268</v>
+        <v>12980.177</v>
       </c>
       <c r="G54">
         <v>3263.7</v>
@@ -5721,28 +5721,28 @@
         <v>1778</v>
       </c>
       <c r="M54">
-        <v>991.2701734106375</v>
+        <v>1010.333061360842</v>
       </c>
       <c r="N54">
-        <v>786.7298265893622</v>
+        <v>767.6669386391577</v>
       </c>
       <c r="O54">
-        <v>98.34122832367028</v>
+        <v>95.95836732989471</v>
       </c>
       <c r="P54">
-        <v>688.3885982656919</v>
+        <v>671.708571309263</v>
       </c>
       <c r="Q54">
-        <v>1946.588598265692</v>
+        <v>1929.908571309263</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1261695011237335</v>
+        <v>0.1277697585701612</v>
       </c>
       <c r="T54">
-        <v>1.566551168575341</v>
+        <v>1.597743164763837</v>
       </c>
       <c r="U54">
         <v>0.07783661666253411</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.793658326147836</v>
+        <v>1.759815716220519</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09614851750522596</v>
+        <v>0.09816276388960685</v>
       </c>
       <c r="C55">
-        <v>8107.227538578119</v>
+        <v>7220.173111829952</v>
       </c>
       <c r="D55">
-        <v>17823.70453857812</v>
+        <v>17181.55911182995</v>
       </c>
       <c r="E55">
-        <v>9920.777000000002</v>
+        <v>10165.686</v>
       </c>
       <c r="F55">
-        <v>12980.177</v>
+        <v>13225.086</v>
       </c>
       <c r="G55">
         <v>3263.7</v>
@@ -5803,45 +5803,45 @@
         <v>1778</v>
       </c>
       <c r="M55">
-        <v>1010.333061360842</v>
+        <v>1080.973784711046</v>
       </c>
       <c r="N55">
-        <v>767.6669386391577</v>
+        <v>697.0262152889534</v>
       </c>
       <c r="O55">
-        <v>95.95836732989471</v>
+        <v>87.12827691111917</v>
       </c>
       <c r="P55">
-        <v>671.708571309263</v>
+        <v>609.8979383778342</v>
       </c>
       <c r="Q55">
-        <v>1929.908571309263</v>
+        <v>1868.097938377834</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1277697585701612</v>
+        <v>0.1294395924273032</v>
       </c>
       <c r="T55">
-        <v>1.597743164763837</v>
+        <v>1.630291334699658</v>
       </c>
       <c r="U55">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V55">
         <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.759815716220519</v>
+        <v>1.64481324630391</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09816276388960685</v>
+        <v>0.09836838527398772</v>
       </c>
       <c r="C56">
-        <v>7220.173111829952</v>
+        <v>6912.304890653289</v>
       </c>
       <c r="D56">
-        <v>17181.55911182995</v>
+        <v>17118.59989065329</v>
       </c>
       <c r="E56">
-        <v>10165.686</v>
+        <v>10410.595</v>
       </c>
       <c r="F56">
-        <v>13225.086</v>
+        <v>13469.995</v>
       </c>
       <c r="G56">
         <v>3263.7</v>
@@ -5885,28 +5885,28 @@
         <v>1778</v>
       </c>
       <c r="M56">
-        <v>1080.973784711046</v>
+        <v>1100.991817761251</v>
       </c>
       <c r="N56">
-        <v>697.0262152889534</v>
+        <v>677.0081822387485</v>
       </c>
       <c r="O56">
-        <v>87.12827691111917</v>
+        <v>84.62602277984357</v>
       </c>
       <c r="P56">
-        <v>609.8979383778342</v>
+        <v>592.382159458905</v>
       </c>
       <c r="Q56">
-        <v>1868.097938377834</v>
+        <v>1850.582159458905</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1294395924273032</v>
+        <v>0.1311836411225404</v>
       </c>
       <c r="T56">
-        <v>1.630291334699658</v>
+        <v>1.66428608996596</v>
       </c>
       <c r="U56">
         <v>0.0817366166625341</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.64481324630391</v>
+        <v>1.614907550916565</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09836838527398772</v>
+        <v>0.09857400665836857</v>
       </c>
       <c r="C57">
-        <v>6912.304890653289</v>
+        <v>6604.896393947292</v>
       </c>
       <c r="D57">
-        <v>17118.59989065329</v>
+        <v>17056.10039394729</v>
       </c>
       <c r="E57">
-        <v>10410.595</v>
+        <v>10655.504</v>
       </c>
       <c r="F57">
-        <v>13469.995</v>
+        <v>13714.904</v>
       </c>
       <c r="G57">
         <v>3263.7</v>
@@ -5967,28 +5967,28 @@
         <v>1778</v>
       </c>
       <c r="M57">
-        <v>1100.991817761251</v>
+        <v>1121.009850811456</v>
       </c>
       <c r="N57">
-        <v>677.0081822387485</v>
+        <v>656.9901491885441</v>
       </c>
       <c r="O57">
-        <v>84.62602277984357</v>
+        <v>82.12376864856802</v>
       </c>
       <c r="P57">
-        <v>592.382159458905</v>
+        <v>574.8663805399761</v>
       </c>
       <c r="Q57">
-        <v>1850.582159458905</v>
+        <v>1833.066380539976</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1311836411225404</v>
+        <v>0.1330069647584702</v>
       </c>
       <c r="T57">
-        <v>1.66428608996596</v>
+        <v>1.69982606138073</v>
       </c>
       <c r="U57">
         <v>0.0817366166625341</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.614907550916565</v>
+        <v>1.58606991607877</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09857400665836857</v>
+        <v>0.09877962804274945</v>
       </c>
       <c r="C58">
-        <v>6604.896393947292</v>
+        <v>6297.942604707954</v>
       </c>
       <c r="D58">
-        <v>17056.10039394729</v>
+        <v>16994.05560470796</v>
       </c>
       <c r="E58">
-        <v>10655.504</v>
+        <v>10900.413</v>
       </c>
       <c r="F58">
-        <v>13714.904</v>
+        <v>13959.813</v>
       </c>
       <c r="G58">
         <v>3263.7</v>
@@ -6049,28 +6049,28 @@
         <v>1778</v>
       </c>
       <c r="M58">
-        <v>1121.009850811456</v>
+        <v>1141.02788386166</v>
       </c>
       <c r="N58">
-        <v>656.9901491885441</v>
+        <v>636.9721161383395</v>
       </c>
       <c r="O58">
-        <v>82.12376864856802</v>
+        <v>79.62151451729244</v>
       </c>
       <c r="P58">
-        <v>574.8663805399761</v>
+        <v>557.3506016210471</v>
       </c>
       <c r="Q58">
-        <v>1833.066380539976</v>
+        <v>1815.550601621047</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1330069647584702</v>
+        <v>0.1349150941449083</v>
       </c>
       <c r="T58">
-        <v>1.69982606138073</v>
+        <v>1.737019054721769</v>
       </c>
       <c r="U58">
         <v>0.0817366166625341</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.58606991607877</v>
+        <v>1.558244128077388</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09877962804274945</v>
+        <v>0.09898524942713034</v>
       </c>
       <c r="C59">
-        <v>6297.942604707954</v>
+        <v>5991.438578667899</v>
       </c>
       <c r="D59">
-        <v>16994.05560470796</v>
+        <v>16932.4605786679</v>
       </c>
       <c r="E59">
-        <v>10900.413</v>
+        <v>11145.322</v>
       </c>
       <c r="F59">
-        <v>13959.813</v>
+        <v>14204.722</v>
       </c>
       <c r="G59">
         <v>3263.7</v>
@@ -6131,28 +6131,28 @@
         <v>1778</v>
       </c>
       <c r="M59">
-        <v>1141.02788386166</v>
+        <v>1161.045916911865</v>
       </c>
       <c r="N59">
-        <v>636.9721161383395</v>
+        <v>616.9540830881349</v>
       </c>
       <c r="O59">
-        <v>79.62151451729244</v>
+        <v>77.11926038601686</v>
       </c>
       <c r="P59">
-        <v>557.3506016210471</v>
+        <v>539.834822702118</v>
       </c>
       <c r="Q59">
-        <v>1815.550601621047</v>
+        <v>1798.034822702118</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1349150941449083</v>
+        <v>0.1369140868354626</v>
       </c>
       <c r="T59">
-        <v>1.737019054721769</v>
+        <v>1.77598314298381</v>
       </c>
       <c r="U59">
         <v>0.0817366166625341</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.558244128077388</v>
+        <v>1.531377850007088</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09898524942713033</v>
+        <v>0.09919087081151121</v>
       </c>
       <c r="C60">
-        <v>5991.438578667907</v>
+        <v>5685.37944298297</v>
       </c>
       <c r="D60">
-        <v>16932.46057866791</v>
+        <v>16871.31044298297</v>
       </c>
       <c r="E60">
-        <v>11145.322</v>
+        <v>11390.231</v>
       </c>
       <c r="F60">
-        <v>14204.722</v>
+        <v>14449.631</v>
       </c>
       <c r="G60">
         <v>3263.7</v>
@@ -6213,28 +6213,28 @@
         <v>1778</v>
       </c>
       <c r="M60">
-        <v>1161.045916911865</v>
+        <v>1181.063949962069</v>
       </c>
       <c r="N60">
-        <v>616.9540830881351</v>
+        <v>596.9360500379307</v>
       </c>
       <c r="O60">
-        <v>77.11926038601689</v>
+        <v>74.61700625474134</v>
       </c>
       <c r="P60">
-        <v>539.8348227021182</v>
+        <v>522.3190437831894</v>
       </c>
       <c r="Q60">
-        <v>1798.034822702118</v>
+        <v>1780.519043783189</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1369140868354626</v>
+        <v>0.1390105913645804</v>
       </c>
       <c r="T60">
-        <v>1.775983142983809</v>
+        <v>1.816847918478144</v>
       </c>
       <c r="U60">
         <v>0.0817366166625341</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.531377850007088</v>
+        <v>1.505422293227307</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09919087081151121</v>
+        <v>0.1068514921958921</v>
       </c>
       <c r="C61">
-        <v>5685.37944298297</v>
+        <v>3439.689653425161</v>
       </c>
       <c r="D61">
-        <v>16871.31044298297</v>
+        <v>14870.52965342516</v>
       </c>
       <c r="E61">
-        <v>11390.231</v>
+        <v>11635.14</v>
       </c>
       <c r="F61">
-        <v>14449.631</v>
+        <v>14694.54</v>
       </c>
       <c r="G61">
         <v>3263.7</v>
@@ -6295,45 +6295,45 @@
         <v>1778</v>
       </c>
       <c r="M61">
-        <v>1181.063949962069</v>
+        <v>1409.744451012274</v>
       </c>
       <c r="N61">
-        <v>596.9360500379307</v>
+        <v>368.2555489877259</v>
       </c>
       <c r="O61">
-        <v>74.61700625474134</v>
+        <v>46.03194362346574</v>
       </c>
       <c r="P61">
-        <v>522.3190437831894</v>
+        <v>322.2236053642602</v>
       </c>
       <c r="Q61">
-        <v>1780.519043783189</v>
+        <v>1580.42360536426</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1390105913645804</v>
+        <v>0.1412119211201542</v>
       </c>
       <c r="T61">
-        <v>1.816847918478144</v>
+        <v>1.859755932747197</v>
       </c>
       <c r="U61">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V61">
         <v>0.125</v>
       </c>
       <c r="W61">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.505422293227307</v>
+        <v>1.261221492110359</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1068514921958921</v>
+        <v>0.1230072484909918</v>
       </c>
       <c r="C62">
-        <v>3439.689653425161</v>
+        <v>219.7214671904185</v>
       </c>
       <c r="D62">
-        <v>14870.52965342516</v>
+        <v>11895.47046719042</v>
       </c>
       <c r="E62">
-        <v>11635.14</v>
+        <v>11880.049</v>
       </c>
       <c r="F62">
-        <v>14694.54</v>
+        <v>14939.449</v>
       </c>
       <c r="G62">
         <v>3263.7</v>
@@ -6377,45 +6377,45 @@
         <v>1778</v>
       </c>
       <c r="M62">
-        <v>1409.744451012274</v>
+        <v>1860.508433262479</v>
       </c>
       <c r="N62">
-        <v>368.2555489877259</v>
+        <v>-82.50843326247877</v>
       </c>
       <c r="O62">
-        <v>46.03194362346574</v>
+        <v>-10.31355415780985</v>
       </c>
       <c r="P62">
-        <v>322.2236053642602</v>
+        <v>-72.19487910466893</v>
       </c>
       <c r="Q62">
-        <v>1580.42360536426</v>
+        <v>1186.005120895331</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1412119211201542</v>
+        <v>0.1438838757384142</v>
       </c>
       <c r="T62">
-        <v>1.859755932747197</v>
+        <v>1.911837301563599</v>
       </c>
       <c r="U62">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.125</v>
+        <v>0.1194565937066329</v>
       </c>
       <c r="W62">
-        <v>0.08394453957971734</v>
+        <v>0.1096598966442791</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.261221492110359</v>
+        <v>0.9556527496530629</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1230072484909918</v>
+        <v>0.1237946146576171</v>
       </c>
       <c r="C63">
-        <v>219.7214671904185</v>
+        <v>-140.0521459984193</v>
       </c>
       <c r="D63">
-        <v>11895.47046719042</v>
+        <v>11780.60585400158</v>
       </c>
       <c r="E63">
-        <v>11880.049</v>
+        <v>12124.958</v>
       </c>
       <c r="F63">
-        <v>14939.449</v>
+        <v>15184.358</v>
       </c>
       <c r="G63">
         <v>3263.7</v>
@@ -6459,37 +6459,37 @@
         <v>1778</v>
       </c>
       <c r="M63">
-        <v>1860.508433262479</v>
+        <v>1891.008571512683</v>
       </c>
       <c r="N63">
-        <v>-82.50843326247877</v>
+        <v>-113.0085715126831</v>
       </c>
       <c r="O63">
-        <v>-10.31355415780985</v>
+        <v>-14.12607143908539</v>
       </c>
       <c r="P63">
-        <v>-72.19487910466893</v>
+        <v>-98.88250007359775</v>
       </c>
       <c r="Q63">
-        <v>1186.005120895331</v>
+        <v>1159.317499926402</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1438838757384142</v>
+        <v>0.1464650303631093</v>
       </c>
       <c r="T63">
-        <v>1.911837301563599</v>
+        <v>1.962148809499483</v>
       </c>
       <c r="U63">
         <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.1194565937066329</v>
+        <v>0.1175298744533001</v>
       </c>
       <c r="W63">
-        <v>0.1096598966442791</v>
+        <v>0.1098998437413477</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9556527496530629</v>
+        <v>0.9402389956264008</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1237946146576171</v>
+        <v>0.1245819808242424</v>
       </c>
       <c r="C64">
-        <v>-140.0521459984193</v>
+        <v>-497.6286715498663</v>
       </c>
       <c r="D64">
-        <v>11780.60585400158</v>
+        <v>11667.93832845013</v>
       </c>
       <c r="E64">
-        <v>12124.958</v>
+        <v>12369.867</v>
       </c>
       <c r="F64">
-        <v>15184.358</v>
+        <v>15429.267</v>
       </c>
       <c r="G64">
         <v>3263.7</v>
@@ -6541,37 +6541,37 @@
         <v>1778</v>
       </c>
       <c r="M64">
-        <v>1891.008571512683</v>
+        <v>1921.508709762888</v>
       </c>
       <c r="N64">
-        <v>-113.0085715126831</v>
+        <v>-143.508709762888</v>
       </c>
       <c r="O64">
-        <v>-14.12607143908539</v>
+        <v>-17.938588720361</v>
       </c>
       <c r="P64">
-        <v>-98.88250007359775</v>
+        <v>-125.570121042527</v>
       </c>
       <c r="Q64">
-        <v>1159.317499926402</v>
+        <v>1132.629878957473</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1464650303631093</v>
+        <v>0.1491857068594095</v>
       </c>
       <c r="T64">
-        <v>1.962148809499483</v>
+        <v>2.015179858404874</v>
       </c>
       <c r="U64">
         <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.1175298744533001</v>
+        <v>0.1156643208905493</v>
       </c>
       <c r="W64">
-        <v>0.1098998437413477</v>
+        <v>0.1101321734702554</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9402389956264008</v>
+        <v>0.9253145671243943</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1245819808242424</v>
+        <v>0.1253693469908678</v>
       </c>
       <c r="C65">
-        <v>-497.6286715498663</v>
+        <v>-853.0705499089436</v>
       </c>
       <c r="D65">
-        <v>11667.93832845013</v>
+        <v>11557.40545009106</v>
       </c>
       <c r="E65">
-        <v>12369.867</v>
+        <v>12614.776</v>
       </c>
       <c r="F65">
-        <v>15429.267</v>
+        <v>15674.176</v>
       </c>
       <c r="G65">
         <v>3263.7</v>
@@ -6623,37 +6623,37 @@
         <v>1778</v>
       </c>
       <c r="M65">
-        <v>1921.508709762888</v>
+        <v>1952.008848013092</v>
       </c>
       <c r="N65">
-        <v>-143.508709762888</v>
+        <v>-174.0088480130926</v>
       </c>
       <c r="O65">
-        <v>-17.938588720361</v>
+        <v>-21.75110600163657</v>
       </c>
       <c r="P65">
-        <v>-125.570121042527</v>
+        <v>-152.257742011456</v>
       </c>
       <c r="Q65">
-        <v>1132.629878957473</v>
+        <v>1105.942257988544</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1491857068594095</v>
+        <v>0.1520575320499487</v>
       </c>
       <c r="T65">
-        <v>2.015179858404874</v>
+        <v>2.071157076693899</v>
       </c>
       <c r="U65">
         <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.1156643208905493</v>
+        <v>0.1138570658766345</v>
       </c>
       <c r="W65">
-        <v>0.1101321734702554</v>
+        <v>0.1103572428951348</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9253145671243943</v>
+        <v>0.9108565270130755</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1253693469908678</v>
+        <v>0.1261567131574931</v>
       </c>
       <c r="C66">
-        <v>-853.0705499089436</v>
+        <v>-1206.437877677568</v>
       </c>
       <c r="D66">
-        <v>11557.40545009106</v>
+        <v>11448.94712232243</v>
       </c>
       <c r="E66">
-        <v>12614.776</v>
+        <v>12859.685</v>
       </c>
       <c r="F66">
-        <v>15674.176</v>
+        <v>15919.085</v>
       </c>
       <c r="G66">
         <v>3263.7</v>
@@ -6705,37 +6705,37 @@
         <v>1778</v>
       </c>
       <c r="M66">
-        <v>1952.008848013092</v>
+        <v>1982.508986263297</v>
       </c>
       <c r="N66">
-        <v>-174.0088480130926</v>
+        <v>-204.5089862632969</v>
       </c>
       <c r="O66">
-        <v>-21.75110600163657</v>
+        <v>-25.56362328291212</v>
       </c>
       <c r="P66">
-        <v>-152.257742011456</v>
+        <v>-178.9453629803848</v>
       </c>
       <c r="Q66">
-        <v>1105.942257988544</v>
+        <v>1079.254637019615</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1520575320499487</v>
+        <v>0.1550934615370901</v>
       </c>
       <c r="T66">
-        <v>2.071157076693899</v>
+        <v>2.130332993170867</v>
       </c>
       <c r="U66">
         <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.1138570658766345</v>
+        <v>0.1121054187093016</v>
       </c>
       <c r="W66">
-        <v>0.1103572428951348</v>
+        <v>0.1105753871069409</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9108565270130755</v>
+        <v>0.8968433496744129</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1261567131574931</v>
+        <v>0.1269440793241185</v>
       </c>
       <c r="C67">
-        <v>-1206.437877677568</v>
+        <v>-1557.788516568908</v>
       </c>
       <c r="D67">
-        <v>11448.94712232243</v>
+        <v>11342.5054834311</v>
       </c>
       <c r="E67">
-        <v>12859.685</v>
+        <v>13104.594</v>
       </c>
       <c r="F67">
-        <v>15919.085</v>
+        <v>16163.994</v>
       </c>
       <c r="G67">
         <v>3263.7</v>
@@ -6787,37 +6787,37 @@
         <v>1778</v>
       </c>
       <c r="M67">
-        <v>1982.508986263297</v>
+        <v>2013.009124513502</v>
       </c>
       <c r="N67">
-        <v>-204.5089862632969</v>
+        <v>-235.0091245135018</v>
       </c>
       <c r="O67">
-        <v>-25.56362328291212</v>
+        <v>-29.37614056418772</v>
       </c>
       <c r="P67">
-        <v>-178.9453629803848</v>
+        <v>-205.6329839493141</v>
       </c>
       <c r="Q67">
-        <v>1079.254637019615</v>
+        <v>1052.567016050686</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1550934615370901</v>
+        <v>0.1583079751117104</v>
       </c>
       <c r="T67">
-        <v>2.130332993170867</v>
+        <v>2.192989845911187</v>
       </c>
       <c r="U67">
         <v>0.1245366166625341</v>
       </c>
       <c r="V67">
-        <v>0.1121054187093016</v>
+        <v>0.1104068517591607</v>
       </c>
       <c r="W67">
-        <v>0.1105753871069409</v>
+        <v>0.1107869208880863</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8968433496744129</v>
+        <v>0.8832548140732854</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1269440793241185</v>
+        <v>0.1277314454907438</v>
       </c>
       <c r="C68">
-        <v>-1557.788516568908</v>
+        <v>-1907.178196339963</v>
       </c>
       <c r="D68">
-        <v>11342.5054834311</v>
+        <v>11238.02480366004</v>
       </c>
       <c r="E68">
-        <v>13104.594</v>
+        <v>13349.503</v>
       </c>
       <c r="F68">
-        <v>16163.994</v>
+        <v>16408.903</v>
       </c>
       <c r="G68">
         <v>3263.7</v>
@@ -6869,37 +6869,37 @@
         <v>1778</v>
       </c>
       <c r="M68">
-        <v>2013.009124513502</v>
+        <v>2043.509262763706</v>
       </c>
       <c r="N68">
-        <v>-235.0091245135018</v>
+        <v>-265.5092627637064</v>
       </c>
       <c r="O68">
-        <v>-29.37614056418772</v>
+        <v>-33.1886578454633</v>
       </c>
       <c r="P68">
-        <v>-205.6329839493141</v>
+        <v>-232.3206049182431</v>
       </c>
       <c r="Q68">
-        <v>1052.567016050686</v>
+        <v>1025.879395081757</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1583079751117104</v>
+        <v>0.1617173076908532</v>
       </c>
       <c r="T68">
-        <v>2.192989845911187</v>
+        <v>2.259444083666072</v>
       </c>
       <c r="U68">
         <v>0.1245366166625341</v>
       </c>
       <c r="V68">
-        <v>0.1104068517591607</v>
+        <v>0.1087589883000687</v>
       </c>
       <c r="W68">
-        <v>0.1107869208880863</v>
+        <v>0.1109921402280034</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8832548140732854</v>
+        <v>0.8700719064005498</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1277314454907438</v>
+        <v>0.1285188116573692</v>
       </c>
       <c r="C69">
-        <v>-1907.178196339963</v>
+        <v>-2254.66061208714</v>
       </c>
       <c r="D69">
-        <v>11238.02480366004</v>
+        <v>11135.45138791286</v>
       </c>
       <c r="E69">
-        <v>13349.503</v>
+        <v>13594.412</v>
       </c>
       <c r="F69">
-        <v>16408.903</v>
+        <v>16653.812</v>
       </c>
       <c r="G69">
         <v>3263.7</v>
@@ -6951,37 +6951,37 @@
         <v>1778</v>
       </c>
       <c r="M69">
-        <v>2043.509262763706</v>
+        <v>2074.009401013911</v>
       </c>
       <c r="N69">
-        <v>-265.5092627637064</v>
+        <v>-296.0094010139107</v>
       </c>
       <c r="O69">
-        <v>-33.1886578454633</v>
+        <v>-37.00117512673884</v>
       </c>
       <c r="P69">
-        <v>-232.3206049182431</v>
+        <v>-259.0082258871719</v>
       </c>
       <c r="Q69">
-        <v>1025.879395081757</v>
+        <v>999.1917741128282</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1617173076908532</v>
+        <v>0.1653397235561923</v>
       </c>
       <c r="T69">
-        <v>2.259444083666072</v>
+        <v>2.330051711280636</v>
       </c>
       <c r="U69">
         <v>0.1245366166625341</v>
       </c>
       <c r="V69">
-        <v>0.1087589883000687</v>
+        <v>0.107159591413303</v>
       </c>
       <c r="W69">
-        <v>0.1109921402280034</v>
+        <v>0.1111913237049818</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8700719064005498</v>
+        <v>0.8572767313064241</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1285188116573692</v>
+        <v>0.1293061778239945</v>
       </c>
       <c r="C70">
-        <v>-2254.66061208714</v>
+        <v>-2600.287516261742</v>
       </c>
       <c r="D70">
-        <v>11135.45138791286</v>
+        <v>11034.73348373826</v>
       </c>
       <c r="E70">
-        <v>13594.412</v>
+        <v>13839.321</v>
       </c>
       <c r="F70">
-        <v>16653.812</v>
+        <v>16898.721</v>
       </c>
       <c r="G70">
         <v>3263.7</v>
@@ -7033,37 +7033,37 @@
         <v>1778</v>
       </c>
       <c r="M70">
-        <v>2074.009401013911</v>
+        <v>2104.509539264115</v>
       </c>
       <c r="N70">
-        <v>-296.0094010139107</v>
+        <v>-326.5095392641153</v>
       </c>
       <c r="O70">
-        <v>-37.00117512673884</v>
+        <v>-40.81369240801442</v>
       </c>
       <c r="P70">
-        <v>-259.0082258871719</v>
+        <v>-285.695846856101</v>
       </c>
       <c r="Q70">
-        <v>999.1917741128282</v>
+        <v>972.5041531438991</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1653397235561923</v>
+        <v>0.1691958436709082</v>
       </c>
       <c r="T70">
-        <v>2.330051711280636</v>
+        <v>2.405214669709044</v>
       </c>
       <c r="U70">
         <v>0.1245366166625341</v>
       </c>
       <c r="V70">
-        <v>0.107159591413303</v>
+        <v>0.1056065538565885</v>
       </c>
       <c r="W70">
-        <v>0.1111913237049818</v>
+        <v>0.1113847337478449</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8572767313064241</v>
+        <v>0.8448524308527078</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1293061778239945</v>
+        <v>0.1300935439906198</v>
       </c>
       <c r="C71">
-        <v>-2600.287516261742</v>
+        <v>-2944.108805736592</v>
       </c>
       <c r="D71">
-        <v>11034.73348373826</v>
+        <v>10935.82119426341</v>
       </c>
       <c r="E71">
-        <v>13839.321</v>
+        <v>14084.23</v>
       </c>
       <c r="F71">
-        <v>16898.721</v>
+        <v>17143.63</v>
       </c>
       <c r="G71">
         <v>3263.7</v>
@@ -7115,37 +7115,37 @@
         <v>1778</v>
       </c>
       <c r="M71">
-        <v>2104.509539264115</v>
+        <v>2135.00967751432</v>
       </c>
       <c r="N71">
-        <v>-326.5095392641153</v>
+        <v>-357.0096775143199</v>
       </c>
       <c r="O71">
-        <v>-40.81369240801442</v>
+        <v>-44.62620968928999</v>
       </c>
       <c r="P71">
-        <v>-285.695846856101</v>
+        <v>-312.3834678250299</v>
       </c>
       <c r="Q71">
-        <v>972.5041531438991</v>
+        <v>945.8165321749701</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1691958436709082</v>
+        <v>0.1733090384599384</v>
       </c>
       <c r="T71">
-        <v>2.405214669709044</v>
+        <v>2.485388492032679</v>
       </c>
       <c r="U71">
         <v>0.1245366166625341</v>
       </c>
       <c r="V71">
-        <v>0.1056065538565885</v>
+        <v>0.1040978888014944</v>
       </c>
       <c r="W71">
-        <v>0.1113847337478449</v>
+        <v>0.1115726177894833</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8448524308527078</v>
+        <v>0.8327831104119549</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1300935439906198</v>
+        <v>0.1308809101572452</v>
       </c>
       <c r="C72">
-        <v>-2944.108805736592</v>
+        <v>-3286.172604231684</v>
       </c>
       <c r="D72">
-        <v>10935.82119426341</v>
+        <v>10838.66639576832</v>
       </c>
       <c r="E72">
-        <v>14084.23</v>
+        <v>14329.139</v>
       </c>
       <c r="F72">
-        <v>17143.63</v>
+        <v>17388.539</v>
       </c>
       <c r="G72">
         <v>3263.7</v>
@@ -7197,37 +7197,37 @@
         <v>1778</v>
       </c>
       <c r="M72">
-        <v>2135.00967751432</v>
+        <v>2165.509815764525</v>
       </c>
       <c r="N72">
-        <v>-357.0096775143199</v>
+        <v>-387.509815764525</v>
       </c>
       <c r="O72">
-        <v>-44.62620968928999</v>
+        <v>-48.43872697056563</v>
       </c>
       <c r="P72">
-        <v>-312.3834678250299</v>
+        <v>-339.0710887939593</v>
       </c>
       <c r="Q72">
-        <v>945.8165321749701</v>
+        <v>919.1289112060407</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1733090384599384</v>
+        <v>0.1777059018551088</v>
       </c>
       <c r="T72">
-        <v>2.485388492032679</v>
+        <v>2.571091543482082</v>
       </c>
       <c r="U72">
         <v>0.1245366166625341</v>
       </c>
       <c r="V72">
-        <v>0.1040978888014944</v>
+        <v>0.102631721353586</v>
       </c>
       <c r="W72">
-        <v>0.1115726177894833</v>
+        <v>0.1117552093229065</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8327831104119549</v>
+        <v>0.8210537708286877</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1308809101572452</v>
+        <v>0.1316682763238705</v>
       </c>
       <c r="C73">
-        <v>-3286.17260423168</v>
+        <v>-3626.525340384786</v>
       </c>
       <c r="D73">
-        <v>10838.66639576832</v>
+        <v>10743.22265961522</v>
       </c>
       <c r="E73">
-        <v>14329.139</v>
+        <v>14574.048</v>
       </c>
       <c r="F73">
-        <v>17388.539</v>
+        <v>17633.448</v>
       </c>
       <c r="G73">
         <v>3263.7</v>
@@ -7279,37 +7279,37 @@
         <v>1778</v>
       </c>
       <c r="M73">
-        <v>2165.509815764524</v>
+        <v>2196.009954014728</v>
       </c>
       <c r="N73">
-        <v>-387.5098157645245</v>
+        <v>-418.0099540147287</v>
       </c>
       <c r="O73">
-        <v>-48.43872697056557</v>
+        <v>-52.25124425184109</v>
       </c>
       <c r="P73">
-        <v>-339.071088793959</v>
+        <v>-365.7587097628876</v>
       </c>
       <c r="Q73">
-        <v>919.128911206041</v>
+        <v>892.4412902371124</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1777059018551087</v>
+        <v>0.1824168269213626</v>
       </c>
       <c r="T73">
-        <v>2.571091543482081</v>
+        <v>2.662916241463584</v>
       </c>
       <c r="U73">
         <v>0.1245366166625341</v>
       </c>
       <c r="V73">
-        <v>0.102631721353586</v>
+        <v>0.1012062807792306</v>
       </c>
       <c r="W73">
-        <v>0.1117552093229065</v>
+        <v>0.1119327288692903</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8210537708286878</v>
+        <v>0.8096502462338451</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1316682763238705</v>
+        <v>0.1535967368354751</v>
       </c>
       <c r="C74">
-        <v>-3626.525340384786</v>
+        <v>-5987.271265884727</v>
       </c>
       <c r="D74">
-        <v>10743.22265961522</v>
+        <v>8627.385734115274</v>
       </c>
       <c r="E74">
-        <v>14574.048</v>
+        <v>14818.957</v>
       </c>
       <c r="F74">
-        <v>17633.448</v>
+        <v>17878.357</v>
       </c>
       <c r="G74">
         <v>3263.7</v>
@@ -7361,45 +7361,45 @@
         <v>1778</v>
       </c>
       <c r="M74">
-        <v>2196.009954014728</v>
+        <v>2730.679759664933</v>
       </c>
       <c r="N74">
-        <v>-418.0099540147287</v>
+        <v>-952.6797596649333</v>
       </c>
       <c r="O74">
-        <v>-52.25124425184109</v>
+        <v>-119.0849699581167</v>
       </c>
       <c r="P74">
-        <v>-365.7587097628876</v>
+        <v>-833.5947897068166</v>
       </c>
       <c r="Q74">
-        <v>892.4412902371124</v>
+        <v>424.6052102931834</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1824168269213626</v>
+        <v>0.1895326143813363</v>
       </c>
       <c r="T74">
-        <v>2.662916241463584</v>
+        <v>2.801616183666705</v>
       </c>
       <c r="U74">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V74">
-        <v>0.1012062807792306</v>
+        <v>0.08138999061071558</v>
       </c>
       <c r="W74">
-        <v>0.1119327288692903</v>
+        <v>0.140305384866458</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8096502462338451</v>
+        <v>0.6511199248857247</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1535967368354751</v>
+        <v>0.1952664142234084</v>
       </c>
       <c r="C75">
-        <v>-5987.271265884727</v>
+        <v>-8581.67069071639</v>
       </c>
       <c r="D75">
-        <v>8627.385734115274</v>
+        <v>6277.895309283609</v>
       </c>
       <c r="E75">
-        <v>14818.957</v>
+        <v>15063.866</v>
       </c>
       <c r="F75">
-        <v>17878.357</v>
+        <v>18123.266</v>
       </c>
       <c r="G75">
         <v>3263.7</v>
@@ -7443,45 +7443,45 @@
         <v>1778</v>
       </c>
       <c r="M75">
-        <v>2730.679759664933</v>
+        <v>3746.742695715137</v>
       </c>
       <c r="N75">
-        <v>-952.6797596649333</v>
+        <v>-1968.742695715138</v>
       </c>
       <c r="O75">
-        <v>-119.0849699581167</v>
+        <v>-246.0928369643922</v>
       </c>
       <c r="P75">
-        <v>-833.5947897068166</v>
+        <v>-1722.649858750745</v>
       </c>
       <c r="Q75">
-        <v>424.6052102931834</v>
+        <v>-464.4498587507453</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1895326143813363</v>
+        <v>0.1975235273241105</v>
       </c>
       <c r="T75">
-        <v>2.801616183666705</v>
+        <v>2.957373950399814</v>
       </c>
       <c r="U75">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.08138999061071558</v>
+        <v>0.05931819130632329</v>
       </c>
       <c r="W75">
-        <v>0.140305384866458</v>
+        <v>0.1944733744853239</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.6511199248857247</v>
+        <v>0.4745455304505863</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1952664142234084</v>
+        <v>0.1968757803900337</v>
       </c>
       <c r="C76">
-        <v>-8581.67069071639</v>
+        <v>-8891.922717682011</v>
       </c>
       <c r="D76">
-        <v>6277.895309283609</v>
+        <v>6212.552282317992</v>
       </c>
       <c r="E76">
-        <v>15063.866</v>
+        <v>15308.775</v>
       </c>
       <c r="F76">
-        <v>18123.266</v>
+        <v>18368.175</v>
       </c>
       <c r="G76">
         <v>3263.7</v>
@@ -7525,37 +7525,37 @@
         <v>1778</v>
       </c>
       <c r="M76">
-        <v>3746.742695715137</v>
+        <v>3797.374353765343</v>
       </c>
       <c r="N76">
-        <v>-1968.742695715138</v>
+        <v>-2019.374353765343</v>
       </c>
       <c r="O76">
-        <v>-246.0928369643922</v>
+        <v>-252.4217942206679</v>
       </c>
       <c r="P76">
-        <v>-1722.649858750745</v>
+        <v>-1766.952559544675</v>
       </c>
       <c r="Q76">
-        <v>-464.4498587507453</v>
+        <v>-508.752559544675</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1975235273241105</v>
+        <v>0.203592468417075</v>
       </c>
       <c r="T76">
-        <v>2.957373950399814</v>
+        <v>3.075668908415807</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05931819130632329</v>
+        <v>0.05852728208890564</v>
       </c>
       <c r="W76">
-        <v>0.1944733744853239</v>
+        <v>0.19463688438102</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4745455304505863</v>
+        <v>0.4682182567112452</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1968757803900337</v>
+        <v>0.1984851465566591</v>
       </c>
       <c r="C77">
-        <v>-8891.922717682011</v>
+        <v>-9200.828520228275</v>
       </c>
       <c r="D77">
-        <v>6212.552282317992</v>
+        <v>6148.555479771728</v>
       </c>
       <c r="E77">
-        <v>15308.775</v>
+        <v>15553.684</v>
       </c>
       <c r="F77">
-        <v>18368.175</v>
+        <v>18613.084</v>
       </c>
       <c r="G77">
         <v>3263.7</v>
@@ -7607,37 +7607,37 @@
         <v>1778</v>
       </c>
       <c r="M77">
-        <v>3797.374353765343</v>
+        <v>3848.006011815547</v>
       </c>
       <c r="N77">
-        <v>-2019.374353765343</v>
+        <v>-2070.006011815548</v>
       </c>
       <c r="O77">
-        <v>-252.4217942206679</v>
+        <v>-258.7507514769435</v>
       </c>
       <c r="P77">
-        <v>-1766.952559544675</v>
+        <v>-1811.255260338604</v>
       </c>
       <c r="Q77">
-        <v>-508.752559544675</v>
+        <v>-553.0552603386043</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.203592468417075</v>
+        <v>0.2101671546011197</v>
       </c>
       <c r="T77">
-        <v>3.075668908415807</v>
+        <v>3.203821779599799</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05852728208890564</v>
+        <v>0.05775718627194635</v>
       </c>
       <c r="W77">
-        <v>0.19463688438102</v>
+        <v>0.1947960913847241</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4682182567112452</v>
+        <v>0.4620574901755707</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1984851465566591</v>
+        <v>0.2000945127232844</v>
       </c>
       <c r="C78">
-        <v>-9200.828520228275</v>
+        <v>-9508.429277380714</v>
       </c>
       <c r="D78">
-        <v>6148.555479771728</v>
+        <v>6085.863722619288</v>
       </c>
       <c r="E78">
-        <v>15553.684</v>
+        <v>15798.593</v>
       </c>
       <c r="F78">
-        <v>18613.084</v>
+        <v>18857.993</v>
       </c>
       <c r="G78">
         <v>3263.7</v>
@@ -7689,37 +7689,37 @@
         <v>1778</v>
       </c>
       <c r="M78">
-        <v>3848.006011815547</v>
+        <v>3898.637669865752</v>
       </c>
       <c r="N78">
-        <v>-2070.006011815548</v>
+        <v>-2120.637669865752</v>
       </c>
       <c r="O78">
-        <v>-258.7507514769435</v>
+        <v>-265.079708733219</v>
       </c>
       <c r="P78">
-        <v>-1811.255260338604</v>
+        <v>-1855.557961132533</v>
       </c>
       <c r="Q78">
-        <v>-553.0552603386043</v>
+        <v>-597.3579611325333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2101671546011197</v>
+        <v>0.2173135526272554</v>
       </c>
       <c r="T78">
-        <v>3.203821779599799</v>
+        <v>3.343118378712834</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05775718627194635</v>
+        <v>0.05700709294373926</v>
       </c>
       <c r="W78">
-        <v>0.1947960913847241</v>
+        <v>0.1949511631415788</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4620574901755707</v>
+        <v>0.456056743549914</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2000945127232844</v>
+        <v>0.2017038788899098</v>
       </c>
       <c r="C79">
-        <v>-9508.429277380714</v>
+        <v>-9814.764505641795</v>
       </c>
       <c r="D79">
-        <v>6085.863722619288</v>
+        <v>6024.437494358207</v>
       </c>
       <c r="E79">
-        <v>15798.593</v>
+        <v>16043.502</v>
       </c>
       <c r="F79">
-        <v>18857.993</v>
+        <v>19102.902</v>
       </c>
       <c r="G79">
         <v>3263.7</v>
@@ -7771,37 +7771,37 @@
         <v>1778</v>
       </c>
       <c r="M79">
-        <v>3898.637669865752</v>
+        <v>3949.269327915956</v>
       </c>
       <c r="N79">
-        <v>-2120.637669865752</v>
+        <v>-2171.269327915957</v>
       </c>
       <c r="O79">
-        <v>-265.079708733219</v>
+        <v>-271.4086659894946</v>
       </c>
       <c r="P79">
-        <v>-1855.557961132533</v>
+        <v>-1899.860661926462</v>
       </c>
       <c r="Q79">
-        <v>-597.3579611325333</v>
+        <v>-641.6606619264619</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2173135526272554</v>
+        <v>0.2251096232012215</v>
       </c>
       <c r="T79">
-        <v>3.343118378712834</v>
+        <v>3.495078305017963</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05700709294373926</v>
+        <v>0.05627623277779389</v>
       </c>
       <c r="W79">
-        <v>0.1949511631415788</v>
+        <v>0.1951022586995398</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.456056743549914</v>
+        <v>0.450209862222351</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2017038788899098</v>
+        <v>0.2033132450565351</v>
       </c>
       <c r="C80">
-        <v>-9814.764505641795</v>
+        <v>-10119.87214205394</v>
       </c>
       <c r="D80">
-        <v>6024.437494358207</v>
+        <v>5964.238857946066</v>
       </c>
       <c r="E80">
-        <v>16043.502</v>
+        <v>16288.411</v>
       </c>
       <c r="F80">
-        <v>19102.902</v>
+        <v>19347.811</v>
       </c>
       <c r="G80">
         <v>3263.7</v>
@@ -7853,37 +7853,37 @@
         <v>1778</v>
       </c>
       <c r="M80">
-        <v>3949.269327915956</v>
+        <v>3999.900985966161</v>
       </c>
       <c r="N80">
-        <v>-2171.269327915957</v>
+        <v>-2221.900985966161</v>
       </c>
       <c r="O80">
-        <v>-271.4086659894946</v>
+        <v>-277.7376232457701</v>
       </c>
       <c r="P80">
-        <v>-1899.860661926462</v>
+        <v>-1944.163362720391</v>
       </c>
       <c r="Q80">
-        <v>-641.6606619264619</v>
+        <v>-685.9633627203909</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2251096232012215</v>
+        <v>0.2336481766869941</v>
       </c>
       <c r="T80">
-        <v>3.495078305017963</v>
+        <v>3.661510605256914</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05627623277779389</v>
+        <v>0.05556387540085978</v>
       </c>
       <c r="W80">
-        <v>0.1951022586995398</v>
+        <v>0.1952495290535017</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.450209862222351</v>
+        <v>0.4445110032068783</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2033132450565351</v>
+        <v>0.2049226112231605</v>
       </c>
       <c r="C81">
-        <v>-10119.87214205394</v>
+        <v>-10423.78862233184</v>
       </c>
       <c r="D81">
-        <v>5964.238857946066</v>
+        <v>5905.23137766816</v>
       </c>
       <c r="E81">
-        <v>16288.411</v>
+        <v>16533.32</v>
       </c>
       <c r="F81">
-        <v>19347.811</v>
+        <v>19592.72</v>
       </c>
       <c r="G81">
         <v>3263.7</v>
@@ -7935,37 +7935,37 @@
         <v>1778</v>
       </c>
       <c r="M81">
-        <v>3999.900985966161</v>
+        <v>4050.532644016365</v>
       </c>
       <c r="N81">
-        <v>-2221.900985966161</v>
+        <v>-2272.532644016365</v>
       </c>
       <c r="O81">
-        <v>-277.7376232457701</v>
+        <v>-284.0665805020457</v>
       </c>
       <c r="P81">
-        <v>-1944.163362720391</v>
+        <v>-1988.46606351432</v>
       </c>
       <c r="Q81">
-        <v>-685.9633627203909</v>
+        <v>-730.2660635143195</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2336481766869941</v>
+        <v>0.2430405855213437</v>
       </c>
       <c r="T81">
-        <v>3.661510605256914</v>
+        <v>3.844586135519759</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05556387540085978</v>
+        <v>0.05486932695834904</v>
       </c>
       <c r="W81">
-        <v>0.1952495290535017</v>
+        <v>0.1953931176486146</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4445110032068783</v>
+        <v>0.4389546156667924</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2049226112231605</v>
+        <v>0.2065319773897858</v>
       </c>
       <c r="C82">
-        <v>-10423.78862233184</v>
+        <v>-10726.5489544022</v>
       </c>
       <c r="D82">
-        <v>5905.23137766816</v>
+        <v>5847.380045597797</v>
       </c>
       <c r="E82">
-        <v>16533.32</v>
+        <v>16778.229</v>
       </c>
       <c r="F82">
-        <v>19592.72</v>
+        <v>19837.629</v>
       </c>
       <c r="G82">
         <v>3263.7</v>
@@ -8017,37 +8017,37 @@
         <v>1778</v>
       </c>
       <c r="M82">
-        <v>4050.532644016365</v>
+        <v>4101.16430206657</v>
       </c>
       <c r="N82">
-        <v>-2272.532644016365</v>
+        <v>-2323.16430206657</v>
       </c>
       <c r="O82">
-        <v>-284.0665805020457</v>
+        <v>-290.3955377583212</v>
       </c>
       <c r="P82">
-        <v>-1988.46606351432</v>
+        <v>-2032.768764308249</v>
       </c>
       <c r="Q82">
-        <v>-730.2660635143195</v>
+        <v>-774.5687643082485</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2430405855213437</v>
+        <v>0.2534216689698355</v>
       </c>
       <c r="T82">
-        <v>3.844586135519759</v>
+        <v>4.046932774231326</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.05486932695834904</v>
+        <v>0.05419192786009782</v>
       </c>
       <c r="W82">
-        <v>0.1953931176486146</v>
+        <v>0.1955331608463173</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4389546156667924</v>
+        <v>0.4335354228807826</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2065319773897858</v>
+        <v>0.2081413435564111</v>
       </c>
       <c r="C83">
-        <v>-10726.5489544022</v>
+        <v>-11028.18678766274</v>
       </c>
       <c r="D83">
-        <v>5847.380045597797</v>
+        <v>5790.651212337264</v>
       </c>
       <c r="E83">
-        <v>16778.229</v>
+        <v>17023.138</v>
       </c>
       <c r="F83">
-        <v>19837.629</v>
+        <v>20082.538</v>
       </c>
       <c r="G83">
         <v>3263.7</v>
@@ -8099,37 +8099,37 @@
         <v>1778</v>
       </c>
       <c r="M83">
-        <v>4101.16430206657</v>
+        <v>4151.795960116775</v>
       </c>
       <c r="N83">
-        <v>-2323.16430206657</v>
+        <v>-2373.795960116775</v>
       </c>
       <c r="O83">
-        <v>-290.3955377583212</v>
+        <v>-296.7244950145969</v>
       </c>
       <c r="P83">
-        <v>-2032.768764308249</v>
+        <v>-2077.071465102178</v>
       </c>
       <c r="Q83">
-        <v>-774.5687643082485</v>
+        <v>-818.871465102178</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2534216689698355</v>
+        <v>0.2649562061348263</v>
       </c>
       <c r="T83">
-        <v>4.046932774231326</v>
+        <v>4.271762372799733</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.05419192786009782</v>
+        <v>0.05353105069107223</v>
       </c>
       <c r="W83">
-        <v>0.1955331608463173</v>
+        <v>0.1956697883562712</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4335354228807826</v>
+        <v>0.4282484055285779</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2081413435564111</v>
+        <v>0.2097507097230365</v>
       </c>
       <c r="C84">
-        <v>-11028.18678766274</v>
+        <v>-11328.73447824836</v>
       </c>
       <c r="D84">
-        <v>5790.651212337264</v>
+        <v>5735.012521751649</v>
       </c>
       <c r="E84">
-        <v>17023.138</v>
+        <v>17268.047</v>
       </c>
       <c r="F84">
-        <v>20082.538</v>
+        <v>20327.447</v>
       </c>
       <c r="G84">
         <v>3263.7</v>
@@ -8181,37 +8181,37 @@
         <v>1778</v>
       </c>
       <c r="M84">
-        <v>4151.795960116775</v>
+        <v>4202.427618166979</v>
       </c>
       <c r="N84">
-        <v>-2373.795960116775</v>
+        <v>-2424.427618166979</v>
       </c>
       <c r="O84">
-        <v>-296.7244950145969</v>
+        <v>-303.0534522708724</v>
       </c>
       <c r="P84">
-        <v>-2077.071465102178</v>
+        <v>-2121.374165896107</v>
       </c>
       <c r="Q84">
-        <v>-818.871465102178</v>
+        <v>-863.1741658961071</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2649562061348263</v>
+        <v>0.2778477476721691</v>
       </c>
       <c r="T84">
-        <v>4.271762372799733</v>
+        <v>4.523042512376188</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.05353105069107223</v>
+        <v>0.05288609827310751</v>
       </c>
       <c r="W84">
-        <v>0.1956697883562712</v>
+        <v>0.1958031236370696</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4282484055285779</v>
+        <v>0.4230887861848601</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2097507097230365</v>
+        <v>0.2113600758896618</v>
       </c>
       <c r="C85">
-        <v>-11328.73447824836</v>
+        <v>-11628.2231505706</v>
       </c>
       <c r="D85">
-        <v>5735.012521751649</v>
+        <v>5680.432849429407</v>
       </c>
       <c r="E85">
-        <v>17268.047</v>
+        <v>17512.956</v>
       </c>
       <c r="F85">
-        <v>20327.447</v>
+        <v>20572.356</v>
       </c>
       <c r="G85">
         <v>3263.7</v>
@@ -8263,37 +8263,37 @@
         <v>1778</v>
       </c>
       <c r="M85">
-        <v>4202.427618166979</v>
+        <v>4253.059276217184</v>
       </c>
       <c r="N85">
-        <v>-2424.427618166979</v>
+        <v>-2475.059276217184</v>
       </c>
       <c r="O85">
-        <v>-303.0534522708724</v>
+        <v>-309.382409527148</v>
       </c>
       <c r="P85">
-        <v>-2121.374165896107</v>
+        <v>-2165.676866690036</v>
       </c>
       <c r="Q85">
-        <v>-863.1741658961071</v>
+        <v>-907.4768666900356</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2778477476721691</v>
+        <v>0.2923507319016797</v>
       </c>
       <c r="T85">
-        <v>4.523042512376188</v>
+        <v>4.805732669399701</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.05288609827310751</v>
+        <v>0.05225650186509433</v>
       </c>
       <c r="W85">
-        <v>0.1958031236370696</v>
+        <v>0.1959332842683251</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4230887861848601</v>
+        <v>0.4180520149207546</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2113600758896618</v>
+        <v>0.2129694420562872</v>
       </c>
       <c r="C86">
-        <v>-11628.22315057059</v>
+        <v>-11926.68275537618</v>
       </c>
       <c r="D86">
-        <v>5680.432849429407</v>
+        <v>5626.882244623822</v>
       </c>
       <c r="E86">
-        <v>17512.956</v>
+        <v>17757.865</v>
       </c>
       <c r="F86">
-        <v>20572.356</v>
+        <v>20817.265</v>
       </c>
       <c r="G86">
         <v>3263.7</v>
@@ -8345,37 +8345,37 @@
         <v>1778</v>
       </c>
       <c r="M86">
-        <v>4253.059276217184</v>
+        <v>4303.690934267388</v>
       </c>
       <c r="N86">
-        <v>-2475.059276217184</v>
+        <v>-2525.690934267388</v>
       </c>
       <c r="O86">
-        <v>-309.382409527148</v>
+        <v>-315.7113667834235</v>
       </c>
       <c r="P86">
-        <v>-2165.676866690036</v>
+        <v>-2209.979567483964</v>
       </c>
       <c r="Q86">
-        <v>-907.4768666900356</v>
+        <v>-951.7795674839642</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2923507319016796</v>
+        <v>0.3087874473617915</v>
       </c>
       <c r="T86">
-        <v>4.805732669399698</v>
+        <v>5.126114847359678</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.05225650186509433</v>
+        <v>0.05164171949021086</v>
       </c>
       <c r="W86">
-        <v>0.1959332842683251</v>
+        <v>0.1960603822964923</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4180520149207546</v>
+        <v>0.413133755921687</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2129694420562872</v>
+        <v>0.2145788082229125</v>
       </c>
       <c r="C87">
-        <v>-11926.68275537618</v>
+        <v>-12224.14212455223</v>
       </c>
       <c r="D87">
-        <v>5626.882244623822</v>
+        <v>5574.331875447769</v>
       </c>
       <c r="E87">
-        <v>17757.865</v>
+        <v>18002.774</v>
       </c>
       <c r="F87">
-        <v>20817.265</v>
+        <v>21062.174</v>
       </c>
       <c r="G87">
         <v>3263.7</v>
@@ -8427,37 +8427,37 @@
         <v>1778</v>
       </c>
       <c r="M87">
-        <v>4303.690934267388</v>
+        <v>4354.322592317593</v>
       </c>
       <c r="N87">
-        <v>-2525.690934267388</v>
+        <v>-2576.322592317593</v>
       </c>
       <c r="O87">
-        <v>-315.7113667834235</v>
+        <v>-322.0403240396992</v>
       </c>
       <c r="P87">
-        <v>-2209.979567483964</v>
+        <v>-2254.282268277894</v>
       </c>
       <c r="Q87">
-        <v>-951.7795674839642</v>
+        <v>-996.0822682778942</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3087874473617915</v>
+        <v>0.327572265030491</v>
       </c>
       <c r="T87">
-        <v>5.126114847359678</v>
+        <v>5.492265907885369</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.05164171949021086</v>
+        <v>0.05104123437985957</v>
       </c>
       <c r="W87">
-        <v>0.1960603822964923</v>
+        <v>0.1961845245565625</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.413133755921687</v>
+        <v>0.4083298750388766</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2145788082229125</v>
+        <v>0.2161881743895379</v>
       </c>
       <c r="C88">
-        <v>-12224.14212455223</v>
+        <v>-12520.62902288892</v>
       </c>
       <c r="D88">
-        <v>5574.331875447769</v>
+        <v>5522.753977111085</v>
       </c>
       <c r="E88">
-        <v>18002.774</v>
+        <v>18247.683</v>
       </c>
       <c r="F88">
-        <v>21062.174</v>
+        <v>21307.083</v>
       </c>
       <c r="G88">
         <v>3263.7</v>
@@ -8509,37 +8509,37 @@
         <v>1778</v>
       </c>
       <c r="M88">
-        <v>4354.322592317593</v>
+        <v>4404.954250367798</v>
       </c>
       <c r="N88">
-        <v>-2576.322592317593</v>
+        <v>-2626.954250367798</v>
       </c>
       <c r="O88">
-        <v>-322.0403240396992</v>
+        <v>-328.3692812959747</v>
       </c>
       <c r="P88">
-        <v>-2254.282268277894</v>
+        <v>-2298.584969071823</v>
       </c>
       <c r="Q88">
-        <v>-996.0822682778942</v>
+        <v>-1040.384969071823</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.327572265030491</v>
+        <v>0.349247054648221</v>
       </c>
       <c r="T88">
-        <v>5.492265907885369</v>
+        <v>5.914747900799628</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.05104123437985957</v>
+        <v>0.05045455352491866</v>
       </c>
       <c r="W88">
-        <v>0.1961845245565625</v>
+        <v>0.1963058129715737</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4083298750388766</v>
+        <v>0.4036364281993493</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2161881743895379</v>
+        <v>0.2177975405561632</v>
       </c>
       <c r="C89">
-        <v>-12520.62902288892</v>
+        <v>-12816.17019699475</v>
       </c>
       <c r="D89">
-        <v>5522.753977111085</v>
+        <v>5472.121803005256</v>
       </c>
       <c r="E89">
-        <v>18247.683</v>
+        <v>18492.592</v>
       </c>
       <c r="F89">
-        <v>21307.083</v>
+        <v>21551.992</v>
       </c>
       <c r="G89">
         <v>3263.7</v>
@@ -8591,37 +8591,37 @@
         <v>1778</v>
       </c>
       <c r="M89">
-        <v>4404.954250367798</v>
+        <v>4455.585908418002</v>
       </c>
       <c r="N89">
-        <v>-2626.954250367798</v>
+        <v>-2677.585908418002</v>
       </c>
       <c r="O89">
-        <v>-328.3692812959747</v>
+        <v>-334.6982385522502</v>
       </c>
       <c r="P89">
-        <v>-2298.584969071823</v>
+        <v>-2342.887669865752</v>
       </c>
       <c r="Q89">
-        <v>-1040.384969071823</v>
+        <v>-1084.687669865752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.349247054648221</v>
+        <v>0.3745343092022395</v>
       </c>
       <c r="T89">
-        <v>5.914747900799628</v>
+        <v>6.407643559199598</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.05045455352491866</v>
+        <v>0.04988120632577185</v>
       </c>
       <c r="W89">
-        <v>0.1963058129715737</v>
+        <v>0.1964243448316982</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4036364281993493</v>
+        <v>0.3990496506061749</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2177975405561632</v>
+        <v>0.2194069067227885</v>
       </c>
       <c r="C90">
-        <v>-12816.17019699475</v>
+        <v>-13110.79142154563</v>
       </c>
       <c r="D90">
-        <v>5472.121803005256</v>
+        <v>5422.409578454375</v>
       </c>
       <c r="E90">
-        <v>18492.592</v>
+        <v>18737.501</v>
       </c>
       <c r="F90">
-        <v>21551.992</v>
+        <v>21796.901</v>
       </c>
       <c r="G90">
         <v>3263.7</v>
@@ -8673,37 +8673,37 @@
         <v>1778</v>
       </c>
       <c r="M90">
-        <v>4455.585908418002</v>
+        <v>4506.217566468206</v>
       </c>
       <c r="N90">
-        <v>-2677.585908418002</v>
+        <v>-2728.217566468206</v>
       </c>
       <c r="O90">
-        <v>-334.6982385522502</v>
+        <v>-341.0271958085258</v>
       </c>
       <c r="P90">
-        <v>-2342.887669865752</v>
+        <v>-2387.19037065968</v>
       </c>
       <c r="Q90">
-        <v>-1084.687669865752</v>
+        <v>-1128.99037065968</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3745343092022395</v>
+        <v>0.4044192464024431</v>
       </c>
       <c r="T90">
-        <v>6.407643559199598</v>
+        <v>6.990156610035926</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04988120632577185</v>
+        <v>0.04932074333334745</v>
       </c>
       <c r="W90">
-        <v>0.1964243448316982</v>
+        <v>0.1965402130545166</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3990496506061749</v>
+        <v>0.3945659466667797</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2194069067227885</v>
+        <v>0.2210162728894139</v>
       </c>
       <c r="C91">
-        <v>-13110.79142154563</v>
+        <v>-13404.51754303565</v>
       </c>
       <c r="D91">
-        <v>5422.409578454375</v>
+        <v>5373.592456964347</v>
       </c>
       <c r="E91">
-        <v>18737.501</v>
+        <v>18982.41</v>
       </c>
       <c r="F91">
-        <v>21796.901</v>
+        <v>22041.81</v>
       </c>
       <c r="G91">
         <v>3263.7</v>
@@ -8755,37 +8755,37 @@
         <v>1778</v>
       </c>
       <c r="M91">
-        <v>4506.217566468206</v>
+        <v>4556.849224518411</v>
       </c>
       <c r="N91">
-        <v>-2728.217566468206</v>
+        <v>-2778.849224518411</v>
       </c>
       <c r="O91">
-        <v>-341.0271958085258</v>
+        <v>-347.3561530648013</v>
       </c>
       <c r="P91">
-        <v>-2387.19037065968</v>
+        <v>-2431.493071453609</v>
       </c>
       <c r="Q91">
-        <v>-1128.99037065968</v>
+        <v>-1173.293071453609</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4044192464024431</v>
+        <v>0.4402811710426874</v>
       </c>
       <c r="T91">
-        <v>6.990156610035926</v>
+        <v>7.689172271039518</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04932074333334745</v>
+        <v>0.04877273507408804</v>
       </c>
       <c r="W91">
-        <v>0.1965402130545166</v>
+        <v>0.196653506427939</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3945659466667797</v>
+        <v>0.3901818805927043</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2210162728894139</v>
+        <v>0.2226256390560392</v>
       </c>
       <c r="C92">
-        <v>-13404.51754303565</v>
+        <v>-13697.37252118571</v>
       </c>
       <c r="D92">
-        <v>5373.592456964347</v>
+        <v>5325.646478814293</v>
       </c>
       <c r="E92">
-        <v>18982.41</v>
+        <v>19227.319</v>
       </c>
       <c r="F92">
-        <v>22041.81</v>
+        <v>22286.719</v>
       </c>
       <c r="G92">
         <v>3263.7</v>
@@ -8837,37 +8837,37 @@
         <v>1778</v>
       </c>
       <c r="M92">
-        <v>4556.849224518411</v>
+        <v>4607.480882568615</v>
       </c>
       <c r="N92">
-        <v>-2778.849224518411</v>
+        <v>-2829.480882568615</v>
       </c>
       <c r="O92">
-        <v>-347.3561530648013</v>
+        <v>-353.6851103210769</v>
       </c>
       <c r="P92">
-        <v>-2431.493071453609</v>
+        <v>-2475.795772247538</v>
       </c>
       <c r="Q92">
-        <v>-1173.293071453609</v>
+        <v>-1217.595772247538</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4402811710426874</v>
+        <v>0.4841124122696527</v>
       </c>
       <c r="T92">
-        <v>7.689172271039518</v>
+        <v>8.543524745599466</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04877273507408804</v>
+        <v>0.04823677095239477</v>
       </c>
       <c r="W92">
-        <v>0.196653506427939</v>
+        <v>0.1967643098371104</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3901818805927043</v>
+        <v>0.3858941676191582</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2226256390560392</v>
+        <v>0.2242350052226646</v>
       </c>
       <c r="C93">
-        <v>-13697.37252118571</v>
+        <v>-13989.37946815484</v>
       </c>
       <c r="D93">
-        <v>5325.646478814293</v>
+        <v>5278.548531845157</v>
       </c>
       <c r="E93">
-        <v>19227.319</v>
+        <v>19472.228</v>
       </c>
       <c r="F93">
-        <v>22286.719</v>
+        <v>22531.628</v>
       </c>
       <c r="G93">
         <v>3263.7</v>
@@ -8919,37 +8919,37 @@
         <v>1778</v>
       </c>
       <c r="M93">
-        <v>4607.480882568615</v>
+        <v>4658.11254061882</v>
       </c>
       <c r="N93">
-        <v>-2829.480882568615</v>
+        <v>-2880.11254061882</v>
       </c>
       <c r="O93">
-        <v>-353.6851103210769</v>
+        <v>-360.0140675773525</v>
       </c>
       <c r="P93">
-        <v>-2475.795772247538</v>
+        <v>-2520.098473041468</v>
       </c>
       <c r="Q93">
-        <v>-1217.595772247538</v>
+        <v>-1261.898473041467</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4841124122696527</v>
+        <v>0.5389014638033596</v>
       </c>
       <c r="T93">
-        <v>8.543524745599466</v>
+        <v>9.611465338799404</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04823677095239477</v>
+        <v>0.04771245822465134</v>
       </c>
       <c r="W93">
-        <v>0.1967643098371104</v>
+        <v>0.1968727044765172</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3858941676191582</v>
+        <v>0.3816996657972107</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2242350052226646</v>
+        <v>0.2258443713892899</v>
       </c>
       <c r="C94">
-        <v>-13989.37946815484</v>
+        <v>-14280.5606856893</v>
       </c>
       <c r="D94">
-        <v>5278.548531845157</v>
+        <v>5232.276314310709</v>
       </c>
       <c r="E94">
-        <v>19472.228</v>
+        <v>19717.137</v>
       </c>
       <c r="F94">
-        <v>22531.628</v>
+        <v>22776.537</v>
       </c>
       <c r="G94">
         <v>3263.7</v>
@@ -9001,37 +9001,37 @@
         <v>1778</v>
       </c>
       <c r="M94">
-        <v>4658.11254061882</v>
+        <v>4708.744198669026</v>
       </c>
       <c r="N94">
-        <v>-2880.11254061882</v>
+        <v>-2930.744198669026</v>
       </c>
       <c r="O94">
-        <v>-360.0140675773525</v>
+        <v>-366.3430248336282</v>
       </c>
       <c r="P94">
-        <v>-2520.098473041468</v>
+        <v>-2564.401173835397</v>
       </c>
       <c r="Q94">
-        <v>-1261.898473041467</v>
+        <v>-1306.201173835397</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5389014638033596</v>
+        <v>0.6093445300609823</v>
       </c>
       <c r="T94">
-        <v>9.611465338799404</v>
+        <v>10.98453181577075</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04771245822465134</v>
+        <v>0.04719942103944003</v>
       </c>
       <c r="W94">
-        <v>0.1968727044765172</v>
+        <v>0.1969787680484099</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3816996657972107</v>
+        <v>0.3775953683155202</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2258443713892899</v>
+        <v>0.2274537375559152</v>
       </c>
       <c r="C95">
-        <v>-14280.5606856893</v>
+        <v>-14570.93770033454</v>
       </c>
       <c r="D95">
-        <v>5232.276314310709</v>
+        <v>5186.808299665459</v>
       </c>
       <c r="E95">
-        <v>19717.137</v>
+        <v>19962.046</v>
       </c>
       <c r="F95">
-        <v>22776.537</v>
+        <v>23021.446</v>
       </c>
       <c r="G95">
         <v>3263.7</v>
@@ -9083,37 +9083,37 @@
         <v>1778</v>
       </c>
       <c r="M95">
-        <v>4708.744198669026</v>
+        <v>4759.37585671923</v>
       </c>
       <c r="N95">
-        <v>-2930.744198669026</v>
+        <v>-2981.37585671923</v>
       </c>
       <c r="O95">
-        <v>-366.3430248336282</v>
+        <v>-372.6719820899037</v>
       </c>
       <c r="P95">
-        <v>-2564.401173835397</v>
+        <v>-2608.703874629326</v>
       </c>
       <c r="Q95">
-        <v>-1306.201173835397</v>
+        <v>-1350.503874629326</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6093445300609823</v>
+        <v>0.7032686184044795</v>
       </c>
       <c r="T95">
-        <v>10.98453181577075</v>
+        <v>12.81528711839921</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04719942103944003</v>
+        <v>0.04669729953902045</v>
       </c>
       <c r="W95">
-        <v>0.1969787680484099</v>
+        <v>0.1970825749485601</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3775953683155202</v>
+        <v>0.3735783963121637</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2274537375559152</v>
+        <v>0.2290631037225405</v>
       </c>
       <c r="C96">
-        <v>-14570.93770033454</v>
+        <v>-14860.53129682729</v>
       </c>
       <c r="D96">
-        <v>5186.808299665459</v>
+        <v>5142.123703172711</v>
       </c>
       <c r="E96">
-        <v>19962.046</v>
+        <v>20206.955</v>
       </c>
       <c r="F96">
-        <v>23021.446</v>
+        <v>23266.355</v>
       </c>
       <c r="G96">
         <v>3263.7</v>
@@ -9165,37 +9165,37 @@
         <v>1778</v>
       </c>
       <c r="M96">
-        <v>4759.37585671923</v>
+        <v>4810.007514769434</v>
       </c>
       <c r="N96">
-        <v>-2981.37585671923</v>
+        <v>-3032.007514769434</v>
       </c>
       <c r="O96">
-        <v>-372.6719820899037</v>
+        <v>-379.0009393461793</v>
       </c>
       <c r="P96">
-        <v>-2608.703874629326</v>
+        <v>-2653.006575423255</v>
       </c>
       <c r="Q96">
-        <v>-1350.503874629326</v>
+        <v>-1394.806575423255</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7032686184044795</v>
+        <v>0.8347623420853757</v>
       </c>
       <c r="T96">
-        <v>12.81528711839921</v>
+        <v>15.37834454207906</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.04669729953902045</v>
+        <v>0.04620574901755709</v>
       </c>
       <c r="W96">
-        <v>0.1970825749485601</v>
+        <v>0.1971841964402861</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3735783963121637</v>
+        <v>0.3696459921404567</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2290631037225405</v>
+        <v>0.2306724698891659</v>
       </c>
       <c r="C97">
-        <v>-14860.53129682729</v>
+        <v>-15149.36154977611</v>
       </c>
       <c r="D97">
-        <v>5142.123703172711</v>
+        <v>5098.202450223896</v>
       </c>
       <c r="E97">
-        <v>20206.955</v>
+        <v>20451.864</v>
       </c>
       <c r="F97">
-        <v>23266.355</v>
+        <v>23511.264</v>
       </c>
       <c r="G97">
         <v>3263.7</v>
@@ -9247,37 +9247,37 @@
         <v>1778</v>
       </c>
       <c r="M97">
-        <v>4810.007514769434</v>
+        <v>4860.639172819639</v>
       </c>
       <c r="N97">
-        <v>-3032.007514769434</v>
+        <v>-3082.639172819639</v>
       </c>
       <c r="O97">
-        <v>-379.0009393461793</v>
+        <v>-385.3298966024548</v>
       </c>
       <c r="P97">
-        <v>-2653.006575423255</v>
+        <v>-2697.309276217184</v>
       </c>
       <c r="Q97">
-        <v>-1394.806575423255</v>
+        <v>-1439.109276217184</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8347623420853757</v>
+        <v>1.03200292760672</v>
       </c>
       <c r="T97">
-        <v>15.37834454207906</v>
+        <v>19.22293067759883</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04620574901755709</v>
+        <v>0.04572443913195753</v>
       </c>
       <c r="W97">
-        <v>0.1971841964402861</v>
+        <v>0.1972837008176012</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3696459921404567</v>
+        <v>0.3657955130556603</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2306724698891659</v>
+        <v>0.2322818360557912</v>
       </c>
       <c r="C98">
-        <v>-15149.3615497761</v>
+        <v>-15437.44785373222</v>
       </c>
       <c r="D98">
-        <v>5098.202450223898</v>
+        <v>5055.025146267782</v>
       </c>
       <c r="E98">
-        <v>20451.864</v>
+        <v>20696.773</v>
       </c>
       <c r="F98">
-        <v>23511.264</v>
+        <v>23756.173</v>
       </c>
       <c r="G98">
         <v>3263.7</v>
@@ -9329,37 +9329,37 @@
         <v>1778</v>
       </c>
       <c r="M98">
-        <v>4860.639172819638</v>
+        <v>4911.270830869843</v>
       </c>
       <c r="N98">
-        <v>-3082.639172819638</v>
+        <v>-3133.270830869843</v>
       </c>
       <c r="O98">
-        <v>-385.3298966024547</v>
+        <v>-391.6588538587304</v>
       </c>
       <c r="P98">
-        <v>-2697.309276217183</v>
+        <v>-2741.611977011113</v>
       </c>
       <c r="Q98">
-        <v>-1439.109276217183</v>
+        <v>-1483.411977011113</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.032002927606718</v>
+        <v>1.360737236808957</v>
       </c>
       <c r="T98">
-        <v>19.22293067759878</v>
+        <v>25.63057423679837</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04572443913195754</v>
+        <v>0.04525305316152498</v>
       </c>
       <c r="W98">
-        <v>0.1972837008176012</v>
+        <v>0.1973811535582706</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3657955130556604</v>
+        <v>0.3620244252921999</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2322818360557912</v>
+        <v>0.2338912022224166</v>
       </c>
       <c r="C99">
-        <v>-15437.44785373222</v>
+        <v>-15724.80895174516</v>
       </c>
       <c r="D99">
-        <v>5055.025146267782</v>
+        <v>5012.57304825484</v>
       </c>
       <c r="E99">
-        <v>20696.773</v>
+        <v>20941.682</v>
       </c>
       <c r="F99">
-        <v>23756.173</v>
+        <v>24001.082</v>
       </c>
       <c r="G99">
         <v>3263.7</v>
@@ -9411,37 +9411,37 @@
         <v>1778</v>
       </c>
       <c r="M99">
-        <v>4911.270830869843</v>
+        <v>4961.902488920047</v>
       </c>
       <c r="N99">
-        <v>-3133.270830869843</v>
+        <v>-3183.902488920047</v>
       </c>
       <c r="O99">
-        <v>-391.6588538587304</v>
+        <v>-397.9878111150059</v>
       </c>
       <c r="P99">
-        <v>-2741.611977011113</v>
+        <v>-2785.914677805041</v>
       </c>
       <c r="Q99">
-        <v>-1483.411977011113</v>
+        <v>-1527.714677805041</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.360737236808957</v>
+        <v>2.018205855213435</v>
       </c>
       <c r="T99">
-        <v>25.63057423679837</v>
+        <v>38.44586135519756</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04525305316152498</v>
+        <v>0.04479128731293799</v>
       </c>
       <c r="W99">
-        <v>0.1973811535582706</v>
+        <v>0.1974766174674978</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3620244252921999</v>
+        <v>0.358330298503504</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2338912022224166</v>
+        <v>0.2355005683890419</v>
       </c>
       <c r="C100">
-        <v>-15724.80895174516</v>
+        <v>-16011.46296249147</v>
       </c>
       <c r="D100">
-        <v>5012.57304825484</v>
+        <v>4970.828037508532</v>
       </c>
       <c r="E100">
-        <v>20941.682</v>
+        <v>21186.591</v>
       </c>
       <c r="F100">
-        <v>24001.082</v>
+        <v>24245.991</v>
       </c>
       <c r="G100">
         <v>3263.7</v>
@@ -9493,37 +9493,37 @@
         <v>1778</v>
       </c>
       <c r="M100">
-        <v>4961.902488920047</v>
+        <v>5012.534146970252</v>
       </c>
       <c r="N100">
-        <v>-3183.902488920047</v>
+        <v>-3234.534146970252</v>
       </c>
       <c r="O100">
-        <v>-397.9878111150059</v>
+        <v>-404.3167683712815</v>
       </c>
       <c r="P100">
-        <v>-2785.914677805041</v>
+        <v>-2830.21737859897</v>
       </c>
       <c r="Q100">
-        <v>-1527.714677805041</v>
+        <v>-1572.01737859897</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.018205855213435</v>
+        <v>3.990611710426871</v>
       </c>
       <c r="T100">
-        <v>38.44586135519756</v>
+        <v>76.89172271039511</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.04479128731293799</v>
+        <v>0.04433885006735276</v>
       </c>
       <c r="W100">
-        <v>0.1974766174674978</v>
+        <v>0.1975701528129022</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.358330298503504</v>
+        <v>0.3547108005388222</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2355005683890419</v>
-      </c>
-      <c r="C101">
-        <v>-16011.46296249147</v>
-      </c>
-      <c r="D101">
-        <v>4970.828037508532</v>
-      </c>
-      <c r="E101">
-        <v>21186.591</v>
-      </c>
-      <c r="F101">
-        <v>24245.991</v>
-      </c>
-      <c r="G101">
-        <v>3263.7</v>
-      </c>
-      <c r="H101">
-        <v>21431.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3036.2</v>
-      </c>
-      <c r="K101">
-        <v>1258.2</v>
-      </c>
-      <c r="L101">
-        <v>1778</v>
-      </c>
-      <c r="M101">
-        <v>5012.534146970252</v>
-      </c>
-      <c r="N101">
-        <v>-3234.534146970252</v>
-      </c>
-      <c r="O101">
-        <v>-404.3167683712815</v>
-      </c>
-      <c r="P101">
-        <v>-2830.21737859897</v>
-      </c>
-      <c r="Q101">
-        <v>-1572.01737859897</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.990611710426871</v>
-      </c>
-      <c r="T101">
-        <v>76.89172271039511</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.04433885006735276</v>
-      </c>
-      <c r="W101">
-        <v>0.1975701528129022</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3547108005388222</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
